--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B1" s="2">
         <f>TODAY()</f>
-        <v>46053</v>
+        <v>46057</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -5538,8 +5538,8 @@
         <v>D. ALAVÉS</v>
       </c>
       <c r="D4" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -5634,12 +5634,12 @@
     </row>
     <row r="10">
       <c r="A10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.0)</f>
-        <v>64</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
       </c>
       <c r="B10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAVI")</f>
-        <v>GAVI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
+        <v>DANI OLMO</v>
       </c>
       <c r="C10" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -5652,16 +5652,16 @@
     </row>
     <row r="11">
       <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
-        <v>67</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
       </c>
       <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
-        <v>DANI OLMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D11" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5670,12 +5670,12 @@
     </row>
     <row r="12">
       <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
-        <v>73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
+        <v>PAU LÓPEZ</v>
       </c>
       <c r="C12" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -5688,52 +5688,52 @@
     </row>
     <row r="13">
       <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
-        <v>PAU LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C13" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
       </c>
       <c r="C14" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
+        <v>93</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
+        <v>IVÁN VILLAR</v>
       </c>
       <c r="C15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D15" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5742,12 +5742,12 @@
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
-        <v>93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
-        <v>IVÁN VILLAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C16" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5760,12 +5760,12 @@
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C17" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5778,12 +5778,12 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C18" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5796,12 +5796,12 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C19" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5814,12 +5814,12 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C20" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5832,12 +5832,12 @@
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
       </c>
       <c r="C21" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5850,16 +5850,16 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
+        <v>IÑAKI PEÑA</v>
       </c>
       <c r="C22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D22" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5868,12 +5868,12 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
-        <v>IÑAKI PEÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C23" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5886,12 +5886,12 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C24" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5904,12 +5904,12 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5922,16 +5922,16 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D26" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5940,12 +5940,12 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C27" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5958,12 +5958,12 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C28" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5976,12 +5976,12 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
       </c>
       <c r="C29" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5994,12 +5994,12 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C30" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -6012,16 +6012,16 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D31" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6030,16 +6030,16 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D32" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6048,12 +6048,12 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -6066,48 +6066,48 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
       </c>
       <c r="C34" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
       </c>
       <c r="D34" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
+        <v>202</v>
+      </c>
+      <c r="B35" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
+        <v>CARVAJAL</v>
+      </c>
+      <c r="C35" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D35" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
-      </c>
-      <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
-      </c>
-      <c r="C35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-      <c r="D35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
-        <v>202</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
-        <v>CARVAJAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C36" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6120,12 +6120,12 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
+        <v>213</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
+        <v>RODRYGO</v>
       </c>
       <c r="C37" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6138,12 +6138,12 @@
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
-        <v>213</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
-        <v>RODRYGO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C38" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6156,16 +6156,16 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
       </c>
       <c r="C39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D39" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6174,12 +6174,12 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
       </c>
       <c r="C40" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -6192,16 +6192,16 @@
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D41" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6210,12 +6210,12 @@
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C42" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -6228,12 +6228,12 @@
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
+        <v>237</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
+        <v>AITOR FERNÁNDEZ</v>
       </c>
       <c r="C43" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -6246,12 +6246,12 @@
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
-        <v>237</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
-        <v>AITOR FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C44" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -6264,16 +6264,16 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D45" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6282,12 +6282,12 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C46" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -6300,12 +6300,12 @@
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C47" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -6318,12 +6318,12 @@
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C48" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -6336,16 +6336,16 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
+        <v>277</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
+        <v>LUIZ FELIPE</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D49" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6354,48 +6354,48 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
-        <v>277</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
-        <v>LUIZ FELIPE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
       </c>
       <c r="C50" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
         <v>RAYO VALLECANO</v>
       </c>
       <c r="D50" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
+      </c>
+      <c r="B51" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
+      </c>
+      <c r="C51" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+      <c r="D51" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
-      </c>
-      <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
-      </c>
-      <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-      <c r="D51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C52" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -6408,16 +6408,16 @@
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D53" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6426,12 +6426,12 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
       </c>
       <c r="C54" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
@@ -6444,52 +6444,52 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
       </c>
       <c r="C55" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
       <c r="D55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
       </c>
       <c r="C56" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
       <c r="D56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D57" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6498,12 +6498,12 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
       </c>
       <c r="C58" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -6516,12 +6516,12 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
       </c>
       <c r="C59" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -6534,12 +6534,12 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
       </c>
       <c r="C60" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -6552,12 +6552,12 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
       </c>
       <c r="C61" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -6570,16 +6570,16 @@
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D62" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6592,8 +6592,8 @@
         <v>343</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C63" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
@@ -6606,12 +6606,12 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
       </c>
       <c r="C64" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
@@ -6624,12 +6624,12 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
       </c>
       <c r="C65" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
@@ -6642,16 +6642,16 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D66" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6660,12 +6660,12 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="C67" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -6678,52 +6678,52 @@
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D68" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
+      </c>
+      <c r="B69" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
+      </c>
+      <c r="C69" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+      <c r="D69" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
-      </c>
-      <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
-      </c>
-      <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6732,16 +6732,16 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D71" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6750,52 +6750,52 @@
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D72" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
+      </c>
+      <c r="B73" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
+      </c>
+      <c r="C73" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D73" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
-      </c>
-      <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
-      </c>
-      <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-      <c r="D73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
       </c>
       <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D74" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6804,16 +6804,16 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
       </c>
       <c r="C75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D75" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6822,16 +6822,16 @@
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
+        <v>425</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
+        <v>CARLOS VICENTE</v>
       </c>
       <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D76" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6840,16 +6840,16 @@
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
-        <v>425</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
-        <v>CARLOS VICENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D77" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6858,16 +6858,16 @@
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
+        <v>444</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
+        <v>OBLAK</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D78" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6876,16 +6876,16 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
-        <v>444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
+        <v>456</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
-        <v>OBLAK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
+        <v>ANTONY</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D79" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6894,16 +6894,16 @@
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
-        <v>456</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
+        <v>458</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
-        <v>ANTONY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
+        <v>CARRERAS</v>
       </c>
       <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D80" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6912,36 +6912,18 @@
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
-        <v>458</v>
-      </c>
-      <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
-        <v>CARRERAS</v>
-      </c>
-      <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B82" s="20" t="str">
+      <c r="B81" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C82" s="20" t="str">
+      <c r="C81" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D82" s="20">
+      <c r="D81" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
@@ -7211,7 +7193,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="19">
@@ -7830,9 +7812,6 @@
       </c>
       <c r="D64" s="21" t="s">
         <v>20</v>
-      </c>
-      <c r="E64" s="22">
-        <v>1.0</v>
       </c>
     </row>
     <row r="65">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="399">
   <si>
     <t>Última actualización:</t>
   </si>
@@ -1833,15 +1833,15 @@
       </c>
       <c r="C3" s="9">
         <f>COUNTIF(REGULARES!D:D, "SI")</f>
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D3" s="9">
         <f t="shared" ref="D3:D12" si="1">B3-C3</f>
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E4" si="2">(C3/B3)</f>
-        <v>0.6722222222</v>
+        <v>0.6916666667</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E3, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1881,15 +1881,15 @@
       </c>
       <c r="C5" s="9">
         <f>COUNTIF('¡VAMOS! (361–380)'!D:D, "SI")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="9">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" ref="E5:E13" si="3">C5/B5</f>
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="F5" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E5, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="4"/>
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="4"/>
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>0.656626506</v>
+        <v>0.6726907631</v>
       </c>
       <c r="F13" s="19" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E13, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2422,6 +2422,9 @@
       </c>
       <c r="D13" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E13" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="14">
@@ -2639,6 +2642,9 @@
       </c>
       <c r="D10" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E10" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="11">
@@ -3190,12 +3196,12 @@
     </row>
     <row r="11">
       <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.0)</f>
-        <v>28</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
+        <v>29</v>
       </c>
       <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAUREGIZAR")</f>
-        <v>JAUREGIZAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VESGA")</f>
+        <v>VESGA</v>
       </c>
       <c r="C11" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3204,12 +3210,12 @@
     </row>
     <row r="12">
       <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
-        <v>29</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
+        <v>30</v>
       </c>
       <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VESGA")</f>
-        <v>VESGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI GÓMEZ")</f>
+        <v>UNAI GÓMEZ</v>
       </c>
       <c r="C12" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3218,12 +3224,12 @@
     </row>
     <row r="13">
       <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
+        <v>35</v>
       </c>
       <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI GÓMEZ")</f>
-        <v>UNAI GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GURUZETA")</f>
+        <v>GURUZETA</v>
       </c>
       <c r="C13" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3232,12 +3238,12 @@
     </row>
     <row r="14">
       <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
-        <v>35</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
+        <v>36</v>
       </c>
       <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GURUZETA")</f>
-        <v>GURUZETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
+        <v>NICO WILLIAMS</v>
       </c>
       <c r="C14" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3246,26 +3252,26 @@
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
-        <v>36</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
-        <v>NICO WILLIAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
-        <v>37</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
+        <v>38</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
+        <v>OBLAK</v>
       </c>
       <c r="C16" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3274,12 +3280,12 @@
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
-        <v>38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
+        <v>48</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
-        <v>OBLAK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX BAENA")</f>
+        <v>ALEX BAENA</v>
       </c>
       <c r="C17" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3288,12 +3294,12 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.0)</f>
-        <v>45</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOKE")</f>
-        <v>KOKE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO GONZÁLEZ")</f>
+        <v>NICO GONZÁLEZ</v>
       </c>
       <c r="C18" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3302,12 +3308,12 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
-        <v>48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.0)</f>
+        <v>51</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX BAENA")</f>
-        <v>ALEX BAENA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIULIANO")</f>
+        <v>GIULIANO</v>
       </c>
       <c r="C19" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3316,12 +3322,12 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
-        <v>50</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.0)</f>
+        <v>54</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO GONZÁLEZ")</f>
-        <v>NICO GONZÁLEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
+        <v>GRIEZMANN</v>
       </c>
       <c r="C20" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3330,40 +3336,40 @@
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.0)</f>
-        <v>51</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
+        <v>57</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIULIANO")</f>
-        <v>GIULIANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SZCZESNY")</f>
+        <v>SZCZESNY</v>
       </c>
       <c r="C21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.0)</f>
-        <v>54</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
+        <v>58</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
-        <v>GRIEZMANN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
+        <v>KOUNDÉ</v>
       </c>
       <c r="C22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
-        <v>57</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.0)</f>
+        <v>60</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SZCZESNY")</f>
-        <v>SZCZESNY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ERIC GARCÍA")</f>
+        <v>ERIC GARCÍA</v>
       </c>
       <c r="C23" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3372,12 +3378,12 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
-        <v>58</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68.0)</f>
+        <v>68</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
-        <v>KOUNDÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
+        <v>RAPHINHA</v>
       </c>
       <c r="C24" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3386,12 +3392,12 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.0)</f>
-        <v>60</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
+        <v>69</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ERIC GARCÍA")</f>
-        <v>ERIC GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
+        <v>LAMINE YAMAL</v>
       </c>
       <c r="C25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3400,12 +3406,12 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68.0)</f>
-        <v>68</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
+        <v>70</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
-        <v>RAPHINHA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERRAN TORRES")</f>
+        <v>FERRAN TORRES</v>
       </c>
       <c r="C26" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3414,40 +3420,40 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
-        <v>69</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),77.0)</f>
+        <v>77</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
-        <v>LAMINE YAMAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARTRA")</f>
+        <v>BARTRA</v>
       </c>
       <c r="C27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
-        <v>70</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.0)</f>
+        <v>80</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERRAN TORRES")</f>
-        <v>FERRAN TORRES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
       </c>
       <c r="C28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),77.0)</f>
-        <v>77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.0)</f>
+        <v>82</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARTRA")</f>
-        <v>BARTRA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALTIMIRA")</f>
+        <v>ALTIMIRA</v>
       </c>
       <c r="C29" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3456,12 +3462,12 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.0)</f>
-        <v>78</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.0)</f>
+        <v>83</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO LLORENTE")</f>
-        <v>DIEGO LLORENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AMRABAT")</f>
+        <v>AMRABAT</v>
       </c>
       <c r="C30" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3470,12 +3476,12 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.0)</f>
-        <v>80</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),85.0)</f>
+        <v>85</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LO CELSO")</f>
+        <v>LO CELSO</v>
       </c>
       <c r="C31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3484,12 +3490,12 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.0)</f>
-        <v>82</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
+        <v>89</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALTIMIRA")</f>
-        <v>ALTIMIRA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIQUELME")</f>
+        <v>RIQUELME</v>
       </c>
       <c r="C32" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3498,12 +3504,12 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.0)</f>
-        <v>83</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.0)</f>
+        <v>90</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AMRABAT")</f>
-        <v>AMRABAT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABDE")</f>
+        <v>ABDE</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3512,54 +3518,54 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),85.0)</f>
-        <v>85</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.0)</f>
+        <v>92</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LO CELSO")</f>
-        <v>LO CELSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RADU")</f>
+        <v>RADU</v>
       </c>
       <c r="C34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
-        <v>89</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIQUELME")</f>
-        <v>RIQUELME</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RODRÍGUEZ")</f>
+        <v>JAVI RODRÍGUEZ</v>
       </c>
       <c r="C35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.0)</f>
-        <v>90</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.0)</f>
+        <v>96</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABDE")</f>
-        <v>ABDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"STARFELT")</f>
+        <v>STARFELT</v>
       </c>
       <c r="C36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.0)</f>
-        <v>92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
+        <v>98</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RADU")</f>
-        <v>RADU</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MINGUEZA")</f>
+        <v>MINGUEZA</v>
       </c>
       <c r="C37" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3568,12 +3574,12 @@
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
-        <v>95</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101.0)</f>
+        <v>101</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RODRÍGUEZ")</f>
-        <v>JAVI RODRÍGUEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN BELTRÁN")</f>
+        <v>FRAN BELTRÁN</v>
       </c>
       <c r="C38" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3582,12 +3588,12 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.0)</f>
-        <v>96</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"STARFELT")</f>
-        <v>STARFELT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C39" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3596,54 +3602,54 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
-        <v>98</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
+        <v>113</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MINGUEZA")</f>
-        <v>MINGUEZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CHUST")</f>
+        <v>CHUST</v>
       </c>
       <c r="C40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101.0)</f>
-        <v>101</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
+        <v>114</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN BELTRÁN")</f>
-        <v>FRAN BELTRÁN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIGAS")</f>
+        <v>BIGAS</v>
       </c>
       <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),118.0)</f>
+        <v>118</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GERMÁN VALERA")</f>
+        <v>GERMÁN VALERA</v>
       </c>
       <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
-        <v>113</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
+        <v>119</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CHUST")</f>
-        <v>CHUST</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARTIM NETO")</f>
+        <v>MARTIM NETO</v>
       </c>
       <c r="C43" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3652,12 +3658,12 @@
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
-        <v>114</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
+        <v>120</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIGAS")</f>
-        <v>BIGAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
+        <v>FEBAS</v>
       </c>
       <c r="C44" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3666,54 +3672,54 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),118.0)</f>
-        <v>118</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
+        <v>128</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GERMÁN VALERA")</f>
-        <v>GERMÁN VALERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
+        <v>DMITROVIC</v>
       </c>
       <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
-        <v>119</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),132.0)</f>
+        <v>132</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARTIM NETO")</f>
-        <v>MARTIM NETO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
+        <v>RIEDEL</v>
       </c>
       <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
-        <v>120</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
+        <v>133</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
-        <v>FEBAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
       </c>
       <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
-        <v>128</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),142.0)</f>
+        <v>142</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
-        <v>DMITROVIC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE GARCÍA")</f>
+        <v>KIKE GARCÍA</v>
       </c>
       <c r="C48" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -3722,12 +3728,12 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),132.0)</f>
-        <v>132</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),143.0)</f>
+        <v>143</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
-        <v>RIEDEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PUADO")</f>
+        <v>PUADO</v>
       </c>
       <c r="C49" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -3736,54 +3742,54 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
-        <v>133</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),142.0)</f>
-        <v>142</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
+        <v>148</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE GARCÍA")</f>
-        <v>KIKE GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IGLESIAS")</f>
+        <v>IGLESIAS</v>
       </c>
       <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),143.0)</f>
-        <v>143</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.0)</f>
+        <v>149</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PUADO")</f>
-        <v>PUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKO FEMENÍA")</f>
+        <v>KIKO FEMENÍA</v>
       </c>
       <c r="C52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.0)</f>
+        <v>150</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DJENÉ")</f>
+        <v>DJENÉ</v>
       </c>
       <c r="C53" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3792,12 +3798,12 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),147.0)</f>
-        <v>147</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
+        <v>151</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LETACEK")</f>
-        <v>LETACEK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOMINGOS DUARTE")</f>
+        <v>DOMINGOS DUARTE</v>
       </c>
       <c r="C54" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3806,12 +3812,12 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
-        <v>148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),155.0)</f>
+        <v>155</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IGLESIAS")</f>
-        <v>IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIO MARTÍN")</f>
+        <v>MARIO MARTÍN</v>
       </c>
       <c r="C55" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3820,12 +3826,12 @@
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.0)</f>
-        <v>149</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),157.0)</f>
+        <v>157</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKO FEMENÍA")</f>
-        <v>KIKO FEMENÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
       </c>
       <c r="C56" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3834,12 +3840,12 @@
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.0)</f>
-        <v>150</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),161.0)</f>
+        <v>161</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DJENÉ")</f>
-        <v>DJENÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C57" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3848,12 +3854,12 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
-        <v>151</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),162.0)</f>
+        <v>162</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOMINGOS DUARTE")</f>
-        <v>DOMINGOS DUARTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COBA")</f>
+        <v>COBA</v>
       </c>
       <c r="C58" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3862,68 +3868,68 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),155.0)</f>
-        <v>155</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
+        <v>164</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIO MARTÍN")</f>
-        <v>MARIO MARTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAZZANIGA")</f>
+        <v>GAZZANIGA</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),157.0)</f>
-        <v>157</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),167.0)</f>
+        <v>167</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO RINCÓN")</f>
+        <v>HUGO RINCÓN</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),161.0)</f>
-        <v>161</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
+        <v>168</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VITOR REIS")</f>
+        <v>VITOR REIS</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),162.0)</f>
-        <v>162</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.0)</f>
+        <v>169</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COBA")</f>
-        <v>COBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BLIND")</f>
+        <v>BLIND</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
-        <v>164</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.0)</f>
+        <v>178</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAZZANIGA")</f>
-        <v>GAZZANIGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
+        <v>VANAT</v>
       </c>
       <c r="C63" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -3932,68 +3938,68 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),167.0)</f>
-        <v>167</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
+        <v>182</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO RINCÓN")</f>
-        <v>HUGO RINCÓN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RYAN")</f>
+        <v>RYAN</v>
       </c>
       <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
-        <v>168</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
+        <v>183</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VITOR REIS")</f>
-        <v>VITOR REIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO CAMPOS")</f>
+        <v>PABLO CAMPOS</v>
       </c>
       <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.0)</f>
-        <v>169</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.0)</f>
+        <v>186</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BLIND")</f>
-        <v>BLIND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELGEZABAL")</f>
+        <v>ELGEZABAL</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.0)</f>
-        <v>178</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),191.0)</f>
+        <v>191</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
-        <v>VANAT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARTÍNEZ")</f>
+        <v>PABLO MARTÍNEZ</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
-        <v>182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.0)</f>
+        <v>196</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RYAN")</f>
-        <v>RYAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRUGUÉ")</f>
+        <v>BRUGUÉ</v>
       </c>
       <c r="C68" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -4002,12 +4008,12 @@
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
-        <v>183</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
+        <v>198</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO CAMPOS")</f>
-        <v>PABLO CAMPOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
+        <v>ETTA EYONG</v>
       </c>
       <c r="C69" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -4016,110 +4022,110 @@
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.0)</f>
-        <v>186</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.0)</f>
+        <v>201</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELGEZABAL")</f>
-        <v>ELGEZABAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUNIN")</f>
+        <v>LUNIN</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),191.0)</f>
-        <v>191</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.0)</f>
+        <v>205</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARTÍNEZ")</f>
-        <v>PABLO MARTÍNEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUIJSEN")</f>
+        <v>HUIJSEN</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.0)</f>
-        <v>196</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
+        <v>214</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRUGUÉ")</f>
-        <v>BRUGUÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
+        <v>MBAPPÉ</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
-        <v>198</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
+        <v>217</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
-        <v>ETTA EYONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.0)</f>
-        <v>201</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
+        <v>218</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUNIN")</f>
-        <v>LUNIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
+        <v>LEO ROMÁN</v>
       </c>
       <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.0)</f>
-        <v>205</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
+        <v>224</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUIJSEN")</f>
-        <v>HUIJSEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
+        <v>KUMBULLA</v>
       </c>
       <c r="C75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
-        <v>214</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.0)</f>
+        <v>229</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
-        <v>MBAPPÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORLANES")</f>
+        <v>MORLANES</v>
       </c>
       <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
-        <v>217</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.0)</f>
+        <v>231</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ASANO")</f>
+        <v>ASANO</v>
       </c>
       <c r="C77" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4128,12 +4134,12 @@
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
-        <v>218</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),232.0)</f>
+        <v>232</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
-        <v>LEO ROMÁN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MURIQI")</f>
+        <v>MURIQI</v>
       </c>
       <c r="C78" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4142,12 +4148,12 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
-        <v>224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),233.0)</f>
+        <v>233</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
-        <v>KUMBULLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
+        <v>MATEO JOSEPH</v>
       </c>
       <c r="C79" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4156,138 +4162,138 @@
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.0)</f>
-        <v>229</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.0)</f>
+        <v>239</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORLANES")</f>
-        <v>MORLANES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYOMO")</f>
+        <v>BOYOMO</v>
       </c>
       <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.0)</f>
-        <v>231</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.0)</f>
+        <v>241</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ASANO")</f>
-        <v>ASANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HERRANDO")</f>
+        <v>HERRANDO</v>
       </c>
       <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),232.0)</f>
-        <v>232</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
+        <v>242</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MURIQI")</f>
-        <v>MURIQI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
+        <v>JUAN CRUZ</v>
       </c>
       <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),233.0)</f>
-        <v>233</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),251.0)</f>
+        <v>251</v>
       </c>
       <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
-        <v>MATEO JOSEPH</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUDIMIR")</f>
+        <v>BUDIMIR</v>
       </c>
       <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.0)</f>
-        <v>239</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
+        <v>253</v>
       </c>
       <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYOMO")</f>
-        <v>BOYOMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.0)</f>
-        <v>241</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),254.0)</f>
+        <v>254</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HERRANDO")</f>
-        <v>HERRANDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AARON ESCANDELL")</f>
+        <v>AARON ESCANDELL</v>
       </c>
       <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
-        <v>242</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
+        <v>260</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
-        <v>JUAN CRUZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
+        <v>RAHIM ALHASSANE</v>
       </c>
       <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),251.0)</f>
-        <v>251</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
+        <v>261</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUDIMIR")</f>
-        <v>BUDIMIR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLOMBATTO")</f>
+        <v>COLOMBATTO</v>
       </c>
       <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),252.0)</f>
-        <v>252</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),263.0)</f>
+        <v>263</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECKER")</f>
-        <v>BECKER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DENDONCKER")</f>
+        <v>DENDONCKER</v>
       </c>
       <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
-        <v>253</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),266.0)</f>
+        <v>266</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
+        <v>HASSAN</v>
       </c>
       <c r="C89" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4296,12 +4302,12 @@
     </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),254.0)</f>
-        <v>254</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),268.0)</f>
+        <v>268</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AARON ESCANDELL")</f>
-        <v>AARON ESCANDELL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILYAS CHAIRA")</f>
+        <v>ILYAS CHAIRA</v>
       </c>
       <c r="C90" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4310,82 +4316,82 @@
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
-        <v>260</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),271.0)</f>
+        <v>271</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
-        <v>RAHIM ALHASSANE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
-        <v>261</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.0)</f>
+        <v>273</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLOMBATTO")</f>
-        <v>COLOMBATTO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CÁRDENAS")</f>
+        <v>CÁRDENAS</v>
       </c>
       <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),263.0)</f>
-        <v>263</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),276.0)</f>
+        <v>276</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DENDONCKER")</f>
-        <v>DENDONCKER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
+        <v>LEJEUNE</v>
       </c>
       <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),266.0)</f>
-        <v>266</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),279.0)</f>
+        <v>279</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
-        <v>HASSAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PATHÉ CISS")</f>
+        <v>PATHÉ CISS</v>
       </c>
       <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),268.0)</f>
-        <v>268</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),280.0)</f>
+        <v>280</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILYAS CHAIRA")</f>
-        <v>ILYAS CHAIRA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LOPEZ")</f>
+        <v>UNAI LOPEZ</v>
       </c>
       <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),271.0)</f>
-        <v>271</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),285.0)</f>
+        <v>285</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN PÉREZ")</f>
+        <v>FRAN PÉREZ</v>
       </c>
       <c r="C96" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -4394,320 +4400,320 @@
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.0)</f>
-        <v>273</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
+        <v>289</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CÁRDENAS")</f>
-        <v>CÁRDENAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),276.0)</f>
-        <v>276</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),294.0)</f>
+        <v>294</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
-        <v>LEJEUNE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZUBELDIA")</f>
+        <v>ZUBELDIA</v>
       </c>
       <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),279.0)</f>
-        <v>279</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),297.0)</f>
+        <v>297</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PATHÉ CISS")</f>
-        <v>PATHÉ CISS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
+        <v>GORROTXATEGI</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),280.0)</f>
-        <v>280</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.0)</f>
+        <v>300</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LOPEZ")</f>
-        <v>UNAI LOPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
+        <v>CARLOS SOLER</v>
       </c>
       <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),285.0)</f>
-        <v>285</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),301.0)</f>
+        <v>301</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN PÉREZ")</f>
-        <v>FRAN PÉREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRAIS MÉNDEZ")</f>
+        <v>BRAIS MÉNDEZ</v>
       </c>
       <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),288.0)</f>
-        <v>288</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),305.0)</f>
+        <v>305</v>
       </c>
       <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEMAO")</f>
-        <v>ALEMAO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSKARSSON")</f>
+        <v>ÓSKARSSON</v>
       </c>
       <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
-        <v>289</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),310.0)</f>
+        <v>310</v>
       </c>
       <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARMONA")</f>
+        <v>CARMONA</v>
       </c>
       <c r="C103" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),314.0)</f>
+        <v>314</v>
+      </c>
+      <c r="B104" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCAO")</f>
+        <v>MARCAO</v>
+      </c>
+      <c r="C104" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),320.0)</f>
+        <v>320</v>
+      </c>
+      <c r="B105" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
+        <v>VARGAS</v>
+      </c>
+      <c r="C105" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),324.0)</f>
+        <v>324</v>
+      </c>
+      <c r="B106" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
+      </c>
+      <c r="C106" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),339.0)</f>
+        <v>339</v>
+      </c>
+      <c r="B107" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO LÓPEZ")</f>
+        <v>DIEGO LÓPEZ</v>
+      </c>
+      <c r="C107" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
+        <v>348</v>
+      </c>
+      <c r="B108" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MARÍN")</f>
+        <v>RAFA MARÍN</v>
+      </c>
+      <c r="C108" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),349.0)</f>
+        <v>349</v>
+      </c>
+      <c r="B109" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RENATO VEIGA")</f>
+        <v>RENATO VEIGA</v>
+      </c>
+      <c r="C109" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),357.0)</f>
+        <v>357</v>
+      </c>
+      <c r="B110" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MIKAUTADZE")</f>
+        <v>MIKAUTADZE</v>
+      </c>
+      <c r="C110" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),360.0)</f>
+        <v>360</v>
+      </c>
+      <c r="B111" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AYOZE")</f>
+        <v>AYOZE</v>
+      </c>
+      <c r="C111" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),364.0)</f>
+        <v>364</v>
+      </c>
+      <c r="B112" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="C112" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),365.0)</f>
+        <v>365</v>
+      </c>
+      <c r="B113" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="C113" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
+        <v>366</v>
+      </c>
+      <c r="B114" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="C114" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),373.0)</f>
+        <v>373</v>
+      </c>
+      <c r="B115" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+      <c r="C115" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
+        <v>375</v>
+      </c>
+      <c r="B116" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="C116" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),377.0)</f>
+        <v>377</v>
+      </c>
+      <c r="B117" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),294.0)</f>
-        <v>294</v>
-      </c>
-      <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZUBELDIA")</f>
-        <v>ZUBELDIA</v>
-      </c>
-      <c r="C104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),297.0)</f>
-        <v>297</v>
-      </c>
-      <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
-        <v>GORROTXATEGI</v>
-      </c>
-      <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.0)</f>
-        <v>300</v>
-      </c>
-      <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
-        <v>CARLOS SOLER</v>
-      </c>
-      <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),301.0)</f>
-        <v>301</v>
-      </c>
-      <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRAIS MÉNDEZ")</f>
-        <v>BRAIS MÉNDEZ</v>
-      </c>
-      <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),305.0)</f>
-        <v>305</v>
-      </c>
-      <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSKARSSON")</f>
-        <v>ÓSKARSSON</v>
-      </c>
-      <c r="C108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),310.0)</f>
-        <v>310</v>
-      </c>
-      <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARMONA")</f>
-        <v>CARMONA</v>
-      </c>
-      <c r="C109" s="20" t="str">
+      <c r="C117" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),378.0)</f>
+        <v>378</v>
+      </c>
+      <c r="B118" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),314.0)</f>
-        <v>314</v>
-      </c>
-      <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCAO")</f>
-        <v>MARCAO</v>
-      </c>
-      <c r="C110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),320.0)</f>
-        <v>320</v>
-      </c>
-      <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
-        <v>VARGAS</v>
-      </c>
-      <c r="C111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),324.0)</f>
-        <v>324</v>
-      </c>
-      <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
-      </c>
-      <c r="C112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),339.0)</f>
-        <v>339</v>
-      </c>
-      <c r="B113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO LÓPEZ")</f>
-        <v>DIEGO LÓPEZ</v>
-      </c>
-      <c r="C113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
-        <v>348</v>
-      </c>
-      <c r="B114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MARÍN")</f>
-        <v>RAFA MARÍN</v>
-      </c>
-      <c r="C114" s="20" t="str">
+      <c r="C118" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),380.0)</f>
+        <v>380</v>
+      </c>
+      <c r="B119" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),349.0)</f>
-        <v>349</v>
-      </c>
-      <c r="B115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RENATO VEIGA")</f>
-        <v>RENATO VEIGA</v>
-      </c>
-      <c r="C115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),357.0)</f>
-        <v>357</v>
-      </c>
-      <c r="B116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MIKAUTADZE")</f>
-        <v>MIKAUTADZE</v>
-      </c>
-      <c r="C116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),359.0)</f>
-        <v>359</v>
-      </c>
-      <c r="B117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OLUWASEYI")</f>
-        <v>OLUWASEYI</v>
-      </c>
-      <c r="C117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),360.0)</f>
-        <v>360</v>
-      </c>
-      <c r="B118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AYOZE")</f>
-        <v>AYOZE</v>
-      </c>
-      <c r="C118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),364.0)</f>
-        <v>364</v>
-      </c>
-      <c r="B119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
       </c>
       <c r="C119" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4716,208 +4722,208 @@
     </row>
     <row r="120">
       <c r="A120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),365.0)</f>
-        <v>365</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
+        <v>383</v>
       </c>
       <c r="B120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
-        <v>366</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),384.0)</f>
+        <v>384</v>
       </c>
       <c r="B121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),367.0)</f>
-        <v>367</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.0)</f>
+        <v>385</v>
       </c>
       <c r="B122" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATALLA")</f>
+        <v>BATALLA</v>
+      </c>
+      <c r="C122" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.0)</f>
+        <v>386</v>
+      </c>
+      <c r="B123" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
+      </c>
+      <c r="C123" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.0)</f>
+        <v>388</v>
+      </c>
+      <c r="B124" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
+        <v>LAPORTE</v>
+      </c>
+      <c r="C124" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),390.0)</f>
+        <v>390</v>
+      </c>
+      <c r="B125" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LE NORMAND")</f>
+        <v>LE NORMAND</v>
+      </c>
+      <c r="C125" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),394.0)</f>
+        <v>394</v>
+      </c>
+      <c r="B126" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
+        <v>LEJEUNE</v>
+      </c>
+      <c r="C126" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),397.0)</f>
+        <v>397</v>
+      </c>
+      <c r="B127" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REGO")</f>
+        <v>REGO</v>
+      </c>
+      <c r="C127" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
+        <v>401</v>
+      </c>
+      <c r="B128" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
+        <v>RODRI MENDOZA</v>
+      </c>
+      <c r="C128" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
         <v>ELCHE CF</v>
       </c>
-      <c r="C122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),373.0)</f>
-        <v>373</v>
-      </c>
-      <c r="B123" s="20" t="str">
+    </row>
+    <row r="129">
+      <c r="A129" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),410.0)</f>
+        <v>410</v>
+      </c>
+      <c r="B129" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
+        <v>GONZALO</v>
+      </c>
+      <c r="C129" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),412.0)</f>
+        <v>412</v>
+      </c>
+      <c r="B130" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
+        <v>MATEO JOSEPH</v>
+      </c>
+      <c r="C130" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
-      <c r="C123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
-        <v>375</v>
-      </c>
-      <c r="B124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="C124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),377.0)</f>
-        <v>377</v>
-      </c>
-      <c r="B125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-      <c r="C125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),378.0)</f>
-        <v>378</v>
-      </c>
-      <c r="B126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="C126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),380.0)</f>
-        <v>380</v>
-      </c>
-      <c r="B127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="C127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
-        <v>383</v>
-      </c>
-      <c r="B128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
-      </c>
-      <c r="C128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),384.0)</f>
-        <v>384</v>
-      </c>
-      <c r="B129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
-      </c>
-      <c r="C129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.0)</f>
-        <v>385</v>
-      </c>
-      <c r="B130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATALLA")</f>
-        <v>BATALLA</v>
-      </c>
-      <c r="C130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.0)</f>
-        <v>386</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),417.0)</f>
+        <v>417</v>
       </c>
       <c r="B131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
+        <v>FEBAS</v>
       </c>
       <c r="C131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.0)</f>
-        <v>388</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),418.0)</f>
+        <v>418</v>
       </c>
       <c r="B132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
-        <v>LAPORTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),390.0)</f>
-        <v>390</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),420.0)</f>
+        <v>420</v>
       </c>
       <c r="B133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LE NORMAND")</f>
-        <v>LE NORMAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
+        <v>DARDER</v>
       </c>
       <c r="C133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),394.0)</f>
-        <v>394</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),423.0)</f>
+        <v>423</v>
       </c>
       <c r="B134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
-        <v>LEJEUNE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LÓPEZ")</f>
+        <v>UNAI LÓPEZ</v>
       </c>
       <c r="C134" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -4926,518 +4932,406 @@
     </row>
     <row r="135">
       <c r="A135" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),397.0)</f>
-        <v>397</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),424.0)</f>
+        <v>424</v>
       </c>
       <c r="B135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REGO")</f>
-        <v>REGO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
+        <v>TENAGLIA</v>
       </c>
       <c r="C135" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),428.0)</f>
+        <v>428</v>
+      </c>
+      <c r="B136" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
+      </c>
+      <c r="C136" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),429.0)</f>
+        <v>429</v>
+      </c>
+      <c r="B137" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
+      </c>
+      <c r="C137" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),430.0)</f>
+        <v>430</v>
+      </c>
+      <c r="B138" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
+        <v>VANAT</v>
+      </c>
+      <c r="C138" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),433.0)</f>
+        <v>433</v>
+      </c>
+      <c r="B139" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
+        <v>LEO ROMÁN</v>
+      </c>
+      <c r="C139" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),435.0)</f>
+        <v>435</v>
+      </c>
+      <c r="B140" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
+        <v>HASSAN</v>
+      </c>
+      <c r="C140" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),437.0)</f>
+        <v>437</v>
+      </c>
+      <c r="B141" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
+        <v>GORROTXATEGI</v>
+      </c>
+      <c r="C141" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),438.0)</f>
+        <v>438</v>
+      </c>
+      <c r="B142" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATISTA MENDY")</f>
+        <v>BATISTA MENDY</v>
+      </c>
+      <c r="C142" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),441.0)</f>
+        <v>441</v>
+      </c>
+      <c r="B143" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUCHANAN")</f>
+        <v>BUCHANAN</v>
+      </c>
+      <c r="C143" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),442.0)</f>
+        <v>442</v>
+      </c>
+      <c r="B144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
+        <v>UNAI SIMÓN</v>
+      </c>
+      <c r="C144" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
         <v>ATHLETIC CLUB</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
-        <v>401</v>
-      </c>
-      <c r="B136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
-        <v>RODRI MENDOZA</v>
-      </c>
-      <c r="C136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),410.0)</f>
-        <v>410</v>
-      </c>
-      <c r="B137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
-        <v>GONZALO</v>
-      </c>
-      <c r="C137" s="20" t="str">
+    <row r="145">
+      <c r="A145" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),443.0)</f>
+        <v>443</v>
+      </c>
+      <c r="B145" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAUREGIZAR")</f>
+        <v>JAUREGIZAR</v>
+      </c>
+      <c r="C145" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),445.0)</f>
+        <v>445</v>
+      </c>
+      <c r="B146" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
+        <v>MARCOS LLORENTE</v>
+      </c>
+      <c r="C146" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446.0)</f>
+        <v>446</v>
+      </c>
+      <c r="B147" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLEX BAENA")</f>
+        <v>ÁLEX BAENA</v>
+      </c>
+      <c r="C147" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),451.0)</f>
+        <v>451</v>
+      </c>
+      <c r="B148" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
+        <v>RAPHINHA</v>
+      </c>
+      <c r="C148" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),453.0)</f>
+        <v>453</v>
+      </c>
+      <c r="B149" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RASHFORD")</f>
+        <v>RASHFORD</v>
+      </c>
+      <c r="C149" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
+        <v>454</v>
+      </c>
+      <c r="B150" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
+        <v>ISCO</v>
+      </c>
+      <c r="C150" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),459.0)</f>
+        <v>459</v>
+      </c>
+      <c r="B151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
+      </c>
+      <c r="C151" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
         <v>REAL MADRID</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),412.0)</f>
-        <v>412</v>
-      </c>
-      <c r="B138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
-        <v>MATEO JOSEPH</v>
-      </c>
-      <c r="C138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),417.0)</f>
-        <v>417</v>
-      </c>
-      <c r="B139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
-        <v>FEBAS</v>
-      </c>
-      <c r="C139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),418.0)</f>
-        <v>418</v>
-      </c>
-      <c r="B140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
-      </c>
-      <c r="C140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),420.0)</f>
-        <v>420</v>
-      </c>
-      <c r="B141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
-        <v>DARDER</v>
-      </c>
-      <c r="C141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),423.0)</f>
-        <v>423</v>
-      </c>
-      <c r="B142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LÓPEZ")</f>
-        <v>UNAI LÓPEZ</v>
-      </c>
-      <c r="C142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),424.0)</f>
-        <v>424</v>
-      </c>
-      <c r="B143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
-        <v>TENAGLIA</v>
-      </c>
-      <c r="C143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),428.0)</f>
-        <v>428</v>
-      </c>
-      <c r="B144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
-      </c>
-      <c r="C144" s="20" t="str">
+    <row r="152">
+      <c r="A152" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),460.0)</f>
+        <v>460</v>
+      </c>
+      <c r="B152" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
+      </c>
+      <c r="C152" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),464.0)</f>
+        <v>464</v>
+      </c>
+      <c r="B153" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
+        <v>VARGAS</v>
+      </c>
+      <c r="C153" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),466.0)</f>
+        <v>466</v>
+      </c>
+      <c r="B154" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
+        <v>MOLEIRO</v>
+      </c>
+      <c r="C154" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),468.0)</f>
+        <v>468</v>
+      </c>
+      <c r="B155" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD CHAMPIONS")</f>
+        <v>CARD CHAMPIONS</v>
+      </c>
+      <c r="C155" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.0)</f>
+        <v>470</v>
+      </c>
+      <c r="B156" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ÁLVAREZ")</f>
+        <v>JULIÁN ÁLVAREZ</v>
+      </c>
+      <c r="C156" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATLÉTICO)")</f>
+        <v>BALÓN DE ORO (ATLÉTICO)</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),471.0)</f>
+        <v>471</v>
+      </c>
+      <c r="B157" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRI")</f>
+        <v>PEDRI</v>
+      </c>
+      <c r="C157" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
+        <v>BALÓN DE ORO (BARÇA)</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),472.0)</f>
+        <v>472</v>
+      </c>
+      <c r="B158" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
+        <v>LAMINE YAMAL</v>
+      </c>
+      <c r="C158" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
+        <v>BALÓN DE ORO (BARÇA)</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),473.0)</f>
+        <v>473</v>
+      </c>
+      <c r="B159" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
+      </c>
+      <c r="C159" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (REAL MADRID)")</f>
+        <v>BALÓN DE ORO (REAL MADRID)</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),475.0)</f>
+        <v>475</v>
+      </c>
+      <c r="B160" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO EXCELLENCE")</f>
+        <v>BALÓN DE ORO EXCELLENCE</v>
+      </c>
+      <c r="C160" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.0)</f>
+        <v>476</v>
+      </c>
+      <c r="B161" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD ATÓMICA")</f>
+        <v>CARD ATÓMICA</v>
+      </c>
+      <c r="C161" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
+        <v>91</v>
+      </c>
+      <c r="B162" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
+      </c>
+      <c r="C162" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),429.0)</f>
-        <v>429</v>
-      </c>
-      <c r="B145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
-      </c>
-      <c r="C145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),430.0)</f>
-        <v>430</v>
-      </c>
-      <c r="B146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
-        <v>VANAT</v>
-      </c>
-      <c r="C146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),433.0)</f>
-        <v>433</v>
-      </c>
-      <c r="B147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
-        <v>LEO ROMÁN</v>
-      </c>
-      <c r="C147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),435.0)</f>
-        <v>435</v>
-      </c>
-      <c r="B148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
-        <v>HASSAN</v>
-      </c>
-      <c r="C148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),437.0)</f>
-        <v>437</v>
-      </c>
-      <c r="B149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
-        <v>GORROTXATEGI</v>
-      </c>
-      <c r="C149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),438.0)</f>
-        <v>438</v>
-      </c>
-      <c r="B150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATISTA MENDY")</f>
-        <v>BATISTA MENDY</v>
-      </c>
-      <c r="C150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),441.0)</f>
-        <v>441</v>
-      </c>
-      <c r="B151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUCHANAN")</f>
-        <v>BUCHANAN</v>
-      </c>
-      <c r="C151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),442.0)</f>
-        <v>442</v>
-      </c>
-      <c r="B152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
-        <v>UNAI SIMÓN</v>
-      </c>
-      <c r="C152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),443.0)</f>
-        <v>443</v>
-      </c>
-      <c r="B153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAUREGIZAR")</f>
-        <v>JAUREGIZAR</v>
-      </c>
-      <c r="C153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),445.0)</f>
-        <v>445</v>
-      </c>
-      <c r="B154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
-        <v>MARCOS LLORENTE</v>
-      </c>
-      <c r="C154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446.0)</f>
-        <v>446</v>
-      </c>
-      <c r="B155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLEX BAENA")</f>
-        <v>ÁLEX BAENA</v>
-      </c>
-      <c r="C155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),451.0)</f>
-        <v>451</v>
-      </c>
-      <c r="B156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
-        <v>RAPHINHA</v>
-      </c>
-      <c r="C156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),453.0)</f>
-        <v>453</v>
-      </c>
-      <c r="B157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RASHFORD")</f>
-        <v>RASHFORD</v>
-      </c>
-      <c r="C157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
-        <v>454</v>
-      </c>
-      <c r="B158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
-        <v>ISCO</v>
-      </c>
-      <c r="C158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),459.0)</f>
-        <v>459</v>
-      </c>
-      <c r="B159" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
-      </c>
-      <c r="C159" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),460.0)</f>
-        <v>460</v>
-      </c>
-      <c r="B160" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
-      </c>
-      <c r="C160" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),464.0)</f>
-        <v>464</v>
-      </c>
-      <c r="B161" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
-        <v>VARGAS</v>
-      </c>
-      <c r="C161" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),466.0)</f>
-        <v>466</v>
-      </c>
-      <c r="B162" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
-        <v>MOLEIRO</v>
-      </c>
-      <c r="C162" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
     <row r="163">
       <c r="A163" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),468.0)</f>
-        <v>468</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),181.0)</f>
+        <v>181</v>
       </c>
       <c r="B163" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD CHAMPIONS")</f>
-        <v>CARD CHAMPIONS</v>
-      </c>
-      <c r="C163" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.0)</f>
-        <v>470</v>
-      </c>
-      <c r="B164" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ÁLVAREZ")</f>
-        <v>JULIÁN ÁLVAREZ</v>
-      </c>
-      <c r="C164" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATLÉTICO)")</f>
-        <v>BALÓN DE ORO (ATLÉTICO)</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),471.0)</f>
-        <v>471</v>
-      </c>
-      <c r="B165" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRI")</f>
-        <v>PEDRI</v>
-      </c>
-      <c r="C165" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
-        <v>BALÓN DE ORO (BARÇA)</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),472.0)</f>
-        <v>472</v>
-      </c>
-      <c r="B166" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
-        <v>LAMINE YAMAL</v>
-      </c>
-      <c r="C166" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
-        <v>BALÓN DE ORO (BARÇA)</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),473.0)</f>
-        <v>473</v>
-      </c>
-      <c r="B167" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
-      </c>
-      <c r="C167" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (REAL MADRID)")</f>
-        <v>BALÓN DE ORO (REAL MADRID)</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),475.0)</f>
-        <v>475</v>
-      </c>
-      <c r="B168" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO EXCELLENCE")</f>
-        <v>BALÓN DE ORO EXCELLENCE</v>
-      </c>
-      <c r="C168" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.0)</f>
-        <v>476</v>
-      </c>
-      <c r="B169" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD ATÓMICA")</f>
-        <v>CARD ATÓMICA</v>
-      </c>
-      <c r="C169" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
-        <v>91</v>
-      </c>
-      <c r="B170" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
         <v>ESTADIO</v>
       </c>
-      <c r="C170" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),181.0)</f>
-        <v>181</v>
-      </c>
-      <c r="B171" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C171" s="20" t="str">
+      <c r="C163" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
         <v>LEVANTE UD</v>
       </c>
@@ -5904,12 +5798,12 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
+        <v>117</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
+        <v>FEDE REDONDO</v>
       </c>
       <c r="C25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5922,16 +5816,16 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D26" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5940,12 +5834,12 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C27" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5958,12 +5852,12 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C28" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5976,12 +5870,12 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C29" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5994,12 +5888,12 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
       </c>
       <c r="C30" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -6012,16 +5906,16 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D31" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6030,16 +5924,16 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D32" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6048,12 +5942,12 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -6066,48 +5960,48 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C34" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
       </c>
       <c r="D34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
+      </c>
+      <c r="B35" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
+      </c>
+      <c r="C35" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+      <c r="D35" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
         <v>202</v>
       </c>
-      <c r="B35" s="20" t="str">
+      <c r="B36" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
         <v>CARVAJAL</v>
-      </c>
-      <c r="C35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
-      </c>
-      <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
       </c>
       <c r="C36" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6120,12 +6014,12 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
-        <v>213</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
-        <v>RODRYGO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C37" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6138,12 +6032,12 @@
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
       </c>
       <c r="C38" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6156,16 +6050,16 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
+        <v>213</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
+        <v>RODRYGO</v>
       </c>
       <c r="C39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D39" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6174,34 +6068,34 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C40" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D40" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
+      </c>
+      <c r="B41" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
+      </c>
+      <c r="C41" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
-      </c>
-      <c r="D40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
-      </c>
-      <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
       </c>
       <c r="D41" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6210,16 +6104,16 @@
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
+        <v>225</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
+        <v>MOJICA</v>
       </c>
       <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D42" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6228,16 +6122,16 @@
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
-        <v>237</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
-        <v>AITOR FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
       </c>
       <c r="C43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D43" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6246,12 +6140,12 @@
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C44" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -6264,16 +6158,16 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D45" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6282,34 +6176,34 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
+        <v>237</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
+        <v>AITOR FERNÁNDEZ</v>
       </c>
       <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D47" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6318,12 +6212,12 @@
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C48" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -6336,16 +6230,16 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
-        <v>277</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
-        <v>LUIZ FELIPE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D49" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6354,34 +6248,34 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D51" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6390,16 +6284,16 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
+        <v>277</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
+        <v>LUIZ FELIPE</v>
       </c>
       <c r="C52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D52" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6408,34 +6302,34 @@
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
       </c>
       <c r="C53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
       </c>
       <c r="C54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D54" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6444,34 +6338,34 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
       </c>
       <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
+        <v>296</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
+        <v>SERGIO GÓMEZ</v>
       </c>
       <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D56" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6480,16 +6374,16 @@
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D57" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6498,16 +6392,16 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D58" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6516,16 +6410,16 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
+        <v>312</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
+        <v>AZPILICUETA</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D59" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6534,16 +6428,16 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D60" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6552,34 +6446,34 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D62" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6588,16 +6482,16 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D63" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6606,16 +6500,16 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
       </c>
       <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D64" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6624,16 +6518,16 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
       </c>
       <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D65" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6642,16 +6536,16 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D66" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6660,16 +6554,16 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D67" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6678,12 +6572,12 @@
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
       </c>
       <c r="C68" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -6696,16 +6590,16 @@
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D69" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6714,16 +6608,16 @@
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6732,16 +6626,16 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D71" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6750,34 +6644,34 @@
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D73" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6786,16 +6680,16 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
-      </c>
-      <c r="C74" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
         <v>GETAFE CF</v>
+      </c>
+      <c r="C74" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D74" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6804,34 +6698,34 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
-        <v>425</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
-        <v>CARLOS VICENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
       </c>
       <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D76" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6840,16 +6734,16 @@
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D77" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6858,16 +6752,16 @@
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
-        <v>444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
-        <v>OBLAK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D78" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6876,16 +6770,16 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
-        <v>456</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
-        <v>ANTONY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D79" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6894,38 +6788,218 @@
     </row>
     <row r="80">
       <c r="A80" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
+      </c>
+      <c r="B80" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
+      </c>
+      <c r="C80" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D80" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
+      </c>
+      <c r="B81" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
+      </c>
+      <c r="C81" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D81" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
+      </c>
+      <c r="B82" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
+      </c>
+      <c r="C82" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D82" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
+      </c>
+      <c r="B83" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
+      </c>
+      <c r="C83" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D83" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
+        <v>425</v>
+      </c>
+      <c r="B84" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
+        <v>CARLOS VICENTE</v>
+      </c>
+      <c r="C84" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
+      </c>
+      <c r="D84" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
+        <v>436</v>
+      </c>
+      <c r="B85" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
+        <v>CARLOS SOLER</v>
+      </c>
+      <c r="C85" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+      <c r="D85" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
+      </c>
+      <c r="B86" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
+      </c>
+      <c r="C86" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D86" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
+        <v>444</v>
+      </c>
+      <c r="B87" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
+        <v>OBLAK</v>
+      </c>
+      <c r="C87" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D87" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
+        <v>456</v>
+      </c>
+      <c r="B88" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
+        <v>ANTONY</v>
+      </c>
+      <c r="C88" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D88" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
         <v>458</v>
       </c>
-      <c r="B80" s="20" t="str">
+      <c r="B89" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
         <v>CARRERAS</v>
       </c>
-      <c r="C80" s="20" t="str">
+      <c r="C89" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
         <v>REAL MADRID</v>
       </c>
-      <c r="D80" s="20">
+      <c r="D89" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20">
+    <row r="90">
+      <c r="A90" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B81" s="20" t="str">
+      <c r="B90" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C81" s="20" t="str">
+      <c r="C90" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D81" s="20">
+      <c r="D90" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),477.0)</f>
+        <v>477</v>
+      </c>
+      <c r="B91" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD INVENCIBLE")</f>
+        <v>CARD INVENCIBLE</v>
+      </c>
+      <c r="C91" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
+      </c>
+      <c r="D91" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7327,7 +7401,9 @@
       <c r="C28" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="21"/>
+      <c r="D28" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="21">
@@ -7557,7 +7633,9 @@
       <c r="C45" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D45" s="21"/>
+      <c r="D45" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="21">
@@ -8004,7 +8082,9 @@
       <c r="C78" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D78" s="21"/>
+      <c r="D78" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="21">
@@ -8559,6 +8639,9 @@
       <c r="D117" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E117" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="21">
@@ -8979,7 +9062,9 @@
       <c r="C147" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D147" s="21"/>
+      <c r="D147" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="21">
@@ -9355,7 +9440,7 @@
         <v>20</v>
       </c>
       <c r="E175" s="22">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="176">
@@ -9849,6 +9934,9 @@
       <c r="D211" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E211" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="21">
@@ -9921,7 +10009,7 @@
         <v>20</v>
       </c>
       <c r="E216" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="217">
@@ -10046,6 +10134,9 @@
       <c r="D225" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E225" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="21">
@@ -10216,7 +10307,7 @@
         <v>20</v>
       </c>
       <c r="E237" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="238">
@@ -10420,7 +10511,9 @@
       <c r="C252" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D252" s="21"/>
+      <c r="D252" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="21">
@@ -10849,6 +10942,9 @@
       <c r="D283" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E283" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="21">
@@ -10914,7 +11010,9 @@
       <c r="C288" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="D288" s="21"/>
+      <c r="D288" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="21">
@@ -11026,6 +11124,9 @@
       <c r="D296" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E296" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="21">
@@ -11246,6 +11347,9 @@
       <c r="D312" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E312" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="21">
@@ -11372,7 +11476,7 @@
         <v>20</v>
       </c>
       <c r="E321" s="22">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="322">
@@ -11462,6 +11566,9 @@
       <c r="D327" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E327" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="21">
@@ -11626,7 +11733,7 @@
         <v>20</v>
       </c>
       <c r="E338" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="339">
@@ -11920,7 +12027,9 @@
       <c r="C359" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="D359" s="21"/>
+      <c r="D359" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="21">
@@ -12356,7 +12465,9 @@
       <c r="C7" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="D7" s="21"/>
+      <c r="D7" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21">
@@ -14960,6 +15071,9 @@
       <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E8" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="21">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="399">
   <si>
     <t>Última actualización:</t>
   </si>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B1" s="2">
         <f>TODAY()</f>
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1833,15 +1833,15 @@
       </c>
       <c r="C3" s="9">
         <f>COUNTIF(REGULARES!D:D, "SI")</f>
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D3" s="9">
         <f t="shared" ref="D3:D12" si="1">B3-C3</f>
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E4" si="2">(C3/B3)</f>
-        <v>0.6916666667</v>
+        <v>0.7</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E3, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1857,15 +1857,15 @@
       </c>
       <c r="C4" s="9">
         <f>COUNTIF(Estadios!D:D, "SI")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="9">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="10">
         <f t="shared" si="2"/>
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F4" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E4, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="4"/>
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="4"/>
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>0.6726907631</v>
+        <v>0.6807228916</v>
       </c>
       <c r="F13" s="19" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E13, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2787,6 +2787,9 @@
       <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E8" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="21">
@@ -2826,6 +2829,9 @@
       </c>
       <c r="D11" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E11" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="12">
@@ -3420,12 +3426,12 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),77.0)</f>
-        <v>77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.0)</f>
+        <v>80</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARTRA")</f>
-        <v>BARTRA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
       </c>
       <c r="C27" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3434,12 +3440,12 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.0)</f>
-        <v>80</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.0)</f>
+        <v>82</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALTIMIRA")</f>
+        <v>ALTIMIRA</v>
       </c>
       <c r="C28" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3448,12 +3454,12 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.0)</f>
-        <v>82</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.0)</f>
+        <v>83</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALTIMIRA")</f>
-        <v>ALTIMIRA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AMRABAT")</f>
+        <v>AMRABAT</v>
       </c>
       <c r="C29" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3462,12 +3468,12 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.0)</f>
-        <v>83</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),85.0)</f>
+        <v>85</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AMRABAT")</f>
-        <v>AMRABAT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LO CELSO")</f>
+        <v>LO CELSO</v>
       </c>
       <c r="C30" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3476,12 +3482,12 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),85.0)</f>
-        <v>85</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
+        <v>89</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LO CELSO")</f>
-        <v>LO CELSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIQUELME")</f>
+        <v>RIQUELME</v>
       </c>
       <c r="C31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3490,12 +3496,12 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
-        <v>89</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.0)</f>
+        <v>90</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIQUELME")</f>
-        <v>RIQUELME</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABDE")</f>
+        <v>ABDE</v>
       </c>
       <c r="C32" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3504,26 +3510,26 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.0)</f>
-        <v>90</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.0)</f>
+        <v>92</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABDE")</f>
-        <v>ABDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RADU")</f>
+        <v>RADU</v>
       </c>
       <c r="C33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.0)</f>
-        <v>92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RADU")</f>
-        <v>RADU</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RODRÍGUEZ")</f>
+        <v>JAVI RODRÍGUEZ</v>
       </c>
       <c r="C34" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3532,12 +3538,12 @@
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
-        <v>95</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.0)</f>
+        <v>96</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RODRÍGUEZ")</f>
-        <v>JAVI RODRÍGUEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"STARFELT")</f>
+        <v>STARFELT</v>
       </c>
       <c r="C35" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3546,12 +3552,12 @@
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.0)</f>
-        <v>96</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
+        <v>98</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"STARFELT")</f>
-        <v>STARFELT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MINGUEZA")</f>
+        <v>MINGUEZA</v>
       </c>
       <c r="C36" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3560,12 +3566,12 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
-        <v>98</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101.0)</f>
+        <v>101</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MINGUEZA")</f>
-        <v>MINGUEZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN BELTRÁN")</f>
+        <v>FRAN BELTRÁN</v>
       </c>
       <c r="C37" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3574,12 +3580,12 @@
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101.0)</f>
-        <v>101</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN BELTRÁN")</f>
-        <v>FRAN BELTRÁN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C38" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3588,26 +3594,26 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
+        <v>113</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CHUST")</f>
+        <v>CHUST</v>
       </c>
       <c r="C39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
-        <v>113</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
+        <v>114</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CHUST")</f>
-        <v>CHUST</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIGAS")</f>
+        <v>BIGAS</v>
       </c>
       <c r="C40" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3616,12 +3622,12 @@
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
-        <v>114</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),118.0)</f>
+        <v>118</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIGAS")</f>
-        <v>BIGAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GERMÁN VALERA")</f>
+        <v>GERMÁN VALERA</v>
       </c>
       <c r="C41" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3630,12 +3636,12 @@
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),118.0)</f>
-        <v>118</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
+        <v>119</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GERMÁN VALERA")</f>
-        <v>GERMÁN VALERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARTIM NETO")</f>
+        <v>MARTIM NETO</v>
       </c>
       <c r="C42" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3644,12 +3650,12 @@
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
-        <v>119</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
+        <v>120</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARTIM NETO")</f>
-        <v>MARTIM NETO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
+        <v>FEBAS</v>
       </c>
       <c r="C43" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3658,26 +3664,26 @@
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
-        <v>120</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
+        <v>128</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
-        <v>FEBAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
+        <v>DMITROVIC</v>
       </c>
       <c r="C44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
-        <v>128</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),132.0)</f>
+        <v>132</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
-        <v>DMITROVIC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
+        <v>RIEDEL</v>
       </c>
       <c r="C45" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -3686,12 +3692,12 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),132.0)</f>
-        <v>132</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
+        <v>133</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
-        <v>RIEDEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
       </c>
       <c r="C46" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -3700,12 +3706,12 @@
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
-        <v>133</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),143.0)</f>
+        <v>143</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PUADO")</f>
+        <v>PUADO</v>
       </c>
       <c r="C47" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -3714,40 +3720,40 @@
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),142.0)</f>
-        <v>142</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE GARCÍA")</f>
-        <v>KIKE GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),143.0)</f>
-        <v>143</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
+        <v>148</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PUADO")</f>
-        <v>PUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IGLESIAS")</f>
+        <v>IGLESIAS</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.0)</f>
+        <v>149</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKO FEMENÍA")</f>
+        <v>KIKO FEMENÍA</v>
       </c>
       <c r="C50" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3756,12 +3762,12 @@
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
-        <v>148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.0)</f>
+        <v>150</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IGLESIAS")</f>
-        <v>IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DJENÉ")</f>
+        <v>DJENÉ</v>
       </c>
       <c r="C51" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3770,12 +3776,12 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.0)</f>
-        <v>149</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
+        <v>151</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKO FEMENÍA")</f>
-        <v>KIKO FEMENÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOMINGOS DUARTE")</f>
+        <v>DOMINGOS DUARTE</v>
       </c>
       <c r="C52" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3784,12 +3790,12 @@
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.0)</f>
-        <v>150</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),155.0)</f>
+        <v>155</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DJENÉ")</f>
-        <v>DJENÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIO MARTÍN")</f>
+        <v>MARIO MARTÍN</v>
       </c>
       <c r="C53" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3798,12 +3804,12 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
-        <v>151</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),157.0)</f>
+        <v>157</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOMINGOS DUARTE")</f>
-        <v>DOMINGOS DUARTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
       </c>
       <c r="C54" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3812,12 +3818,12 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),155.0)</f>
-        <v>155</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),161.0)</f>
+        <v>161</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIO MARTÍN")</f>
-        <v>MARIO MARTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C55" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3826,12 +3832,12 @@
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),157.0)</f>
-        <v>157</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),162.0)</f>
+        <v>162</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COBA")</f>
+        <v>COBA</v>
       </c>
       <c r="C56" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3840,40 +3846,40 @@
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),161.0)</f>
-        <v>161</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
+        <v>164</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAZZANIGA")</f>
+        <v>GAZZANIGA</v>
       </c>
       <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),162.0)</f>
-        <v>162</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),167.0)</f>
+        <v>167</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COBA")</f>
-        <v>COBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO RINCÓN")</f>
+        <v>HUGO RINCÓN</v>
       </c>
       <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
-        <v>164</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
+        <v>168</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAZZANIGA")</f>
-        <v>GAZZANIGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VITOR REIS")</f>
+        <v>VITOR REIS</v>
       </c>
       <c r="C59" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -3882,12 +3888,12 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),167.0)</f>
-        <v>167</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.0)</f>
+        <v>169</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO RINCÓN")</f>
-        <v>HUGO RINCÓN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BLIND")</f>
+        <v>BLIND</v>
       </c>
       <c r="C60" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -3896,12 +3902,12 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
-        <v>168</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.0)</f>
+        <v>178</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VITOR REIS")</f>
-        <v>VITOR REIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
+        <v>VANAT</v>
       </c>
       <c r="C61" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -3910,40 +3916,40 @@
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.0)</f>
-        <v>169</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
+        <v>182</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BLIND")</f>
-        <v>BLIND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RYAN")</f>
+        <v>RYAN</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.0)</f>
-        <v>178</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
+        <v>183</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
-        <v>VANAT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO CAMPOS")</f>
+        <v>PABLO CAMPOS</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
-        <v>182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.0)</f>
+        <v>186</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RYAN")</f>
-        <v>RYAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELGEZABAL")</f>
+        <v>ELGEZABAL</v>
       </c>
       <c r="C64" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -3952,12 +3958,12 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
-        <v>183</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),191.0)</f>
+        <v>191</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO CAMPOS")</f>
-        <v>PABLO CAMPOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARTÍNEZ")</f>
+        <v>PABLO MARTÍNEZ</v>
       </c>
       <c r="C65" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -3966,12 +3972,12 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.0)</f>
-        <v>186</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.0)</f>
+        <v>196</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELGEZABAL")</f>
-        <v>ELGEZABAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRUGUÉ")</f>
+        <v>BRUGUÉ</v>
       </c>
       <c r="C66" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -3980,12 +3986,12 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),191.0)</f>
-        <v>191</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
+        <v>198</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARTÍNEZ")</f>
-        <v>PABLO MARTÍNEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
+        <v>ETTA EYONG</v>
       </c>
       <c r="C67" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -3994,40 +4000,40 @@
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.0)</f>
-        <v>196</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.0)</f>
+        <v>201</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRUGUÉ")</f>
-        <v>BRUGUÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUNIN")</f>
+        <v>LUNIN</v>
       </c>
       <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
-        <v>198</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.0)</f>
+        <v>205</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
-        <v>ETTA EYONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUIJSEN")</f>
+        <v>HUIJSEN</v>
       </c>
       <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.0)</f>
-        <v>201</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
+        <v>214</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUNIN")</f>
-        <v>LUNIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
+        <v>MBAPPÉ</v>
       </c>
       <c r="C70" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -4036,40 +4042,40 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.0)</f>
-        <v>205</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
+        <v>217</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUIJSEN")</f>
-        <v>HUIJSEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
-        <v>214</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
+        <v>218</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
-        <v>MBAPPÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
+        <v>LEO ROMÁN</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
-        <v>217</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
+        <v>224</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
+        <v>KUMBULLA</v>
       </c>
       <c r="C73" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4078,12 +4084,12 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
-        <v>218</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.0)</f>
+        <v>229</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
-        <v>LEO ROMÁN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORLANES")</f>
+        <v>MORLANES</v>
       </c>
       <c r="C74" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4092,12 +4098,12 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
-        <v>224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.0)</f>
+        <v>231</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
-        <v>KUMBULLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ASANO")</f>
+        <v>ASANO</v>
       </c>
       <c r="C75" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4106,12 +4112,12 @@
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.0)</f>
-        <v>229</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),232.0)</f>
+        <v>232</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORLANES")</f>
-        <v>MORLANES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MURIQI")</f>
+        <v>MURIQI</v>
       </c>
       <c r="C76" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4120,12 +4126,12 @@
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.0)</f>
-        <v>231</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),233.0)</f>
+        <v>233</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ASANO")</f>
-        <v>ASANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
+        <v>MATEO JOSEPH</v>
       </c>
       <c r="C77" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4134,40 +4140,40 @@
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),232.0)</f>
-        <v>232</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.0)</f>
+        <v>239</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MURIQI")</f>
-        <v>MURIQI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYOMO")</f>
+        <v>BOYOMO</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),233.0)</f>
-        <v>233</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.0)</f>
+        <v>241</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
-        <v>MATEO JOSEPH</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HERRANDO")</f>
+        <v>HERRANDO</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.0)</f>
-        <v>239</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
+        <v>242</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYOMO")</f>
-        <v>BOYOMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
+        <v>JUAN CRUZ</v>
       </c>
       <c r="C80" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -4176,12 +4182,12 @@
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.0)</f>
-        <v>241</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),251.0)</f>
+        <v>251</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HERRANDO")</f>
-        <v>HERRANDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUDIMIR")</f>
+        <v>BUDIMIR</v>
       </c>
       <c r="C81" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -4190,40 +4196,40 @@
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
-        <v>242</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
+        <v>253</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
-        <v>JUAN CRUZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),251.0)</f>
-        <v>251</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),254.0)</f>
+        <v>254</v>
       </c>
       <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUDIMIR")</f>
-        <v>BUDIMIR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AARON ESCANDELL")</f>
+        <v>AARON ESCANDELL</v>
       </c>
       <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
-        <v>253</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
+        <v>260</v>
       </c>
       <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
+        <v>RAHIM ALHASSANE</v>
       </c>
       <c r="C84" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4232,12 +4238,12 @@
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),254.0)</f>
-        <v>254</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
+        <v>261</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AARON ESCANDELL")</f>
-        <v>AARON ESCANDELL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLOMBATTO")</f>
+        <v>COLOMBATTO</v>
       </c>
       <c r="C85" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4246,12 +4252,12 @@
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
-        <v>260</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),263.0)</f>
+        <v>263</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
-        <v>RAHIM ALHASSANE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DENDONCKER")</f>
+        <v>DENDONCKER</v>
       </c>
       <c r="C86" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4260,12 +4266,12 @@
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
-        <v>261</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),266.0)</f>
+        <v>266</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLOMBATTO")</f>
-        <v>COLOMBATTO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
+        <v>HASSAN</v>
       </c>
       <c r="C87" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4274,12 +4280,12 @@
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),263.0)</f>
-        <v>263</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),268.0)</f>
+        <v>268</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DENDONCKER")</f>
-        <v>DENDONCKER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILYAS CHAIRA")</f>
+        <v>ILYAS CHAIRA</v>
       </c>
       <c r="C88" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4288,40 +4294,40 @@
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),266.0)</f>
-        <v>266</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),271.0)</f>
+        <v>271</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
-        <v>HASSAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),268.0)</f>
-        <v>268</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.0)</f>
+        <v>273</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILYAS CHAIRA")</f>
-        <v>ILYAS CHAIRA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CÁRDENAS")</f>
+        <v>CÁRDENAS</v>
       </c>
       <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),271.0)</f>
-        <v>271</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),276.0)</f>
+        <v>276</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
+        <v>LEJEUNE</v>
       </c>
       <c r="C91" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -4330,12 +4336,12 @@
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.0)</f>
-        <v>273</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),279.0)</f>
+        <v>279</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CÁRDENAS")</f>
-        <v>CÁRDENAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PATHÉ CISS")</f>
+        <v>PATHÉ CISS</v>
       </c>
       <c r="C92" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -4344,12 +4350,12 @@
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),276.0)</f>
-        <v>276</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),280.0)</f>
+        <v>280</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
-        <v>LEJEUNE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LOPEZ")</f>
+        <v>UNAI LOPEZ</v>
       </c>
       <c r="C93" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -4358,12 +4364,12 @@
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),279.0)</f>
-        <v>279</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),285.0)</f>
+        <v>285</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PATHÉ CISS")</f>
-        <v>PATHÉ CISS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN PÉREZ")</f>
+        <v>FRAN PÉREZ</v>
       </c>
       <c r="C94" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -4372,40 +4378,40 @@
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),280.0)</f>
-        <v>280</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
+        <v>289</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LOPEZ")</f>
-        <v>UNAI LOPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),285.0)</f>
-        <v>285</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),294.0)</f>
+        <v>294</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN PÉREZ")</f>
-        <v>FRAN PÉREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZUBELDIA")</f>
+        <v>ZUBELDIA</v>
       </c>
       <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
-        <v>289</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),297.0)</f>
+        <v>297</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
+        <v>GORROTXATEGI</v>
       </c>
       <c r="C97" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -4414,12 +4420,12 @@
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),294.0)</f>
-        <v>294</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.0)</f>
+        <v>300</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZUBELDIA")</f>
-        <v>ZUBELDIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
+        <v>CARLOS SOLER</v>
       </c>
       <c r="C98" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -4428,12 +4434,12 @@
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),297.0)</f>
-        <v>297</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),301.0)</f>
+        <v>301</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
-        <v>GORROTXATEGI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRAIS MÉNDEZ")</f>
+        <v>BRAIS MÉNDEZ</v>
       </c>
       <c r="C99" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -4442,12 +4448,12 @@
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.0)</f>
-        <v>300</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),305.0)</f>
+        <v>305</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
-        <v>CARLOS SOLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSKARSSON")</f>
+        <v>ÓSKARSSON</v>
       </c>
       <c r="C100" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -4456,40 +4462,40 @@
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),301.0)</f>
-        <v>301</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),310.0)</f>
+        <v>310</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRAIS MÉNDEZ")</f>
-        <v>BRAIS MÉNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARMONA")</f>
+        <v>CARMONA</v>
       </c>
       <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),305.0)</f>
-        <v>305</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),314.0)</f>
+        <v>314</v>
       </c>
       <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSKARSSON")</f>
-        <v>ÓSKARSSON</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCAO")</f>
+        <v>MARCAO</v>
       </c>
       <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),310.0)</f>
-        <v>310</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),320.0)</f>
+        <v>320</v>
       </c>
       <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARMONA")</f>
-        <v>CARMONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
+        <v>VARGAS</v>
       </c>
       <c r="C103" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
@@ -4498,12 +4504,12 @@
     </row>
     <row r="104">
       <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),314.0)</f>
-        <v>314</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),324.0)</f>
+        <v>324</v>
       </c>
       <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCAO")</f>
-        <v>MARCAO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
       </c>
       <c r="C104" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
@@ -4512,54 +4518,54 @@
     </row>
     <row r="105">
       <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),320.0)</f>
-        <v>320</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),339.0)</f>
+        <v>339</v>
       </c>
       <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
-        <v>VARGAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO LÓPEZ")</f>
+        <v>DIEGO LÓPEZ</v>
       </c>
       <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),324.0)</f>
-        <v>324</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
+        <v>348</v>
       </c>
       <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MARÍN")</f>
+        <v>RAFA MARÍN</v>
       </c>
       <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),339.0)</f>
-        <v>339</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),349.0)</f>
+        <v>349</v>
       </c>
       <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO LÓPEZ")</f>
-        <v>DIEGO LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RENATO VEIGA")</f>
+        <v>RENATO VEIGA</v>
       </c>
       <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
-        <v>348</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),360.0)</f>
+        <v>360</v>
       </c>
       <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MARÍN")</f>
-        <v>RAFA MARÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AYOZE")</f>
+        <v>AYOZE</v>
       </c>
       <c r="C108" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
@@ -4568,54 +4574,54 @@
     </row>
     <row r="109">
       <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),349.0)</f>
-        <v>349</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),364.0)</f>
+        <v>364</v>
       </c>
       <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RENATO VEIGA")</f>
-        <v>RENATO VEIGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="C109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),357.0)</f>
-        <v>357</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),365.0)</f>
+        <v>365</v>
       </c>
       <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MIKAUTADZE")</f>
-        <v>MIKAUTADZE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="C110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),360.0)</f>
-        <v>360</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
+        <v>366</v>
       </c>
       <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AYOZE")</f>
-        <v>AYOZE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="C111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),364.0)</f>
-        <v>364</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),373.0)</f>
+        <v>373</v>
       </c>
       <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="C112" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4624,12 +4630,12 @@
     </row>
     <row r="113">
       <c r="A113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),365.0)</f>
-        <v>365</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
+        <v>375</v>
       </c>
       <c r="B113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="C113" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4638,12 +4644,12 @@
     </row>
     <row r="114">
       <c r="A114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
-        <v>366</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),377.0)</f>
+        <v>377</v>
       </c>
       <c r="B114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="C114" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4652,12 +4658,12 @@
     </row>
     <row r="115">
       <c r="A115" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),373.0)</f>
-        <v>373</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),378.0)</f>
+        <v>378</v>
       </c>
       <c r="B115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="C115" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4666,12 +4672,12 @@
     </row>
     <row r="116">
       <c r="A116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
-        <v>375</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),380.0)</f>
+        <v>380</v>
       </c>
       <c r="B116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="C116" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4680,110 +4686,110 @@
     </row>
     <row r="117">
       <c r="A117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),377.0)</f>
-        <v>377</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
+        <v>383</v>
       </c>
       <c r="B117" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
+      </c>
+      <c r="C117" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),384.0)</f>
+        <v>384</v>
+      </c>
+      <c r="B118" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
+      </c>
+      <c r="C118" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.0)</f>
+        <v>385</v>
+      </c>
+      <c r="B119" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATALLA")</f>
+        <v>BATALLA</v>
+      </c>
+      <c r="C119" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.0)</f>
+        <v>386</v>
+      </c>
+      <c r="B120" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
+      </c>
+      <c r="C120" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-      <c r="C117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),378.0)</f>
-        <v>378</v>
-      </c>
-      <c r="B118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="C118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),380.0)</f>
-        <v>380</v>
-      </c>
-      <c r="B119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="C119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
-        <v>383</v>
-      </c>
-      <c r="B120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
-      </c>
-      <c r="C120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),384.0)</f>
-        <v>384</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.0)</f>
+        <v>388</v>
       </c>
       <c r="B121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
+        <v>LAPORTE</v>
       </c>
       <c r="C121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.0)</f>
-        <v>385</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),390.0)</f>
+        <v>390</v>
       </c>
       <c r="B122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATALLA")</f>
-        <v>BATALLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LE NORMAND")</f>
+        <v>LE NORMAND</v>
       </c>
       <c r="C122" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),394.0)</f>
+        <v>394</v>
+      </c>
+      <c r="B123" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
+        <v>LEJEUNE</v>
+      </c>
+      <c r="C123" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
         <v>RAYO VALLECANO</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.0)</f>
-        <v>386</v>
-      </c>
-      <c r="B123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
-      </c>
-      <c r="C123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
     <row r="124">
       <c r="A124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.0)</f>
-        <v>388</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),397.0)</f>
+        <v>397</v>
       </c>
       <c r="B124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
-        <v>LAPORTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REGO")</f>
+        <v>REGO</v>
       </c>
       <c r="C124" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -4792,54 +4798,54 @@
     </row>
     <row r="125">
       <c r="A125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),390.0)</f>
-        <v>390</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
+        <v>401</v>
       </c>
       <c r="B125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LE NORMAND")</f>
-        <v>LE NORMAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
+        <v>RODRI MENDOZA</v>
       </c>
       <c r="C125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),394.0)</f>
-        <v>394</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),410.0)</f>
+        <v>410</v>
       </c>
       <c r="B126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
-        <v>LEJEUNE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
+        <v>GONZALO</v>
       </c>
       <c r="C126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),397.0)</f>
-        <v>397</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),412.0)</f>
+        <v>412</v>
       </c>
       <c r="B127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REGO")</f>
-        <v>REGO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
+        <v>MATEO JOSEPH</v>
       </c>
       <c r="C127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
-        <v>401</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),417.0)</f>
+        <v>417</v>
       </c>
       <c r="B128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
-        <v>RODRI MENDOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
+        <v>FEBAS</v>
       </c>
       <c r="C128" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -4848,26 +4854,26 @@
     </row>
     <row r="129">
       <c r="A129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),410.0)</f>
-        <v>410</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),418.0)</f>
+        <v>418</v>
       </c>
       <c r="B129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
-        <v>GONZALO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),412.0)</f>
-        <v>412</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),420.0)</f>
+        <v>420</v>
       </c>
       <c r="B130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
-        <v>MATEO JOSEPH</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
+        <v>DARDER</v>
       </c>
       <c r="C130" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4876,464 +4882,408 @@
     </row>
     <row r="131">
       <c r="A131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),417.0)</f>
-        <v>417</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),423.0)</f>
+        <v>423</v>
       </c>
       <c r="B131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
-        <v>FEBAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LÓPEZ")</f>
+        <v>UNAI LÓPEZ</v>
       </c>
       <c r="C131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),418.0)</f>
-        <v>418</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),424.0)</f>
+        <v>424</v>
       </c>
       <c r="B132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
+        <v>TENAGLIA</v>
       </c>
       <c r="C132" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),428.0)</f>
+        <v>428</v>
+      </c>
+      <c r="B133" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
+      </c>
+      <c r="C133" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),429.0)</f>
+        <v>429</v>
+      </c>
+      <c r="B134" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
+      </c>
+      <c r="C134" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),420.0)</f>
-        <v>420</v>
-      </c>
-      <c r="B133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
-        <v>DARDER</v>
-      </c>
-      <c r="C133" s="20" t="str">
+    <row r="135">
+      <c r="A135" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),430.0)</f>
+        <v>430</v>
+      </c>
+      <c r="B135" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
+        <v>VANAT</v>
+      </c>
+      <c r="C135" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),433.0)</f>
+        <v>433</v>
+      </c>
+      <c r="B136" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
+        <v>LEO ROMÁN</v>
+      </c>
+      <c r="C136" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),423.0)</f>
-        <v>423</v>
-      </c>
-      <c r="B134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LÓPEZ")</f>
-        <v>UNAI LÓPEZ</v>
-      </c>
-      <c r="C134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),424.0)</f>
-        <v>424</v>
-      </c>
-      <c r="B135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
-        <v>TENAGLIA</v>
-      </c>
-      <c r="C135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),428.0)</f>
-        <v>428</v>
-      </c>
-      <c r="B136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
-      </c>
-      <c r="C136" s="20" t="str">
+    <row r="137">
+      <c r="A137" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),435.0)</f>
+        <v>435</v>
+      </c>
+      <c r="B137" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
+        <v>HASSAN</v>
+      </c>
+      <c r="C137" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),437.0)</f>
+        <v>437</v>
+      </c>
+      <c r="B138" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
+        <v>GORROTXATEGI</v>
+      </c>
+      <c r="C138" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),438.0)</f>
+        <v>438</v>
+      </c>
+      <c r="B139" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATISTA MENDY")</f>
+        <v>BATISTA MENDY</v>
+      </c>
+      <c r="C139" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),441.0)</f>
+        <v>441</v>
+      </c>
+      <c r="B140" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUCHANAN")</f>
+        <v>BUCHANAN</v>
+      </c>
+      <c r="C140" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),442.0)</f>
+        <v>442</v>
+      </c>
+      <c r="B141" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
+        <v>UNAI SIMÓN</v>
+      </c>
+      <c r="C141" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),443.0)</f>
+        <v>443</v>
+      </c>
+      <c r="B142" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAUREGIZAR")</f>
+        <v>JAUREGIZAR</v>
+      </c>
+      <c r="C142" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),445.0)</f>
+        <v>445</v>
+      </c>
+      <c r="B143" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
+        <v>MARCOS LLORENTE</v>
+      </c>
+      <c r="C143" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446.0)</f>
+        <v>446</v>
+      </c>
+      <c r="B144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLEX BAENA")</f>
+        <v>ÁLEX BAENA</v>
+      </c>
+      <c r="C144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),451.0)</f>
+        <v>451</v>
+      </c>
+      <c r="B145" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
+        <v>RAPHINHA</v>
+      </c>
+      <c r="C145" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),453.0)</f>
+        <v>453</v>
+      </c>
+      <c r="B146" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RASHFORD")</f>
+        <v>RASHFORD</v>
+      </c>
+      <c r="C146" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
+        <v>454</v>
+      </c>
+      <c r="B147" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
+        <v>ISCO</v>
+      </c>
+      <c r="C147" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),459.0)</f>
+        <v>459</v>
+      </c>
+      <c r="B148" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
+      </c>
+      <c r="C148" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),460.0)</f>
+        <v>460</v>
+      </c>
+      <c r="B149" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
+      </c>
+      <c r="C149" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),464.0)</f>
+        <v>464</v>
+      </c>
+      <c r="B150" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
+        <v>VARGAS</v>
+      </c>
+      <c r="C150" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),466.0)</f>
+        <v>466</v>
+      </c>
+      <c r="B151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
+        <v>MOLEIRO</v>
+      </c>
+      <c r="C151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),468.0)</f>
+        <v>468</v>
+      </c>
+      <c r="B152" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD CHAMPIONS")</f>
+        <v>CARD CHAMPIONS</v>
+      </c>
+      <c r="C152" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.0)</f>
+        <v>470</v>
+      </c>
+      <c r="B153" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ÁLVAREZ")</f>
+        <v>JULIÁN ÁLVAREZ</v>
+      </c>
+      <c r="C153" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATLÉTICO)")</f>
+        <v>BALÓN DE ORO (ATLÉTICO)</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),471.0)</f>
+        <v>471</v>
+      </c>
+      <c r="B154" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRI")</f>
+        <v>PEDRI</v>
+      </c>
+      <c r="C154" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
+        <v>BALÓN DE ORO (BARÇA)</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),472.0)</f>
+        <v>472</v>
+      </c>
+      <c r="B155" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
+        <v>LAMINE YAMAL</v>
+      </c>
+      <c r="C155" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
+        <v>BALÓN DE ORO (BARÇA)</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),473.0)</f>
+        <v>473</v>
+      </c>
+      <c r="B156" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
+      </c>
+      <c r="C156" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (REAL MADRID)")</f>
+        <v>BALÓN DE ORO (REAL MADRID)</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),475.0)</f>
+        <v>475</v>
+      </c>
+      <c r="B157" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO EXCELLENCE")</f>
+        <v>BALÓN DE ORO EXCELLENCE</v>
+      </c>
+      <c r="C157" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.0)</f>
+        <v>476</v>
+      </c>
+      <c r="B158" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD ATÓMICA")</f>
+        <v>CARD ATÓMICA</v>
+      </c>
+      <c r="C158" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
+        <v>91</v>
+      </c>
+      <c r="B159" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
+      </c>
+      <c r="C159" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),429.0)</f>
-        <v>429</v>
-      </c>
-      <c r="B137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
-      </c>
-      <c r="C137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),430.0)</f>
-        <v>430</v>
-      </c>
-      <c r="B138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
-        <v>VANAT</v>
-      </c>
-      <c r="C138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),433.0)</f>
-        <v>433</v>
-      </c>
-      <c r="B139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
-        <v>LEO ROMÁN</v>
-      </c>
-      <c r="C139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),435.0)</f>
-        <v>435</v>
-      </c>
-      <c r="B140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
-        <v>HASSAN</v>
-      </c>
-      <c r="C140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),437.0)</f>
-        <v>437</v>
-      </c>
-      <c r="B141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
-        <v>GORROTXATEGI</v>
-      </c>
-      <c r="C141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),438.0)</f>
-        <v>438</v>
-      </c>
-      <c r="B142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATISTA MENDY")</f>
-        <v>BATISTA MENDY</v>
-      </c>
-      <c r="C142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),441.0)</f>
-        <v>441</v>
-      </c>
-      <c r="B143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUCHANAN")</f>
-        <v>BUCHANAN</v>
-      </c>
-      <c r="C143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),442.0)</f>
-        <v>442</v>
-      </c>
-      <c r="B144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
-        <v>UNAI SIMÓN</v>
-      </c>
-      <c r="C144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),443.0)</f>
-        <v>443</v>
-      </c>
-      <c r="B145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAUREGIZAR")</f>
-        <v>JAUREGIZAR</v>
-      </c>
-      <c r="C145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),445.0)</f>
-        <v>445</v>
-      </c>
-      <c r="B146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
-        <v>MARCOS LLORENTE</v>
-      </c>
-      <c r="C146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446.0)</f>
-        <v>446</v>
-      </c>
-      <c r="B147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLEX BAENA")</f>
-        <v>ÁLEX BAENA</v>
-      </c>
-      <c r="C147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),451.0)</f>
-        <v>451</v>
-      </c>
-      <c r="B148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
-        <v>RAPHINHA</v>
-      </c>
-      <c r="C148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),453.0)</f>
-        <v>453</v>
-      </c>
-      <c r="B149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RASHFORD")</f>
-        <v>RASHFORD</v>
-      </c>
-      <c r="C149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
-        <v>454</v>
-      </c>
-      <c r="B150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
-        <v>ISCO</v>
-      </c>
-      <c r="C150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),459.0)</f>
-        <v>459</v>
-      </c>
-      <c r="B151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
-      </c>
-      <c r="C151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),460.0)</f>
-        <v>460</v>
-      </c>
-      <c r="B152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
-      </c>
-      <c r="C152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),464.0)</f>
-        <v>464</v>
-      </c>
-      <c r="B153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
-        <v>VARGAS</v>
-      </c>
-      <c r="C153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),466.0)</f>
-        <v>466</v>
-      </c>
-      <c r="B154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
-        <v>MOLEIRO</v>
-      </c>
-      <c r="C154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),468.0)</f>
-        <v>468</v>
-      </c>
-      <c r="B155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD CHAMPIONS")</f>
-        <v>CARD CHAMPIONS</v>
-      </c>
-      <c r="C155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.0)</f>
-        <v>470</v>
-      </c>
-      <c r="B156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ÁLVAREZ")</f>
-        <v>JULIÁN ÁLVAREZ</v>
-      </c>
-      <c r="C156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATLÉTICO)")</f>
-        <v>BALÓN DE ORO (ATLÉTICO)</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),471.0)</f>
-        <v>471</v>
-      </c>
-      <c r="B157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRI")</f>
-        <v>PEDRI</v>
-      </c>
-      <c r="C157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
-        <v>BALÓN DE ORO (BARÇA)</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),472.0)</f>
-        <v>472</v>
-      </c>
-      <c r="B158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
-        <v>LAMINE YAMAL</v>
-      </c>
-      <c r="C158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
-        <v>BALÓN DE ORO (BARÇA)</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),473.0)</f>
-        <v>473</v>
-      </c>
-      <c r="B159" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
-      </c>
-      <c r="C159" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (REAL MADRID)")</f>
-        <v>BALÓN DE ORO (REAL MADRID)</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),475.0)</f>
-        <v>475</v>
-      </c>
-      <c r="B160" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO EXCELLENCE")</f>
-        <v>BALÓN DE ORO EXCELLENCE</v>
-      </c>
-      <c r="C160" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.0)</f>
-        <v>476</v>
-      </c>
-      <c r="B161" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD ATÓMICA")</f>
-        <v>CARD ATÓMICA</v>
-      </c>
-      <c r="C161" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
-        <v>91</v>
-      </c>
-      <c r="B162" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C162" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),181.0)</f>
-        <v>181</v>
-      </c>
-      <c r="B163" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C163" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
       </c>
     </row>
   </sheetData>
@@ -5378,8 +5328,8 @@
         <v>D. ALAVÉS</v>
       </c>
       <c r="D1" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
@@ -5420,12 +5370,12 @@
     </row>
     <row r="4">
       <c r="A4" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="B4" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIANO")</f>
-        <v>MARIANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYÉ")</f>
+        <v>BOYÉ</v>
       </c>
       <c r="C4" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -5438,16 +5388,16 @@
     </row>
     <row r="5">
       <c r="A5" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
+        <v>18</v>
       </c>
       <c r="B5" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIANO")</f>
+        <v>MARIANO</v>
       </c>
       <c r="C5" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D5" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5456,88 +5406,88 @@
     </row>
     <row r="6">
       <c r="A6" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
-        <v>27</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="B6" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUIZ DE GALARRETA")</f>
-        <v>RUIZ DE GALARRETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C6" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
         <v>ATHLETIC CLUB</v>
       </c>
       <c r="D6" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
-        <v>34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="B7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
-        <v>MAROAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUIZ DE GALARRETA")</f>
+        <v>RUIZ DE GALARRETA</v>
       </c>
       <c r="C7" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
         <v>ATHLETIC CLUB</v>
       </c>
       <c r="D7" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
+        <v>34</v>
+      </c>
+      <c r="B8" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
+        <v>MAROAN</v>
+      </c>
+      <c r="C8" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
+      </c>
+      <c r="D8" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="20">
+    <row r="9">
+      <c r="A9" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
         <v>42</v>
       </c>
-      <c r="B8" s="20" t="str">
+      <c r="B9" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
         <v>LENGLET</v>
-      </c>
-      <c r="C8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-      <c r="D8" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
-      </c>
-      <c r="B9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
-        <v>ALMADA</v>
       </c>
       <c r="C9" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
         <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
-        <v>67</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
       </c>
       <c r="B10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
-        <v>DANI OLMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
+        <v>ALMADA</v>
       </c>
       <c r="C10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D10" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5546,16 +5496,16 @@
     </row>
     <row r="11">
       <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
-        <v>73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
       </c>
       <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
+        <v>DANI OLMO</v>
       </c>
       <c r="C11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D11" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5564,12 +5514,12 @@
     </row>
     <row r="12">
       <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
       </c>
       <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
-        <v>PAU LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C12" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -5582,12 +5532,12 @@
     </row>
     <row r="13">
       <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
+        <v>PAU LÓPEZ</v>
       </c>
       <c r="C13" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -5600,34 +5550,34 @@
     </row>
     <row r="14">
       <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C14" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
-        <v>93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
-        <v>IVÁN VILLAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
       </c>
       <c r="C15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D15" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5636,12 +5586,12 @@
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
+        <v>93</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
+        <v>IVÁN VILLAR</v>
       </c>
       <c r="C16" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5654,12 +5604,12 @@
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C17" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5672,12 +5622,12 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C18" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5690,12 +5640,12 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C19" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5708,12 +5658,12 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C20" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5726,12 +5676,12 @@
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
+        <v>IAGO ASPAS</v>
       </c>
       <c r="C21" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5744,16 +5694,16 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
-        <v>IÑAKI PEÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D22" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5762,16 +5712,16 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
       </c>
       <c r="C23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D23" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5780,12 +5730,12 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
+        <v>IÑAKI PEÑA</v>
       </c>
       <c r="C24" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5798,12 +5748,12 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
-        <v>117</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
-        <v>FEDE REDONDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5816,12 +5766,12 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C26" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5834,16 +5784,16 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
+        <v>117</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
+        <v>FEDE REDONDO</v>
       </c>
       <c r="C27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D27" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5852,16 +5802,16 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D28" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5870,12 +5820,12 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C29" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5888,12 +5838,12 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C30" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5906,34 +5856,34 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
       </c>
       <c r="C32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D32" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5942,16 +5892,16 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D33" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5960,16 +5910,16 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D34" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5978,34 +5928,34 @@
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C35" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D35" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
+      </c>
+      <c r="B36" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C36" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
-      </c>
-      <c r="D35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
-        <v>202</v>
-      </c>
-      <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
-        <v>CARVAJAL</v>
-      </c>
-      <c r="C36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
       </c>
       <c r="D36" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6014,16 +5964,16 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D37" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6032,34 +5982,34 @@
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
-        <v>211</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
-        <v>GÜLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
       </c>
       <c r="C38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
-        <v>213</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.0)</f>
+        <v>177</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
-        <v>RODRYGO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TSYGANKOV")</f>
+        <v>TSYGANKOV</v>
       </c>
       <c r="C39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D39" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6068,52 +6018,52 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
+        <v>202</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
+        <v>CARVAJAL</v>
       </c>
       <c r="C40" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
         <v>REAL MADRID</v>
       </c>
       <c r="D40" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
+      </c>
+      <c r="B41" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
+      </c>
+      <c r="C41" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D41" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
-      </c>
-      <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
-      </c>
-      <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-      <c r="D41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
-        <v>225</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
-        <v>MOJICA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
       </c>
       <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D42" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6122,16 +6072,16 @@
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
+        <v>213</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
+        <v>RODRYGO</v>
       </c>
       <c r="C43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D43" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6140,34 +6090,34 @@
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
       </c>
       <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D45" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6176,34 +6126,34 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
-        <v>237</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
+        <v>225</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
-        <v>AITOR FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
+        <v>MOJICA</v>
       </c>
       <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
       </c>
       <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D47" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6212,16 +6162,16 @@
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D48" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6230,16 +6180,16 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D49" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6248,34 +6198,34 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
+        <v>237</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
+        <v>AITOR FERNÁNDEZ</v>
       </c>
       <c r="C50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
+        <v>248</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
       </c>
       <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D51" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6284,16 +6234,16 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
-        <v>277</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
-        <v>LUIZ FELIPE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D52" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6302,34 +6252,34 @@
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
-        <v>283</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
-        <v>PEDRO DÍAZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D54" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6338,16 +6288,16 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D55" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6356,16 +6306,16 @@
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
-        <v>296</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.0)</f>
+        <v>267</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
-        <v>SERGIO GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BREKALO")</f>
+        <v>BREKALO</v>
       </c>
       <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D56" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6374,16 +6324,16 @@
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D57" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6392,16 +6342,16 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
+        <v>277</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
+        <v>LUIZ FELIPE</v>
       </c>
       <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D58" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6410,34 +6360,34 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
-        <v>312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
-        <v>AZPILICUETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D60" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6446,34 +6396,34 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
+        <v>286</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
+        <v>CAMELLO</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D62" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6482,16 +6432,16 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
+        <v>296</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
+        <v>SERGIO GÓMEZ</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D63" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6500,16 +6450,16 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
-        <v>327</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
-        <v>DIMITRIEVSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D64" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6518,16 +6468,16 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D65" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6536,16 +6486,16 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
+        <v>312</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
+        <v>AZPILICUETA</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D66" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6554,16 +6504,16 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D67" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6572,52 +6522,52 @@
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
       </c>
       <c r="C68" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D68" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
+      </c>
+      <c r="B69" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
+      </c>
+      <c r="C69" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D69" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
+      </c>
+      <c r="B70" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C70" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
-      </c>
-      <c r="D68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
-      </c>
-      <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
-      </c>
-      <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
       </c>
       <c r="D70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6626,16 +6576,16 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D71" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6644,16 +6594,16 @@
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D72" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6662,16 +6612,16 @@
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
       </c>
       <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D73" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6680,16 +6630,16 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
+        <v>331</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
+        <v>COPETE</v>
       </c>
       <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D74" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6698,52 +6648,52 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
       </c>
       <c r="C75" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D75" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
+      </c>
+      <c r="B76" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
+      </c>
+      <c r="C76" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D76" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
-      </c>
-      <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
-      </c>
-      <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-      <c r="D76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D77" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6752,16 +6702,16 @@
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
-        <v>404</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D78" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6770,16 +6720,16 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
+        <v>350</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
+        <v>SERGI CARDONA</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D79" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6788,34 +6738,34 @@
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
       </c>
       <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
       </c>
       <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D81" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6824,16 +6774,16 @@
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D82" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6842,16 +6792,16 @@
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
       </c>
       <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D83" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6860,16 +6810,16 @@
     </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
-        <v>425</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
+        <v>371</v>
       </c>
       <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
-        <v>CARLOS VICENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D84" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6878,34 +6828,34 @@
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
-        <v>436</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
-        <v>CARLOS SOLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
       </c>
       <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D86" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6914,16 +6864,16 @@
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
-        <v>444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
-        <v>OBLAK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
       </c>
       <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D87" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6932,12 +6882,12 @@
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
-        <v>456</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),400.0)</f>
+        <v>400</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
-        <v>ANTONY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO GARCÍA")</f>
+        <v>PABLO GARCÍA</v>
       </c>
       <c r="C88" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -6950,16 +6900,16 @@
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
-        <v>458</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
-        <v>CARRERAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D89" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6968,36 +6918,288 @@
     </row>
     <row r="90">
       <c r="A90" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
+        <v>409</v>
+      </c>
+      <c r="B90" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
+        <v>FRAN GONZÁLEZ</v>
+      </c>
+      <c r="C90" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D90" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
+      </c>
+      <c r="B91" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
+      </c>
+      <c r="C91" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D91" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
+      </c>
+      <c r="B92" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
+      </c>
+      <c r="C92" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D92" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
+      </c>
+      <c r="B93" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
+      </c>
+      <c r="C93" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D93" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
+      </c>
+      <c r="B94" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
+      </c>
+      <c r="C94" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D94" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
+      </c>
+      <c r="B95" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
+      </c>
+      <c r="C95" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D95" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
+        <v>425</v>
+      </c>
+      <c r="B96" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
+        <v>CARLOS VICENTE</v>
+      </c>
+      <c r="C96" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
+      </c>
+      <c r="D96" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
+        <v>436</v>
+      </c>
+      <c r="B97" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
+        <v>CARLOS SOLER</v>
+      </c>
+      <c r="C97" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+      <c r="D97" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
+      </c>
+      <c r="B98" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
+      </c>
+      <c r="C98" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D98" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
+        <v>444</v>
+      </c>
+      <c r="B99" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
+        <v>OBLAK</v>
+      </c>
+      <c r="C99" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D99" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),449.0)</f>
+        <v>449</v>
+      </c>
+      <c r="B100" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
+        <v>KOUNDÉ</v>
+      </c>
+      <c r="C100" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D100" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
+        <v>452</v>
+      </c>
+      <c r="B101" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
+        <v>LEWANDOWSKI</v>
+      </c>
+      <c r="C101" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D101" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
+        <v>456</v>
+      </c>
+      <c r="B102" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
+        <v>ANTONY</v>
+      </c>
+      <c r="C102" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D102" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
+        <v>458</v>
+      </c>
+      <c r="B103" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
+        <v>CARRERAS</v>
+      </c>
+      <c r="C103" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D103" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B90" s="20" t="str">
+      <c r="B104" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C90" s="20" t="str">
+      <c r="C104" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D90" s="20">
+      <c r="D104" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="20">
+    <row r="105">
+      <c r="A105" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),477.0)</f>
         <v>477</v>
       </c>
-      <c r="B91" s="20" t="str">
+      <c r="B105" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD INVENCIBLE")</f>
         <v>CARD INVENCIBLE</v>
       </c>
-      <c r="C91" s="20" t="str">
+      <c r="C105" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
         <v>ÚNICA</v>
       </c>
-      <c r="D91" s="20">
+      <c r="D105" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
@@ -7032,7 +7234,7 @@
         <v>20</v>
       </c>
       <c r="E1" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="2">
@@ -7252,6 +7454,9 @@
       <c r="D17" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E17" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="21">
@@ -8029,7 +8234,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="75">
@@ -8070,7 +8275,9 @@
       <c r="C77" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D77" s="21"/>
+      <c r="D77" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="21">
@@ -8476,6 +8683,9 @@
       <c r="D106" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E106" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="21">
@@ -8962,7 +9172,7 @@
         <v>20</v>
       </c>
       <c r="E140" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="141">
@@ -8992,7 +9202,9 @@
       <c r="C142" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D142" s="21"/>
+      <c r="D142" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="21">
@@ -9470,6 +9682,9 @@
       <c r="D177" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E177" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="21">
@@ -9904,7 +10119,7 @@
         <v>20</v>
       </c>
       <c r="E209" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="210">
@@ -10457,6 +10672,9 @@
       <c r="D248" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E248" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="21">
@@ -10721,6 +10939,9 @@
       <c r="D267" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E267" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="21">
@@ -10985,6 +11206,9 @@
       <c r="D286" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E286" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="21">
@@ -11507,7 +11731,7 @@
         <v>20</v>
       </c>
       <c r="E323" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="324">
@@ -11631,6 +11855,9 @@
       <c r="D331" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E331" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="21">
@@ -11900,6 +12127,9 @@
       <c r="D350" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E350" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="21">
@@ -12001,7 +12231,9 @@
       <c r="C357" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="D357" s="21"/>
+      <c r="D357" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="21">
@@ -12198,6 +12430,9 @@
       <c r="D9" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E9" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="21">
@@ -12223,7 +12458,9 @@
       <c r="C11" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D11" s="21"/>
+      <c r="D11" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21">
@@ -12526,6 +12763,9 @@
       </c>
       <c r="D11" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E11" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="12">
@@ -15017,6 +15257,9 @@
       <c r="D4" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E4" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="21">
@@ -15143,6 +15386,9 @@
       </c>
       <c r="D13" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E13" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="14">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B1" s="2">
         <f>TODAY()</f>
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -5460,52 +5460,52 @@
     </row>
     <row r="9">
       <c r="A9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
+        <v>40</v>
       </c>
       <c r="B9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
-        <v>LENGLET</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
+        <v>MARCOS LLORENTE</v>
       </c>
       <c r="C9" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
         <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
       </c>
       <c r="B10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
-        <v>ALMADA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
+        <v>LENGLET</v>
       </c>
       <c r="C10" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
         <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
-        <v>67</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
       </c>
       <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
-        <v>DANI OLMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
+        <v>ALMADA</v>
       </c>
       <c r="C11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D11" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5514,16 +5514,16 @@
     </row>
     <row r="12">
       <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
-        <v>73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
       </c>
       <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
+        <v>DANI OLMO</v>
       </c>
       <c r="C12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D12" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5532,30 +5532,30 @@
     </row>
     <row r="13">
       <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
       </c>
       <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
-        <v>PAU LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C13" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
+        <v>PAU LÓPEZ</v>
       </c>
       <c r="C14" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -5568,34 +5568,34 @@
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C15" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
-        <v>93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
-        <v>IVÁN VILLAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
       </c>
       <c r="C16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D16" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5604,12 +5604,12 @@
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
+        <v>93</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
+        <v>IVÁN VILLAR</v>
       </c>
       <c r="C17" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5622,12 +5622,12 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C18" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5640,12 +5640,12 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C19" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5658,12 +5658,12 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C20" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5676,12 +5676,12 @@
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
-        <v>106</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
-        <v>IAGO ASPAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C21" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5694,12 +5694,12 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
+        <v>IAGO ASPAS</v>
       </c>
       <c r="C22" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5712,12 +5712,12 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C23" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5730,16 +5730,16 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
-        <v>IÑAKI PEÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
       </c>
       <c r="C24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D24" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5748,12 +5748,12 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
+        <v>IÑAKI PEÑA</v>
       </c>
       <c r="C25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5766,12 +5766,12 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C26" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5784,12 +5784,12 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
-        <v>117</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
-        <v>FEDE REDONDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C27" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5802,12 +5802,12 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
+        <v>117</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
+        <v>FEDE REDONDO</v>
       </c>
       <c r="C28" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5820,16 +5820,16 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D29" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5838,12 +5838,12 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C30" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5856,48 +5856,48 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C32" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5910,16 +5910,16 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D34" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5928,12 +5928,12 @@
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C35" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -5946,16 +5946,16 @@
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D36" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5964,12 +5964,12 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C37" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -5982,30 +5982,30 @@
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C38" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
       </c>
       <c r="D38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.0)</f>
-        <v>177</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
+        <v>174</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TSYGANKOV")</f>
-        <v>TSYGANKOV</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
+        <v>IVÁN MARTÍN</v>
       </c>
       <c r="C39" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -6018,48 +6018,48 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
+      </c>
+      <c r="B40" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
+      </c>
+      <c r="C40" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+      <c r="D40" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.0)</f>
+        <v>177</v>
+      </c>
+      <c r="B41" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TSYGANKOV")</f>
+        <v>TSYGANKOV</v>
+      </c>
+      <c r="C41" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+      <c r="D41" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
         <v>202</v>
       </c>
-      <c r="B40" s="20" t="str">
+      <c r="B42" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
         <v>CARVAJAL</v>
-      </c>
-      <c r="C40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
-      </c>
-      <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
-      </c>
-      <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
-        <v>211</v>
-      </c>
-      <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
-        <v>GÜLER</v>
       </c>
       <c r="C42" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6072,52 +6072,52 @@
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
-        <v>213</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
-        <v>RODRYGO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C43" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
         <v>REAL MADRID</v>
       </c>
       <c r="D43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
       </c>
       <c r="C44" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
         <v>REAL MADRID</v>
       </c>
       <c r="D44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
+        <v>213</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
+        <v>RODRYGO</v>
       </c>
       <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D45" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6126,30 +6126,30 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
-        <v>225</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
-        <v>MOJICA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
       </c>
       <c r="C47" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -6162,16 +6162,16 @@
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
+        <v>225</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
+        <v>MOJICA</v>
       </c>
       <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D48" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6180,16 +6180,16 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D49" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6198,30 +6198,30 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
-        <v>237</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
-        <v>AITOR FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C50" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
         <v>CA OSASUNA</v>
       </c>
       <c r="D50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
-        <v>248</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C51" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -6234,34 +6234,34 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
+        <v>237</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
+        <v>AITOR FERNÁNDEZ</v>
       </c>
       <c r="C52" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
         <v>CA OSASUNA</v>
       </c>
       <c r="D52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
+        <v>248</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
       </c>
       <c r="C53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D53" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6270,16 +6270,16 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D54" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6288,12 +6288,12 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C55" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -6306,12 +6306,12 @@
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.0)</f>
-        <v>267</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BREKALO")</f>
-        <v>BREKALO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C56" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -6324,12 +6324,12 @@
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C57" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -6342,16 +6342,16 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
-        <v>277</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.0)</f>
+        <v>267</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
-        <v>LUIZ FELIPE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BREKALO")</f>
+        <v>BREKALO</v>
       </c>
       <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D58" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6360,30 +6360,30 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
-        <v>283</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
+        <v>277</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
-        <v>PEDRO DÍAZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
+        <v>LUIZ FELIPE</v>
       </c>
       <c r="C60" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -6396,34 +6396,34 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
-        <v>286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
-        <v>CAMELLO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
       </c>
       <c r="C61" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
         <v>RAYO VALLECANO</v>
       </c>
       <c r="D61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D62" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6432,16 +6432,16 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
-        <v>296</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
+        <v>286</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
-        <v>SERGIO GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
+        <v>CAMELLO</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D63" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6450,12 +6450,12 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
+        <v>290</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
       </c>
       <c r="C64" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -6468,16 +6468,16 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
       </c>
       <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D65" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6486,16 +6486,16 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
-        <v>312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
+        <v>296</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
-        <v>AZPILICUETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
+        <v>SERGIO GÓMEZ</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D66" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6504,16 +6504,16 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D67" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6522,52 +6522,52 @@
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C68" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
       <c r="D68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
+        <v>312</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
+        <v>AZPILICUETA</v>
       </c>
       <c r="C69" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
       <c r="D69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6576,48 +6576,48 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
-        <v>327</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
-        <v>DIMITRIEVSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C73" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -6630,12 +6630,12 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
-        <v>331</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
-        <v>COPETE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
       </c>
       <c r="C74" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -6648,12 +6648,12 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
       </c>
       <c r="C75" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -6666,34 +6666,34 @@
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
       </c>
       <c r="C76" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
+        <v>331</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
+        <v>COPETE</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D77" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6702,16 +6702,16 @@
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D78" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6720,30 +6720,30 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
-        <v>350</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
-        <v>SERGI CARDONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C80" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
@@ -6756,12 +6756,12 @@
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C81" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
@@ -6774,16 +6774,16 @@
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
+        <v>350</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
+        <v>SERGI CARDONA</v>
       </c>
       <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D82" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6792,16 +6792,16 @@
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
       </c>
       <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
       </c>
       <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D83" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6810,16 +6810,16 @@
     </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
-        <v>371</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
       </c>
       <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
       </c>
       <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D84" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6828,34 +6828,34 @@
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D86" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6864,16 +6864,16 @@
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
+        <v>371</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D87" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6882,34 +6882,34 @@
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),400.0)</f>
-        <v>400</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO GARCÍA")</f>
-        <v>PABLO GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
-        <v>404</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
       </c>
       <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D89" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6918,16 +6918,16 @@
     </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
-        <v>409</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
-        <v>FRAN GONZÁLEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
       </c>
       <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D90" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6936,16 +6936,16 @@
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),400.0)</f>
+        <v>400</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO GARCÍA")</f>
+        <v>PABLO GARCÍA</v>
       </c>
       <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D91" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6954,34 +6954,34 @@
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
+        <v>409</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
+        <v>FRAN GONZÁLEZ</v>
       </c>
       <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D93" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6990,16 +6990,16 @@
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
       </c>
       <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D94" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7008,34 +7008,34 @@
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
       </c>
       <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
-        <v>425</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
-        <v>CARLOS VICENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
       </c>
       <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D96" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7044,16 +7044,16 @@
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
-        <v>436</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
-        <v>CARLOS SOLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
       </c>
       <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D97" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7062,16 +7062,16 @@
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
       </c>
       <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D98" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7080,16 +7080,16 @@
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
-        <v>444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
+        <v>425</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
-        <v>OBLAK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
+        <v>CARLOS VICENTE</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D99" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7098,16 +7098,16 @@
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),449.0)</f>
-        <v>449</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
+        <v>436</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
-        <v>KOUNDÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
+        <v>CARLOS SOLER</v>
       </c>
       <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D100" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7116,16 +7116,16 @@
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
-        <v>452</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
-        <v>LEWANDOWSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
       </c>
       <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D101" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7134,16 +7134,16 @@
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
-        <v>456</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
+        <v>444</v>
       </c>
       <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
-        <v>ANTONY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
+        <v>OBLAK</v>
       </c>
       <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D102" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7152,16 +7152,16 @@
     </row>
     <row r="103">
       <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
-        <v>458</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),449.0)</f>
+        <v>449</v>
       </c>
       <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
-        <v>CARRERAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
+        <v>KOUNDÉ</v>
       </c>
       <c r="C103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D103" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7170,36 +7170,90 @@
     </row>
     <row r="104">
       <c r="A104" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
+        <v>452</v>
+      </c>
+      <c r="B104" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
+        <v>LEWANDOWSKI</v>
+      </c>
+      <c r="C104" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D104" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
+        <v>456</v>
+      </c>
+      <c r="B105" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
+        <v>ANTONY</v>
+      </c>
+      <c r="C105" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D105" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
+        <v>458</v>
+      </c>
+      <c r="B106" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
+        <v>CARRERAS</v>
+      </c>
+      <c r="C106" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D106" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B104" s="20" t="str">
+      <c r="B107" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C104" s="20" t="str">
+      <c r="C107" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D104" s="20">
+      <c r="D107" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="20">
+    <row r="108">
+      <c r="A108" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),477.0)</f>
         <v>477</v>
       </c>
-      <c r="B105" s="20" t="str">
+      <c r="B108" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD INVENCIBLE")</f>
         <v>CARD INVENCIBLE</v>
       </c>
-      <c r="C105" s="20" t="str">
+      <c r="C108" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
         <v>ÚNICA</v>
       </c>
-      <c r="D105" s="20">
+      <c r="D108" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
@@ -7768,6 +7822,9 @@
       <c r="D40" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E40" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="21">
@@ -9637,6 +9694,9 @@
       <c r="D174" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E174" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="21">
@@ -11262,6 +11322,9 @@
       </c>
       <c r="D290" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E290" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="291">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="399">
   <si>
     <t>Última actualización:</t>
   </si>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B1" s="2">
         <f>TODAY()</f>
-        <v>46059</v>
+        <v>46061</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1833,15 +1833,15 @@
       </c>
       <c r="C3" s="9">
         <f>COUNTIF(REGULARES!D:D, "SI")</f>
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D3" s="9">
         <f t="shared" ref="D3:D12" si="1">B3-C3</f>
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E4" si="2">(C3/B3)</f>
-        <v>0.7</v>
+        <v>0.7083333333</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E3, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2001,15 +2001,15 @@
       </c>
       <c r="C10" s="14">
         <f>COUNTIF('Protas (424–441)'!D:D, "SI")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.5555555556</v>
       </c>
       <c r="F10" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E10, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2025,15 +2025,15 @@
       </c>
       <c r="C11" s="14">
         <f>COUNTIF('Super Cracks (442–467)'!D:D, "SI")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="15">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="3"/>
-        <v>0.5769230769</v>
+        <v>0.6153846154</v>
       </c>
       <c r="F11" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E11, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="4"/>
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="4"/>
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>0.6807228916</v>
+        <v>0.6907630522</v>
       </c>
       <c r="F13" s="19" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E13, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2330,7 +2330,9 @@
       <c r="C6" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D6" s="21"/>
+      <c r="D6" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21">
@@ -2930,7 +2932,9 @@
       <c r="C18" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="21"/>
+      <c r="D18" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21">
@@ -3062,12 +3066,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("{FILTER(REGULARES!A:C, REGULARES!D:D&lt;&gt;""SI"", REGULARES!A:A&lt;&gt;""""); FILTER('¡VAMOS! (361–380)'!A:C, '¡VAMOS! (361–380)'!D:D&lt;&gt;""SI"", '¡VAMOS! (361–380)'!A:A&lt;&gt;""""); FILTER('Guantes de Oro (381–387)'!A:C, 'Guantes de Oro (381–387)'!D:D&lt;&gt;""SI"", 'Guantes de"&amp;" Oro (381–387)'!A:A&lt;&gt;""""); FILTER('Kryptonita (388–396)'!A:C, 'Kryptonita (388–396)'!D:D&lt;&gt;""SI"", 'Kryptonita (388–396)'!A:A&lt;&gt;""""); FILTER('Diamantes (397–414)'!A:C, 'Diamantes (397–414)'!D:D&lt;&gt;""SI"", 'Diamantes (397–414)'!A:A&lt;&gt;""""); FILTER('Influencer"&amp;"s (415–423)'!A:C, 'Influencers (415–423)'!D:D&lt;&gt;""SI"", 'Influencers (415–423)'!A:A&lt;&gt;""""); FILTER('Protas (424–441)'!A:C, 'Protas (424–441)'!D:D&lt;&gt;""SI"", 'Protas (424–441)'!A:A&lt;&gt;""""); FILTER('Super Cracks (442–467)'!A:C, 'Super Cracks (442–467)'!D:D&lt;&gt;""S"&amp;"I"", 'Super Cracks (442–467)'!A:A&lt;&gt;""""); FILTER('Cartas Top y Únicas (468–478)'!A:C, 'Cartas Top y Únicas (468–478)'!D:D&lt;&gt;""SI"", 'Cartas Top y Únicas (468–478)'!A:A&lt;&gt;""""); FILTER(Estadios!A:C, Estadios!D:D&lt;&gt;""SI"", Estadios!A:A&lt;&gt;"""")}"),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("{FILTER(REGULARES!A:C, REGULARES!D:D&lt;&gt;""SI"", REGULARES!A:A&lt;&gt;""""); FILTER('¡VAMOS! (361–380)'!A:C, '¡VAMOS! (361–380)'!D:D&lt;&gt;""SI"", '¡VAMOS! (361–380)'!A:A&lt;&gt;""""); FILTER('Guantes de Oro (381–387)'!A:C, 'Guantes de Oro (381–387)'!D:D&lt;&gt;""SI"", 'Guantes de"&amp;" Oro (381–387)'!A:A&lt;&gt;""""); FILTER('Kryptonita (388–396)'!A:C, 'Kryptonita (388–396)'!D:D&lt;&gt;""SI"", 'Kryptonita (388–396)'!A:A&lt;&gt;""""); FILTER('Diamantes (397–414)'!A:C, 'Diamantes (397–414)'!D:D&lt;&gt;""SI"", 'Diamantes (397–414)'!A:A&lt;&gt;""""); FILTER('Influencer"&amp;"s (415–423)'!A:C, 'Influencers (415–423)'!D:D&lt;&gt;""SI"", 'Influencers (415–423)'!A:A&lt;&gt;""""); FILTER('Protas (424–441)'!A:C, 'Protas (424–441)'!D:D&lt;&gt;""SI"", 'Protas (424–441)'!A:A&lt;&gt;""""); FILTER('Super Cracks (442–467)'!A:C, 'Super Cracks (442–467)'!D:D&lt;&gt;""S"&amp;"I"", 'Super Cracks (442–467)'!A:A&lt;&gt;""""); FILTER('Cartas Top y Únicas (468–478)'!A:C, 'Cartas Top y Únicas (468–478)'!D:D&lt;&gt;""SI"", 'Cartas Top y Únicas (468–478)'!A:A&lt;&gt;""""); FILTER(Estadios!A:C, Estadios!D:D&lt;&gt;""SI"", Estadios!A:A&lt;&gt;"""")}"),5.0)</f>
+        <v>5</v>
       </c>
       <c r="B1" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SIVERA")</f>
-        <v>SIVERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
+        <v>TENAGLIA</v>
       </c>
       <c r="C1" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -3076,12 +3080,12 @@
     </row>
     <row r="2">
       <c r="A2" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
+        <v>11</v>
       </c>
       <c r="B2" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
-        <v>TENAGLIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GURIDI")</f>
+        <v>GURIDI</v>
       </c>
       <c r="C2" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -3090,12 +3094,12 @@
     </row>
     <row r="3">
       <c r="A3" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
       </c>
       <c r="B3" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GURIDI")</f>
-        <v>GURIDI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEÑÁ")</f>
+        <v>ALEÑÁ</v>
       </c>
       <c r="C3" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -3104,12 +3108,12 @@
     </row>
     <row r="4">
       <c r="A4" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
       </c>
       <c r="B4" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEÑÁ")</f>
-        <v>ALEÑÁ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO IBÁÑEZ")</f>
+        <v>PABLO IBÁÑEZ</v>
       </c>
       <c r="C4" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -3118,12 +3122,12 @@
     </row>
     <row r="5">
       <c r="A5" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
       </c>
       <c r="B5" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO IBÁÑEZ")</f>
-        <v>PABLO IBÁÑEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TONI MARTÍNEZ")</f>
+        <v>TONI MARTÍNEZ</v>
       </c>
       <c r="C5" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -3132,26 +3136,26 @@
     </row>
     <row r="6">
       <c r="A6" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
-        <v>16</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
+        <v>20</v>
       </c>
       <c r="B6" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TONI MARTÍNEZ")</f>
-        <v>TONI MARTÍNEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
+        <v>UNAI SIMÓN</v>
       </c>
       <c r="C6" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
       </c>
       <c r="B7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
-        <v>UNAI SIMÓN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAREDES")</f>
+        <v>PAREDES</v>
       </c>
       <c r="C7" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3160,12 +3164,12 @@
     </row>
     <row r="8">
       <c r="A8" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
+        <v>25</v>
       </c>
       <c r="B8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAREDES")</f>
-        <v>PAREDES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
+        <v>LAPORTE</v>
       </c>
       <c r="C8" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3174,12 +3178,12 @@
     </row>
     <row r="9">
       <c r="A9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
-        <v>25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.0)</f>
+        <v>26</v>
       </c>
       <c r="B9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
-        <v>LAPORTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YURI")</f>
+        <v>YURI</v>
       </c>
       <c r="C9" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3188,12 +3192,12 @@
     </row>
     <row r="10">
       <c r="A10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.0)</f>
-        <v>26</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
+        <v>29</v>
       </c>
       <c r="B10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YURI")</f>
-        <v>YURI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VESGA")</f>
+        <v>VESGA</v>
       </c>
       <c r="C10" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3202,12 +3206,12 @@
     </row>
     <row r="11">
       <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
-        <v>29</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
+        <v>30</v>
       </c>
       <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VESGA")</f>
-        <v>VESGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI GÓMEZ")</f>
+        <v>UNAI GÓMEZ</v>
       </c>
       <c r="C11" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3216,12 +3220,12 @@
     </row>
     <row r="12">
       <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
+        <v>35</v>
       </c>
       <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI GÓMEZ")</f>
-        <v>UNAI GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GURUZETA")</f>
+        <v>GURUZETA</v>
       </c>
       <c r="C12" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3230,12 +3234,12 @@
     </row>
     <row r="13">
       <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
-        <v>35</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
+        <v>36</v>
       </c>
       <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GURUZETA")</f>
-        <v>GURUZETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
+        <v>NICO WILLIAMS</v>
       </c>
       <c r="C13" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3244,26 +3248,26 @@
     </row>
     <row r="14">
       <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
-        <v>36</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
       </c>
       <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
-        <v>NICO WILLIAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
-        <v>37</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
+        <v>38</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
+        <v>OBLAK</v>
       </c>
       <c r="C15" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3272,12 +3276,12 @@
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
-        <v>38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
+        <v>48</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
-        <v>OBLAK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX BAENA")</f>
+        <v>ALEX BAENA</v>
       </c>
       <c r="C16" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3286,12 +3290,12 @@
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
-        <v>48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX BAENA")</f>
-        <v>ALEX BAENA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO GONZÁLEZ")</f>
+        <v>NICO GONZÁLEZ</v>
       </c>
       <c r="C17" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3300,12 +3304,12 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
-        <v>50</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.0)</f>
+        <v>51</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO GONZÁLEZ")</f>
-        <v>NICO GONZÁLEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIULIANO")</f>
+        <v>GIULIANO</v>
       </c>
       <c r="C18" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3314,12 +3318,12 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.0)</f>
-        <v>51</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.0)</f>
+        <v>54</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIULIANO")</f>
-        <v>GIULIANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
+        <v>GRIEZMANN</v>
       </c>
       <c r="C19" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3328,26 +3332,26 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.0)</f>
-        <v>54</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
+        <v>57</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
-        <v>GRIEZMANN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SZCZESNY")</f>
+        <v>SZCZESNY</v>
       </c>
       <c r="C20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
-        <v>57</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
+        <v>58</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SZCZESNY")</f>
-        <v>SZCZESNY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
+        <v>KOUNDÉ</v>
       </c>
       <c r="C21" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3356,12 +3360,12 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
-        <v>58</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.0)</f>
+        <v>60</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
-        <v>KOUNDÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ERIC GARCÍA")</f>
+        <v>ERIC GARCÍA</v>
       </c>
       <c r="C22" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3370,12 +3374,12 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.0)</f>
-        <v>60</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68.0)</f>
+        <v>68</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ERIC GARCÍA")</f>
-        <v>ERIC GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
+        <v>RAPHINHA</v>
       </c>
       <c r="C23" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3384,12 +3388,12 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68.0)</f>
-        <v>68</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
+        <v>69</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
-        <v>RAPHINHA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
+        <v>LAMINE YAMAL</v>
       </c>
       <c r="C24" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3398,12 +3402,12 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
-        <v>69</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
+        <v>70</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
-        <v>LAMINE YAMAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERRAN TORRES")</f>
+        <v>FERRAN TORRES</v>
       </c>
       <c r="C25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3412,26 +3416,26 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
-        <v>70</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.0)</f>
+        <v>80</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERRAN TORRES")</f>
-        <v>FERRAN TORRES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
       </c>
       <c r="C26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.0)</f>
-        <v>80</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.0)</f>
+        <v>82</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALTIMIRA")</f>
+        <v>ALTIMIRA</v>
       </c>
       <c r="C27" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3440,12 +3444,12 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.0)</f>
-        <v>82</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.0)</f>
+        <v>83</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALTIMIRA")</f>
-        <v>ALTIMIRA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AMRABAT")</f>
+        <v>AMRABAT</v>
       </c>
       <c r="C28" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3454,12 +3458,12 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.0)</f>
-        <v>83</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),85.0)</f>
+        <v>85</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AMRABAT")</f>
-        <v>AMRABAT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LO CELSO")</f>
+        <v>LO CELSO</v>
       </c>
       <c r="C29" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3468,12 +3472,12 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),85.0)</f>
-        <v>85</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
+        <v>89</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LO CELSO")</f>
-        <v>LO CELSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIQUELME")</f>
+        <v>RIQUELME</v>
       </c>
       <c r="C30" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3482,12 +3486,12 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
-        <v>89</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.0)</f>
+        <v>90</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIQUELME")</f>
-        <v>RIQUELME</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABDE")</f>
+        <v>ABDE</v>
       </c>
       <c r="C31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3496,26 +3500,26 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.0)</f>
-        <v>90</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.0)</f>
+        <v>92</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABDE")</f>
-        <v>ABDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RADU")</f>
+        <v>RADU</v>
       </c>
       <c r="C32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.0)</f>
-        <v>92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.0)</f>
+        <v>96</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RADU")</f>
-        <v>RADU</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"STARFELT")</f>
+        <v>STARFELT</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3524,12 +3528,12 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
-        <v>95</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
+        <v>98</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RODRÍGUEZ")</f>
-        <v>JAVI RODRÍGUEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MINGUEZA")</f>
+        <v>MINGUEZA</v>
       </c>
       <c r="C34" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3538,12 +3542,12 @@
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.0)</f>
-        <v>96</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101.0)</f>
+        <v>101</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"STARFELT")</f>
-        <v>STARFELT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN BELTRÁN")</f>
+        <v>FRAN BELTRÁN</v>
       </c>
       <c r="C35" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3552,12 +3556,12 @@
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
-        <v>98</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MINGUEZA")</f>
-        <v>MINGUEZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C36" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3566,40 +3570,40 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101.0)</f>
-        <v>101</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
+        <v>113</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN BELTRÁN")</f>
-        <v>FRAN BELTRÁN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CHUST")</f>
+        <v>CHUST</v>
       </c>
       <c r="C37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
+        <v>114</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIGAS")</f>
+        <v>BIGAS</v>
       </c>
       <c r="C38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
-        <v>113</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),118.0)</f>
+        <v>118</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CHUST")</f>
-        <v>CHUST</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GERMÁN VALERA")</f>
+        <v>GERMÁN VALERA</v>
       </c>
       <c r="C39" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3608,12 +3612,12 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
-        <v>114</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
+        <v>119</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIGAS")</f>
-        <v>BIGAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARTIM NETO")</f>
+        <v>MARTIM NETO</v>
       </c>
       <c r="C40" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3622,12 +3626,12 @@
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),118.0)</f>
-        <v>118</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
+        <v>120</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GERMÁN VALERA")</f>
-        <v>GERMÁN VALERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
+        <v>FEBAS</v>
       </c>
       <c r="C41" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3636,40 +3640,40 @@
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
-        <v>119</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
+        <v>128</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARTIM NETO")</f>
-        <v>MARTIM NETO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
+        <v>DMITROVIC</v>
       </c>
       <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
-        <v>120</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),132.0)</f>
+        <v>132</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
-        <v>FEBAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
+        <v>RIEDEL</v>
       </c>
       <c r="C43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
-        <v>128</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
+        <v>133</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
-        <v>DMITROVIC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
       </c>
       <c r="C44" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -3678,12 +3682,12 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),132.0)</f>
-        <v>132</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),143.0)</f>
+        <v>143</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
-        <v>RIEDEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PUADO")</f>
+        <v>PUADO</v>
       </c>
       <c r="C45" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -3692,40 +3696,40 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
-        <v>133</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),143.0)</f>
-        <v>143</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
+        <v>148</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PUADO")</f>
-        <v>PUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IGLESIAS")</f>
+        <v>IGLESIAS</v>
       </c>
       <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.0)</f>
+        <v>149</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKO FEMENÍA")</f>
+        <v>KIKO FEMENÍA</v>
       </c>
       <c r="C48" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3734,12 +3738,12 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
-        <v>148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.0)</f>
+        <v>150</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IGLESIAS")</f>
-        <v>IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DJENÉ")</f>
+        <v>DJENÉ</v>
       </c>
       <c r="C49" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3748,12 +3752,12 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.0)</f>
-        <v>149</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
+        <v>151</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKO FEMENÍA")</f>
-        <v>KIKO FEMENÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOMINGOS DUARTE")</f>
+        <v>DOMINGOS DUARTE</v>
       </c>
       <c r="C50" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3762,12 +3766,12 @@
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.0)</f>
-        <v>150</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),155.0)</f>
+        <v>155</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DJENÉ")</f>
-        <v>DJENÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIO MARTÍN")</f>
+        <v>MARIO MARTÍN</v>
       </c>
       <c r="C51" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3776,12 +3780,12 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
-        <v>151</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),157.0)</f>
+        <v>157</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOMINGOS DUARTE")</f>
-        <v>DOMINGOS DUARTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
       </c>
       <c r="C52" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3790,12 +3794,12 @@
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),155.0)</f>
-        <v>155</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),161.0)</f>
+        <v>161</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIO MARTÍN")</f>
-        <v>MARIO MARTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C53" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3804,12 +3808,12 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),157.0)</f>
-        <v>157</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),162.0)</f>
+        <v>162</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COBA")</f>
+        <v>COBA</v>
       </c>
       <c r="C54" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -3818,40 +3822,40 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),161.0)</f>
-        <v>161</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
+        <v>164</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAZZANIGA")</f>
+        <v>GAZZANIGA</v>
       </c>
       <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),162.0)</f>
-        <v>162</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),167.0)</f>
+        <v>167</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COBA")</f>
-        <v>COBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO RINCÓN")</f>
+        <v>HUGO RINCÓN</v>
       </c>
       <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
-        <v>164</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
+        <v>168</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAZZANIGA")</f>
-        <v>GAZZANIGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VITOR REIS")</f>
+        <v>VITOR REIS</v>
       </c>
       <c r="C57" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -3860,12 +3864,12 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),167.0)</f>
-        <v>167</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.0)</f>
+        <v>169</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO RINCÓN")</f>
-        <v>HUGO RINCÓN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BLIND")</f>
+        <v>BLIND</v>
       </c>
       <c r="C58" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -3874,12 +3878,12 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
-        <v>168</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.0)</f>
+        <v>178</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VITOR REIS")</f>
-        <v>VITOR REIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
+        <v>VANAT</v>
       </c>
       <c r="C59" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -3888,40 +3892,40 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.0)</f>
-        <v>169</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
+        <v>182</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BLIND")</f>
-        <v>BLIND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RYAN")</f>
+        <v>RYAN</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.0)</f>
-        <v>178</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
+        <v>183</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
-        <v>VANAT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO CAMPOS")</f>
+        <v>PABLO CAMPOS</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
-        <v>182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.0)</f>
+        <v>186</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RYAN")</f>
-        <v>RYAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELGEZABAL")</f>
+        <v>ELGEZABAL</v>
       </c>
       <c r="C62" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -3930,12 +3934,12 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
-        <v>183</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),191.0)</f>
+        <v>191</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO CAMPOS")</f>
-        <v>PABLO CAMPOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARTÍNEZ")</f>
+        <v>PABLO MARTÍNEZ</v>
       </c>
       <c r="C63" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -3944,12 +3948,12 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.0)</f>
-        <v>186</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.0)</f>
+        <v>196</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELGEZABAL")</f>
-        <v>ELGEZABAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRUGUÉ")</f>
+        <v>BRUGUÉ</v>
       </c>
       <c r="C64" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -3958,12 +3962,12 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),191.0)</f>
-        <v>191</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
+        <v>198</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARTÍNEZ")</f>
-        <v>PABLO MARTÍNEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
+        <v>ETTA EYONG</v>
       </c>
       <c r="C65" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -3972,40 +3976,40 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.0)</f>
-        <v>196</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.0)</f>
+        <v>201</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRUGUÉ")</f>
-        <v>BRUGUÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUNIN")</f>
+        <v>LUNIN</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
-        <v>198</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.0)</f>
+        <v>205</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
-        <v>ETTA EYONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUIJSEN")</f>
+        <v>HUIJSEN</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.0)</f>
-        <v>201</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
+        <v>214</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUNIN")</f>
-        <v>LUNIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
+        <v>MBAPPÉ</v>
       </c>
       <c r="C68" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -4014,40 +4018,40 @@
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.0)</f>
-        <v>205</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
+        <v>217</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUIJSEN")</f>
-        <v>HUIJSEN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
-        <v>214</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
+        <v>218</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
-        <v>MBAPPÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
+        <v>LEO ROMÁN</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
-        <v>217</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
+        <v>224</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
+        <v>KUMBULLA</v>
       </c>
       <c r="C71" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4056,12 +4060,12 @@
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
-        <v>218</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.0)</f>
+        <v>229</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
-        <v>LEO ROMÁN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORLANES")</f>
+        <v>MORLANES</v>
       </c>
       <c r="C72" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4070,12 +4074,12 @@
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
-        <v>224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.0)</f>
+        <v>231</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
-        <v>KUMBULLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ASANO")</f>
+        <v>ASANO</v>
       </c>
       <c r="C73" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4084,12 +4088,12 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.0)</f>
-        <v>229</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),232.0)</f>
+        <v>232</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORLANES")</f>
-        <v>MORLANES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MURIQI")</f>
+        <v>MURIQI</v>
       </c>
       <c r="C74" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4098,12 +4102,12 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.0)</f>
-        <v>231</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),233.0)</f>
+        <v>233</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ASANO")</f>
-        <v>ASANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
+        <v>MATEO JOSEPH</v>
       </c>
       <c r="C75" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4112,40 +4116,40 @@
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),232.0)</f>
-        <v>232</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.0)</f>
+        <v>239</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MURIQI")</f>
-        <v>MURIQI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYOMO")</f>
+        <v>BOYOMO</v>
       </c>
       <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),233.0)</f>
-        <v>233</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.0)</f>
+        <v>241</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
-        <v>MATEO JOSEPH</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HERRANDO")</f>
+        <v>HERRANDO</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.0)</f>
-        <v>239</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
+        <v>242</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYOMO")</f>
-        <v>BOYOMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
+        <v>JUAN CRUZ</v>
       </c>
       <c r="C78" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -4154,54 +4158,54 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.0)</f>
-        <v>241</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
+        <v>253</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HERRANDO")</f>
-        <v>HERRANDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
-        <v>242</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),254.0)</f>
+        <v>254</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
-        <v>JUAN CRUZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AARON ESCANDELL")</f>
+        <v>AARON ESCANDELL</v>
       </c>
       <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),251.0)</f>
-        <v>251</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
+        <v>260</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUDIMIR")</f>
-        <v>BUDIMIR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
+        <v>RAHIM ALHASSANE</v>
       </c>
       <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
-        <v>253</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
+        <v>261</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLOMBATTO")</f>
+        <v>COLOMBATTO</v>
       </c>
       <c r="C82" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4210,12 +4214,12 @@
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),254.0)</f>
-        <v>254</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),263.0)</f>
+        <v>263</v>
       </c>
       <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AARON ESCANDELL")</f>
-        <v>AARON ESCANDELL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DENDONCKER")</f>
+        <v>DENDONCKER</v>
       </c>
       <c r="C83" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4224,12 +4228,12 @@
     </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
-        <v>260</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),266.0)</f>
+        <v>266</v>
       </c>
       <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
-        <v>RAHIM ALHASSANE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
+        <v>HASSAN</v>
       </c>
       <c r="C84" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4238,12 +4242,12 @@
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
-        <v>261</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),268.0)</f>
+        <v>268</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLOMBATTO")</f>
-        <v>COLOMBATTO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILYAS CHAIRA")</f>
+        <v>ILYAS CHAIRA</v>
       </c>
       <c r="C85" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -4252,54 +4256,54 @@
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),263.0)</f>
-        <v>263</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),271.0)</f>
+        <v>271</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DENDONCKER")</f>
-        <v>DENDONCKER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),266.0)</f>
-        <v>266</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.0)</f>
+        <v>273</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
-        <v>HASSAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CÁRDENAS")</f>
+        <v>CÁRDENAS</v>
       </c>
       <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),268.0)</f>
-        <v>268</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),276.0)</f>
+        <v>276</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILYAS CHAIRA")</f>
-        <v>ILYAS CHAIRA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
+        <v>LEJEUNE</v>
       </c>
       <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),271.0)</f>
-        <v>271</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),279.0)</f>
+        <v>279</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PATHÉ CISS")</f>
+        <v>PATHÉ CISS</v>
       </c>
       <c r="C89" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -4308,12 +4312,12 @@
     </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.0)</f>
-        <v>273</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),280.0)</f>
+        <v>280</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CÁRDENAS")</f>
-        <v>CÁRDENAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LOPEZ")</f>
+        <v>UNAI LOPEZ</v>
       </c>
       <c r="C90" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -4322,12 +4326,12 @@
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),276.0)</f>
-        <v>276</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),285.0)</f>
+        <v>285</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
-        <v>LEJEUNE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN PÉREZ")</f>
+        <v>FRAN PÉREZ</v>
       </c>
       <c r="C91" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -4336,54 +4340,54 @@
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),279.0)</f>
-        <v>279</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
+        <v>289</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PATHÉ CISS")</f>
-        <v>PATHÉ CISS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),280.0)</f>
-        <v>280</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),294.0)</f>
+        <v>294</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LOPEZ")</f>
-        <v>UNAI LOPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZUBELDIA")</f>
+        <v>ZUBELDIA</v>
       </c>
       <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),285.0)</f>
-        <v>285</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),297.0)</f>
+        <v>297</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN PÉREZ")</f>
-        <v>FRAN PÉREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
+        <v>GORROTXATEGI</v>
       </c>
       <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
-        <v>289</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.0)</f>
+        <v>300</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
+        <v>CARLOS SOLER</v>
       </c>
       <c r="C95" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -4392,12 +4396,12 @@
     </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),294.0)</f>
-        <v>294</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),301.0)</f>
+        <v>301</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZUBELDIA")</f>
-        <v>ZUBELDIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRAIS MÉNDEZ")</f>
+        <v>BRAIS MÉNDEZ</v>
       </c>
       <c r="C96" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -4406,12 +4410,12 @@
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),297.0)</f>
-        <v>297</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),305.0)</f>
+        <v>305</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
-        <v>GORROTXATEGI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSKARSSON")</f>
+        <v>ÓSKARSSON</v>
       </c>
       <c r="C97" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -4420,54 +4424,54 @@
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.0)</f>
-        <v>300</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),310.0)</f>
+        <v>310</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
-        <v>CARLOS SOLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARMONA")</f>
+        <v>CARMONA</v>
       </c>
       <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),301.0)</f>
-        <v>301</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),314.0)</f>
+        <v>314</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRAIS MÉNDEZ")</f>
-        <v>BRAIS MÉNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCAO")</f>
+        <v>MARCAO</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),305.0)</f>
-        <v>305</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),320.0)</f>
+        <v>320</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSKARSSON")</f>
-        <v>ÓSKARSSON</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
+        <v>VARGAS</v>
       </c>
       <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),310.0)</f>
-        <v>310</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),324.0)</f>
+        <v>324</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARMONA")</f>
-        <v>CARMONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
       </c>
       <c r="C101" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
@@ -4476,110 +4480,110 @@
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),314.0)</f>
-        <v>314</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),339.0)</f>
+        <v>339</v>
       </c>
       <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCAO")</f>
-        <v>MARCAO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO LÓPEZ")</f>
+        <v>DIEGO LÓPEZ</v>
       </c>
       <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),320.0)</f>
-        <v>320</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
+        <v>348</v>
       </c>
       <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
-        <v>VARGAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MARÍN")</f>
+        <v>RAFA MARÍN</v>
       </c>
       <c r="C103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),324.0)</f>
-        <v>324</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),349.0)</f>
+        <v>349</v>
       </c>
       <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RENATO VEIGA")</f>
+        <v>RENATO VEIGA</v>
       </c>
       <c r="C104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),339.0)</f>
-        <v>339</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),360.0)</f>
+        <v>360</v>
       </c>
       <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO LÓPEZ")</f>
-        <v>DIEGO LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AYOZE")</f>
+        <v>AYOZE</v>
       </c>
       <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
-        <v>348</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),364.0)</f>
+        <v>364</v>
       </c>
       <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MARÍN")</f>
-        <v>RAFA MARÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),349.0)</f>
-        <v>349</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),365.0)</f>
+        <v>365</v>
       </c>
       <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RENATO VEIGA")</f>
-        <v>RENATO VEIGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),360.0)</f>
-        <v>360</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
+        <v>366</v>
       </c>
       <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AYOZE")</f>
-        <v>AYOZE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="C108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),364.0)</f>
-        <v>364</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),373.0)</f>
+        <v>373</v>
       </c>
       <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="C109" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4588,12 +4592,12 @@
     </row>
     <row r="110">
       <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),365.0)</f>
-        <v>365</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
+        <v>375</v>
       </c>
       <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="C110" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4602,12 +4606,12 @@
     </row>
     <row r="111">
       <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
-        <v>366</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),377.0)</f>
+        <v>377</v>
       </c>
       <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="C111" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4616,12 +4620,12 @@
     </row>
     <row r="112">
       <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),373.0)</f>
-        <v>373</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),378.0)</f>
+        <v>378</v>
       </c>
       <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="C112" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4630,12 +4634,12 @@
     </row>
     <row r="113">
       <c r="A113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
-        <v>375</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),380.0)</f>
+        <v>380</v>
       </c>
       <c r="B113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="C113" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
@@ -4644,110 +4648,110 @@
     </row>
     <row r="114">
       <c r="A114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),377.0)</f>
-        <v>377</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
+        <v>383</v>
       </c>
       <c r="B114" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
+      </c>
+      <c r="C114" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),384.0)</f>
+        <v>384</v>
+      </c>
+      <c r="B115" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
+      </c>
+      <c r="C115" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.0)</f>
+        <v>385</v>
+      </c>
+      <c r="B116" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATALLA")</f>
+        <v>BATALLA</v>
+      </c>
+      <c r="C116" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.0)</f>
+        <v>386</v>
+      </c>
+      <c r="B117" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
+      </c>
+      <c r="C117" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-      <c r="C114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),378.0)</f>
-        <v>378</v>
-      </c>
-      <c r="B115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="C115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),380.0)</f>
-        <v>380</v>
-      </c>
-      <c r="B116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="C116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
-        <v>383</v>
-      </c>
-      <c r="B117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
-      </c>
-      <c r="C117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),384.0)</f>
-        <v>384</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.0)</f>
+        <v>388</v>
       </c>
       <c r="B118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
+        <v>LAPORTE</v>
       </c>
       <c r="C118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.0)</f>
-        <v>385</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),390.0)</f>
+        <v>390</v>
       </c>
       <c r="B119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATALLA")</f>
-        <v>BATALLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LE NORMAND")</f>
+        <v>LE NORMAND</v>
       </c>
       <c r="C119" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),394.0)</f>
+        <v>394</v>
+      </c>
+      <c r="B120" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
+        <v>LEJEUNE</v>
+      </c>
+      <c r="C120" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
         <v>RAYO VALLECANO</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.0)</f>
-        <v>386</v>
-      </c>
-      <c r="B120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
-      </c>
-      <c r="C120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
     <row r="121">
       <c r="A121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.0)</f>
-        <v>388</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),397.0)</f>
+        <v>397</v>
       </c>
       <c r="B121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
-        <v>LAPORTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REGO")</f>
+        <v>REGO</v>
       </c>
       <c r="C121" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -4756,54 +4760,54 @@
     </row>
     <row r="122">
       <c r="A122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),390.0)</f>
-        <v>390</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
+        <v>401</v>
       </c>
       <c r="B122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LE NORMAND")</f>
-        <v>LE NORMAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
+        <v>RODRI MENDOZA</v>
       </c>
       <c r="C122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),394.0)</f>
-        <v>394</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),410.0)</f>
+        <v>410</v>
       </c>
       <c r="B123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
-        <v>LEJEUNE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
+        <v>GONZALO</v>
       </c>
       <c r="C123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),397.0)</f>
-        <v>397</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),412.0)</f>
+        <v>412</v>
       </c>
       <c r="B124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REGO")</f>
-        <v>REGO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
+        <v>MATEO JOSEPH</v>
       </c>
       <c r="C124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
-        <v>401</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),417.0)</f>
+        <v>417</v>
       </c>
       <c r="B125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
-        <v>RODRI MENDOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
+        <v>FEBAS</v>
       </c>
       <c r="C125" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -4812,26 +4816,26 @@
     </row>
     <row r="126">
       <c r="A126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),410.0)</f>
-        <v>410</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),418.0)</f>
+        <v>418</v>
       </c>
       <c r="B126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
-        <v>GONZALO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),412.0)</f>
-        <v>412</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),420.0)</f>
+        <v>420</v>
       </c>
       <c r="B127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
-        <v>MATEO JOSEPH</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
+        <v>DARDER</v>
       </c>
       <c r="C127" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4840,348 +4844,348 @@
     </row>
     <row r="128">
       <c r="A128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),417.0)</f>
-        <v>417</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),423.0)</f>
+        <v>423</v>
       </c>
       <c r="B128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
-        <v>FEBAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LÓPEZ")</f>
+        <v>UNAI LÓPEZ</v>
       </c>
       <c r="C128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),418.0)</f>
-        <v>418</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),424.0)</f>
+        <v>424</v>
       </c>
       <c r="B129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
+        <v>TENAGLIA</v>
       </c>
       <c r="C129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),420.0)</f>
-        <v>420</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),428.0)</f>
+        <v>428</v>
       </c>
       <c r="B130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
-        <v>DARDER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C130" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),430.0)</f>
+        <v>430</v>
+      </c>
+      <c r="B131" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
+        <v>VANAT</v>
+      </c>
+      <c r="C131" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),433.0)</f>
+        <v>433</v>
+      </c>
+      <c r="B132" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
+        <v>LEO ROMÁN</v>
+      </c>
+      <c r="C132" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),423.0)</f>
-        <v>423</v>
-      </c>
-      <c r="B131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LÓPEZ")</f>
-        <v>UNAI LÓPEZ</v>
-      </c>
-      <c r="C131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),424.0)</f>
-        <v>424</v>
-      </c>
-      <c r="B132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
-        <v>TENAGLIA</v>
-      </c>
-      <c r="C132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
-      </c>
-    </row>
     <row r="133">
       <c r="A133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),428.0)</f>
-        <v>428</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),435.0)</f>
+        <v>435</v>
       </c>
       <c r="B133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
+        <v>HASSAN</v>
       </c>
       <c r="C133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),429.0)</f>
-        <v>429</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),437.0)</f>
+        <v>437</v>
       </c>
       <c r="B134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
+        <v>GORROTXATEGI</v>
       </c>
       <c r="C134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),430.0)</f>
-        <v>430</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),438.0)</f>
+        <v>438</v>
       </c>
       <c r="B135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
-        <v>VANAT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATISTA MENDY")</f>
+        <v>BATISTA MENDY</v>
       </c>
       <c r="C135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),433.0)</f>
-        <v>433</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),441.0)</f>
+        <v>441</v>
       </c>
       <c r="B136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
-        <v>LEO ROMÁN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUCHANAN")</f>
+        <v>BUCHANAN</v>
       </c>
       <c r="C136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),435.0)</f>
-        <v>435</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),442.0)</f>
+        <v>442</v>
       </c>
       <c r="B137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
-        <v>HASSAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
+        <v>UNAI SIMÓN</v>
       </c>
       <c r="C137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),437.0)</f>
-        <v>437</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),443.0)</f>
+        <v>443</v>
       </c>
       <c r="B138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
-        <v>GORROTXATEGI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAUREGIZAR")</f>
+        <v>JAUREGIZAR</v>
       </c>
       <c r="C138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),438.0)</f>
-        <v>438</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),445.0)</f>
+        <v>445</v>
       </c>
       <c r="B139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATISTA MENDY")</f>
-        <v>BATISTA MENDY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
+        <v>MARCOS LLORENTE</v>
       </c>
       <c r="C139" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446.0)</f>
+        <v>446</v>
+      </c>
+      <c r="B140" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLEX BAENA")</f>
+        <v>ÁLEX BAENA</v>
+      </c>
+      <c r="C140" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),451.0)</f>
+        <v>451</v>
+      </c>
+      <c r="B141" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
+        <v>RAPHINHA</v>
+      </c>
+      <c r="C141" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),453.0)</f>
+        <v>453</v>
+      </c>
+      <c r="B142" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RASHFORD")</f>
+        <v>RASHFORD</v>
+      </c>
+      <c r="C142" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
+        <v>454</v>
+      </c>
+      <c r="B143" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
+        <v>ISCO</v>
+      </c>
+      <c r="C143" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),460.0)</f>
+        <v>460</v>
+      </c>
+      <c r="B144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
+      </c>
+      <c r="C144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),464.0)</f>
+        <v>464</v>
+      </c>
+      <c r="B145" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
+        <v>VARGAS</v>
+      </c>
+      <c r="C145" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),441.0)</f>
-        <v>441</v>
-      </c>
-      <c r="B140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUCHANAN")</f>
-        <v>BUCHANAN</v>
-      </c>
-      <c r="C140" s="20" t="str">
+    <row r="146">
+      <c r="A146" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),466.0)</f>
+        <v>466</v>
+      </c>
+      <c r="B146" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
+        <v>MOLEIRO</v>
+      </c>
+      <c r="C146" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),442.0)</f>
-        <v>442</v>
-      </c>
-      <c r="B141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
-        <v>UNAI SIMÓN</v>
-      </c>
-      <c r="C141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),443.0)</f>
-        <v>443</v>
-      </c>
-      <c r="B142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAUREGIZAR")</f>
-        <v>JAUREGIZAR</v>
-      </c>
-      <c r="C142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),445.0)</f>
-        <v>445</v>
-      </c>
-      <c r="B143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
-        <v>MARCOS LLORENTE</v>
-      </c>
-      <c r="C143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446.0)</f>
-        <v>446</v>
-      </c>
-      <c r="B144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLEX BAENA")</f>
-        <v>ÁLEX BAENA</v>
-      </c>
-      <c r="C144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),451.0)</f>
-        <v>451</v>
-      </c>
-      <c r="B145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
-        <v>RAPHINHA</v>
-      </c>
-      <c r="C145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),453.0)</f>
-        <v>453</v>
-      </c>
-      <c r="B146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RASHFORD")</f>
-        <v>RASHFORD</v>
-      </c>
-      <c r="C146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
     <row r="147">
       <c r="A147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
-        <v>454</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),468.0)</f>
+        <v>468</v>
       </c>
       <c r="B147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
-        <v>ISCO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD CHAMPIONS")</f>
+        <v>CARD CHAMPIONS</v>
       </c>
       <c r="C147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),459.0)</f>
-        <v>459</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.0)</f>
+        <v>470</v>
       </c>
       <c r="B148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ÁLVAREZ")</f>
+        <v>JULIÁN ÁLVAREZ</v>
       </c>
       <c r="C148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATLÉTICO)")</f>
+        <v>BALÓN DE ORO (ATLÉTICO)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),460.0)</f>
-        <v>460</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),471.0)</f>
+        <v>471</v>
       </c>
       <c r="B149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRI")</f>
+        <v>PEDRI</v>
       </c>
       <c r="C149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
+        <v>BALÓN DE ORO (BARÇA)</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),464.0)</f>
-        <v>464</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),472.0)</f>
+        <v>472</v>
       </c>
       <c r="B150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
-        <v>VARGAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
+        <v>LAMINE YAMAL</v>
       </c>
       <c r="C150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
+        <v>BALÓN DE ORO (BARÇA)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),466.0)</f>
-        <v>466</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),473.0)</f>
+        <v>473</v>
       </c>
       <c r="B151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
-        <v>MOLEIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (REAL MADRID)")</f>
+        <v>BALÓN DE ORO (REAL MADRID)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),468.0)</f>
-        <v>468</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),475.0)</f>
+        <v>475</v>
       </c>
       <c r="B152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD CHAMPIONS")</f>
-        <v>CARD CHAMPIONS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO EXCELLENCE")</f>
+        <v>BALÓN DE ORO EXCELLENCE</v>
       </c>
       <c r="C152" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
@@ -5190,98 +5194,28 @@
     </row>
     <row r="153">
       <c r="A153" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.0)</f>
-        <v>470</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.0)</f>
+        <v>476</v>
       </c>
       <c r="B153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ÁLVAREZ")</f>
-        <v>JULIÁN ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD ATÓMICA")</f>
+        <v>CARD ATÓMICA</v>
       </c>
       <c r="C153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATLÉTICO)")</f>
-        <v>BALÓN DE ORO (ATLÉTICO)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),471.0)</f>
-        <v>471</v>
-      </c>
-      <c r="B154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRI")</f>
-        <v>PEDRI</v>
-      </c>
-      <c r="C154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
-        <v>BALÓN DE ORO (BARÇA)</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),472.0)</f>
-        <v>472</v>
-      </c>
-      <c r="B155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
-        <v>LAMINE YAMAL</v>
-      </c>
-      <c r="C155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
-        <v>BALÓN DE ORO (BARÇA)</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),473.0)</f>
-        <v>473</v>
-      </c>
-      <c r="B156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
-      </c>
-      <c r="C156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (REAL MADRID)")</f>
-        <v>BALÓN DE ORO (REAL MADRID)</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),475.0)</f>
-        <v>475</v>
-      </c>
-      <c r="B157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO EXCELLENCE")</f>
-        <v>BALÓN DE ORO EXCELLENCE</v>
-      </c>
-      <c r="C157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.0)</f>
-        <v>476</v>
-      </c>
-      <c r="B158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD ATÓMICA")</f>
-        <v>CARD ATÓMICA</v>
-      </c>
-      <c r="C158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
         <v>91</v>
       </c>
-      <c r="B159" s="20" t="str">
+      <c r="B154" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
         <v>ESTADIO</v>
       </c>
-      <c r="C159" s="20" t="str">
+      <c r="C154" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
@@ -5568,52 +5502,52 @@
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
+        <v>BELLERÍN</v>
       </c>
       <c r="C15" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C16" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
-        <v>93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
-        <v>IVÁN VILLAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
       </c>
       <c r="C17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D17" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5622,12 +5556,12 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
+        <v>93</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
+        <v>IVÁN VILLAR</v>
       </c>
       <c r="C18" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5640,12 +5574,12 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C19" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5658,12 +5592,12 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C20" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5676,12 +5610,12 @@
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C21" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5694,12 +5628,12 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
-        <v>106</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
-        <v>IAGO ASPAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C22" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5712,12 +5646,12 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
+        <v>IAGO ASPAS</v>
       </c>
       <c r="C23" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5730,12 +5664,12 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C24" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5748,16 +5682,16 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
-        <v>IÑAKI PEÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
       </c>
       <c r="C25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D25" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5766,12 +5700,12 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
+        <v>IÑAKI PEÑA</v>
       </c>
       <c r="C26" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5784,12 +5718,12 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C27" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5802,12 +5736,12 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
-        <v>117</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
-        <v>FEDE REDONDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
+        <v>ÁLVARO NÚÑEZ</v>
       </c>
       <c r="C28" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5820,12 +5754,12 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C29" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5838,16 +5772,16 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
+        <v>117</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
+        <v>FEDE REDONDO</v>
       </c>
       <c r="C30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D30" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5856,16 +5790,16 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D31" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5874,30 +5808,30 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C32" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5910,34 +5844,34 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C34" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
       </c>
       <c r="C35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D35" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5946,16 +5880,16 @@
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D36" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5964,16 +5898,16 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D37" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5982,16 +5916,16 @@
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D38" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6000,16 +5934,16 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
-        <v>174</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
+        <v>153</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
-        <v>IVÁN MARTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
+        <v>DIEGO RICO</v>
       </c>
       <c r="C39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D39" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6018,30 +5952,30 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C40" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
       </c>
       <c r="D40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.0)</f>
-        <v>177</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TSYGANKOV")</f>
-        <v>TSYGANKOV</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C41" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -6054,16 +5988,16 @@
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
-        <v>202</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
+        <v>174</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
-        <v>CARVAJAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
+        <v>IVÁN MARTÍN</v>
       </c>
       <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D42" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6072,34 +6006,34 @@
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
       </c>
       <c r="C43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
-        <v>211</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
+        <v>176</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
-        <v>GÜLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
+        <v>JOEL ROCA</v>
       </c>
       <c r="C44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D44" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6108,16 +6042,16 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
-        <v>213</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.0)</f>
+        <v>177</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
-        <v>RODRYGO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TSYGANKOV")</f>
+        <v>TSYGANKOV</v>
       </c>
       <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D45" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6126,12 +6060,12 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
+        <v>202</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
+        <v>CARVAJAL</v>
       </c>
       <c r="C46" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6144,34 +6078,34 @@
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
-        <v>225</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
-        <v>MOJICA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
       </c>
       <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D48" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6180,16 +6114,16 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
+        <v>213</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
+        <v>RODRYGO</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D49" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6198,34 +6132,34 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
       </c>
       <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D51" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6234,34 +6168,34 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
-        <v>237</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
+        <v>225</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
-        <v>AITOR FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
+        <v>MOJICA</v>
       </c>
       <c r="C52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
-        <v>248</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
       </c>
       <c r="C53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D53" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6270,12 +6204,12 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C54" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -6288,16 +6222,16 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D55" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6306,34 +6240,34 @@
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
+        <v>237</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
+        <v>AITOR FERNÁNDEZ</v>
       </c>
       <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),247.0)</f>
+        <v>247</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUBÉN GARCÍA")</f>
+        <v>RUBÉN GARCÍA</v>
       </c>
       <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D57" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6342,16 +6276,16 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.0)</f>
-        <v>267</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
+        <v>248</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BREKALO")</f>
-        <v>BREKALO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
       </c>
       <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D58" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6360,16 +6294,16 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D59" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6378,16 +6312,16 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
-        <v>277</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),255.0)</f>
+        <v>255</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
-        <v>LUIZ FELIPE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLDOVAN")</f>
+        <v>MOLDOVAN</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D60" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6396,34 +6330,34 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
-        <v>283</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
-        <v>PEDRO DÍAZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D62" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6432,16 +6366,16 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
-        <v>286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
-        <v>CAMELLO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D63" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6450,16 +6384,16 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
-        <v>290</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.0)</f>
+        <v>267</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BREKALO")</f>
+        <v>BREKALO</v>
       </c>
       <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D64" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6468,16 +6402,16 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D65" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6486,16 +6420,16 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
-        <v>296</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
+        <v>277</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
-        <v>SERGIO GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
+        <v>LUIZ FELIPE</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D66" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6504,34 +6438,34 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
       </c>
       <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D68" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6540,16 +6474,16 @@
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
-        <v>312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
+        <v>286</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
-        <v>AZPILICUETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
+        <v>CAMELLO</v>
       </c>
       <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D69" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6558,16 +6492,16 @@
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
+        <v>290</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6576,52 +6510,52 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
+        <v>296</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
+        <v>SERGIO GÓMEZ</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D73" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6630,16 +6564,16 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
-        <v>327</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
-        <v>DIMITRIEVSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D74" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6648,16 +6582,16 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
+        <v>312</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
+        <v>AZPILICUETA</v>
       </c>
       <c r="C75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D75" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6666,16 +6600,16 @@
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
       </c>
       <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D76" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6684,70 +6618,70 @@
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
-        <v>331</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
-        <v>COPETE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C79" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
       </c>
       <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D80" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6756,16 +6690,16 @@
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
       </c>
       <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D81" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6774,16 +6708,16 @@
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
-        <v>350</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
-        <v>SERGI CARDONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
       </c>
       <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D82" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6792,16 +6726,16 @@
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
+        <v>331</v>
       </c>
       <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
+        <v>COPETE</v>
       </c>
       <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D83" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6810,16 +6744,16 @@
     </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
       </c>
       <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
       </c>
       <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D84" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6828,34 +6762,34 @@
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
       </c>
       <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D86" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6864,16 +6798,16 @@
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
-        <v>371</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D87" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6882,34 +6816,34 @@
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
+        <v>350</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
+        <v>SERGI CARDONA</v>
       </c>
       <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
       </c>
       <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D89" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6918,16 +6852,16 @@
     </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
       </c>
       <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D90" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6936,16 +6870,16 @@
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),400.0)</f>
-        <v>400</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO GARCÍA")</f>
-        <v>PABLO GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D91" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6954,16 +6888,16 @@
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
-        <v>404</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
-      </c>
-      <c r="C92" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
         <v>GETAFE CF</v>
+      </c>
+      <c r="C92" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D92" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6972,16 +6906,16 @@
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
-        <v>409</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
+        <v>371</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
-        <v>FRAN GONZÁLEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D93" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6990,52 +6924,52 @@
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D94" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
+      </c>
+      <c r="B95" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
+      </c>
+      <c r="C95" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+      <c r="D95" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
-      </c>
-      <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
-      </c>
-      <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-      <c r="D95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
       </c>
       <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D96" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7044,16 +6978,16 @@
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),400.0)</f>
+        <v>400</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO GARCÍA")</f>
+        <v>PABLO GARCÍA</v>
       </c>
       <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D97" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7062,16 +6996,16 @@
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D98" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7080,16 +7014,16 @@
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
-        <v>425</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
+        <v>409</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
-        <v>CARLOS VICENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
+        <v>FRAN GONZÁLEZ</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D99" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7098,16 +7032,16 @@
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
-        <v>436</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
-        <v>CARLOS SOLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
       </c>
       <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D100" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7116,34 +7050,34 @@
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
       </c>
       <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
-        <v>444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
       </c>
       <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
-        <v>OBLAK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
       </c>
       <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D102" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7152,16 +7086,16 @@
     </row>
     <row r="103">
       <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),449.0)</f>
-        <v>449</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
       </c>
       <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
-        <v>KOUNDÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
       </c>
       <c r="C103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D103" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7170,16 +7104,16 @@
     </row>
     <row r="104">
       <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
-        <v>452</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
       </c>
       <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
-        <v>LEWANDOWSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
       </c>
       <c r="C104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D104" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7188,16 +7122,16 @@
     </row>
     <row r="105">
       <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
-        <v>456</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
+        <v>425</v>
       </c>
       <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
-        <v>ANTONY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
+        <v>CARLOS VICENTE</v>
       </c>
       <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D105" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7206,16 +7140,16 @@
     </row>
     <row r="106">
       <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
-        <v>458</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
+        <v>436</v>
       </c>
       <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
-        <v>CARRERAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
+        <v>CARLOS SOLER</v>
       </c>
       <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D106" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7224,36 +7158,144 @@
     </row>
     <row r="107">
       <c r="A107" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
+      </c>
+      <c r="B107" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
+      </c>
+      <c r="C107" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D107" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
+        <v>444</v>
+      </c>
+      <c r="B108" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
+        <v>OBLAK</v>
+      </c>
+      <c r="C108" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D108" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),449.0)</f>
+        <v>449</v>
+      </c>
+      <c r="B109" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
+        <v>KOUNDÉ</v>
+      </c>
+      <c r="C109" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D109" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
+        <v>452</v>
+      </c>
+      <c r="B110" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
+        <v>LEWANDOWSKI</v>
+      </c>
+      <c r="C110" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D110" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
+        <v>456</v>
+      </c>
+      <c r="B111" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
+        <v>ANTONY</v>
+      </c>
+      <c r="C111" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D111" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
+        <v>458</v>
+      </c>
+      <c r="B112" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
+        <v>CARRERAS</v>
+      </c>
+      <c r="C112" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D112" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B107" s="20" t="str">
+      <c r="B113" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C107" s="20" t="str">
+      <c r="C113" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D107" s="20">
+      <c r="D113" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="20">
+    <row r="114">
+      <c r="A114" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),477.0)</f>
         <v>477</v>
       </c>
-      <c r="B108" s="20" t="str">
+      <c r="B114" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD INVENCIBLE")</f>
         <v>CARD INVENCIBLE</v>
       </c>
-      <c r="C108" s="20" t="str">
+      <c r="C114" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
         <v>ÚNICA</v>
       </c>
-      <c r="D108" s="20">
+      <c r="D114" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
@@ -7301,7 +7343,9 @@
       <c r="C2" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="21"/>
+      <c r="D2" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="21">
@@ -8321,6 +8365,9 @@
       <c r="D76" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E76" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="21">
@@ -8579,7 +8626,9 @@
       <c r="C95" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D95" s="21"/>
+      <c r="D95" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="21">
@@ -8837,6 +8886,9 @@
       <c r="D112" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E112" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="21">
@@ -9410,6 +9462,9 @@
       <c r="D153" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E153" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="21">
@@ -9728,6 +9783,9 @@
       <c r="D176" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E176" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="21">
@@ -10080,7 +10138,7 @@
         <v>20</v>
       </c>
       <c r="E202" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="203">
@@ -10718,6 +10776,9 @@
       <c r="D247" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E247" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="21">
@@ -10777,7 +10838,9 @@
       <c r="C251" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D251" s="21"/>
+      <c r="D251" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="21">
@@ -10829,6 +10892,9 @@
       </c>
       <c r="D255" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E255" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="256">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="399">
   <si>
     <t>Última actualización:</t>
   </si>
@@ -1833,15 +1833,15 @@
       </c>
       <c r="C3" s="9">
         <f>COUNTIF(REGULARES!D:D, "SI")</f>
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="D3" s="9">
         <f t="shared" ref="D3:D12" si="1">B3-C3</f>
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E4" si="2">(C3/B3)</f>
-        <v>0.7083333333</v>
+        <v>0.7888888889</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E3, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1881,15 +1881,15 @@
       </c>
       <c r="C5" s="9">
         <f>COUNTIF('¡VAMOS! (361–380)'!D:D, "SI")</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" s="9">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" ref="E5:E13" si="3">C5/B5</f>
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F5" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E5, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1905,15 +1905,15 @@
       </c>
       <c r="C6" s="14">
         <f>COUNTIF('Guantes de Oro (381–387)'!D:D, "SI")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="15">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" si="3"/>
-        <v>0.4285714286</v>
+        <v>0.5714285714</v>
       </c>
       <c r="F6" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E6, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2001,15 +2001,15 @@
       </c>
       <c r="C10" s="14">
         <f>COUNTIF('Protas (424–441)'!D:D, "SI")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="3"/>
-        <v>0.5555555556</v>
+        <v>0.6666666667</v>
       </c>
       <c r="F10" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E10, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2025,15 +2025,15 @@
       </c>
       <c r="C11" s="14">
         <f>COUNTIF('Super Cracks (442–467)'!D:D, "SI")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" s="15">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="3"/>
-        <v>0.6153846154</v>
+        <v>0.6923076923</v>
       </c>
       <c r="F11" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E11, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2049,15 +2049,15 @@
       </c>
       <c r="C12" s="14">
         <f>COUNTIF('Cartas Top y Únicas (468–478)'!D:D, "SI")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="15">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="10">
         <f t="shared" si="3"/>
-        <v>0.3636363636</v>
+        <v>0.4545454545</v>
       </c>
       <c r="F12" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E12, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="4"/>
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="4"/>
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>0.6907630522</v>
+        <v>0.7670682731</v>
       </c>
       <c r="F13" s="19" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E13, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2203,6 +2203,9 @@
       </c>
       <c r="D7" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E7" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
@@ -2410,7 +2413,9 @@
       <c r="C12" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="D12" s="21"/>
+      <c r="D12" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="21">
@@ -2439,7 +2444,9 @@
       <c r="C14" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="D14" s="21"/>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="21">
@@ -2592,7 +2599,9 @@
       <c r="C6" s="21" t="s">
         <v>393</v>
       </c>
-      <c r="D6" s="21"/>
+      <c r="D6" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21">
@@ -2734,7 +2743,9 @@
       <c r="C4" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="21">
@@ -2775,6 +2786,9 @@
       <c r="D7" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E7" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21">
@@ -2858,7 +2872,9 @@
       <c r="C13" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="21"/>
+      <c r="D13" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21">
@@ -2975,6 +2991,9 @@
       <c r="D21" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E21" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="21">
@@ -3040,6 +3059,9 @@
       </c>
       <c r="D26" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E26" s="22">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -3066,12 +3088,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("{FILTER(REGULARES!A:C, REGULARES!D:D&lt;&gt;""SI"", REGULARES!A:A&lt;&gt;""""); FILTER('¡VAMOS! (361–380)'!A:C, '¡VAMOS! (361–380)'!D:D&lt;&gt;""SI"", '¡VAMOS! (361–380)'!A:A&lt;&gt;""""); FILTER('Guantes de Oro (381–387)'!A:C, 'Guantes de Oro (381–387)'!D:D&lt;&gt;""SI"", 'Guantes de"&amp;" Oro (381–387)'!A:A&lt;&gt;""""); FILTER('Kryptonita (388–396)'!A:C, 'Kryptonita (388–396)'!D:D&lt;&gt;""SI"", 'Kryptonita (388–396)'!A:A&lt;&gt;""""); FILTER('Diamantes (397–414)'!A:C, 'Diamantes (397–414)'!D:D&lt;&gt;""SI"", 'Diamantes (397–414)'!A:A&lt;&gt;""""); FILTER('Influencer"&amp;"s (415–423)'!A:C, 'Influencers (415–423)'!D:D&lt;&gt;""SI"", 'Influencers (415–423)'!A:A&lt;&gt;""""); FILTER('Protas (424–441)'!A:C, 'Protas (424–441)'!D:D&lt;&gt;""SI"", 'Protas (424–441)'!A:A&lt;&gt;""""); FILTER('Super Cracks (442–467)'!A:C, 'Super Cracks (442–467)'!D:D&lt;&gt;""S"&amp;"I"", 'Super Cracks (442–467)'!A:A&lt;&gt;""""); FILTER('Cartas Top y Únicas (468–478)'!A:C, 'Cartas Top y Únicas (468–478)'!D:D&lt;&gt;""SI"", 'Cartas Top y Únicas (468–478)'!A:A&lt;&gt;""""); FILTER(Estadios!A:C, Estadios!D:D&lt;&gt;""SI"", Estadios!A:A&lt;&gt;"""")}"),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("{FILTER(REGULARES!A:C, REGULARES!D:D&lt;&gt;""SI"", REGULARES!A:A&lt;&gt;""""); FILTER('¡VAMOS! (361–380)'!A:C, '¡VAMOS! (361–380)'!D:D&lt;&gt;""SI"", '¡VAMOS! (361–380)'!A:A&lt;&gt;""""); FILTER('Guantes de Oro (381–387)'!A:C, 'Guantes de Oro (381–387)'!D:D&lt;&gt;""SI"", 'Guantes de"&amp;" Oro (381–387)'!A:A&lt;&gt;""""); FILTER('Kryptonita (388–396)'!A:C, 'Kryptonita (388–396)'!D:D&lt;&gt;""SI"", 'Kryptonita (388–396)'!A:A&lt;&gt;""""); FILTER('Diamantes (397–414)'!A:C, 'Diamantes (397–414)'!D:D&lt;&gt;""SI"", 'Diamantes (397–414)'!A:A&lt;&gt;""""); FILTER('Influencer"&amp;"s (415–423)'!A:C, 'Influencers (415–423)'!D:D&lt;&gt;""SI"", 'Influencers (415–423)'!A:A&lt;&gt;""""); FILTER('Protas (424–441)'!A:C, 'Protas (424–441)'!D:D&lt;&gt;""SI"", 'Protas (424–441)'!A:A&lt;&gt;""""); FILTER('Super Cracks (442–467)'!A:C, 'Super Cracks (442–467)'!D:D&lt;&gt;""S"&amp;"I"", 'Super Cracks (442–467)'!A:A&lt;&gt;""""); FILTER('Cartas Top y Únicas (468–478)'!A:C, 'Cartas Top y Únicas (468–478)'!D:D&lt;&gt;""SI"", 'Cartas Top y Únicas (468–478)'!A:A&lt;&gt;""""); FILTER(Estadios!A:C, Estadios!D:D&lt;&gt;""SI"", Estadios!A:A&lt;&gt;"""")}"),12.0)</f>
+        <v>12</v>
       </c>
       <c r="B1" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
-        <v>TENAGLIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEÑÁ")</f>
+        <v>ALEÑÁ</v>
       </c>
       <c r="C1" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -3080,12 +3102,12 @@
     </row>
     <row r="2">
       <c r="A2" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
       </c>
       <c r="B2" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GURIDI")</f>
-        <v>GURIDI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO IBÁÑEZ")</f>
+        <v>PABLO IBÁÑEZ</v>
       </c>
       <c r="C2" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -3094,54 +3116,54 @@
     </row>
     <row r="3">
       <c r="A3" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
+        <v>20</v>
       </c>
       <c r="B3" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEÑÁ")</f>
-        <v>ALEÑÁ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
+        <v>UNAI SIMÓN</v>
       </c>
       <c r="C3" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
+        <v>25</v>
       </c>
       <c r="B4" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO IBÁÑEZ")</f>
-        <v>PABLO IBÁÑEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
+        <v>LAPORTE</v>
       </c>
       <c r="C4" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
-        <v>16</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.0)</f>
+        <v>26</v>
       </c>
       <c r="B5" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TONI MARTÍNEZ")</f>
-        <v>TONI MARTÍNEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YURI")</f>
+        <v>YURI</v>
       </c>
       <c r="C5" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
+        <v>29</v>
       </c>
       <c r="B6" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
-        <v>UNAI SIMÓN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VESGA")</f>
+        <v>VESGA</v>
       </c>
       <c r="C6" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3150,12 +3172,12 @@
     </row>
     <row r="7">
       <c r="A7" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
+        <v>30</v>
       </c>
       <c r="B7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAREDES")</f>
-        <v>PAREDES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI GÓMEZ")</f>
+        <v>UNAI GÓMEZ</v>
       </c>
       <c r="C7" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3164,12 +3186,12 @@
     </row>
     <row r="8">
       <c r="A8" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
-        <v>25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
+        <v>35</v>
       </c>
       <c r="B8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
-        <v>LAPORTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GURUZETA")</f>
+        <v>GURUZETA</v>
       </c>
       <c r="C8" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3178,1104 +3200,1104 @@
     </row>
     <row r="9">
       <c r="A9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.0)</f>
-        <v>26</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
       </c>
       <c r="B9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YURI")</f>
-        <v>YURI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C9" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
+        <v>48</v>
+      </c>
+      <c r="B10" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX BAENA")</f>
+        <v>ALEX BAENA</v>
+      </c>
+      <c r="C10" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="B11" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO GONZÁLEZ")</f>
+        <v>NICO GONZÁLEZ</v>
+      </c>
+      <c r="C11" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.0)</f>
+        <v>51</v>
+      </c>
+      <c r="B12" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIULIANO")</f>
+        <v>GIULIANO</v>
+      </c>
+      <c r="C12" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
+        <v>57</v>
+      </c>
+      <c r="B13" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SZCZESNY")</f>
+        <v>SZCZESNY</v>
+      </c>
+      <c r="C13" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
+        <v>58</v>
+      </c>
+      <c r="B14" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
+        <v>KOUNDÉ</v>
+      </c>
+      <c r="C14" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.0)</f>
+        <v>60</v>
+      </c>
+      <c r="B15" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ERIC GARCÍA")</f>
+        <v>ERIC GARCÍA</v>
+      </c>
+      <c r="C15" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
+        <v>69</v>
+      </c>
+      <c r="B16" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
+        <v>LAMINE YAMAL</v>
+      </c>
+      <c r="C16" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.0)</f>
+        <v>80</v>
+      </c>
+      <c r="B17" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
+      </c>
+      <c r="C17" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.0)</f>
+        <v>82</v>
+      </c>
+      <c r="B18" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALTIMIRA")</f>
+        <v>ALTIMIRA</v>
+      </c>
+      <c r="C18" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.0)</f>
+        <v>83</v>
+      </c>
+      <c r="B19" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AMRABAT")</f>
+        <v>AMRABAT</v>
+      </c>
+      <c r="C19" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),85.0)</f>
+        <v>85</v>
+      </c>
+      <c r="B20" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LO CELSO")</f>
+        <v>LO CELSO</v>
+      </c>
+      <c r="C20" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
+        <v>89</v>
+      </c>
+      <c r="B21" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIQUELME")</f>
+        <v>RIQUELME</v>
+      </c>
+      <c r="C21" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.0)</f>
+        <v>90</v>
+      </c>
+      <c r="B22" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABDE")</f>
+        <v>ABDE</v>
+      </c>
+      <c r="C22" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.0)</f>
+        <v>92</v>
+      </c>
+      <c r="B23" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RADU")</f>
+        <v>RADU</v>
+      </c>
+      <c r="C23" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
+        <v>98</v>
+      </c>
+      <c r="B24" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MINGUEZA")</f>
+        <v>MINGUEZA</v>
+      </c>
+      <c r="C24" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101.0)</f>
+        <v>101</v>
+      </c>
+      <c r="B25" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN BELTRÁN")</f>
+        <v>FRAN BELTRÁN</v>
+      </c>
+      <c r="C25" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
+      </c>
+      <c r="B26" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
+      </c>
+      <c r="C26" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
+        <v>113</v>
+      </c>
+      <c r="B27" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CHUST")</f>
+        <v>CHUST</v>
+      </c>
+      <c r="C27" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
+        <v>119</v>
+      </c>
+      <c r="B28" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARTIM NETO")</f>
+        <v>MARTIM NETO</v>
+      </c>
+      <c r="C28" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
+        <v>120</v>
+      </c>
+      <c r="B29" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
+        <v>FEBAS</v>
+      </c>
+      <c r="C29" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
+        <v>128</v>
+      </c>
+      <c r="B30" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
+        <v>DMITROVIC</v>
+      </c>
+      <c r="C30" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
+        <v>133</v>
+      </c>
+      <c r="B31" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
+      </c>
+      <c r="C31" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
+      </c>
+      <c r="B32" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C32" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
+        <v>148</v>
+      </c>
+      <c r="B33" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IGLESIAS")</f>
+        <v>IGLESIAS</v>
+      </c>
+      <c r="C33" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.0)</f>
+        <v>149</v>
+      </c>
+      <c r="B34" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKO FEMENÍA")</f>
+        <v>KIKO FEMENÍA</v>
+      </c>
+      <c r="C34" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.0)</f>
+        <v>150</v>
+      </c>
+      <c r="B35" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DJENÉ")</f>
+        <v>DJENÉ</v>
+      </c>
+      <c r="C35" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
+        <v>151</v>
+      </c>
+      <c r="B36" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOMINGOS DUARTE")</f>
+        <v>DOMINGOS DUARTE</v>
+      </c>
+      <c r="C36" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),157.0)</f>
+        <v>157</v>
+      </c>
+      <c r="B37" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
+      </c>
+      <c r="C37" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),162.0)</f>
+        <v>162</v>
+      </c>
+      <c r="B38" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COBA")</f>
+        <v>COBA</v>
+      </c>
+      <c r="C38" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
+        <v>168</v>
+      </c>
+      <c r="B39" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VITOR REIS")</f>
+        <v>VITOR REIS</v>
+      </c>
+      <c r="C39" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.0)</f>
+        <v>178</v>
+      </c>
+      <c r="B40" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
+        <v>VANAT</v>
+      </c>
+      <c r="C40" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
+        <v>182</v>
+      </c>
+      <c r="B41" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RYAN")</f>
+        <v>RYAN</v>
+      </c>
+      <c r="C41" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
+        <v>183</v>
+      </c>
+      <c r="B42" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO CAMPOS")</f>
+        <v>PABLO CAMPOS</v>
+      </c>
+      <c r="C42" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),191.0)</f>
+        <v>191</v>
+      </c>
+      <c r="B43" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARTÍNEZ")</f>
+        <v>PABLO MARTÍNEZ</v>
+      </c>
+      <c r="C43" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.0)</f>
+        <v>196</v>
+      </c>
+      <c r="B44" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRUGUÉ")</f>
+        <v>BRUGUÉ</v>
+      </c>
+      <c r="C44" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
+        <v>198</v>
+      </c>
+      <c r="B45" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
+        <v>ETTA EYONG</v>
+      </c>
+      <c r="C45" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.0)</f>
+        <v>201</v>
+      </c>
+      <c r="B46" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUNIN")</f>
+        <v>LUNIN</v>
+      </c>
+      <c r="C46" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.0)</f>
+        <v>205</v>
+      </c>
+      <c r="B47" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUIJSEN")</f>
+        <v>HUIJSEN</v>
+      </c>
+      <c r="C47" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
+        <v>218</v>
+      </c>
+      <c r="B48" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
+        <v>LEO ROMÁN</v>
+      </c>
+      <c r="C48" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.0)</f>
+        <v>231</v>
+      </c>
+      <c r="B49" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ASANO")</f>
+        <v>ASANO</v>
+      </c>
+      <c r="C49" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),232.0)</f>
+        <v>232</v>
+      </c>
+      <c r="B50" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MURIQI")</f>
+        <v>MURIQI</v>
+      </c>
+      <c r="C50" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),233.0)</f>
+        <v>233</v>
+      </c>
+      <c r="B51" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
+        <v>MATEO JOSEPH</v>
+      </c>
+      <c r="C51" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.0)</f>
+        <v>239</v>
+      </c>
+      <c r="B52" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYOMO")</f>
+        <v>BOYOMO</v>
+      </c>
+      <c r="C52" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.0)</f>
+        <v>241</v>
+      </c>
+      <c r="B53" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HERRANDO")</f>
+        <v>HERRANDO</v>
+      </c>
+      <c r="C53" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
+        <v>253</v>
+      </c>
+      <c r="B54" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C54" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),254.0)</f>
+        <v>254</v>
+      </c>
+      <c r="B55" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AARON ESCANDELL")</f>
+        <v>AARON ESCANDELL</v>
+      </c>
+      <c r="C55" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
+        <v>260</v>
+      </c>
+      <c r="B56" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
+        <v>RAHIM ALHASSANE</v>
+      </c>
+      <c r="C56" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
+        <v>261</v>
+      </c>
+      <c r="B57" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLOMBATTO")</f>
+        <v>COLOMBATTO</v>
+      </c>
+      <c r="C57" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),263.0)</f>
+        <v>263</v>
+      </c>
+      <c r="B58" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DENDONCKER")</f>
+        <v>DENDONCKER</v>
+      </c>
+      <c r="C58" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),268.0)</f>
+        <v>268</v>
+      </c>
+      <c r="B59" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILYAS CHAIRA")</f>
+        <v>ILYAS CHAIRA</v>
+      </c>
+      <c r="C59" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),271.0)</f>
+        <v>271</v>
+      </c>
+      <c r="B60" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C60" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.0)</f>
+        <v>273</v>
+      </c>
+      <c r="B61" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CÁRDENAS")</f>
+        <v>CÁRDENAS</v>
+      </c>
+      <c r="C61" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),276.0)</f>
+        <v>276</v>
+      </c>
+      <c r="B62" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
+        <v>LEJEUNE</v>
+      </c>
+      <c r="C62" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),279.0)</f>
+        <v>279</v>
+      </c>
+      <c r="B63" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PATHÉ CISS")</f>
+        <v>PATHÉ CISS</v>
+      </c>
+      <c r="C63" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),280.0)</f>
+        <v>280</v>
+      </c>
+      <c r="B64" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LOPEZ")</f>
+        <v>UNAI LOPEZ</v>
+      </c>
+      <c r="C64" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
+        <v>289</v>
+      </c>
+      <c r="B65" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C65" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),297.0)</f>
+        <v>297</v>
+      </c>
+      <c r="B66" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
+        <v>GORROTXATEGI</v>
+      </c>
+      <c r="C66" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.0)</f>
+        <v>300</v>
+      </c>
+      <c r="B67" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
+        <v>CARLOS SOLER</v>
+      </c>
+      <c r="C67" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),301.0)</f>
+        <v>301</v>
+      </c>
+      <c r="B68" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRAIS MÉNDEZ")</f>
+        <v>BRAIS MÉNDEZ</v>
+      </c>
+      <c r="C68" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),305.0)</f>
+        <v>305</v>
+      </c>
+      <c r="B69" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSKARSSON")</f>
+        <v>ÓSKARSSON</v>
+      </c>
+      <c r="C69" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),310.0)</f>
+        <v>310</v>
+      </c>
+      <c r="B70" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARMONA")</f>
+        <v>CARMONA</v>
+      </c>
+      <c r="C70" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),314.0)</f>
+        <v>314</v>
+      </c>
+      <c r="B71" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCAO")</f>
+        <v>MARCAO</v>
+      </c>
+      <c r="C71" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),324.0)</f>
+        <v>324</v>
+      </c>
+      <c r="B72" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
+      </c>
+      <c r="C72" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),339.0)</f>
+        <v>339</v>
+      </c>
+      <c r="B73" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO LÓPEZ")</f>
+        <v>DIEGO LÓPEZ</v>
+      </c>
+      <c r="C73" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
+        <v>348</v>
+      </c>
+      <c r="B74" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MARÍN")</f>
+        <v>RAFA MARÍN</v>
+      </c>
+      <c r="C74" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),349.0)</f>
+        <v>349</v>
+      </c>
+      <c r="B75" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RENATO VEIGA")</f>
+        <v>RENATO VEIGA</v>
+      </c>
+      <c r="C75" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),360.0)</f>
+        <v>360</v>
+      </c>
+      <c r="B76" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AYOZE")</f>
+        <v>AYOZE</v>
+      </c>
+      <c r="C76" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),364.0)</f>
+        <v>364</v>
+      </c>
+      <c r="B77" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="C77" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),365.0)</f>
+        <v>365</v>
+      </c>
+      <c r="B78" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="C78" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
+        <v>375</v>
+      </c>
+      <c r="B79" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="C79" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),378.0)</f>
+        <v>378</v>
+      </c>
+      <c r="B80" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="C80" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),380.0)</f>
+        <v>380</v>
+      </c>
+      <c r="B81" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="C81" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),384.0)</f>
+        <v>384</v>
+      </c>
+      <c r="B82" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
+      </c>
+      <c r="C82" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.0)</f>
+        <v>385</v>
+      </c>
+      <c r="B83" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATALLA")</f>
+        <v>BATALLA</v>
+      </c>
+      <c r="C83" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.0)</f>
+        <v>386</v>
+      </c>
+      <c r="B84" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
+      </c>
+      <c r="C84" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.0)</f>
+        <v>388</v>
+      </c>
+      <c r="B85" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
+        <v>LAPORTE</v>
+      </c>
+      <c r="C85" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
         <v>ATHLETIC CLUB</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
-        <v>29</v>
-      </c>
-      <c r="B10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VESGA")</f>
-        <v>VESGA</v>
-      </c>
-      <c r="C10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
-      </c>
-      <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI GÓMEZ")</f>
-        <v>UNAI GÓMEZ</v>
-      </c>
-      <c r="C11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
-        <v>35</v>
-      </c>
-      <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GURUZETA")</f>
-        <v>GURUZETA</v>
-      </c>
-      <c r="C12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
-        <v>36</v>
-      </c>
-      <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
-        <v>NICO WILLIAMS</v>
-      </c>
-      <c r="C13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
-        <v>37</v>
-      </c>
-      <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C14" s="20" t="str">
+    <row r="86">
+      <c r="A86" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),390.0)</f>
+        <v>390</v>
+      </c>
+      <c r="B86" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LE NORMAND")</f>
+        <v>LE NORMAND</v>
+      </c>
+      <c r="C86" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
         <v>ATLÉTICO DE MADRID</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
-        <v>38</v>
-      </c>
-      <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
-        <v>OBLAK</v>
-      </c>
-      <c r="C15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
-        <v>48</v>
-      </c>
-      <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX BAENA")</f>
-        <v>ALEX BAENA</v>
-      </c>
-      <c r="C16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
-        <v>50</v>
-      </c>
-      <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO GONZÁLEZ")</f>
-        <v>NICO GONZÁLEZ</v>
-      </c>
-      <c r="C17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.0)</f>
-        <v>51</v>
-      </c>
-      <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIULIANO")</f>
-        <v>GIULIANO</v>
-      </c>
-      <c r="C18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.0)</f>
-        <v>54</v>
-      </c>
-      <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
-        <v>GRIEZMANN</v>
-      </c>
-      <c r="C19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
-        <v>57</v>
-      </c>
-      <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SZCZESNY")</f>
-        <v>SZCZESNY</v>
-      </c>
-      <c r="C20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
-        <v>58</v>
-      </c>
-      <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
-        <v>KOUNDÉ</v>
-      </c>
-      <c r="C21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.0)</f>
-        <v>60</v>
-      </c>
-      <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ERIC GARCÍA")</f>
-        <v>ERIC GARCÍA</v>
-      </c>
-      <c r="C22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68.0)</f>
-        <v>68</v>
-      </c>
-      <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
-        <v>RAPHINHA</v>
-      </c>
-      <c r="C23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
-        <v>69</v>
-      </c>
-      <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
-        <v>LAMINE YAMAL</v>
-      </c>
-      <c r="C24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
-        <v>70</v>
-      </c>
-      <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERRAN TORRES")</f>
-        <v>FERRAN TORRES</v>
-      </c>
-      <c r="C25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.0)</f>
-        <v>80</v>
-      </c>
-      <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
-      </c>
-      <c r="C26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.0)</f>
-        <v>82</v>
-      </c>
-      <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALTIMIRA")</f>
-        <v>ALTIMIRA</v>
-      </c>
-      <c r="C27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.0)</f>
-        <v>83</v>
-      </c>
-      <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AMRABAT")</f>
-        <v>AMRABAT</v>
-      </c>
-      <c r="C28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),85.0)</f>
-        <v>85</v>
-      </c>
-      <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LO CELSO")</f>
-        <v>LO CELSO</v>
-      </c>
-      <c r="C29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
-        <v>89</v>
-      </c>
-      <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIQUELME")</f>
-        <v>RIQUELME</v>
-      </c>
-      <c r="C30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.0)</f>
-        <v>90</v>
-      </c>
-      <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABDE")</f>
-        <v>ABDE</v>
-      </c>
-      <c r="C31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.0)</f>
-        <v>92</v>
-      </c>
-      <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RADU")</f>
-        <v>RADU</v>
-      </c>
-      <c r="C32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.0)</f>
-        <v>96</v>
-      </c>
-      <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"STARFELT")</f>
-        <v>STARFELT</v>
-      </c>
-      <c r="C33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
-        <v>98</v>
-      </c>
-      <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MINGUEZA")</f>
-        <v>MINGUEZA</v>
-      </c>
-      <c r="C34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101.0)</f>
-        <v>101</v>
-      </c>
-      <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN BELTRÁN")</f>
-        <v>FRAN BELTRÁN</v>
-      </c>
-      <c r="C35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
-      </c>
-      <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
-      </c>
-      <c r="C36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
-        <v>113</v>
-      </c>
-      <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CHUST")</f>
-        <v>CHUST</v>
-      </c>
-      <c r="C37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
-        <v>114</v>
-      </c>
-      <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIGAS")</f>
-        <v>BIGAS</v>
-      </c>
-      <c r="C38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),118.0)</f>
-        <v>118</v>
-      </c>
-      <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GERMÁN VALERA")</f>
-        <v>GERMÁN VALERA</v>
-      </c>
-      <c r="C39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
-        <v>119</v>
-      </c>
-      <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARTIM NETO")</f>
-        <v>MARTIM NETO</v>
-      </c>
-      <c r="C40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
-        <v>120</v>
-      </c>
-      <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
-        <v>FEBAS</v>
-      </c>
-      <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
-        <v>128</v>
-      </c>
-      <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
-        <v>DMITROVIC</v>
-      </c>
-      <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),132.0)</f>
-        <v>132</v>
-      </c>
-      <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
-        <v>RIEDEL</v>
-      </c>
-      <c r="C43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
-        <v>133</v>
-      </c>
-      <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
-      </c>
-      <c r="C44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),143.0)</f>
-        <v>143</v>
-      </c>
-      <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PUADO")</f>
-        <v>PUADO</v>
-      </c>
-      <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
-      </c>
-      <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
-        <v>148</v>
-      </c>
-      <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IGLESIAS")</f>
-        <v>IGLESIAS</v>
-      </c>
-      <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.0)</f>
-        <v>149</v>
-      </c>
-      <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKO FEMENÍA")</f>
-        <v>KIKO FEMENÍA</v>
-      </c>
-      <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.0)</f>
-        <v>150</v>
-      </c>
-      <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DJENÉ")</f>
-        <v>DJENÉ</v>
-      </c>
-      <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
-        <v>151</v>
-      </c>
-      <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOMINGOS DUARTE")</f>
-        <v>DOMINGOS DUARTE</v>
-      </c>
-      <c r="C50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),155.0)</f>
-        <v>155</v>
-      </c>
-      <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIO MARTÍN")</f>
-        <v>MARIO MARTÍN</v>
-      </c>
-      <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),157.0)</f>
-        <v>157</v>
-      </c>
-      <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
-      </c>
-      <c r="C52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),161.0)</f>
-        <v>161</v>
-      </c>
-      <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
-      </c>
-      <c r="C53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),162.0)</f>
-        <v>162</v>
-      </c>
-      <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COBA")</f>
-        <v>COBA</v>
-      </c>
-      <c r="C54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
-        <v>164</v>
-      </c>
-      <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAZZANIGA")</f>
-        <v>GAZZANIGA</v>
-      </c>
-      <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),167.0)</f>
-        <v>167</v>
-      </c>
-      <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO RINCÓN")</f>
-        <v>HUGO RINCÓN</v>
-      </c>
-      <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
-        <v>168</v>
-      </c>
-      <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VITOR REIS")</f>
-        <v>VITOR REIS</v>
-      </c>
-      <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.0)</f>
-        <v>169</v>
-      </c>
-      <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BLIND")</f>
-        <v>BLIND</v>
-      </c>
-      <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.0)</f>
-        <v>178</v>
-      </c>
-      <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
-        <v>VANAT</v>
-      </c>
-      <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
-        <v>182</v>
-      </c>
-      <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RYAN")</f>
-        <v>RYAN</v>
-      </c>
-      <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
-        <v>183</v>
-      </c>
-      <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO CAMPOS")</f>
-        <v>PABLO CAMPOS</v>
-      </c>
-      <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.0)</f>
-        <v>186</v>
-      </c>
-      <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELGEZABAL")</f>
-        <v>ELGEZABAL</v>
-      </c>
-      <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),191.0)</f>
-        <v>191</v>
-      </c>
-      <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARTÍNEZ")</f>
-        <v>PABLO MARTÍNEZ</v>
-      </c>
-      <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.0)</f>
-        <v>196</v>
-      </c>
-      <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRUGUÉ")</f>
-        <v>BRUGUÉ</v>
-      </c>
-      <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
-        <v>198</v>
-      </c>
-      <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
-        <v>ETTA EYONG</v>
-      </c>
-      <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.0)</f>
-        <v>201</v>
-      </c>
-      <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUNIN")</f>
-        <v>LUNIN</v>
-      </c>
-      <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.0)</f>
-        <v>205</v>
-      </c>
-      <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUIJSEN")</f>
-        <v>HUIJSEN</v>
-      </c>
-      <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
-        <v>214</v>
-      </c>
-      <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
-        <v>MBAPPÉ</v>
-      </c>
-      <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
-        <v>217</v>
-      </c>
-      <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
-        <v>218</v>
-      </c>
-      <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
-        <v>LEO ROMÁN</v>
-      </c>
-      <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
-        <v>224</v>
-      </c>
-      <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
-        <v>KUMBULLA</v>
-      </c>
-      <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.0)</f>
-        <v>229</v>
-      </c>
-      <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORLANES")</f>
-        <v>MORLANES</v>
-      </c>
-      <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.0)</f>
-        <v>231</v>
-      </c>
-      <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ASANO")</f>
-        <v>ASANO</v>
-      </c>
-      <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),232.0)</f>
-        <v>232</v>
-      </c>
-      <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MURIQI")</f>
-        <v>MURIQI</v>
-      </c>
-      <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),233.0)</f>
-        <v>233</v>
-      </c>
-      <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
-        <v>MATEO JOSEPH</v>
-      </c>
-      <c r="C75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.0)</f>
-        <v>239</v>
-      </c>
-      <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYOMO")</f>
-        <v>BOYOMO</v>
-      </c>
-      <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.0)</f>
-        <v>241</v>
-      </c>
-      <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HERRANDO")</f>
-        <v>HERRANDO</v>
-      </c>
-      <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
-        <v>242</v>
-      </c>
-      <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
-        <v>JUAN CRUZ</v>
-      </c>
-      <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
-        <v>253</v>
-      </c>
-      <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),254.0)</f>
-        <v>254</v>
-      </c>
-      <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AARON ESCANDELL")</f>
-        <v>AARON ESCANDELL</v>
-      </c>
-      <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
-        <v>260</v>
-      </c>
-      <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
-        <v>RAHIM ALHASSANE</v>
-      </c>
-      <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
-        <v>261</v>
-      </c>
-      <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLOMBATTO")</f>
-        <v>COLOMBATTO</v>
-      </c>
-      <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),263.0)</f>
-        <v>263</v>
-      </c>
-      <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DENDONCKER")</f>
-        <v>DENDONCKER</v>
-      </c>
-      <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),266.0)</f>
-        <v>266</v>
-      </c>
-      <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
-        <v>HASSAN</v>
-      </c>
-      <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),268.0)</f>
-        <v>268</v>
-      </c>
-      <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILYAS CHAIRA")</f>
-        <v>ILYAS CHAIRA</v>
-      </c>
-      <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),271.0)</f>
-        <v>271</v>
-      </c>
-      <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.0)</f>
-        <v>273</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),394.0)</f>
+        <v>394</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CÁRDENAS")</f>
-        <v>CÁRDENAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
+        <v>LEJEUNE</v>
       </c>
       <c r="C87" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -4284,180 +4306,180 @@
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),276.0)</f>
-        <v>276</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),397.0)</f>
+        <v>397</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
-        <v>LEJEUNE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REGO")</f>
+        <v>REGO</v>
       </c>
       <c r="C88" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
+        <v>401</v>
+      </c>
+      <c r="B89" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
+        <v>RODRI MENDOZA</v>
+      </c>
+      <c r="C89" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),410.0)</f>
+        <v>410</v>
+      </c>
+      <c r="B90" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
+        <v>GONZALO</v>
+      </c>
+      <c r="C90" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),412.0)</f>
+        <v>412</v>
+      </c>
+      <c r="B91" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
+        <v>MATEO JOSEPH</v>
+      </c>
+      <c r="C91" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),417.0)</f>
+        <v>417</v>
+      </c>
+      <c r="B92" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
+        <v>FEBAS</v>
+      </c>
+      <c r="C92" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),418.0)</f>
+        <v>418</v>
+      </c>
+      <c r="B93" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
+      </c>
+      <c r="C93" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),420.0)</f>
+        <v>420</v>
+      </c>
+      <c r="B94" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
+        <v>DARDER</v>
+      </c>
+      <c r="C94" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),423.0)</f>
+        <v>423</v>
+      </c>
+      <c r="B95" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LÓPEZ")</f>
+        <v>UNAI LÓPEZ</v>
+      </c>
+      <c r="C95" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
         <v>RAYO VALLECANO</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),279.0)</f>
-        <v>279</v>
-      </c>
-      <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PATHÉ CISS")</f>
-        <v>PATHÉ CISS</v>
-      </c>
-      <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),280.0)</f>
-        <v>280</v>
-      </c>
-      <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LOPEZ")</f>
-        <v>UNAI LOPEZ</v>
-      </c>
-      <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),285.0)</f>
-        <v>285</v>
-      </c>
-      <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN PÉREZ")</f>
-        <v>FRAN PÉREZ</v>
-      </c>
-      <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
-        <v>289</v>
-      </c>
-      <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),294.0)</f>
-        <v>294</v>
-      </c>
-      <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZUBELDIA")</f>
-        <v>ZUBELDIA</v>
-      </c>
-      <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),297.0)</f>
-        <v>297</v>
-      </c>
-      <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
-        <v>GORROTXATEGI</v>
-      </c>
-      <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.0)</f>
-        <v>300</v>
-      </c>
-      <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
-        <v>CARLOS SOLER</v>
-      </c>
-      <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),301.0)</f>
-        <v>301</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),424.0)</f>
+        <v>424</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRAIS MÉNDEZ")</f>
-        <v>BRAIS MÉNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
+        <v>TENAGLIA</v>
       </c>
       <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),305.0)</f>
-        <v>305</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),428.0)</f>
+        <v>428</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSKARSSON")</f>
-        <v>ÓSKARSSON</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),310.0)</f>
-        <v>310</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),430.0)</f>
+        <v>430</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARMONA")</f>
-        <v>CARMONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
+        <v>VANAT</v>
       </c>
       <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),314.0)</f>
-        <v>314</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),433.0)</f>
+        <v>433</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCAO")</f>
-        <v>MARCAO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
+        <v>LEO ROMÁN</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),320.0)</f>
-        <v>320</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),438.0)</f>
+        <v>438</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
-        <v>VARGAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATISTA MENDY")</f>
+        <v>BATISTA MENDY</v>
       </c>
       <c r="C100" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
@@ -4466,756 +4488,224 @@
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),324.0)</f>
-        <v>324</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),441.0)</f>
+        <v>441</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUCHANAN")</f>
+        <v>BUCHANAN</v>
       </c>
       <c r="C101" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),442.0)</f>
+        <v>442</v>
+      </c>
+      <c r="B102" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
+        <v>UNAI SIMÓN</v>
+      </c>
+      <c r="C102" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),443.0)</f>
+        <v>443</v>
+      </c>
+      <c r="B103" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAUREGIZAR")</f>
+        <v>JAUREGIZAR</v>
+      </c>
+      <c r="C103" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446.0)</f>
+        <v>446</v>
+      </c>
+      <c r="B104" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLEX BAENA")</f>
+        <v>ÁLEX BAENA</v>
+      </c>
+      <c r="C104" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),451.0)</f>
+        <v>451</v>
+      </c>
+      <c r="B105" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
+        <v>RAPHINHA</v>
+      </c>
+      <c r="C105" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),453.0)</f>
+        <v>453</v>
+      </c>
+      <c r="B106" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RASHFORD")</f>
+        <v>RASHFORD</v>
+      </c>
+      <c r="C106" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),460.0)</f>
+        <v>460</v>
+      </c>
+      <c r="B107" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
+      </c>
+      <c r="C107" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),464.0)</f>
+        <v>464</v>
+      </c>
+      <c r="B108" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
+        <v>VARGAS</v>
+      </c>
+      <c r="C108" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),339.0)</f>
-        <v>339</v>
-      </c>
-      <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO LÓPEZ")</f>
-        <v>DIEGO LÓPEZ</v>
-      </c>
-      <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
-        <v>348</v>
-      </c>
-      <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MARÍN")</f>
-        <v>RAFA MARÍN</v>
-      </c>
-      <c r="C103" s="20" t="str">
+    <row r="109">
+      <c r="A109" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),466.0)</f>
+        <v>466</v>
+      </c>
+      <c r="B109" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
+        <v>MOLEIRO</v>
+      </c>
+      <c r="C109" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),349.0)</f>
-        <v>349</v>
-      </c>
-      <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RENATO VEIGA")</f>
-        <v>RENATO VEIGA</v>
-      </c>
-      <c r="C104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),360.0)</f>
-        <v>360</v>
-      </c>
-      <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AYOZE")</f>
-        <v>AYOZE</v>
-      </c>
-      <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),364.0)</f>
-        <v>364</v>
-      </c>
-      <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-      <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),365.0)</f>
-        <v>365</v>
-      </c>
-      <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-      <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
-        <v>366</v>
-      </c>
-      <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-      <c r="C108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),373.0)</f>
-        <v>373</v>
-      </c>
-      <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-      <c r="C109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
     <row r="110">
       <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
-        <v>375</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),468.0)</f>
+        <v>468</v>
       </c>
       <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD CHAMPIONS")</f>
+        <v>CARD CHAMPIONS</v>
       </c>
       <c r="C110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),377.0)</f>
-        <v>377</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.0)</f>
+        <v>470</v>
       </c>
       <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ÁLVAREZ")</f>
+        <v>JULIÁN ÁLVAREZ</v>
       </c>
       <c r="C111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATLÉTICO)")</f>
+        <v>BALÓN DE ORO (ATLÉTICO)</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),378.0)</f>
-        <v>378</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),471.0)</f>
+        <v>471</v>
       </c>
       <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRI")</f>
+        <v>PEDRI</v>
       </c>
       <c r="C112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
+        <v>BALÓN DE ORO (BARÇA)</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),380.0)</f>
-        <v>380</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),472.0)</f>
+        <v>472</v>
       </c>
       <c r="B113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
+        <v>LAMINE YAMAL</v>
       </c>
       <c r="C113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
+        <v>BALÓN DE ORO (BARÇA)</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
-        <v>383</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),475.0)</f>
+        <v>475</v>
       </c>
       <c r="B114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO EXCELLENCE")</f>
+        <v>BALÓN DE ORO EXCELLENCE</v>
       </c>
       <c r="C114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),384.0)</f>
-        <v>384</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.0)</f>
+        <v>476</v>
       </c>
       <c r="B115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD ATÓMICA")</f>
+        <v>CARD ATÓMICA</v>
       </c>
       <c r="C115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
+        <v>ÚNICA</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.0)</f>
-        <v>385</v>
-      </c>
-      <c r="B116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATALLA")</f>
-        <v>BATALLA</v>
-      </c>
-      <c r="C116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.0)</f>
-        <v>386</v>
-      </c>
-      <c r="B117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
-      </c>
-      <c r="C117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.0)</f>
-        <v>388</v>
-      </c>
-      <c r="B118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
-        <v>LAPORTE</v>
-      </c>
-      <c r="C118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),390.0)</f>
-        <v>390</v>
-      </c>
-      <c r="B119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LE NORMAND")</f>
-        <v>LE NORMAND</v>
-      </c>
-      <c r="C119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),394.0)</f>
-        <v>394</v>
-      </c>
-      <c r="B120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
-        <v>LEJEUNE</v>
-      </c>
-      <c r="C120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),397.0)</f>
-        <v>397</v>
-      </c>
-      <c r="B121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REGO")</f>
-        <v>REGO</v>
-      </c>
-      <c r="C121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
-        <v>401</v>
-      </c>
-      <c r="B122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
-        <v>RODRI MENDOZA</v>
-      </c>
-      <c r="C122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),410.0)</f>
-        <v>410</v>
-      </c>
-      <c r="B123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
-        <v>GONZALO</v>
-      </c>
-      <c r="C123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),412.0)</f>
-        <v>412</v>
-      </c>
-      <c r="B124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
-        <v>MATEO JOSEPH</v>
-      </c>
-      <c r="C124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),417.0)</f>
-        <v>417</v>
-      </c>
-      <c r="B125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
-        <v>FEBAS</v>
-      </c>
-      <c r="C125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),418.0)</f>
-        <v>418</v>
-      </c>
-      <c r="B126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
-      </c>
-      <c r="C126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),420.0)</f>
-        <v>420</v>
-      </c>
-      <c r="B127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
-        <v>DARDER</v>
-      </c>
-      <c r="C127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),423.0)</f>
-        <v>423</v>
-      </c>
-      <c r="B128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LÓPEZ")</f>
-        <v>UNAI LÓPEZ</v>
-      </c>
-      <c r="C128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),424.0)</f>
-        <v>424</v>
-      </c>
-      <c r="B129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
-        <v>TENAGLIA</v>
-      </c>
-      <c r="C129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),428.0)</f>
-        <v>428</v>
-      </c>
-      <c r="B130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
-      </c>
-      <c r="C130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),430.0)</f>
-        <v>430</v>
-      </c>
-      <c r="B131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
-        <v>VANAT</v>
-      </c>
-      <c r="C131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),433.0)</f>
-        <v>433</v>
-      </c>
-      <c r="B132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
-        <v>LEO ROMÁN</v>
-      </c>
-      <c r="C132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),435.0)</f>
-        <v>435</v>
-      </c>
-      <c r="B133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HASSAN")</f>
-        <v>HASSAN</v>
-      </c>
-      <c r="C133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),437.0)</f>
-        <v>437</v>
-      </c>
-      <c r="B134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
-        <v>GORROTXATEGI</v>
-      </c>
-      <c r="C134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),438.0)</f>
-        <v>438</v>
-      </c>
-      <c r="B135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATISTA MENDY")</f>
-        <v>BATISTA MENDY</v>
-      </c>
-      <c r="C135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),441.0)</f>
-        <v>441</v>
-      </c>
-      <c r="B136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUCHANAN")</f>
-        <v>BUCHANAN</v>
-      </c>
-      <c r="C136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),442.0)</f>
-        <v>442</v>
-      </c>
-      <c r="B137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
-        <v>UNAI SIMÓN</v>
-      </c>
-      <c r="C137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),443.0)</f>
-        <v>443</v>
-      </c>
-      <c r="B138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAUREGIZAR")</f>
-        <v>JAUREGIZAR</v>
-      </c>
-      <c r="C138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),445.0)</f>
-        <v>445</v>
-      </c>
-      <c r="B139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
-        <v>MARCOS LLORENTE</v>
-      </c>
-      <c r="C139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446.0)</f>
-        <v>446</v>
-      </c>
-      <c r="B140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLEX BAENA")</f>
-        <v>ÁLEX BAENA</v>
-      </c>
-      <c r="C140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),451.0)</f>
-        <v>451</v>
-      </c>
-      <c r="B141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
-        <v>RAPHINHA</v>
-      </c>
-      <c r="C141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),453.0)</f>
-        <v>453</v>
-      </c>
-      <c r="B142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RASHFORD")</f>
-        <v>RASHFORD</v>
-      </c>
-      <c r="C142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
-        <v>454</v>
-      </c>
-      <c r="B143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
-        <v>ISCO</v>
-      </c>
-      <c r="C143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),460.0)</f>
-        <v>460</v>
-      </c>
-      <c r="B144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
-      </c>
-      <c r="C144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),464.0)</f>
-        <v>464</v>
-      </c>
-      <c r="B145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
-        <v>VARGAS</v>
-      </c>
-      <c r="C145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),466.0)</f>
-        <v>466</v>
-      </c>
-      <c r="B146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
-        <v>MOLEIRO</v>
-      </c>
-      <c r="C146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),468.0)</f>
-        <v>468</v>
-      </c>
-      <c r="B147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD CHAMPIONS")</f>
-        <v>CARD CHAMPIONS</v>
-      </c>
-      <c r="C147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.0)</f>
-        <v>470</v>
-      </c>
-      <c r="B148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ÁLVAREZ")</f>
-        <v>JULIÁN ÁLVAREZ</v>
-      </c>
-      <c r="C148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATLÉTICO)")</f>
-        <v>BALÓN DE ORO (ATLÉTICO)</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),471.0)</f>
-        <v>471</v>
-      </c>
-      <c r="B149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRI")</f>
-        <v>PEDRI</v>
-      </c>
-      <c r="C149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
-        <v>BALÓN DE ORO (BARÇA)</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),472.0)</f>
-        <v>472</v>
-      </c>
-      <c r="B150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
-        <v>LAMINE YAMAL</v>
-      </c>
-      <c r="C150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
-        <v>BALÓN DE ORO (BARÇA)</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),473.0)</f>
-        <v>473</v>
-      </c>
-      <c r="B151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
-      </c>
-      <c r="C151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (REAL MADRID)")</f>
-        <v>BALÓN DE ORO (REAL MADRID)</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),475.0)</f>
-        <v>475</v>
-      </c>
-      <c r="B152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO EXCELLENCE")</f>
-        <v>BALÓN DE ORO EXCELLENCE</v>
-      </c>
-      <c r="C152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.0)</f>
-        <v>476</v>
-      </c>
-      <c r="B153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD ATÓMICA")</f>
-        <v>CARD ATÓMICA</v>
-      </c>
-      <c r="C153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
         <v>91</v>
       </c>
-      <c r="B154" s="20" t="str">
+      <c r="B116" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
         <v>ESTADIO</v>
       </c>
-      <c r="C154" s="20" t="str">
+      <c r="C116" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
@@ -5262,18 +4752,18 @@
         <v>D. ALAVÉS</v>
       </c>
       <c r="D1" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="B2" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JONNY")</f>
-        <v>JONNY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C2" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -5286,12 +4776,12 @@
     </row>
     <row r="3">
       <c r="A3" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
-        <v>15</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="B3" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
-        <v>CARLOS VICENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL FERNÁNDEZ")</f>
+        <v>RAÚL FERNÁNDEZ</v>
       </c>
       <c r="C3" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -5304,12 +4794,12 @@
     </row>
     <row r="4">
       <c r="A4" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
-        <v>17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="B4" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYÉ")</f>
-        <v>BOYÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JONNY")</f>
+        <v>JONNY</v>
       </c>
       <c r="C4" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -5322,12 +4812,12 @@
     </row>
     <row r="5">
       <c r="A5" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="B5" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIANO")</f>
-        <v>MARIANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
+        <v>TENAGLIA</v>
       </c>
       <c r="C5" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -5340,16 +4830,16 @@
     </row>
     <row r="6">
       <c r="A6" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
+        <v>7</v>
       </c>
       <c r="B6" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PARADA")</f>
+        <v>PARADA</v>
       </c>
       <c r="C6" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D6" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5358,34 +4848,34 @@
     </row>
     <row r="7">
       <c r="A7" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
-        <v>27</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
+        <v>15</v>
       </c>
       <c r="B7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUIZ DE GALARRETA")</f>
-        <v>RUIZ DE GALARRETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
+        <v>CARLOS VICENTE</v>
       </c>
       <c r="C7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D7" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
-        <v>34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="B8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
-        <v>MAROAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYÉ")</f>
+        <v>BOYÉ</v>
       </c>
       <c r="C8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D8" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5394,16 +4884,16 @@
     </row>
     <row r="9">
       <c r="A9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
-        <v>40</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
+        <v>18</v>
       </c>
       <c r="B9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
-        <v>MARCOS LLORENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIANO")</f>
+        <v>MARIANO</v>
       </c>
       <c r="C9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D9" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5412,34 +4902,34 @@
     </row>
     <row r="10">
       <c r="A10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="B10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
-        <v>LENGLET</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
+        <v>21</v>
       </c>
       <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
-        <v>ALMADA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PADILLA")</f>
+        <v>PADILLA</v>
       </c>
       <c r="C11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D11" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5448,16 +4938,16 @@
     </row>
     <row r="12">
       <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
-        <v>67</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
+        <v>23</v>
       </c>
       <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
-        <v>DANI OLMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VIVIAN")</f>
+        <v>VIVIAN</v>
       </c>
       <c r="C12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D12" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5466,16 +4956,16 @@
     </row>
     <row r="13">
       <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
-        <v>73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUIZ DE GALARRETA")</f>
+        <v>RUIZ DE GALARRETA</v>
       </c>
       <c r="C13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D13" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5484,34 +4974,34 @@
     </row>
     <row r="14">
       <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
+        <v>34</v>
       </c>
       <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
-        <v>PAU LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
+        <v>MAROAN</v>
       </c>
       <c r="C14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
-        <v>76</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
+        <v>40</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
-        <v>BELLERÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
+        <v>MARCOS LLORENTE</v>
       </c>
       <c r="C15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D15" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5520,34 +5010,34 @@
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
+        <v>LENGLET</v>
       </c>
       <c r="C16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
+        <v>ALMADA</v>
       </c>
       <c r="C17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D17" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5556,16 +5046,16 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
-        <v>93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
+        <v>52</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
-        <v>IVÁN VILLAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
+        <v>JULIÁN ALVAREZ</v>
       </c>
       <c r="C18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D18" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5574,16 +5064,16 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
+        <v>55</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D19" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5592,16 +5082,16 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOAN GARCÍA")</f>
+        <v>JOAN GARCÍA</v>
       </c>
       <c r="C20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D20" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5610,16 +5100,16 @@
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
+        <v>FERMÍN</v>
       </c>
       <c r="C21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D21" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5628,16 +5118,16 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
+        <v>DANI OLMO</v>
       </c>
       <c r="C22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D22" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5646,16 +5136,16 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
-        <v>106</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
-        <v>IAGO ASPAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D23" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5664,16 +5154,16 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
+        <v>PAU LÓPEZ</v>
       </c>
       <c r="C24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D24" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5682,16 +5172,16 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
+        <v>BELLERÍN</v>
       </c>
       <c r="C25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D25" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5700,16 +5190,16 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
-        <v>IÑAKI PEÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D26" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5718,16 +5208,16 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
+        <v>84</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
+        <v>PABLO FORNALS</v>
       </c>
       <c r="C27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D27" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5736,16 +5226,16 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
-        <v>112</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
-        <v>ÁLVARO NÚÑEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
       </c>
       <c r="C28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D28" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5754,16 +5244,16 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
+        <v>91</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D29" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5772,16 +5262,16 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
-        <v>117</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
+        <v>93</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
-        <v>FEDE REDONDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
+        <v>IVÁN VILLAR</v>
       </c>
       <c r="C30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D30" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5790,16 +5280,16 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
+        <v>94</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
+        <v>JAVI RUEDA</v>
       </c>
       <c r="C31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D31" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5808,16 +5298,16 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D32" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5826,16 +5316,16 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D33" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5844,34 +5334,34 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
+        <v>104</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
+        <v>SWEDBERG</v>
       </c>
       <c r="C35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D35" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5880,16 +5370,16 @@
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D36" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5898,16 +5388,16 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
+        <v>IAGO ASPAS</v>
       </c>
       <c r="C37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D37" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5916,16 +5406,16 @@
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D38" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5934,16 +5424,16 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
-        <v>153</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
-        <v>DIEGO RICO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
       </c>
       <c r="C39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D39" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5952,16 +5442,16 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
+        <v>IÑAKI PEÑA</v>
       </c>
       <c r="C40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D40" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5970,16 +5460,16 @@
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D41" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5988,16 +5478,16 @@
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
-        <v>174</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
-        <v>IVÁN MARTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
+        <v>ÁLVARO NÚÑEZ</v>
       </c>
       <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D42" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6006,34 +5496,34 @@
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
-        <v>176</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
+        <v>117</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
-        <v>JOEL ROCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
+        <v>FEDE REDONDO</v>
       </c>
       <c r="C44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D44" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6042,16 +5532,16 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.0)</f>
-        <v>177</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TSYGANKOV")</f>
-        <v>TSYGANKOV</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D45" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6060,52 +5550,52 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
-        <v>202</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
+        <v>127</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
-        <v>CARVAJAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
-        <v>211</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
-        <v>GÜLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D48" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6114,16 +5604,16 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
-        <v>213</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
-        <v>RODRYGO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D49" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6132,34 +5622,34 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
       </c>
       <c r="C50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D51" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6168,16 +5658,16 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
-        <v>225</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
-        <v>MOJICA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D52" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6186,16 +5676,16 @@
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D53" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6204,16 +5694,16 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
+        <v>153</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
+        <v>DIEGO RICO</v>
       </c>
       <c r="C54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D54" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6222,16 +5712,16 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D55" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6240,34 +5730,34 @@
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
-        <v>237</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
-        <v>AITOR FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),247.0)</f>
-        <v>247</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
+        <v>174</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUBÉN GARCÍA")</f>
-        <v>RUBÉN GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
+        <v>IVÁN MARTÍN</v>
       </c>
       <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D57" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6276,34 +5766,34 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
-        <v>248</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
       </c>
       <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
+        <v>176</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
+        <v>JOEL ROCA</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D59" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6312,16 +5802,16 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),255.0)</f>
-        <v>255</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.0)</f>
+        <v>177</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLDOVAN")</f>
-        <v>MOLDOVAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TSYGANKOV")</f>
+        <v>TSYGANKOV</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D60" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6330,16 +5820,16 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),181.0)</f>
+        <v>181</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D61" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6348,16 +5838,16 @@
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),184.0)</f>
+        <v>184</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TOLJAN")</f>
+        <v>TOLJAN</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D62" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6366,16 +5856,16 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),185.0)</f>
+        <v>185</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DELA")</f>
+        <v>DELA</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D63" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6384,16 +5874,16 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.0)</f>
-        <v>267</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.0)</f>
+        <v>186</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BREKALO")</f>
-        <v>BREKALO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELGEZABAL")</f>
+        <v>ELGEZABAL</v>
       </c>
       <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D64" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6402,16 +5892,16 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
+        <v>189</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
+        <v>PAMPÍN</v>
       </c>
       <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D65" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6420,16 +5910,16 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
-        <v>277</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
+        <v>202</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
-        <v>LUIZ FELIPE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
+        <v>CARVAJAL</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D66" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6438,34 +5928,34 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),208.0)</f>
+        <v>208</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TCHOUAMÉNI")</f>
+        <v>TCHOUAMÉNI</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
-        <v>283</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
-        <v>PEDRO DÍAZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D68" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6474,16 +5964,16 @@
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
-        <v>286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
-        <v>CAMELLO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
       </c>
       <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D69" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6492,16 +5982,16 @@
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
-        <v>290</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
+        <v>212</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6510,16 +6000,16 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
+        <v>213</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
+        <v>RODRYGO</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D71" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6528,16 +6018,16 @@
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
-        <v>296</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
+        <v>214</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
-        <v>SERGIO GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
+        <v>MBAPPÉ</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D72" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6546,16 +6036,16 @@
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D73" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6564,16 +6054,16 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
+        <v>219</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
+        <v>BERGSTRÖM</v>
       </c>
       <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D74" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6582,16 +6072,16 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
-        <v>312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
-        <v>AZPILICUETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
       </c>
       <c r="C75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D75" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6600,16 +6090,16 @@
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
+        <v>225</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
+        <v>MOJICA</v>
       </c>
       <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D76" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6618,52 +6108,52 @@
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),226.0)</f>
+        <v>226</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SAMÚ COSTA")</f>
+        <v>SAMÚ COSTA</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.0)</f>
+        <v>229</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORLANES")</f>
+        <v>MORLANES</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D79" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6672,34 +6162,34 @@
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
-        <v>327</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
-        <v>DIMITRIEVSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D81" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6708,16 +6198,16 @@
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
+        <v>237</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
+        <v>AITOR FERNÁNDEZ</v>
       </c>
       <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D82" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6726,16 +6216,16 @@
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
-        <v>331</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
+        <v>242</v>
       </c>
       <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
-        <v>COPETE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
+        <v>JUAN CRUZ</v>
       </c>
       <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D83" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6744,16 +6234,16 @@
     </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
+        <v>245</v>
       </c>
       <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
+        <v>MONCAYOLA</v>
       </c>
       <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D84" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6762,34 +6252,34 @@
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),247.0)</f>
+        <v>247</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUBÉN GARCÍA")</f>
+        <v>RUBÉN GARCÍA</v>
       </c>
       <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
+        <v>248</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
       </c>
       <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D86" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6798,16 +6288,16 @@
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D87" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6816,16 +6306,16 @@
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
-        <v>350</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
+        <v>253</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
-        <v>SERGI CARDONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D88" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6834,16 +6324,16 @@
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),255.0)</f>
+        <v>255</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLDOVAN")</f>
+        <v>MOLDOVAN</v>
       </c>
       <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D89" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6852,16 +6342,16 @@
     </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D90" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6870,16 +6360,16 @@
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D91" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6888,16 +6378,16 @@
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D92" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6906,16 +6396,16 @@
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
-        <v>371</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
+        <v>265</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
+        <v>ILIC</v>
       </c>
       <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D93" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6924,34 +6414,34 @@
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.0)</f>
+        <v>267</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BREKALO")</f>
+        <v>BREKALO</v>
       </c>
       <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D95" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6960,16 +6450,16 @@
     </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),275.0)</f>
+        <v>275</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALLIU")</f>
+        <v>BALLIU</v>
       </c>
       <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D96" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6978,16 +6468,16 @@
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),400.0)</f>
-        <v>400</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
+        <v>277</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO GARCÍA")</f>
-        <v>PABLO GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
+        <v>LUIZ FELIPE</v>
       </c>
       <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D97" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6996,16 +6486,16 @@
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
-        <v>404</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
       </c>
       <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D98" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7014,16 +6504,16 @@
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
-        <v>409</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
+        <v>281</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
-        <v>FRAN GONZÁLEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
+        <v>ÓSCAR VALENTÍN</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D99" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7032,16 +6522,16 @@
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
       </c>
       <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D100" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7050,34 +6540,34 @@
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),284.0)</f>
+        <v>284</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO GARCÍA")</f>
+        <v>ÁLVARO GARCÍA</v>
       </c>
       <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
+        <v>286</v>
       </c>
       <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
+        <v>CAMELLO</v>
       </c>
       <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D102" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7086,16 +6576,16 @@
     </row>
     <row r="103">
       <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
+        <v>289</v>
       </c>
       <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D103" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7104,16 +6594,16 @@
     </row>
     <row r="104">
       <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
+        <v>290</v>
       </c>
       <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
       </c>
       <c r="C104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D104" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7122,16 +6612,16 @@
     </row>
     <row r="105">
       <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
-        <v>425</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
+        <v>292</v>
       </c>
       <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
-        <v>CARLOS VICENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
+        <v>ARAMBURU</v>
       </c>
       <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D105" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7140,12 +6630,12 @@
     </row>
     <row r="106">
       <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
-        <v>436</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),293.0)</f>
+        <v>293</v>
       </c>
       <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
-        <v>CARLOS SOLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARITZ ELUSTONDO")</f>
+        <v>ARITZ ELUSTONDO</v>
       </c>
       <c r="C106" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -7158,16 +6648,16 @@
     </row>
     <row r="107">
       <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
       </c>
       <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
       </c>
       <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D107" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7176,16 +6666,16 @@
     </row>
     <row r="108">
       <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
-        <v>444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
+        <v>296</v>
       </c>
       <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
-        <v>OBLAK</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
+        <v>SERGIO GÓMEZ</v>
       </c>
       <c r="C108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D108" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7194,16 +6684,16 @@
     </row>
     <row r="109">
       <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),449.0)</f>
-        <v>449</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
-        <v>KOUNDÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D109" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7212,16 +6702,16 @@
     </row>
     <row r="110">
       <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
-        <v>452</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
-        <v>LEWANDOWSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D110" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7230,16 +6720,16 @@
     </row>
     <row r="111">
       <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
-        <v>456</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
+        <v>312</v>
       </c>
       <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
-        <v>ANTONY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
+        <v>AZPILICUETA</v>
       </c>
       <c r="C111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D111" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7248,16 +6738,16 @@
     </row>
     <row r="112">
       <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
-        <v>458</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
       </c>
       <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
-        <v>CARRERAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
       </c>
       <c r="C112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D112" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -7266,36 +6756,990 @@
     </row>
     <row r="113">
       <c r="A113" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),316.0)</f>
+        <v>316</v>
+      </c>
+      <c r="B113" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GUDELJ")</f>
+        <v>GUDELJ</v>
+      </c>
+      <c r="C113" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D113" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
+        <v>317</v>
+      </c>
+      <c r="B114" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
+        <v>AGOUME</v>
+      </c>
+      <c r="C114" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D114" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
+      </c>
+      <c r="B115" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
+      </c>
+      <c r="C115" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D115" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
+      </c>
+      <c r="B116" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
+      </c>
+      <c r="C116" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D116" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
+      </c>
+      <c r="B117" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C117" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D117" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
+        <v>326</v>
+      </c>
+      <c r="B118" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
+      </c>
+      <c r="C118" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D118" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
+      </c>
+      <c r="B119" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
+      </c>
+      <c r="C119" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D119" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
+      </c>
+      <c r="B120" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
+      </c>
+      <c r="C120" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D120" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
+      </c>
+      <c r="B121" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
+      </c>
+      <c r="C121" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D121" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
+        <v>331</v>
+      </c>
+      <c r="B122" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
+        <v>COPETE</v>
+      </c>
+      <c r="C122" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D122" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
+      </c>
+      <c r="B123" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
+      </c>
+      <c r="C123" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D123" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),335.0)</f>
+        <v>335</v>
+      </c>
+      <c r="B124" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTAMARÍA")</f>
+        <v>SANTAMARÍA</v>
+      </c>
+      <c r="C124" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D124" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
+        <v>337</v>
+      </c>
+      <c r="B125" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
+        <v>ANDRÉ ALMEIDA</v>
+      </c>
+      <c r="C125" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D125" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
+      </c>
+      <c r="B126" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
+      </c>
+      <c r="C126" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D126" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),341.0)</f>
+        <v>341</v>
+      </c>
+      <c r="B127" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANJUMA")</f>
+        <v>DANJUMA</v>
+      </c>
+      <c r="C127" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D127" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
+      </c>
+      <c r="B128" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C128" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D128" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
+      </c>
+      <c r="B129" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
+      </c>
+      <c r="C129" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D129" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),347.0)</f>
+        <v>347</v>
+      </c>
+      <c r="B130" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOYTH")</f>
+        <v>FOYTH</v>
+      </c>
+      <c r="C130" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D130" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
+        <v>350</v>
+      </c>
+      <c r="B131" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
+        <v>SERGI CARDONA</v>
+      </c>
+      <c r="C131" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D131" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
+      </c>
+      <c r="B132" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
+      </c>
+      <c r="C132" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D132" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
+      </c>
+      <c r="B133" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
+      </c>
+      <c r="C133" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D133" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),354.0)</f>
+        <v>354</v>
+      </c>
+      <c r="B134" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"THOMAS")</f>
+        <v>THOMAS</v>
+      </c>
+      <c r="C134" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D134" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
+        <v>355</v>
+      </c>
+      <c r="B135" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
+        <v>MOLEIRO</v>
+      </c>
+      <c r="C135" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D135" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
+      </c>
+      <c r="B136" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
+      </c>
+      <c r="C136" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+      <c r="D136" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
+      </c>
+      <c r="B137" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="C137" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+      <c r="D137" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
+        <v>371</v>
+      </c>
+      <c r="B138" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+      <c r="C138" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
+      </c>
+      <c r="D138" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),381.0)</f>
+        <v>381</v>
+      </c>
+      <c r="B139" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SIVERA")</f>
+        <v>SIVERA</v>
+      </c>
+      <c r="C139" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
+      </c>
+      <c r="D139" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
+      </c>
+      <c r="B140" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
+      </c>
+      <c r="C140" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D140" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),391.0)</f>
+        <v>391</v>
+      </c>
+      <c r="B141" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
+      </c>
+      <c r="C141" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
+      </c>
+      <c r="D141" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
+      </c>
+      <c r="B142" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
+      </c>
+      <c r="C142" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+      <c r="D142" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
+      </c>
+      <c r="B143" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
+      </c>
+      <c r="C143" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D143" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
+        <v>399</v>
+      </c>
+      <c r="B144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
+      </c>
+      <c r="C144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D144" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),400.0)</f>
+        <v>400</v>
+      </c>
+      <c r="B145" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO GARCÍA")</f>
+        <v>PABLO GARCÍA</v>
+      </c>
+      <c r="C145" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D145" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
+      </c>
+      <c r="B146" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
+      </c>
+      <c r="C146" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D146" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
+        <v>407</v>
+      </c>
+      <c r="B147" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
+        <v>CARLOS ÁLVAREZ</v>
+      </c>
+      <c r="C147" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+      <c r="D147" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
+        <v>409</v>
+      </c>
+      <c r="B148" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
+        <v>FRAN GONZÁLEZ</v>
+      </c>
+      <c r="C148" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D148" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
+      </c>
+      <c r="B149" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
+      </c>
+      <c r="C149" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D149" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
+      </c>
+      <c r="B150" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
+      </c>
+      <c r="C150" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D150" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
+      </c>
+      <c r="B151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
+      </c>
+      <c r="C151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D151" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
+      </c>
+      <c r="B152" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
+      </c>
+      <c r="C152" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D152" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
+        <v>421</v>
+      </c>
+      <c r="B153" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
+      </c>
+      <c r="C153" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D153" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
+      </c>
+      <c r="B154" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
+      </c>
+      <c r="C154" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D154" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
+        <v>425</v>
+      </c>
+      <c r="B155" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
+        <v>CARLOS VICENTE</v>
+      </c>
+      <c r="C155" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
+      </c>
+      <c r="D155" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
+        <v>436</v>
+      </c>
+      <c r="B156" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
+        <v>CARLOS SOLER</v>
+      </c>
+      <c r="C156" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+      <c r="D156" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
+      </c>
+      <c r="B157" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
+      </c>
+      <c r="C157" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D157" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
+        <v>444</v>
+      </c>
+      <c r="B158" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
+        <v>OBLAK</v>
+      </c>
+      <c r="C158" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D158" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
+        <v>448</v>
+      </c>
+      <c r="B159" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
+        <v>GRIEZMANN</v>
+      </c>
+      <c r="C159" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D159" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),449.0)</f>
+        <v>449</v>
+      </c>
+      <c r="B160" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
+        <v>KOUNDÉ</v>
+      </c>
+      <c r="C160" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D160" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
+        <v>452</v>
+      </c>
+      <c r="B161" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
+        <v>LEWANDOWSKI</v>
+      </c>
+      <c r="C161" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D161" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
+        <v>456</v>
+      </c>
+      <c r="B162" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
+        <v>ANTONY</v>
+      </c>
+      <c r="C162" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D162" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
+        <v>458</v>
+      </c>
+      <c r="B163" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
+        <v>CARRERAS</v>
+      </c>
+      <c r="C163" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D163" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
+        <v>462</v>
+      </c>
+      <c r="B164" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
+      </c>
+      <c r="C164" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D164" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),467.0)</f>
+        <v>467</v>
+      </c>
+      <c r="B165" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PÉPÉ")</f>
+        <v>PÉPÉ</v>
+      </c>
+      <c r="C165" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D165" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B113" s="20" t="str">
+      <c r="B166" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C113" s="20" t="str">
+      <c r="C166" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D113" s="20">
+      <c r="D166" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="20">
+    <row r="167">
+      <c r="A167" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),477.0)</f>
         <v>477</v>
       </c>
-      <c r="B114" s="20" t="str">
+      <c r="B167" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD INVENCIBLE")</f>
         <v>CARD INVENCIBLE</v>
       </c>
-      <c r="C114" s="20" t="str">
+      <c r="C167" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
         <v>ÚNICA</v>
       </c>
-      <c r="D114" s="20">
+      <c r="D167" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
@@ -7330,7 +7774,7 @@
         <v>20</v>
       </c>
       <c r="E1" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="2">
@@ -7360,6 +7804,9 @@
       <c r="D3" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E3" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="21">
@@ -7388,7 +7835,12 @@
       <c r="C5" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="21"/>
+      <c r="D5" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="21">
@@ -7417,6 +7869,9 @@
       <c r="D7" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E7" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21">
@@ -7470,7 +7925,9 @@
       <c r="C11" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="21"/>
+      <c r="D11" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21">
@@ -7537,7 +7994,9 @@
       <c r="C16" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="21"/>
+      <c r="D16" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="21">
@@ -7612,6 +8071,9 @@
       <c r="D21" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E21" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="21">
@@ -7640,6 +8102,9 @@
       <c r="D23" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E23" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="21">
@@ -7651,7 +8116,9 @@
       <c r="C24" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="21"/>
+      <c r="D24" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="21">
@@ -7691,7 +8158,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="28">
@@ -7813,7 +8280,9 @@
       <c r="C36" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="21"/>
+      <c r="D36" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="21">
@@ -7837,7 +8306,9 @@
       <c r="C38" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="21"/>
+      <c r="D38" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="21">
@@ -7898,7 +8369,7 @@
         <v>20</v>
       </c>
       <c r="E42" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="43">
@@ -8037,6 +8508,9 @@
       <c r="D52" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E52" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="21">
@@ -8062,7 +8536,9 @@
       <c r="C54" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D54" s="21"/>
+      <c r="D54" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="21">
@@ -8077,6 +8553,9 @@
       <c r="D55" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E55" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="21">
@@ -8091,6 +8570,9 @@
       <c r="D56" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E56" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="21">
@@ -8225,6 +8707,9 @@
       <c r="D66" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E66" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="21">
@@ -8253,7 +8738,9 @@
       <c r="C68" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D68" s="21"/>
+      <c r="D68" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="21">
@@ -8277,7 +8764,9 @@
       <c r="C70" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D70" s="21"/>
+      <c r="D70" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="21">
@@ -8335,7 +8824,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="75">
@@ -8437,7 +8926,7 @@
         <v>20</v>
       </c>
       <c r="E81" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="82">
@@ -8477,6 +8966,9 @@
       <c r="D84" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E84" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="21">
@@ -8572,6 +9064,9 @@
       <c r="D91" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E91" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="21">
@@ -8615,6 +9110,9 @@
       <c r="D94" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E94" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="21">
@@ -8640,7 +9138,9 @@
       <c r="C96" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D96" s="21"/>
+      <c r="D96" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="21">
@@ -8758,6 +9258,9 @@
       <c r="D104" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E104" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="21">
@@ -8912,7 +9415,9 @@
       <c r="C114" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D114" s="21"/>
+      <c r="D114" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="21">
@@ -8972,7 +9477,9 @@
       <c r="C118" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D118" s="21"/>
+      <c r="D118" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="21">
@@ -9098,6 +9605,9 @@
       <c r="D127" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E127" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="21">
@@ -9163,7 +9673,9 @@
       <c r="C132" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D132" s="21"/>
+      <c r="D132" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="21">
@@ -9281,7 +9793,7 @@
         <v>20</v>
       </c>
       <c r="E140" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="141">
@@ -9325,7 +9837,9 @@
       <c r="C143" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D143" s="21"/>
+      <c r="D143" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="21">
@@ -9490,7 +10004,9 @@
       <c r="C155" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D155" s="21"/>
+      <c r="D155" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="21">
@@ -9570,7 +10086,9 @@
       <c r="C161" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D161" s="21"/>
+      <c r="D161" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="21">
@@ -9611,7 +10129,9 @@
       <c r="C164" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D164" s="21"/>
+      <c r="D164" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="21">
@@ -9651,7 +10171,9 @@
       <c r="C167" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D167" s="21"/>
+      <c r="D167" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="21">
@@ -9675,7 +10197,9 @@
       <c r="C169" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D169" s="21"/>
+      <c r="D169" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="21">
@@ -9767,7 +10291,7 @@
         <v>20</v>
       </c>
       <c r="E175" s="22">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="176">
@@ -9857,6 +10381,9 @@
       <c r="D181" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E181" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="21">
@@ -9895,6 +10422,9 @@
       <c r="D184" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E184" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="21">
@@ -9909,6 +10439,9 @@
       <c r="D185" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E185" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="21">
@@ -9920,7 +10453,12 @@
       <c r="C186" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D186" s="21"/>
+      <c r="D186" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E186" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="21">
@@ -9963,6 +10501,9 @@
       <c r="D189" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E189" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="21">
@@ -10138,7 +10679,7 @@
         <v>20</v>
       </c>
       <c r="E202" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="203">
@@ -10222,6 +10763,9 @@
       <c r="D208" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E208" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="21">
@@ -10237,7 +10781,7 @@
         <v>20</v>
       </c>
       <c r="E209" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="210">
@@ -10284,6 +10828,9 @@
       <c r="D212" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E212" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="21">
@@ -10312,7 +10859,12 @@
       <c r="C214" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="D214" s="21"/>
+      <c r="D214" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E214" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="21">
@@ -10342,7 +10894,7 @@
         <v>20</v>
       </c>
       <c r="E216" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="217">
@@ -10355,7 +10907,9 @@
       <c r="C217" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="D217" s="21"/>
+      <c r="D217" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="21">
@@ -10382,6 +10936,9 @@
       <c r="D219" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E219" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="21">
@@ -10452,7 +11009,9 @@
       <c r="C224" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="D224" s="21"/>
+      <c r="D224" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="21">
@@ -10484,6 +11043,9 @@
       <c r="D226" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E226" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="21">
@@ -10523,7 +11085,12 @@
       <c r="C229" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="D229" s="21"/>
+      <c r="D229" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E229" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="21">
@@ -10606,7 +11173,7 @@
         <v>20</v>
       </c>
       <c r="E235" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="236">
@@ -10640,7 +11207,7 @@
         <v>20</v>
       </c>
       <c r="E237" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="238">
@@ -10705,7 +11272,12 @@
       <c r="C242" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D242" s="21"/>
+      <c r="D242" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E242" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="21">
@@ -10748,6 +11320,9 @@
       <c r="D245" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E245" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="21">
@@ -11039,6 +11614,9 @@
       <c r="D265" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E265" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="21">
@@ -11050,7 +11628,9 @@
       <c r="C266" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="D266" s="21"/>
+      <c r="D266" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="21">
@@ -11177,6 +11757,9 @@
       <c r="D275" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E275" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="21">
@@ -11221,7 +11804,7 @@
         <v>20</v>
       </c>
       <c r="E278" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="279">
@@ -11261,6 +11844,9 @@
       <c r="D281" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E281" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="21">
@@ -11306,6 +11892,9 @@
       <c r="D284" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E284" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="21">
@@ -11317,7 +11906,9 @@
       <c r="C285" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="D285" s="21"/>
+      <c r="D285" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="21">
@@ -11420,6 +12011,9 @@
       <c r="D292" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E292" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="21">
@@ -11434,6 +12028,9 @@
       <c r="D293" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E293" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="21">
@@ -11445,7 +12042,9 @@
       <c r="C294" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="D294" s="21"/>
+      <c r="D294" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="21">
@@ -11760,6 +12359,9 @@
       <c r="D316" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E316" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="21">
@@ -11774,6 +12376,9 @@
       <c r="D317" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E317" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="21">
@@ -11813,7 +12418,9 @@
       <c r="C320" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="D320" s="21"/>
+      <c r="D320" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="21">
@@ -11905,6 +12512,9 @@
       <c r="D326" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E326" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="21">
@@ -12046,6 +12656,9 @@
       <c r="D335" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E335" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="21">
@@ -12074,6 +12687,9 @@
       <c r="D337" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E337" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="21">
@@ -12089,7 +12705,7 @@
         <v>20</v>
       </c>
       <c r="E338" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="339">
@@ -12131,6 +12747,9 @@
       <c r="D341" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E341" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="21">
@@ -12218,6 +12837,9 @@
       <c r="D347" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E347" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="21">
@@ -12321,6 +12943,9 @@
       <c r="D354" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E354" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="21">
@@ -12334,6 +12959,9 @@
       </c>
       <c r="D355" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E355" s="22">
+        <v>2.0</v>
       </c>
     </row>
     <row r="356">
@@ -12443,6 +13071,9 @@
       <c r="D1" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E1" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21">
@@ -12646,6 +13277,9 @@
       <c r="D15" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E15" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="21">
@@ -12673,6 +13307,9 @@
       </c>
       <c r="D17" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E17" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="18">
@@ -12819,7 +13456,9 @@
       <c r="C6" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="D6" s="21"/>
+      <c r="D6" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21">
@@ -12921,7 +13560,9 @@
       <c r="C13" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="D13" s="21"/>
+      <c r="D13" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21">
@@ -12973,7 +13614,9 @@
       <c r="C17" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="D17" s="21"/>
+      <c r="D17" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="21">
@@ -15086,6 +15729,9 @@
       <c r="D1" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E1" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21">
@@ -15111,7 +15757,9 @@
       <c r="C3" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D3" s="21"/>
+      <c r="D3" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="21">
@@ -15236,6 +15884,9 @@
       </c>
       <c r="D4" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E4" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
@@ -15372,6 +16023,9 @@
       <c r="D3" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E3" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="21">
@@ -15487,6 +16141,9 @@
       </c>
       <c r="D11" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E11" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="12">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="399">
   <si>
     <t>Última actualización:</t>
   </si>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B1" s="2">
         <f>TODAY()</f>
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1833,15 +1833,15 @@
       </c>
       <c r="C3" s="9">
         <f>COUNTIF(REGULARES!D:D, "SI")</f>
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D3" s="9">
         <f t="shared" ref="D3:D12" si="1">B3-C3</f>
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E4" si="2">(C3/B3)</f>
-        <v>0.7888888889</v>
+        <v>0.8027777778</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E3, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1857,15 +1857,15 @@
       </c>
       <c r="C4" s="9">
         <f>COUNTIF(Estadios!D:D, "SI")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="9">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="10">
         <f t="shared" si="2"/>
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F4" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E4, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1929,15 +1929,15 @@
       </c>
       <c r="C7" s="14">
         <f>COUNTIF('Kryptonita (388–396)'!D:D, "SI")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="15">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="10">
         <f t="shared" si="3"/>
-        <v>0.6666666667</v>
+        <v>0.7777777778</v>
       </c>
       <c r="F7" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E7, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1977,15 +1977,15 @@
       </c>
       <c r="C9" s="14">
         <f>COUNTIF('Influencers (415–423)'!D:D, "SI")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="15">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="10">
         <f t="shared" si="3"/>
-        <v>0.5555555556</v>
+        <v>0.6666666667</v>
       </c>
       <c r="F9" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E9, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2025,15 +2025,15 @@
       </c>
       <c r="C11" s="14">
         <f>COUNTIF('Super Cracks (442–467)'!D:D, "SI")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="15">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="3"/>
-        <v>0.6923076923</v>
+        <v>0.7307692308</v>
       </c>
       <c r="F11" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E11, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="4"/>
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="4"/>
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>0.7670682731</v>
+        <v>0.7851405622</v>
       </c>
       <c r="F13" s="19" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E13, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2135,7 +2135,7 @@
         <v>20</v>
       </c>
       <c r="E2" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="3">
@@ -2160,7 +2160,9 @@
       <c r="C4" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="21">
@@ -3045,7 +3047,9 @@
       <c r="C25" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="D25" s="21"/>
+      <c r="D25" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="21">
@@ -3087,1627 +3091,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("{FILTER(REGULARES!A:C, REGULARES!D:D&lt;&gt;""SI"", REGULARES!A:A&lt;&gt;""""); FILTER('¡VAMOS! (361–380)'!A:C, '¡VAMOS! (361–380)'!D:D&lt;&gt;""SI"", '¡VAMOS! (361–380)'!A:A&lt;&gt;""""); FILTER('Guantes de Oro (381–387)'!A:C, 'Guantes de Oro (381–387)'!D:D&lt;&gt;""SI"", 'Guantes de"&amp;" Oro (381–387)'!A:A&lt;&gt;""""); FILTER('Kryptonita (388–396)'!A:C, 'Kryptonita (388–396)'!D:D&lt;&gt;""SI"", 'Kryptonita (388–396)'!A:A&lt;&gt;""""); FILTER('Diamantes (397–414)'!A:C, 'Diamantes (397–414)'!D:D&lt;&gt;""SI"", 'Diamantes (397–414)'!A:A&lt;&gt;""""); FILTER('Influencer"&amp;"s (415–423)'!A:C, 'Influencers (415–423)'!D:D&lt;&gt;""SI"", 'Influencers (415–423)'!A:A&lt;&gt;""""); FILTER('Protas (424–441)'!A:C, 'Protas (424–441)'!D:D&lt;&gt;""SI"", 'Protas (424–441)'!A:A&lt;&gt;""""); FILTER('Super Cracks (442–467)'!A:C, 'Super Cracks (442–467)'!D:D&lt;&gt;""S"&amp;"I"", 'Super Cracks (442–467)'!A:A&lt;&gt;""""); FILTER('Cartas Top y Únicas (468–478)'!A:C, 'Cartas Top y Únicas (468–478)'!D:D&lt;&gt;""SI"", 'Cartas Top y Únicas (468–478)'!A:A&lt;&gt;""""); FILTER(Estadios!A:C, Estadios!D:D&lt;&gt;""SI"", Estadios!A:A&lt;&gt;"""")}"),12.0)</f>
-        <v>12</v>
-      </c>
-      <c r="B1" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEÑÁ")</f>
-        <v>ALEÑÁ</v>
-      </c>
-      <c r="C1" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
-      </c>
-      <c r="B2" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO IBÁÑEZ")</f>
-        <v>PABLO IBÁÑEZ</v>
-      </c>
-      <c r="C2" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
-      </c>
-      <c r="B3" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
-        <v>UNAI SIMÓN</v>
-      </c>
-      <c r="C3" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
-        <v>25</v>
-      </c>
-      <c r="B4" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
-        <v>LAPORTE</v>
-      </c>
-      <c r="C4" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.0)</f>
-        <v>26</v>
-      </c>
-      <c r="B5" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YURI")</f>
-        <v>YURI</v>
-      </c>
-      <c r="C5" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
-        <v>29</v>
-      </c>
-      <c r="B6" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VESGA")</f>
-        <v>VESGA</v>
-      </c>
-      <c r="C6" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
-      </c>
-      <c r="B7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI GÓMEZ")</f>
-        <v>UNAI GÓMEZ</v>
-      </c>
-      <c r="C7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
-        <v>35</v>
-      </c>
-      <c r="B8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GURUZETA")</f>
-        <v>GURUZETA</v>
-      </c>
-      <c r="C8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
-        <v>37</v>
-      </c>
-      <c r="B9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
-        <v>48</v>
-      </c>
-      <c r="B10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEX BAENA")</f>
-        <v>ALEX BAENA</v>
-      </c>
-      <c r="C10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
-        <v>50</v>
-      </c>
-      <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO GONZÁLEZ")</f>
-        <v>NICO GONZÁLEZ</v>
-      </c>
-      <c r="C11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.0)</f>
-        <v>51</v>
-      </c>
-      <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIULIANO")</f>
-        <v>GIULIANO</v>
-      </c>
-      <c r="C12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
-        <v>57</v>
-      </c>
-      <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SZCZESNY")</f>
-        <v>SZCZESNY</v>
-      </c>
-      <c r="C13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
-        <v>58</v>
-      </c>
-      <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
-        <v>KOUNDÉ</v>
-      </c>
-      <c r="C14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.0)</f>
-        <v>60</v>
-      </c>
-      <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ERIC GARCÍA")</f>
-        <v>ERIC GARCÍA</v>
-      </c>
-      <c r="C15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
-        <v>69</v>
-      </c>
-      <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
-        <v>LAMINE YAMAL</v>
-      </c>
-      <c r="C16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),80.0)</f>
-        <v>80</v>
-      </c>
-      <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
-      </c>
-      <c r="C17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.0)</f>
-        <v>82</v>
-      </c>
-      <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALTIMIRA")</f>
-        <v>ALTIMIRA</v>
-      </c>
-      <c r="C18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.0)</f>
-        <v>83</v>
-      </c>
-      <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AMRABAT")</f>
-        <v>AMRABAT</v>
-      </c>
-      <c r="C19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),85.0)</f>
-        <v>85</v>
-      </c>
-      <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LO CELSO")</f>
-        <v>LO CELSO</v>
-      </c>
-      <c r="C20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
-        <v>89</v>
-      </c>
-      <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIQUELME")</f>
-        <v>RIQUELME</v>
-      </c>
-      <c r="C21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.0)</f>
-        <v>90</v>
-      </c>
-      <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABDE")</f>
-        <v>ABDE</v>
-      </c>
-      <c r="C22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.0)</f>
-        <v>92</v>
-      </c>
-      <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RADU")</f>
-        <v>RADU</v>
-      </c>
-      <c r="C23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
-        <v>98</v>
-      </c>
-      <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MINGUEZA")</f>
-        <v>MINGUEZA</v>
-      </c>
-      <c r="C24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101.0)</f>
-        <v>101</v>
-      </c>
-      <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN BELTRÁN")</f>
-        <v>FRAN BELTRÁN</v>
-      </c>
-      <c r="C25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
-      </c>
-      <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
-      </c>
-      <c r="C26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
-        <v>113</v>
-      </c>
-      <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CHUST")</f>
-        <v>CHUST</v>
-      </c>
-      <c r="C27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
-        <v>119</v>
-      </c>
-      <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARTIM NETO")</f>
-        <v>MARTIM NETO</v>
-      </c>
-      <c r="C28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
-        <v>120</v>
-      </c>
-      <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
-        <v>FEBAS</v>
-      </c>
-      <c r="C29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
-        <v>128</v>
-      </c>
-      <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
-        <v>DMITROVIC</v>
-      </c>
-      <c r="C30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
-        <v>133</v>
-      </c>
-      <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
-      </c>
-      <c r="C31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
-      </c>
-      <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
-        <v>148</v>
-      </c>
-      <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IGLESIAS")</f>
-        <v>IGLESIAS</v>
-      </c>
-      <c r="C33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.0)</f>
-        <v>149</v>
-      </c>
-      <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKO FEMENÍA")</f>
-        <v>KIKO FEMENÍA</v>
-      </c>
-      <c r="C34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.0)</f>
-        <v>150</v>
-      </c>
-      <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DJENÉ")</f>
-        <v>DJENÉ</v>
-      </c>
-      <c r="C35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
-        <v>151</v>
-      </c>
-      <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOMINGOS DUARTE")</f>
-        <v>DOMINGOS DUARTE</v>
-      </c>
-      <c r="C36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),157.0)</f>
-        <v>157</v>
-      </c>
-      <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
-      </c>
-      <c r="C37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),162.0)</f>
-        <v>162</v>
-      </c>
-      <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COBA")</f>
-        <v>COBA</v>
-      </c>
-      <c r="C38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
-        <v>168</v>
-      </c>
-      <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VITOR REIS")</f>
-        <v>VITOR REIS</v>
-      </c>
-      <c r="C39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.0)</f>
-        <v>178</v>
-      </c>
-      <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
-        <v>VANAT</v>
-      </c>
-      <c r="C40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
-        <v>182</v>
-      </c>
-      <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RYAN")</f>
-        <v>RYAN</v>
-      </c>
-      <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
-        <v>183</v>
-      </c>
-      <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO CAMPOS")</f>
-        <v>PABLO CAMPOS</v>
-      </c>
-      <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),191.0)</f>
-        <v>191</v>
-      </c>
-      <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARTÍNEZ")</f>
-        <v>PABLO MARTÍNEZ</v>
-      </c>
-      <c r="C43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.0)</f>
-        <v>196</v>
-      </c>
-      <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRUGUÉ")</f>
-        <v>BRUGUÉ</v>
-      </c>
-      <c r="C44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
-        <v>198</v>
-      </c>
-      <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
-        <v>ETTA EYONG</v>
-      </c>
-      <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.0)</f>
-        <v>201</v>
-      </c>
-      <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUNIN")</f>
-        <v>LUNIN</v>
-      </c>
-      <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.0)</f>
-        <v>205</v>
-      </c>
-      <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUIJSEN")</f>
-        <v>HUIJSEN</v>
-      </c>
-      <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
-        <v>218</v>
-      </c>
-      <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
-        <v>LEO ROMÁN</v>
-      </c>
-      <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.0)</f>
-        <v>231</v>
-      </c>
-      <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ASANO")</f>
-        <v>ASANO</v>
-      </c>
-      <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),232.0)</f>
-        <v>232</v>
-      </c>
-      <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MURIQI")</f>
-        <v>MURIQI</v>
-      </c>
-      <c r="C50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),233.0)</f>
-        <v>233</v>
-      </c>
-      <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
-        <v>MATEO JOSEPH</v>
-      </c>
-      <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.0)</f>
-        <v>239</v>
-      </c>
-      <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYOMO")</f>
-        <v>BOYOMO</v>
-      </c>
-      <c r="C52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.0)</f>
-        <v>241</v>
-      </c>
-      <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HERRANDO")</f>
-        <v>HERRANDO</v>
-      </c>
-      <c r="C53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
-        <v>253</v>
-      </c>
-      <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),254.0)</f>
-        <v>254</v>
-      </c>
-      <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AARON ESCANDELL")</f>
-        <v>AARON ESCANDELL</v>
-      </c>
-      <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
-        <v>260</v>
-      </c>
-      <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
-        <v>RAHIM ALHASSANE</v>
-      </c>
-      <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
-        <v>261</v>
-      </c>
-      <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLOMBATTO")</f>
-        <v>COLOMBATTO</v>
-      </c>
-      <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),263.0)</f>
-        <v>263</v>
-      </c>
-      <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DENDONCKER")</f>
-        <v>DENDONCKER</v>
-      </c>
-      <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),268.0)</f>
-        <v>268</v>
-      </c>
-      <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILYAS CHAIRA")</f>
-        <v>ILYAS CHAIRA</v>
-      </c>
-      <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),271.0)</f>
-        <v>271</v>
-      </c>
-      <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.0)</f>
-        <v>273</v>
-      </c>
-      <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CÁRDENAS")</f>
-        <v>CÁRDENAS</v>
-      </c>
-      <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),276.0)</f>
-        <v>276</v>
-      </c>
-      <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
-        <v>LEJEUNE</v>
-      </c>
-      <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),279.0)</f>
-        <v>279</v>
-      </c>
-      <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PATHÉ CISS")</f>
-        <v>PATHÉ CISS</v>
-      </c>
-      <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),280.0)</f>
-        <v>280</v>
-      </c>
-      <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LOPEZ")</f>
-        <v>UNAI LOPEZ</v>
-      </c>
-      <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
-        <v>289</v>
-      </c>
-      <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),297.0)</f>
-        <v>297</v>
-      </c>
-      <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GORROTXATEGI")</f>
-        <v>GORROTXATEGI</v>
-      </c>
-      <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.0)</f>
-        <v>300</v>
-      </c>
-      <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
-        <v>CARLOS SOLER</v>
-      </c>
-      <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),301.0)</f>
-        <v>301</v>
-      </c>
-      <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRAIS MÉNDEZ")</f>
-        <v>BRAIS MÉNDEZ</v>
-      </c>
-      <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),305.0)</f>
-        <v>305</v>
-      </c>
-      <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSKARSSON")</f>
-        <v>ÓSKARSSON</v>
-      </c>
-      <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),310.0)</f>
-        <v>310</v>
-      </c>
-      <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARMONA")</f>
-        <v>CARMONA</v>
-      </c>
-      <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),314.0)</f>
-        <v>314</v>
-      </c>
-      <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCAO")</f>
-        <v>MARCAO</v>
-      </c>
-      <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),324.0)</f>
-        <v>324</v>
-      </c>
-      <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
-      </c>
-      <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),339.0)</f>
-        <v>339</v>
-      </c>
-      <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO LÓPEZ")</f>
-        <v>DIEGO LÓPEZ</v>
-      </c>
-      <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
-        <v>348</v>
-      </c>
-      <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MARÍN")</f>
-        <v>RAFA MARÍN</v>
-      </c>
-      <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),349.0)</f>
-        <v>349</v>
-      </c>
-      <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RENATO VEIGA")</f>
-        <v>RENATO VEIGA</v>
-      </c>
-      <c r="C75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),360.0)</f>
-        <v>360</v>
-      </c>
-      <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AYOZE")</f>
-        <v>AYOZE</v>
-      </c>
-      <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),364.0)</f>
-        <v>364</v>
-      </c>
-      <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-      <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),365.0)</f>
-        <v>365</v>
-      </c>
-      <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-      <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
-        <v>375</v>
-      </c>
-      <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),378.0)</f>
-        <v>378</v>
-      </c>
-      <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),380.0)</f>
-        <v>380</v>
-      </c>
-      <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),384.0)</f>
-        <v>384</v>
-      </c>
-      <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
-      </c>
-      <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.0)</f>
-        <v>385</v>
-      </c>
-      <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATALLA")</f>
-        <v>BATALLA</v>
-      </c>
-      <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.0)</f>
-        <v>386</v>
-      </c>
-      <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
-      </c>
-      <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.0)</f>
-        <v>388</v>
-      </c>
-      <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAPORTE")</f>
-        <v>LAPORTE</v>
-      </c>
-      <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),390.0)</f>
-        <v>390</v>
-      </c>
-      <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LE NORMAND")</f>
-        <v>LE NORMAND</v>
-      </c>
-      <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),394.0)</f>
-        <v>394</v>
-      </c>
-      <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEJEUNE")</f>
-        <v>LEJEUNE</v>
-      </c>
-      <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),397.0)</f>
-        <v>397</v>
-      </c>
-      <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REGO")</f>
-        <v>REGO</v>
-      </c>
-      <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
-        <v>401</v>
-      </c>
-      <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
-        <v>RODRI MENDOZA</v>
-      </c>
-      <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),410.0)</f>
-        <v>410</v>
-      </c>
-      <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
-        <v>GONZALO</v>
-      </c>
-      <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),412.0)</f>
-        <v>412</v>
-      </c>
-      <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATEO JOSEPH")</f>
-        <v>MATEO JOSEPH</v>
-      </c>
-      <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),417.0)</f>
-        <v>417</v>
-      </c>
-      <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEBAS")</f>
-        <v>FEBAS</v>
-      </c>
-      <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),418.0)</f>
-        <v>418</v>
-      </c>
-      <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
-      </c>
-      <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),420.0)</f>
-        <v>420</v>
-      </c>
-      <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
-        <v>DARDER</v>
-      </c>
-      <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),423.0)</f>
-        <v>423</v>
-      </c>
-      <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI LÓPEZ")</f>
-        <v>UNAI LÓPEZ</v>
-      </c>
-      <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),424.0)</f>
-        <v>424</v>
-      </c>
-      <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
-        <v>TENAGLIA</v>
-      </c>
-      <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),428.0)</f>
-        <v>428</v>
-      </c>
-      <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
-      </c>
-      <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),430.0)</f>
-        <v>430</v>
-      </c>
-      <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VANAT")</f>
-        <v>VANAT</v>
-      </c>
-      <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),433.0)</f>
-        <v>433</v>
-      </c>
-      <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEO ROMÁN")</f>
-        <v>LEO ROMÁN</v>
-      </c>
-      <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),438.0)</f>
-        <v>438</v>
-      </c>
-      <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BATISTA MENDY")</f>
-        <v>BATISTA MENDY</v>
-      </c>
-      <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),441.0)</f>
-        <v>441</v>
-      </c>
-      <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUCHANAN")</f>
-        <v>BUCHANAN</v>
-      </c>
-      <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),442.0)</f>
-        <v>442</v>
-      </c>
-      <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UNAI SIMÓN")</f>
-        <v>UNAI SIMÓN</v>
-      </c>
-      <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),443.0)</f>
-        <v>443</v>
-      </c>
-      <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAUREGIZAR")</f>
-        <v>JAUREGIZAR</v>
-      </c>
-      <c r="C103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446.0)</f>
-        <v>446</v>
-      </c>
-      <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLEX BAENA")</f>
-        <v>ÁLEX BAENA</v>
-      </c>
-      <c r="C104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),451.0)</f>
-        <v>451</v>
-      </c>
-      <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAPHINHA")</f>
-        <v>RAPHINHA</v>
-      </c>
-      <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),453.0)</f>
-        <v>453</v>
-      </c>
-      <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RASHFORD")</f>
-        <v>RASHFORD</v>
-      </c>
-      <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),460.0)</f>
-        <v>460</v>
-      </c>
-      <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
-      </c>
-      <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),464.0)</f>
-        <v>464</v>
-      </c>
-      <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VARGAS")</f>
-        <v>VARGAS</v>
-      </c>
-      <c r="C108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),466.0)</f>
-        <v>466</v>
-      </c>
-      <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
-        <v>MOLEIRO</v>
-      </c>
-      <c r="C109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),468.0)</f>
-        <v>468</v>
-      </c>
-      <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD CHAMPIONS")</f>
-        <v>CARD CHAMPIONS</v>
-      </c>
-      <c r="C110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.0)</f>
-        <v>470</v>
-      </c>
-      <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ÁLVAREZ")</f>
-        <v>JULIÁN ÁLVAREZ</v>
-      </c>
-      <c r="C111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATLÉTICO)")</f>
-        <v>BALÓN DE ORO (ATLÉTICO)</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),471.0)</f>
-        <v>471</v>
-      </c>
-      <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRI")</f>
-        <v>PEDRI</v>
-      </c>
-      <c r="C112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
-        <v>BALÓN DE ORO (BARÇA)</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),472.0)</f>
-        <v>472</v>
-      </c>
-      <c r="B113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LAMINE YAMAL")</f>
-        <v>LAMINE YAMAL</v>
-      </c>
-      <c r="C113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (BARÇA)")</f>
-        <v>BALÓN DE ORO (BARÇA)</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),475.0)</f>
-        <v>475</v>
-      </c>
-      <c r="B114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO EXCELLENCE")</f>
-        <v>BALÓN DE ORO EXCELLENCE</v>
-      </c>
-      <c r="C114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.0)</f>
-        <v>476</v>
-      </c>
-      <c r="B115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD ATÓMICA")</f>
-        <v>CARD ATÓMICA</v>
-      </c>
-      <c r="C115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
-        <v>91</v>
-      </c>
-      <c r="B116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+      <c r="A1" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("{FILTER(REGULARES!A:C, REGULARES!D:D&lt;&gt;""SI"", REGULARES!A:A&lt;&gt;""""); FILTER('¡VAMOS! (361–380)'!A:C, '¡VAMOS! (361–380)'!D:D&lt;&gt;""SI"", '¡VAMOS! (361–380)'!A:A&lt;&gt;""""); FILTER('Guantes de Oro (381–387)'!A:C, 'Guantes de Oro (381–387)'!D:D&lt;&gt;""SI"", 'Guantes de"&amp;" Oro (381–387)'!A:A&lt;&gt;""""); FILTER('Kryptonita (388–396)'!A:C, 'Kryptonita (388–396)'!D:D&lt;&gt;""SI"", 'Kryptonita (388–396)'!A:A&lt;&gt;""""); FILTER('Diamantes (397–414)'!A:C, 'Diamantes (397–414)'!D:D&lt;&gt;""SI"", 'Diamantes (397–414)'!A:A&lt;&gt;""""); FILTER('Influencer"&amp;"s (415–423)'!A:C, 'Influencers (415–423)'!D:D&lt;&gt;""SI"", 'Influencers (415–423)'!A:A&lt;&gt;""""); FILTER('Protas (424–441)'!A:C, 'Protas (424–441)'!D:D&lt;&gt;""SI"", 'Protas (424–441)'!A:A&lt;&gt;""""); FILTER('Super Cracks (442–467)'!A:C, 'Super Cracks (442–467)'!D:D&lt;&gt;""S"&amp;"I"", 'Super Cracks (442–467)'!A:A&lt;&gt;""""); FILTER('Cartas Top y Únicas (468–478)'!A:C, 'Cartas Top y Únicas (468–478)'!D:D&lt;&gt;""SI"", 'Cartas Top y Únicas (468–478)'!A:A&lt;&gt;""""); FILTER(Estadios!A:C, Estadios!D:D&lt;&gt;""SI"", Estadios!A:A&lt;&gt;"""")}"),"#VALUE!")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -4992,12 +3378,12 @@
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
-        <v>40</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
+        <v>39</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
-        <v>MARCOS LLORENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MUSSO")</f>
+        <v>MUSSO</v>
       </c>
       <c r="C15" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -5010,12 +3396,12 @@
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
+        <v>40</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
-        <v>LENGLET</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
+        <v>MARCOS LLORENTE</v>
       </c>
       <c r="C16" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -5028,12 +3414,12 @@
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
-        <v>ALMADA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
+        <v>LENGLET</v>
       </c>
       <c r="C17" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -5046,12 +3432,12 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
-        <v>52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.0)</f>
+        <v>43</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
-        <v>JULIÁN ALVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HANCKO")</f>
+        <v>HANCKO</v>
       </c>
       <c r="C18" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -5064,48 +3450,48 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
+      </c>
+      <c r="B19" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
+        <v>ALMADA</v>
+      </c>
+      <c r="C19" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D19" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
+        <v>52</v>
+      </c>
+      <c r="B20" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
+        <v>JULIÁN ALVAREZ</v>
+      </c>
+      <c r="C20" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D20" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
         <v>55</v>
       </c>
-      <c r="B19" s="20" t="str">
+      <c r="B21" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
         <v>ESCUDO</v>
-      </c>
-      <c r="C19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-      <c r="D19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
-        <v>56</v>
-      </c>
-      <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOAN GARCÍA")</f>
-        <v>JOAN GARCÍA</v>
-      </c>
-      <c r="C20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-      <c r="D20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
-        <v>66</v>
-      </c>
-      <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
-        <v>FERMÍN</v>
       </c>
       <c r="C21" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -5118,12 +3504,12 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
-        <v>67</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
-        <v>DANI OLMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOAN GARCÍA")</f>
+        <v>JOAN GARCÍA</v>
       </c>
       <c r="C22" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -5136,48 +3522,48 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
+      </c>
+      <c r="B23" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
+        <v>FERMÍN</v>
+      </c>
+      <c r="C23" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D23" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
+      </c>
+      <c r="B24" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
+        <v>DANI OLMO</v>
+      </c>
+      <c r="C24" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D24" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
         <v>73</v>
       </c>
-      <c r="B23" s="20" t="str">
+      <c r="B25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
         <v>ESTADIO</v>
-      </c>
-      <c r="C23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-      <c r="D23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
-      </c>
-      <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
-        <v>PAU LÓPEZ</v>
-      </c>
-      <c r="C24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-      <c r="D24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
-        <v>76</v>
-      </c>
-      <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
-        <v>BELLERÍN</v>
       </c>
       <c r="C25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -5190,12 +3576,12 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
+        <v>PAU LÓPEZ</v>
       </c>
       <c r="C26" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -5208,12 +3594,12 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
-        <v>84</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
-        <v>PABLO FORNALS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
+        <v>BELLERÍN</v>
       </c>
       <c r="C27" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -5226,12 +3612,12 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C28" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -5244,48 +3630,48 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
+        <v>84</v>
+      </c>
+      <c r="B29" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
+        <v>PABLO FORNALS</v>
+      </c>
+      <c r="C29" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D29" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
+      </c>
+      <c r="B30" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
+      </c>
+      <c r="C30" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D30" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
         <v>91</v>
       </c>
-      <c r="B29" s="20" t="str">
+      <c r="B31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
         <v>ESCUDO</v>
-      </c>
-      <c r="C29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-      <c r="D29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
-        <v>93</v>
-      </c>
-      <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
-        <v>IVÁN VILLAR</v>
-      </c>
-      <c r="C30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-      <c r="D30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
-        <v>94</v>
-      </c>
-      <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
-        <v>JAVI RUEDA</v>
       </c>
       <c r="C31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5298,12 +3684,12 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
+        <v>93</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
+        <v>IVÁN VILLAR</v>
       </c>
       <c r="C32" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5316,12 +3702,12 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
+        <v>94</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
+        <v>JAVI RUEDA</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5334,12 +3720,12 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C34" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5352,12 +3738,12 @@
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
-        <v>104</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
-        <v>SWEDBERG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C35" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5370,12 +3756,12 @@
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C36" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5388,30 +3774,30 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
-        <v>106</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
+        <v>104</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
-        <v>IAGO ASPAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
+        <v>SWEDBERG</v>
       </c>
       <c r="C37" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C38" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5424,12 +3810,12 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
+        <v>IAGO ASPAS</v>
       </c>
       <c r="C39" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -5442,48 +3828,48 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
+      </c>
+      <c r="B40" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
+      </c>
+      <c r="C40" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D40" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
+      </c>
+      <c r="B41" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
+      </c>
+      <c r="C41" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D41" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
         <v>110</v>
       </c>
-      <c r="B40" s="20" t="str">
+      <c r="B42" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
         <v>IÑAKI PEÑA</v>
-      </c>
-      <c r="C40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-      <c r="D40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
-      </c>
-      <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
-      </c>
-      <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-      <c r="D41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
-        <v>112</v>
-      </c>
-      <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
-        <v>ÁLVARO NÚÑEZ</v>
       </c>
       <c r="C42" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5496,12 +3882,12 @@
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C43" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5514,12 +3900,12 @@
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
-        <v>117</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
-        <v>FEDE REDONDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
+        <v>ÁLVARO NÚÑEZ</v>
       </c>
       <c r="C44" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5532,12 +3918,12 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C45" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -5550,66 +3936,66 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
+        <v>117</v>
+      </c>
+      <c r="B46" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
+        <v>FEDE REDONDO</v>
+      </c>
+      <c r="C46" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
+      </c>
+      <c r="D46" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
+      </c>
+      <c r="B47" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
+      </c>
+      <c r="C47" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
+      </c>
+      <c r="D47" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
+        <v>126</v>
+      </c>
+      <c r="B48" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
+        <v>RAFA MIR</v>
+      </c>
+      <c r="C48" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
+      </c>
+      <c r="D48" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
         <v>127</v>
       </c>
-      <c r="B46" s="20" t="str">
+      <c r="B49" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
         <v>ESCUDO</v>
-      </c>
-      <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-      <c r="D46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
-      </c>
-      <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
-      </c>
-      <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-      <c r="D47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
-      </c>
-      <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
-      </c>
-      <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-      <c r="D48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
-      </c>
-      <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
       </c>
       <c r="C49" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5622,12 +4008,12 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C50" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5640,12 +4026,12 @@
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C51" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -5658,138 +4044,138 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
+        <v>139</v>
+      </c>
+      <c r="B52" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
+        <v>ANTONIU ROCA</v>
+      </c>
+      <c r="C52" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+      <c r="D52" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
+      </c>
+      <c r="B53" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
+      </c>
+      <c r="C53" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+      <c r="D53" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
+      </c>
+      <c r="B54" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
+      </c>
+      <c r="C54" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+      <c r="D54" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
+      </c>
+      <c r="B55" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
+      </c>
+      <c r="C55" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+      <c r="D55" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
         <v>145</v>
       </c>
-      <c r="B52" s="20" t="str">
+      <c r="B56" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
         <v>ESTADIO</v>
       </c>
-      <c r="C52" s="20" t="str">
+      <c r="C56" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
         <v>GETAFE CF</v>
       </c>
-      <c r="D52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="20">
+      <c r="D56" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
         <v>146</v>
       </c>
-      <c r="B53" s="20" t="str">
+      <c r="B57" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
         <v>DAVID SORIA</v>
       </c>
-      <c r="C53" s="20" t="str">
+      <c r="C57" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
         <v>GETAFE CF</v>
       </c>
-      <c r="D53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="20">
+      <c r="D57" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
         <v>153</v>
       </c>
-      <c r="B54" s="20" t="str">
+      <c r="B58" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
         <v>DIEGO RICO</v>
       </c>
-      <c r="C54" s="20" t="str">
+      <c r="C58" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
         <v>GETAFE CF</v>
       </c>
-      <c r="D54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="20">
+      <c r="D58" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
         <v>163</v>
       </c>
-      <c r="B55" s="20" t="str">
+      <c r="B59" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
         <v>ESCUDO</v>
-      </c>
-      <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-      <c r="D55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
-      </c>
-      <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
-      </c>
-      <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-      <c r="D56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
-        <v>174</v>
-      </c>
-      <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
-        <v>IVÁN MARTÍN</v>
-      </c>
-      <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-      <c r="D57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
-      </c>
-      <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
-      </c>
-      <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-      <c r="D58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
-        <v>176</v>
-      </c>
-      <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
-        <v>JOEL ROCA</v>
       </c>
       <c r="C59" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -5802,12 +4188,12 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.0)</f>
-        <v>177</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TSYGANKOV")</f>
-        <v>TSYGANKOV</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C60" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -5820,192 +4206,192 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),173.0)</f>
+        <v>173</v>
+      </c>
+      <c r="B61" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OUNAHI")</f>
+        <v>OUNAHI</v>
+      </c>
+      <c r="C61" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+      <c r="D61" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
+        <v>174</v>
+      </c>
+      <c r="B62" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
+        <v>IVÁN MARTÍN</v>
+      </c>
+      <c r="C62" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+      <c r="D62" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
+      </c>
+      <c r="B63" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
+      </c>
+      <c r="C63" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+      <c r="D63" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
+        <v>176</v>
+      </c>
+      <c r="B64" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
+        <v>JOEL ROCA</v>
+      </c>
+      <c r="C64" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+      <c r="D64" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.0)</f>
+        <v>177</v>
+      </c>
+      <c r="B65" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TSYGANKOV")</f>
+        <v>TSYGANKOV</v>
+      </c>
+      <c r="C65" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
+      </c>
+      <c r="D65" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),181.0)</f>
         <v>181</v>
       </c>
-      <c r="B61" s="20" t="str">
+      <c r="B66" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
         <v>ESCUDO</v>
       </c>
-      <c r="C61" s="20" t="str">
+      <c r="C66" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
         <v>LEVANTE UD</v>
       </c>
-      <c r="D61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="20">
+      <c r="D66" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),184.0)</f>
         <v>184</v>
       </c>
-      <c r="B62" s="20" t="str">
+      <c r="B67" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TOLJAN")</f>
         <v>TOLJAN</v>
       </c>
-      <c r="C62" s="20" t="str">
+      <c r="C67" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
         <v>LEVANTE UD</v>
       </c>
-      <c r="D62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="20">
+      <c r="D67" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),185.0)</f>
         <v>185</v>
       </c>
-      <c r="B63" s="20" t="str">
+      <c r="B68" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DELA")</f>
         <v>DELA</v>
       </c>
-      <c r="C63" s="20" t="str">
+      <c r="C68" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
         <v>LEVANTE UD</v>
       </c>
-      <c r="D63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="20">
+      <c r="D68" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.0)</f>
         <v>186</v>
       </c>
-      <c r="B64" s="20" t="str">
+      <c r="B69" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELGEZABAL")</f>
         <v>ELGEZABAL</v>
       </c>
-      <c r="C64" s="20" t="str">
+      <c r="C69" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
         <v>LEVANTE UD</v>
       </c>
-      <c r="D64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="20">
+      <c r="D69" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
         <v>189</v>
       </c>
-      <c r="B65" s="20" t="str">
+      <c r="B70" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
         <v>PAMPÍN</v>
       </c>
-      <c r="C65" s="20" t="str">
+      <c r="C70" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
         <v>LEVANTE UD</v>
       </c>
-      <c r="D65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="20">
+      <c r="D70" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
         <v>202</v>
       </c>
-      <c r="B66" s="20" t="str">
+      <c r="B71" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
         <v>CARVAJAL</v>
-      </c>
-      <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),208.0)</f>
-        <v>208</v>
-      </c>
-      <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TCHOUAMÉNI")</f>
-        <v>TCHOUAMÉNI</v>
-      </c>
-      <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
-      </c>
-      <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
-      </c>
-      <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
-        <v>211</v>
-      </c>
-      <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
-        <v>GÜLER</v>
-      </c>
-      <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
-        <v>212</v>
-      </c>
-      <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
-      </c>
-      <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
-        <v>213</v>
-      </c>
-      <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
-        <v>RODRYGO</v>
       </c>
       <c r="C71" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6018,12 +4404,12 @@
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
-        <v>214</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),208.0)</f>
+        <v>208</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
-        <v>MBAPPÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TCHOUAMÉNI")</f>
+        <v>TCHOUAMÉNI</v>
       </c>
       <c r="C72" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6036,12 +4422,12 @@
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C73" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -6054,246 +4440,246 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),210.0)</f>
+        <v>210</v>
+      </c>
+      <c r="B74" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLINGHAM")</f>
+        <v>BELLINGHAM</v>
+      </c>
+      <c r="C74" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D74" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
+      </c>
+      <c r="B75" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
+      </c>
+      <c r="C75" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D75" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
+        <v>212</v>
+      </c>
+      <c r="B76" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
+      </c>
+      <c r="C76" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D76" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
+        <v>213</v>
+      </c>
+      <c r="B77" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
+        <v>RODRYGO</v>
+      </c>
+      <c r="C77" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D77" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
+        <v>214</v>
+      </c>
+      <c r="B78" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
+        <v>MBAPPÉ</v>
+      </c>
+      <c r="C78" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D78" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
+      </c>
+      <c r="B79" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
+      </c>
+      <c r="C79" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D79" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
         <v>219</v>
       </c>
-      <c r="B74" s="20" t="str">
+      <c r="B80" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
         <v>BERGSTRÖM</v>
       </c>
-      <c r="C74" s="20" t="str">
+      <c r="C80" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
-      <c r="D74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="20">
+      <c r="D80" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
         <v>222</v>
       </c>
-      <c r="B75" s="20" t="str">
+      <c r="B81" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
         <v>VALJENT</v>
       </c>
-      <c r="C75" s="20" t="str">
+      <c r="C81" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
-      <c r="D75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="20">
+      <c r="D81" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
         <v>225</v>
       </c>
-      <c r="B76" s="20" t="str">
+      <c r="B82" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
         <v>MOJICA</v>
       </c>
-      <c r="C76" s="20" t="str">
+      <c r="C82" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
-      <c r="D76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="20">
+      <c r="D82" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),226.0)</f>
         <v>226</v>
       </c>
-      <c r="B77" s="20" t="str">
+      <c r="B83" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SAMÚ COSTA")</f>
         <v>SAMÚ COSTA</v>
       </c>
-      <c r="C77" s="20" t="str">
+      <c r="C83" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
-      <c r="D77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="20">
+      <c r="D83" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.0)</f>
         <v>229</v>
       </c>
-      <c r="B78" s="20" t="str">
+      <c r="B84" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORLANES")</f>
         <v>MORLANES</v>
       </c>
-      <c r="C78" s="20" t="str">
+      <c r="C84" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
-      <c r="D78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="20">
+      <c r="D84" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
         <v>234</v>
       </c>
-      <c r="B79" s="20" t="str">
+      <c r="B85" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
         <v>JAN VIRGILI</v>
       </c>
-      <c r="C79" s="20" t="str">
+      <c r="C85" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
-      <c r="D79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="20">
+      <c r="D85" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
         <v>235</v>
       </c>
-      <c r="B80" s="20" t="str">
+      <c r="B86" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
         <v>ESCUDO</v>
-      </c>
-      <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
-      </c>
-      <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
-      </c>
-      <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
-        <v>237</v>
-      </c>
-      <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
-        <v>AITOR FERNÁNDEZ</v>
-      </c>
-      <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
-        <v>242</v>
-      </c>
-      <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
-        <v>JUAN CRUZ</v>
-      </c>
-      <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
-        <v>245</v>
-      </c>
-      <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
-        <v>MONCAYOLA</v>
-      </c>
-      <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),247.0)</f>
-        <v>247</v>
-      </c>
-      <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUBÉN GARCÍA")</f>
-        <v>RUBÉN GARCÍA</v>
-      </c>
-      <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
-        <v>248</v>
-      </c>
-      <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
       </c>
       <c r="C86" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
         <v>CA OSASUNA</v>
       </c>
       <c r="D86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C87" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -6306,120 +4692,120 @@
     </row>
     <row r="88">
       <c r="A88" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
+        <v>237</v>
+      </c>
+      <c r="B88" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
+        <v>AITOR FERNÁNDEZ</v>
+      </c>
+      <c r="C88" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D88" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
+        <v>242</v>
+      </c>
+      <c r="B89" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
+        <v>JUAN CRUZ</v>
+      </c>
+      <c r="C89" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D89" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
+        <v>245</v>
+      </c>
+      <c r="B90" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
+        <v>MONCAYOLA</v>
+      </c>
+      <c r="C90" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D90" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),247.0)</f>
+        <v>247</v>
+      </c>
+      <c r="B91" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUBÉN GARCÍA")</f>
+        <v>RUBÉN GARCÍA</v>
+      </c>
+      <c r="C91" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D91" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
+        <v>248</v>
+      </c>
+      <c r="B92" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
+      </c>
+      <c r="C92" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D92" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
+      </c>
+      <c r="B93" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
+      </c>
+      <c r="C93" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D93" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
         <v>253</v>
       </c>
-      <c r="B88" s="20" t="str">
+      <c r="B94" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
         <v>ESTADIO</v>
-      </c>
-      <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="D88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),255.0)</f>
-        <v>255</v>
-      </c>
-      <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLDOVAN")</f>
-        <v>MOLDOVAN</v>
-      </c>
-      <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="D89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
-      </c>
-      <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
-      </c>
-      <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="D90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
-      </c>
-      <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
-      </c>
-      <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="D91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
-      </c>
-      <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
-      </c>
-      <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="D92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
-        <v>265</v>
-      </c>
-      <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
-        <v>ILIC</v>
-      </c>
-      <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="D93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.0)</f>
-        <v>267</v>
-      </c>
-      <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BREKALO")</f>
-        <v>BREKALO</v>
       </c>
       <c r="C94" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -6432,12 +4818,12 @@
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),255.0)</f>
+        <v>255</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLDOVAN")</f>
+        <v>MOLDOVAN</v>
       </c>
       <c r="C95" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -6450,120 +4836,120 @@
     </row>
     <row r="96">
       <c r="A96" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
+      </c>
+      <c r="B96" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
+      </c>
+      <c r="C96" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D96" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
+      </c>
+      <c r="B97" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
+      </c>
+      <c r="C97" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D97" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
+      </c>
+      <c r="B98" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
+      </c>
+      <c r="C98" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D98" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
+        <v>265</v>
+      </c>
+      <c r="B99" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
+        <v>ILIC</v>
+      </c>
+      <c r="C99" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D99" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.0)</f>
+        <v>267</v>
+      </c>
+      <c r="B100" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BREKALO")</f>
+        <v>BREKALO</v>
+      </c>
+      <c r="C100" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D100" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
+      </c>
+      <c r="B101" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
+      </c>
+      <c r="C101" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D101" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),275.0)</f>
         <v>275</v>
       </c>
-      <c r="B96" s="20" t="str">
+      <c r="B102" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALLIU")</f>
         <v>BALLIU</v>
-      </c>
-      <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-      <c r="D96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
-        <v>277</v>
-      </c>
-      <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
-        <v>LUIZ FELIPE</v>
-      </c>
-      <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-      <c r="D97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
-      </c>
-      <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
-      </c>
-      <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-      <c r="D98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
-        <v>281</v>
-      </c>
-      <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
-        <v>ÓSCAR VALENTÍN</v>
-      </c>
-      <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-      <c r="D99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
-        <v>283</v>
-      </c>
-      <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
-        <v>PEDRO DÍAZ</v>
-      </c>
-      <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-      <c r="D100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),284.0)</f>
-        <v>284</v>
-      </c>
-      <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO GARCÍA")</f>
-        <v>ÁLVARO GARCÍA</v>
-      </c>
-      <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-      <c r="D101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
-        <v>286</v>
-      </c>
-      <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
-        <v>CAMELLO</v>
       </c>
       <c r="C102" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -6576,426 +4962,426 @@
     </row>
     <row r="103">
       <c r="A103" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
+        <v>277</v>
+      </c>
+      <c r="B103" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
+        <v>LUIZ FELIPE</v>
+      </c>
+      <c r="C103" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D103" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
+      </c>
+      <c r="B104" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
+      </c>
+      <c r="C104" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D104" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
+        <v>281</v>
+      </c>
+      <c r="B105" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
+        <v>ÓSCAR VALENTÍN</v>
+      </c>
+      <c r="C105" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D105" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
+        <v>282</v>
+      </c>
+      <c r="B106" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
+      </c>
+      <c r="C106" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D106" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
+      </c>
+      <c r="B107" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
+      </c>
+      <c r="C107" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D107" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),284.0)</f>
+        <v>284</v>
+      </c>
+      <c r="B108" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO GARCÍA")</f>
+        <v>ÁLVARO GARCÍA</v>
+      </c>
+      <c r="C108" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D108" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
+        <v>286</v>
+      </c>
+      <c r="B109" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
+        <v>CAMELLO</v>
+      </c>
+      <c r="C109" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D109" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
         <v>289</v>
       </c>
-      <c r="B103" s="20" t="str">
+      <c r="B110" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
         <v>ESTADIO</v>
       </c>
-      <c r="C103" s="20" t="str">
+      <c r="C110" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-      <c r="D103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="20">
+      <c r="D110" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
         <v>290</v>
       </c>
-      <c r="B104" s="20" t="str">
+      <c r="B111" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
         <v>REMIRO</v>
       </c>
-      <c r="C104" s="20" t="str">
+      <c r="C111" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-      <c r="D104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="20">
+      <c r="D111" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
         <v>292</v>
       </c>
-      <c r="B105" s="20" t="str">
+      <c r="B112" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
         <v>ARAMBURU</v>
       </c>
-      <c r="C105" s="20" t="str">
+      <c r="C112" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-      <c r="D105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="20">
+      <c r="D112" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),293.0)</f>
         <v>293</v>
       </c>
-      <c r="B106" s="20" t="str">
+      <c r="B113" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARITZ ELUSTONDO")</f>
         <v>ARITZ ELUSTONDO</v>
       </c>
-      <c r="C106" s="20" t="str">
+      <c r="C113" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-      <c r="D106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="20">
+      <c r="D113" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
         <v>295</v>
       </c>
-      <c r="B107" s="20" t="str">
+      <c r="B114" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
         <v>CALETA-CAR</v>
       </c>
-      <c r="C107" s="20" t="str">
+      <c r="C114" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-      <c r="D107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="20">
+      <c r="D114" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
         <v>296</v>
       </c>
-      <c r="B108" s="20" t="str">
+      <c r="B115" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
         <v>SERGIO GÓMEZ</v>
       </c>
-      <c r="C108" s="20" t="str">
+      <c r="C115" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-      <c r="D108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="20">
+      <c r="D115" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
         <v>299</v>
       </c>
-      <c r="B109" s="20" t="str">
+      <c r="B116" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
         <v>PABLO MARIN</v>
       </c>
-      <c r="C109" s="20" t="str">
+      <c r="C116" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-      <c r="D109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="20">
+      <c r="D116" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
+        <v>302</v>
+      </c>
+      <c r="B117" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
+        <v>KUBO</v>
+      </c>
+      <c r="C117" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+      <c r="D117" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
         <v>309</v>
       </c>
-      <c r="B110" s="20" t="str">
+      <c r="B118" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
         <v>NYLAND</v>
       </c>
-      <c r="C110" s="20" t="str">
+      <c r="C118" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
-      <c r="D110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="20">
+      <c r="D118" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
         <v>312</v>
       </c>
-      <c r="B111" s="20" t="str">
+      <c r="B119" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
         <v>AZPILICUETA</v>
       </c>
-      <c r="C111" s="20" t="str">
+      <c r="C119" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
-      <c r="D111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="20">
+      <c r="D119" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
         <v>313</v>
       </c>
-      <c r="B112" s="20" t="str">
+      <c r="B120" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
         <v>KIKE SALAS</v>
       </c>
-      <c r="C112" s="20" t="str">
+      <c r="C120" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
-      <c r="D112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20">
+      <c r="D120" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),316.0)</f>
         <v>316</v>
       </c>
-      <c r="B113" s="20" t="str">
+      <c r="B121" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GUDELJ")</f>
         <v>GUDELJ</v>
       </c>
-      <c r="C113" s="20" t="str">
+      <c r="C121" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
-      <c r="D113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="20">
+      <c r="D121" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
         <v>317</v>
       </c>
-      <c r="B114" s="20" t="str">
+      <c r="B122" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
         <v>AGOUME</v>
       </c>
-      <c r="C114" s="20" t="str">
+      <c r="C122" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
-      <c r="D114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20">
+      <c r="D122" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
         <v>321</v>
       </c>
-      <c r="B115" s="20" t="str">
+      <c r="B123" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
         <v>EJUKE</v>
       </c>
-      <c r="C115" s="20" t="str">
+      <c r="C123" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
-      <c r="D115" s="20">
+      <c r="D123" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="20">
+    <row r="124">
+      <c r="A124" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),322.0)</f>
+        <v>322</v>
+      </c>
+      <c r="B124" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISAAC ROMERO")</f>
+        <v>ISAAC ROMERO</v>
+      </c>
+      <c r="C124" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D124" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
         <v>323</v>
       </c>
-      <c r="B116" s="20" t="str">
+      <c r="B125" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
         <v>AKOR ADAMS</v>
       </c>
-      <c r="C116" s="20" t="str">
+      <c r="C125" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
-      <c r="D116" s="20">
+      <c r="D125" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="20">
+    <row r="126">
+      <c r="A126" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
         <v>325</v>
       </c>
-      <c r="B117" s="20" t="str">
+      <c r="B126" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
         <v>ESCUDO</v>
-      </c>
-      <c r="C117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
-        <v>326</v>
-      </c>
-      <c r="B118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
-      </c>
-      <c r="C118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
-        <v>327</v>
-      </c>
-      <c r="B119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
-        <v>DIMITRIEVSKI</v>
-      </c>
-      <c r="C119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
-      </c>
-      <c r="B120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
-      </c>
-      <c r="C120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
-      </c>
-      <c r="B121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
-      </c>
-      <c r="C121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
-        <v>331</v>
-      </c>
-      <c r="B122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
-        <v>COPETE</v>
-      </c>
-      <c r="C122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
-      </c>
-      <c r="B123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
-      </c>
-      <c r="C123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),335.0)</f>
-        <v>335</v>
-      </c>
-      <c r="B124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTAMARÍA")</f>
-        <v>SANTAMARÍA</v>
-      </c>
-      <c r="C124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
-        <v>337</v>
-      </c>
-      <c r="B125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
-        <v>ANDRÉ ALMEIDA</v>
-      </c>
-      <c r="C125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
-      </c>
-      <c r="B126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
       </c>
       <c r="C126" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -7008,12 +5394,12 @@
     </row>
     <row r="127">
       <c r="A127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),341.0)</f>
-        <v>341</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
+        <v>326</v>
       </c>
       <c r="B127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANJUMA")</f>
-        <v>DANJUMA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C127" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -7026,412 +5412,412 @@
     </row>
     <row r="128">
       <c r="A128" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
+      </c>
+      <c r="B128" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
+      </c>
+      <c r="C128" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D128" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
+      </c>
+      <c r="B129" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
+      </c>
+      <c r="C129" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D129" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
+        <v>329</v>
+      </c>
+      <c r="B130" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
+        <v>CORREIA</v>
+      </c>
+      <c r="C130" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D130" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
+      </c>
+      <c r="B131" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
+      </c>
+      <c r="C131" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D131" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
+        <v>331</v>
+      </c>
+      <c r="B132" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
+        <v>COPETE</v>
+      </c>
+      <c r="C132" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D132" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
+      </c>
+      <c r="B133" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
+      </c>
+      <c r="C133" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D133" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),335.0)</f>
+        <v>335</v>
+      </c>
+      <c r="B134" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTAMARÍA")</f>
+        <v>SANTAMARÍA</v>
+      </c>
+      <c r="C134" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D134" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
+        <v>337</v>
+      </c>
+      <c r="B135" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
+        <v>ANDRÉ ALMEIDA</v>
+      </c>
+      <c r="C135" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D135" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
+      </c>
+      <c r="B136" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
+      </c>
+      <c r="C136" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D136" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),341.0)</f>
+        <v>341</v>
+      </c>
+      <c r="B137" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANJUMA")</f>
+        <v>DANJUMA</v>
+      </c>
+      <c r="C137" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D137" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
         <v>343</v>
       </c>
-      <c r="B128" s="20" t="str">
+      <c r="B138" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
         <v>ESCUDO</v>
       </c>
-      <c r="C128" s="20" t="str">
+      <c r="C138" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
-      <c r="D128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20">
+      <c r="D138" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
         <v>343</v>
       </c>
-      <c r="B129" s="20" t="str">
+      <c r="B139" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
         <v>ESTADIO</v>
       </c>
-      <c r="C129" s="20" t="str">
+      <c r="C139" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
-      <c r="D129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="20">
+      <c r="D139" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),347.0)</f>
         <v>347</v>
       </c>
-      <c r="B130" s="20" t="str">
+      <c r="B140" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOYTH")</f>
         <v>FOYTH</v>
       </c>
-      <c r="C130" s="20" t="str">
+      <c r="C140" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
-      <c r="D130" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="20">
+      <c r="D140" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
         <v>350</v>
       </c>
-      <c r="B131" s="20" t="str">
+      <c r="B141" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
         <v>SERGI CARDONA</v>
       </c>
-      <c r="C131" s="20" t="str">
+      <c r="C141" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
-      <c r="D131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="20">
+      <c r="D141" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
         <v>351</v>
       </c>
-      <c r="B132" s="20" t="str">
+      <c r="B142" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
         <v>SANTI COMESAÑA</v>
       </c>
-      <c r="C132" s="20" t="str">
+      <c r="C142" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
-      <c r="D132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="20">
+      <c r="D142" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
         <v>352</v>
       </c>
-      <c r="B133" s="20" t="str">
+      <c r="B143" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
         <v>PAPE GUEYE</v>
       </c>
-      <c r="C133" s="20" t="str">
+      <c r="C143" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
-      <c r="D133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="20">
+      <c r="D143" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),354.0)</f>
         <v>354</v>
       </c>
-      <c r="B134" s="20" t="str">
+      <c r="B144" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"THOMAS")</f>
         <v>THOMAS</v>
       </c>
-      <c r="C134" s="20" t="str">
+      <c r="C144" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
-      <c r="D134" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="20">
+      <c r="D144" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
         <v>355</v>
       </c>
-      <c r="B135" s="20" t="str">
+      <c r="B145" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
         <v>MOLEIRO</v>
       </c>
-      <c r="C135" s="20" t="str">
+      <c r="C145" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
-      <c r="D135" s="20">
+      <c r="D145" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="20">
+    <row r="146">
+      <c r="A146" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
         <v>361</v>
       </c>
-      <c r="B136" s="20" t="str">
+      <c r="B146" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
         <v>D. ALAVÉS</v>
       </c>
-      <c r="C136" s="20" t="str">
+      <c r="C146" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
         <v>¡VAMOS!</v>
       </c>
-      <c r="D136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="20">
+      <c r="D146" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
         <v>369</v>
       </c>
-      <c r="B137" s="20" t="str">
+      <c r="B147" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
         <v>GETAFE CF</v>
       </c>
-      <c r="C137" s="20" t="str">
+      <c r="C147" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
         <v>¡VAMOS!</v>
       </c>
-      <c r="D137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="20">
+      <c r="D147" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
         <v>371</v>
       </c>
-      <c r="B138" s="20" t="str">
+      <c r="B148" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
         <v>LEVANTE UD</v>
       </c>
-      <c r="C138" s="20" t="str">
+      <c r="C148" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
         <v>¡VAMOS!</v>
       </c>
-      <c r="D138" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="20">
+      <c r="D148" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),381.0)</f>
         <v>381</v>
       </c>
-      <c r="B139" s="20" t="str">
+      <c r="B149" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SIVERA")</f>
         <v>SIVERA</v>
       </c>
-      <c r="C139" s="20" t="str">
+      <c r="C149" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
         <v>D. ALAVÉS</v>
       </c>
-      <c r="D139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="20">
+      <c r="D149" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
         <v>387</v>
       </c>
-      <c r="B140" s="20" t="str">
+      <c r="B150" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
         <v>AGIRREZABALA</v>
       </c>
-      <c r="C140" s="20" t="str">
+      <c r="C150" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
-      </c>
-      <c r="D140" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),391.0)</f>
-        <v>391</v>
-      </c>
-      <c r="B141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
-      </c>
-      <c r="C141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-      <c r="D141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
-      </c>
-      <c r="B142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
-      </c>
-      <c r="C142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-      <c r="D142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
-      </c>
-      <c r="B143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
-      </c>
-      <c r="C143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-      <c r="D143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
-        <v>399</v>
-      </c>
-      <c r="B144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
-      </c>
-      <c r="C144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-      <c r="D144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),400.0)</f>
-        <v>400</v>
-      </c>
-      <c r="B145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO GARCÍA")</f>
-        <v>PABLO GARCÍA</v>
-      </c>
-      <c r="C145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-      <c r="D145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
-        <v>404</v>
-      </c>
-      <c r="B146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
-      </c>
-      <c r="C146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-      <c r="D146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
-        <v>407</v>
-      </c>
-      <c r="B147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
-        <v>CARLOS ÁLVAREZ</v>
-      </c>
-      <c r="C147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-      <c r="D147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
-        <v>409</v>
-      </c>
-      <c r="B148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
-        <v>FRAN GONZÁLEZ</v>
-      </c>
-      <c r="C148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
-      </c>
-      <c r="B149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
-      </c>
-      <c r="C149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D149" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
-      </c>
-      <c r="B150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
-      </c>
-      <c r="C150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D150" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -7440,306 +5826,486 @@
     </row>
     <row r="151">
       <c r="A151" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),391.0)</f>
+        <v>391</v>
+      </c>
+      <c r="B151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
+      </c>
+      <c r="C151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
+      </c>
+      <c r="D151" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
+      </c>
+      <c r="B152" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
+      </c>
+      <c r="C152" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+      <c r="D152" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
+      </c>
+      <c r="B153" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
+      </c>
+      <c r="C153" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D153" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
+        <v>399</v>
+      </c>
+      <c r="B154" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
+      </c>
+      <c r="C154" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D154" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),400.0)</f>
+        <v>400</v>
+      </c>
+      <c r="B155" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO GARCÍA")</f>
+        <v>PABLO GARCÍA</v>
+      </c>
+      <c r="C155" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D155" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
+      </c>
+      <c r="B156" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
+      </c>
+      <c r="C156" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D156" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
+        <v>407</v>
+      </c>
+      <c r="B157" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
+        <v>CARLOS ÁLVAREZ</v>
+      </c>
+      <c r="C157" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+      <c r="D157" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
+        <v>409</v>
+      </c>
+      <c r="B158" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
+        <v>FRAN GONZÁLEZ</v>
+      </c>
+      <c r="C158" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D158" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
+      </c>
+      <c r="B159" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
+      </c>
+      <c r="C159" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D159" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
+      </c>
+      <c r="B160" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
+      </c>
+      <c r="C160" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D160" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
         <v>416</v>
       </c>
-      <c r="B151" s="20" t="str">
+      <c r="B161" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
         <v>SOTELO</v>
       </c>
-      <c r="C151" s="20" t="str">
+      <c r="C161" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
-      <c r="D151" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="20">
+      <c r="D161" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
         <v>419</v>
       </c>
-      <c r="B152" s="20" t="str">
+      <c r="B162" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
         <v>MILLA</v>
       </c>
-      <c r="C152" s="20" t="str">
+      <c r="C162" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
         <v>GETAFE CF</v>
       </c>
-      <c r="D152" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="20">
+      <c r="D162" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
         <v>421</v>
       </c>
-      <c r="B153" s="20" t="str">
+      <c r="B163" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
         <v>AIMAR OROZ</v>
       </c>
-      <c r="C153" s="20" t="str">
+      <c r="C163" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
         <v>CA OSASUNA</v>
       </c>
-      <c r="D153" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="20">
+      <c r="D163" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
         <v>422</v>
       </c>
-      <c r="B154" s="20" t="str">
+      <c r="B164" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
         <v>CAZORLA</v>
       </c>
-      <c r="C154" s="20" t="str">
+      <c r="C164" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
         <v>REAL OVIEDO</v>
       </c>
-      <c r="D154" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="20">
+      <c r="D164" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
         <v>425</v>
       </c>
-      <c r="B155" s="20" t="str">
+      <c r="B165" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
         <v>CARLOS VICENTE</v>
       </c>
-      <c r="C155" s="20" t="str">
+      <c r="C165" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
         <v>D. ALAVÉS</v>
       </c>
-      <c r="D155" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="20">
+      <c r="D165" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
         <v>436</v>
       </c>
-      <c r="B156" s="20" t="str">
+      <c r="B166" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
         <v>CARLOS SOLER</v>
       </c>
-      <c r="C156" s="20" t="str">
+      <c r="C166" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
-      <c r="D156" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="20">
+      <c r="D166" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
         <v>439</v>
       </c>
-      <c r="B157" s="20" t="str">
+      <c r="B167" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
         <v>ALEXIS SÁNCHEZ</v>
       </c>
-      <c r="C157" s="20" t="str">
+      <c r="C167" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
-      <c r="D157" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="20">
+      <c r="D167" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
         <v>444</v>
       </c>
-      <c r="B158" s="20" t="str">
+      <c r="B168" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
         <v>OBLAK</v>
       </c>
-      <c r="C158" s="20" t="str">
+      <c r="C168" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
         <v>ATLÉTICO DE MADRID</v>
       </c>
-      <c r="D158" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="20">
+      <c r="D168" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
         <v>448</v>
       </c>
-      <c r="B159" s="20" t="str">
+      <c r="B169" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
         <v>GRIEZMANN</v>
       </c>
-      <c r="C159" s="20" t="str">
+      <c r="C169" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
         <v>ATLÉTICO DE MADRID</v>
       </c>
-      <c r="D159" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="20">
+      <c r="D169" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),449.0)</f>
         <v>449</v>
       </c>
-      <c r="B160" s="20" t="str">
+      <c r="B170" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
         <v>KOUNDÉ</v>
       </c>
-      <c r="C160" s="20" t="str">
+      <c r="C170" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
         <v>FC BARCELONA</v>
       </c>
-      <c r="D160" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="20">
+      <c r="D170" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
         <v>452</v>
       </c>
-      <c r="B161" s="20" t="str">
+      <c r="B171" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
         <v>LEWANDOWSKI</v>
       </c>
-      <c r="C161" s="20" t="str">
+      <c r="C171" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
         <v>FC BARCELONA</v>
       </c>
-      <c r="D161" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="20">
+      <c r="D171" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
         <v>456</v>
       </c>
-      <c r="B162" s="20" t="str">
+      <c r="B172" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
         <v>ANTONY</v>
       </c>
-      <c r="C162" s="20" t="str">
+      <c r="C172" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
-      <c r="D162" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="20">
+      <c r="D172" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
         <v>458</v>
       </c>
-      <c r="B163" s="20" t="str">
+      <c r="B173" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
         <v>CARRERAS</v>
       </c>
-      <c r="C163" s="20" t="str">
+      <c r="C173" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
         <v>REAL MADRID</v>
       </c>
-      <c r="D163" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="20">
+      <c r="D173" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
         <v>462</v>
       </c>
-      <c r="B164" s="20" t="str">
+      <c r="B174" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
         <v>ISI</v>
       </c>
-      <c r="C164" s="20" t="str">
+      <c r="C174" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
         <v>RAYO VALLECANO</v>
       </c>
-      <c r="D164" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="20">
+      <c r="D174" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),467.0)</f>
         <v>467</v>
       </c>
-      <c r="B165" s="20" t="str">
+      <c r="B175" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PÉPÉ")</f>
         <v>PÉPÉ</v>
       </c>
-      <c r="C165" s="20" t="str">
+      <c r="C175" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
-      <c r="D165" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="20">
+      <c r="D175" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B166" s="20" t="str">
+      <c r="B176" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C166" s="20" t="str">
+      <c r="C176" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D166" s="20">
+      <c r="D176" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="20">
+    <row r="177">
+      <c r="A177" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),477.0)</f>
         <v>477</v>
       </c>
-      <c r="B167" s="20" t="str">
+      <c r="B177" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD INVENCIBLE")</f>
         <v>CARD INVENCIBLE</v>
       </c>
-      <c r="C167" s="20" t="str">
+      <c r="C177" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
         <v>ÚNICA</v>
       </c>
-      <c r="D167" s="20">
+      <c r="D177" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
@@ -8323,6 +6889,9 @@
       <c r="D39" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E39" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="21">
@@ -8385,6 +6954,9 @@
       <c r="D43" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E43" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="21">
@@ -9259,7 +7831,7 @@
         <v>20</v>
       </c>
       <c r="E104" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="105">
@@ -9591,6 +8163,9 @@
       <c r="D126" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E126" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="21">
@@ -9778,6 +8353,9 @@
       <c r="D139" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E139" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="21">
@@ -10259,6 +8837,9 @@
       <c r="D173" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E173" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="21">
@@ -10338,7 +8919,9 @@
       <c r="C178" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D178" s="21"/>
+      <c r="D178" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="21">
@@ -10720,7 +9303,9 @@
       <c r="C205" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="D205" s="21"/>
+      <c r="D205" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="21">
@@ -10797,6 +9382,9 @@
       <c r="D210" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E210" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="21">
@@ -11116,7 +9704,9 @@
       <c r="C231" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="D231" s="21"/>
+      <c r="D231" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="21">
@@ -11234,7 +9824,9 @@
       <c r="C239" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D239" s="21"/>
+      <c r="D239" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="21">
@@ -11702,7 +10294,9 @@
       <c r="C271" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="D271" s="21"/>
+      <c r="D271" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="21">
@@ -11861,6 +10455,9 @@
       <c r="D282" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E282" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="21">
@@ -12160,6 +10757,9 @@
       <c r="D302" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E302" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="21">
@@ -12317,7 +10917,7 @@
         <v>20</v>
       </c>
       <c r="E313" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="314">
@@ -12452,6 +11052,9 @@
       <c r="D322" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E322" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="21">
@@ -12563,6 +11166,9 @@
       <c r="D329" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E329" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="21">
@@ -12779,7 +11385,7 @@
         <v>20</v>
       </c>
       <c r="E343" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="344">
@@ -13147,7 +11753,9 @@
       <c r="C6" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="21"/>
+      <c r="D6" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21">
@@ -13354,7 +11962,7 @@
         <v>20</v>
       </c>
       <c r="E20" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
@@ -15844,7 +14452,9 @@
       <c r="C1" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="399">
   <si>
     <t>Última actualización:</t>
   </si>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B1" s="2">
         <f>TODAY()</f>
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1833,15 +1833,15 @@
       </c>
       <c r="C3" s="9">
         <f>COUNTIF(REGULARES!D:D, "SI")</f>
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="D3" s="9">
         <f t="shared" ref="D3:D12" si="1">B3-C3</f>
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E4" si="2">(C3/B3)</f>
-        <v>0.8027777778</v>
+        <v>0.8305555556</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E3, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1881,15 +1881,15 @@
       </c>
       <c r="C5" s="9">
         <f>COUNTIF('¡VAMOS! (361–380)'!D:D, "SI")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="9">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" ref="E5:E13" si="3">C5/B5</f>
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F5" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E5, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1953,15 +1953,15 @@
       </c>
       <c r="C8" s="14">
         <f>COUNTIF('Diamantes (397–414)'!D:D, "SI")</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D8" s="15">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" s="10">
         <f t="shared" si="3"/>
-        <v>0.7777777778</v>
+        <v>0.9444444444</v>
       </c>
       <c r="F8" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E8, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2025,15 +2025,15 @@
       </c>
       <c r="C11" s="14">
         <f>COUNTIF('Super Cracks (442–467)'!D:D, "SI")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11" s="15">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="3"/>
-        <v>0.7307692308</v>
+        <v>0.8076923077</v>
       </c>
       <c r="F11" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E11, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="4"/>
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="4"/>
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>0.7851405622</v>
+        <v>0.8192771084</v>
       </c>
       <c r="F13" s="19" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E13, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2281,9 +2281,6 @@
       <c r="D2" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="21">
@@ -2431,9 +2428,6 @@
       </c>
       <c r="D13" s="21" t="s">
         <v>20</v>
-      </c>
-      <c r="E13" s="22">
-        <v>1.0</v>
       </c>
     </row>
     <row r="14">
@@ -2656,9 +2650,6 @@
       <c r="D10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="21">
@@ -2704,7 +2695,9 @@
       <c r="C1" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21">
@@ -2731,9 +2724,6 @@
       <c r="D3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="21">
@@ -2805,9 +2795,6 @@
       <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="21">
@@ -2905,9 +2892,6 @@
       <c r="D15" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="21">
@@ -2964,7 +2948,9 @@
       <c r="C19" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="D19" s="21"/>
+      <c r="D19" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="21">
@@ -3063,9 +3049,6 @@
       </c>
       <c r="D26" s="21" t="s">
         <v>20</v>
-      </c>
-      <c r="E26" s="22">
-        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -3198,12 +3181,12 @@
     </row>
     <row r="5">
       <c r="A5" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
+        <v>7</v>
       </c>
       <c r="B5" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TENAGLIA")</f>
-        <v>TENAGLIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PARADA")</f>
+        <v>PARADA</v>
       </c>
       <c r="C5" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -3216,12 +3199,12 @@
     </row>
     <row r="6">
       <c r="A6" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
+        <v>15</v>
       </c>
       <c r="B6" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PARADA")</f>
-        <v>PARADA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
+        <v>CARLOS VICENTE</v>
       </c>
       <c r="C6" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -3234,16 +3217,16 @@
     </row>
     <row r="7">
       <c r="A7" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
-        <v>15</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="B7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
-        <v>CARLOS VICENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D7" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3252,16 +3235,16 @@
     </row>
     <row r="8">
       <c r="A8" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
-        <v>17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
+        <v>21</v>
       </c>
       <c r="B8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYÉ")</f>
-        <v>BOYÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PADILLA")</f>
+        <v>PADILLA</v>
       </c>
       <c r="C8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D8" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3270,16 +3253,16 @@
     </row>
     <row r="9">
       <c r="A9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
+        <v>23</v>
       </c>
       <c r="B9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIANO")</f>
-        <v>MARIANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VIVIAN")</f>
+        <v>VIVIAN</v>
       </c>
       <c r="C9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D9" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3288,12 +3271,12 @@
     </row>
     <row r="10">
       <c r="A10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="B10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUIZ DE GALARRETA")</f>
+        <v>RUIZ DE GALARRETA</v>
       </c>
       <c r="C10" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3306,12 +3289,12 @@
     </row>
     <row r="11">
       <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
-        <v>21</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
+        <v>34</v>
       </c>
       <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PADILLA")</f>
-        <v>PADILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
+        <v>MAROAN</v>
       </c>
       <c r="C11" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3324,16 +3307,16 @@
     </row>
     <row r="12">
       <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
+        <v>39</v>
       </c>
       <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VIVIAN")</f>
-        <v>VIVIAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MUSSO")</f>
+        <v>MUSSO</v>
       </c>
       <c r="C12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D12" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3342,16 +3325,16 @@
     </row>
     <row r="13">
       <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
-        <v>27</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
       </c>
       <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUIZ DE GALARRETA")</f>
-        <v>RUIZ DE GALARRETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
+        <v>ALMADA</v>
       </c>
       <c r="C13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D13" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3360,16 +3343,16 @@
     </row>
     <row r="14">
       <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
-        <v>34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
+        <v>52</v>
       </c>
       <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
-        <v>MAROAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
+        <v>JULIÁN ALVAREZ</v>
       </c>
       <c r="C14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D14" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3378,16 +3361,16 @@
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
-        <v>39</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
+        <v>55</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MUSSO")</f>
-        <v>MUSSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D15" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3396,16 +3379,16 @@
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
-        <v>40</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
-        <v>MARCOS LLORENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
+        <v>FERMÍN</v>
       </c>
       <c r="C16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D16" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3414,16 +3397,16 @@
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
-        <v>LENGLET</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
+        <v>DANI OLMO</v>
       </c>
       <c r="C17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D17" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3432,16 +3415,16 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.0)</f>
-        <v>43</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HANCKO")</f>
-        <v>HANCKO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D18" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3450,16 +3433,16 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
-        <v>ALMADA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
+        <v>PAU LÓPEZ</v>
       </c>
       <c r="C19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D19" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3468,16 +3451,16 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
-        <v>52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
-        <v>JULIÁN ALVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
+        <v>BELLERÍN</v>
       </c>
       <c r="C20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D20" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3486,16 +3469,16 @@
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
-        <v>55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D21" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3504,16 +3487,16 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
-        <v>56</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
+        <v>84</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOAN GARCÍA")</f>
-        <v>JOAN GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
+        <v>PABLO FORNALS</v>
       </c>
       <c r="C22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D22" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3522,16 +3505,16 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
-        <v>66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
-        <v>FERMÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
       </c>
       <c r="C23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D23" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3540,16 +3523,16 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
-        <v>67</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
+        <v>91</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
-        <v>DANI OLMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D24" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3558,16 +3541,16 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
-        <v>73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
+        <v>94</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
+        <v>JAVI RUEDA</v>
       </c>
       <c r="C25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D25" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3576,16 +3559,16 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
-        <v>PAU LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D26" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3594,16 +3577,16 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
-        <v>76</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
-        <v>BELLERÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D27" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3612,16 +3595,16 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D28" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3630,34 +3613,34 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
-        <v>84</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
+        <v>104</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
-        <v>PABLO FORNALS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
+        <v>SWEDBERG</v>
       </c>
       <c r="C29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D30" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3666,12 +3649,12 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
-        <v>91</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
+        <v>IAGO ASPAS</v>
       </c>
       <c r="C31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3684,12 +3667,12 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93.0)</f>
-        <v>93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN VILLAR")</f>
-        <v>IVÁN VILLAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C32" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3702,12 +3685,12 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
-        <v>94</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
-        <v>JAVI RUEDA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3720,16 +3703,16 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
+        <v>IÑAKI PEÑA</v>
       </c>
       <c r="C34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D34" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3738,16 +3721,16 @@
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D35" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3756,16 +3739,16 @@
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
+        <v>ÁLVARO NÚÑEZ</v>
       </c>
       <c r="C36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D36" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3774,34 +3757,34 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
-        <v>104</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
-        <v>SWEDBERG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D38" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3810,16 +3793,16 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
-        <v>106</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
+        <v>126</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
-        <v>IAGO ASPAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
+        <v>RAFA MIR</v>
       </c>
       <c r="C39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D39" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3828,16 +3811,16 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
+        <v>127</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D40" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3846,16 +3829,16 @@
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D41" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3864,16 +3847,16 @@
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
-        <v>IÑAKI PEÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D42" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3882,16 +3865,16 @@
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
+        <v>139</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
+        <v>ANTONIU ROCA</v>
       </c>
       <c r="C43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D43" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3900,16 +3883,16 @@
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
-        <v>112</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
-        <v>ÁLVARO NÚÑEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D44" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3918,16 +3901,16 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D45" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3936,16 +3919,16 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
-        <v>117</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE REDONDO")</f>
-        <v>FEDE REDONDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D46" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3954,16 +3937,16 @@
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D47" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3972,16 +3955,16 @@
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
-        <v>126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
+        <v>153</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
-        <v>RAFA MIR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
+        <v>DIEGO RICO</v>
       </c>
       <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D48" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3990,16 +3973,16 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
-        <v>127</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B49" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
         <v>ESCUDO</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D49" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4008,16 +3991,16 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D50" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4026,16 +4009,16 @@
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
+        <v>174</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
+        <v>IVÁN MARTÍN</v>
       </c>
       <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D51" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4044,16 +4027,16 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
-        <v>139</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
-        <v>ANTONIU ROCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
       </c>
       <c r="C52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D52" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4062,16 +4045,16 @@
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
+        <v>176</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
+        <v>JOEL ROCA</v>
       </c>
       <c r="C53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D53" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4080,16 +4063,16 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
+        <v>189</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
+        <v>PAMPÍN</v>
       </c>
       <c r="C54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D54" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4098,16 +4081,16 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
+        <v>202</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
+        <v>CARVAJAL</v>
       </c>
       <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D55" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4116,16 +4099,16 @@
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D56" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4134,16 +4117,16 @@
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
       </c>
       <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D57" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4152,16 +4135,16 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
-        <v>153</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
+        <v>212</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
-        <v>DIEGO RICO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
       </c>
       <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D58" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4170,16 +4153,16 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D59" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4188,16 +4171,16 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
+        <v>219</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
+        <v>BERGSTRÖM</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D60" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4206,16 +4189,16 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),173.0)</f>
-        <v>173</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OUNAHI")</f>
-        <v>OUNAHI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D61" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4224,16 +4207,16 @@
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
-        <v>174</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
+        <v>225</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
-        <v>IVÁN MARTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
+        <v>MOJICA</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D62" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4242,52 +4225,52 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D63" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
+      </c>
+      <c r="B64" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C64" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D64" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
-        <v>176</v>
-      </c>
-      <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
-        <v>JOEL ROCA</v>
-      </c>
-      <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
-      </c>
-      <c r="D64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.0)</f>
-        <v>177</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TSYGANKOV")</f>
-        <v>TSYGANKOV</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D65" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4296,16 +4279,16 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),181.0)</f>
-        <v>181</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
+        <v>245</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
+        <v>MONCAYOLA</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D66" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4314,16 +4297,16 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),184.0)</f>
-        <v>184</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
+        <v>248</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TOLJAN")</f>
-        <v>TOLJAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D67" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4332,16 +4315,16 @@
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),185.0)</f>
-        <v>185</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DELA")</f>
-        <v>DELA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D68" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4350,16 +4333,16 @@
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.0)</f>
-        <v>186</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELGEZABAL")</f>
-        <v>ELGEZABAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D69" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4368,16 +4351,16 @@
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
-        <v>189</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
-        <v>PAMPÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4386,16 +4369,16 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
-        <v>202</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
-        <v>CARVAJAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D71" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4404,16 +4387,16 @@
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),208.0)</f>
-        <v>208</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
+        <v>265</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TCHOUAMÉNI")</f>
-        <v>TCHOUAMÉNI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
+        <v>ILIC</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D72" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4422,16 +4405,16 @@
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D73" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4440,16 +4423,16 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),210.0)</f>
-        <v>210</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLINGHAM")</f>
-        <v>BELLINGHAM</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
       </c>
       <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D74" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4458,16 +4441,16 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
-        <v>211</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
+        <v>281</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
-        <v>GÜLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
+        <v>ÓSCAR VALENTÍN</v>
       </c>
       <c r="C75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D75" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4476,16 +4459,16 @@
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
-        <v>212</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
+        <v>282</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
       </c>
       <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D76" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4494,16 +4477,16 @@
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
-        <v>213</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRYGO")</f>
-        <v>RODRYGO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D77" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4512,16 +4495,16 @@
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.0)</f>
-        <v>214</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
+        <v>286</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MBAPPÉ")</f>
-        <v>MBAPPÉ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
+        <v>CAMELLO</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D78" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4530,16 +4513,16 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
+        <v>290</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D79" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4548,16 +4531,16 @@
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
-        <v>219</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
+        <v>292</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
-        <v>BERGSTRÖM</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
+        <v>ARAMBURU</v>
       </c>
       <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D80" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4566,16 +4549,16 @@
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
       </c>
       <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D81" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4584,16 +4567,16 @@
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
-        <v>225</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
+        <v>296</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
-        <v>MOJICA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
+        <v>SERGIO GÓMEZ</v>
       </c>
       <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D82" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4602,16 +4585,16 @@
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),226.0)</f>
-        <v>226</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SAMÚ COSTA")</f>
-        <v>SAMÚ COSTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D83" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4620,16 +4603,16 @@
     </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.0)</f>
-        <v>229</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
+        <v>302</v>
       </c>
       <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORLANES")</f>
-        <v>MORLANES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
+        <v>KUBO</v>
       </c>
       <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D84" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4638,16 +4621,16 @@
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D85" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4656,52 +4639,52 @@
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
+        <v>312</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
+        <v>AZPILICUETA</v>
       </c>
       <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D86" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
+      </c>
+      <c r="B87" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
+      </c>
+      <c r="C87" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D87" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
-      </c>
-      <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
-      </c>
-      <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
-        <v>237</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
+        <v>317</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
-        <v>AITOR FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
+        <v>AGOUME</v>
       </c>
       <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D88" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4710,52 +4693,52 @@
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
-        <v>242</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUAN CRUZ")</f>
-        <v>JUAN CRUZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
       </c>
       <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
-        <v>245</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
-        <v>MONCAYOLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
       </c>
       <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),247.0)</f>
-        <v>247</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUBÉN GARCÍA")</f>
-        <v>RUBÉN GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D91" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4764,16 +4747,16 @@
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
-        <v>248</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
+        <v>326</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D92" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4782,16 +4765,16 @@
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
       </c>
       <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D93" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4800,16 +4783,16 @@
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),253.0)</f>
-        <v>253</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
       </c>
       <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D94" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4818,16 +4801,16 @@
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),255.0)</f>
-        <v>255</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
+        <v>329</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLDOVAN")</f>
-        <v>MOLDOVAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
+        <v>CORREIA</v>
       </c>
       <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D95" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4836,16 +4819,16 @@
     </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
       </c>
       <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D96" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4854,16 +4837,16 @@
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
+        <v>331</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
+        <v>COPETE</v>
       </c>
       <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D97" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4872,16 +4855,16 @@
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
       </c>
       <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D98" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4890,16 +4873,16 @@
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
-        <v>265</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
+        <v>337</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
-        <v>ILIC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
+        <v>ANDRÉ ALMEIDA</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D99" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4908,16 +4891,16 @@
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.0)</f>
-        <v>267</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BREKALO")</f>
-        <v>BREKALO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
       </c>
       <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D100" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4926,52 +4909,52 @@
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),275.0)</f>
-        <v>275</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALLIU")</f>
-        <v>BALLIU</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
-        <v>277</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
+        <v>350</v>
       </c>
       <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
-        <v>LUIZ FELIPE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
+        <v>SERGI CARDONA</v>
       </c>
       <c r="C103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D103" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4980,16 +4963,16 @@
     </row>
     <row r="104">
       <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
       </c>
       <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
       </c>
       <c r="C104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D104" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4998,16 +4981,16 @@
     </row>
     <row r="105">
       <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
-        <v>281</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
       </c>
       <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
-        <v>ÓSCAR VALENTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
       </c>
       <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D105" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5016,34 +4999,34 @@
     </row>
     <row r="106">
       <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
-        <v>282</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
+        <v>355</v>
       </c>
       <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
-        <v>ISI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
+        <v>MOLEIRO</v>
       </c>
       <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
-        <v>283</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
       </c>
       <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
-        <v>PEDRO DÍAZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D107" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5052,16 +5035,16 @@
     </row>
     <row r="108">
       <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),284.0)</f>
-        <v>284</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
       </c>
       <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO GARCÍA")</f>
-        <v>ÁLVARO GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="C108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D108" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5070,16 +5053,16 @@
     </row>
     <row r="109">
       <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
-        <v>286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
+        <v>371</v>
       </c>
       <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
-        <v>CAMELLO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="C109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D109" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5088,34 +5071,34 @@
     </row>
     <row r="110">
       <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),289.0)</f>
-        <v>289</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
       </c>
       <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
-        <v>290</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
       </c>
       <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
       </c>
       <c r="C111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D111" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5124,16 +5107,16 @@
     </row>
     <row r="112">
       <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
-        <v>292</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
       </c>
       <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
-        <v>ARAMBURU</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
       </c>
       <c r="C112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D112" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5142,16 +5125,16 @@
     </row>
     <row r="113">
       <c r="A113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),293.0)</f>
-        <v>293</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
+        <v>399</v>
       </c>
       <c r="B113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARITZ ELUSTONDO")</f>
-        <v>ARITZ ELUSTONDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
       </c>
       <c r="C113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D113" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5160,16 +5143,16 @@
     </row>
     <row r="114">
       <c r="A114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
       </c>
       <c r="B114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D114" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5178,16 +5161,16 @@
     </row>
     <row r="115">
       <c r="A115" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
-        <v>296</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
+        <v>407</v>
       </c>
       <c r="B115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
-        <v>SERGIO GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
+        <v>CARLOS ÁLVAREZ</v>
       </c>
       <c r="C115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D115" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5196,16 +5179,16 @@
     </row>
     <row r="116">
       <c r="A116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
+        <v>409</v>
       </c>
       <c r="B116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
+        <v>FRAN GONZÁLEZ</v>
       </c>
       <c r="C116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D116" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5214,16 +5197,16 @@
     </row>
     <row r="117">
       <c r="A117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
-        <v>302</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
       </c>
       <c r="B117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
-        <v>KUBO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
       </c>
       <c r="C117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D117" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5232,70 +5215,70 @@
     </row>
     <row r="118">
       <c r="A118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
       </c>
       <c r="B118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
       </c>
       <c r="C118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D118" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
+      </c>
+      <c r="B119" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
+      </c>
+      <c r="C119" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D119" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
+      </c>
+      <c r="B120" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
+      </c>
+      <c r="C120" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D120" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
-        <v>312</v>
-      </c>
-      <c r="B119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
-        <v>AZPILICUETA</v>
-      </c>
-      <c r="C119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="D119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
-      </c>
-      <c r="B120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
-      </c>
-      <c r="C120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="D120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="121">
       <c r="A121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),316.0)</f>
-        <v>316</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
+        <v>421</v>
       </c>
       <c r="B121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GUDELJ")</f>
-        <v>GUDELJ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
       </c>
       <c r="C121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D121" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5304,16 +5287,16 @@
     </row>
     <row r="122">
       <c r="A122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
-        <v>317</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
       </c>
       <c r="B122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
-        <v>AGOUME</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
       </c>
       <c r="C122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D122" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5322,34 +5305,34 @@
     </row>
     <row r="123">
       <c r="A123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
       </c>
       <c r="B123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
       </c>
       <c r="C123" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
       <c r="D123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),322.0)</f>
-        <v>322</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
+        <v>448</v>
       </c>
       <c r="B124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISAAC ROMERO")</f>
-        <v>ISAAC ROMERO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
+        <v>GRIEZMANN</v>
       </c>
       <c r="C124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D124" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5358,34 +5341,34 @@
     </row>
     <row r="125">
       <c r="A125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
+        <v>452</v>
       </c>
       <c r="B125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
+        <v>LEWANDOWSKI</v>
       </c>
       <c r="C125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
+        <v>458</v>
       </c>
       <c r="B126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
+        <v>CARRERAS</v>
       </c>
       <c r="C126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D126" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5394,16 +5377,16 @@
     </row>
     <row r="127">
       <c r="A127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
-        <v>326</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
+        <v>462</v>
       </c>
       <c r="B127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
       </c>
       <c r="C127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D127" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5412,902 +5395,20 @@
     </row>
     <row r="128">
       <c r="A128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
-        <v>327</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
+        <v>469</v>
       </c>
       <c r="B128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
-        <v>DIMITRIEVSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
+        <v>NICO WILLIAMS</v>
       </c>
       <c r="C128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
+        <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
       <c r="D128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
-      </c>
-      <c r="B129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
-      </c>
-      <c r="C129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
-        <v>329</v>
-      </c>
-      <c r="B130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
-        <v>CORREIA</v>
-      </c>
-      <c r="C130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D130" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
-      </c>
-      <c r="B131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
-      </c>
-      <c r="C131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
-        <v>331</v>
-      </c>
-      <c r="B132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
-        <v>COPETE</v>
-      </c>
-      <c r="C132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
-      </c>
-      <c r="B133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
-      </c>
-      <c r="C133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),335.0)</f>
-        <v>335</v>
-      </c>
-      <c r="B134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTAMARÍA")</f>
-        <v>SANTAMARÍA</v>
-      </c>
-      <c r="C134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D134" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
-        <v>337</v>
-      </c>
-      <c r="B135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
-        <v>ANDRÉ ALMEIDA</v>
-      </c>
-      <c r="C135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D135" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
-      </c>
-      <c r="B136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
-      </c>
-      <c r="C136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),341.0)</f>
-        <v>341</v>
-      </c>
-      <c r="B137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANJUMA")</f>
-        <v>DANJUMA</v>
-      </c>
-      <c r="C137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
-      </c>
-      <c r="B138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D138" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
-      </c>
-      <c r="B139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),347.0)</f>
-        <v>347</v>
-      </c>
-      <c r="B140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOYTH")</f>
-        <v>FOYTH</v>
-      </c>
-      <c r="C140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D140" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
-        <v>350</v>
-      </c>
-      <c r="B141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
-        <v>SERGI CARDONA</v>
-      </c>
-      <c r="C141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
-      </c>
-      <c r="B142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
-      </c>
-      <c r="C142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
-      </c>
-      <c r="B143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
-      </c>
-      <c r="C143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),354.0)</f>
-        <v>354</v>
-      </c>
-      <c r="B144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"THOMAS")</f>
-        <v>THOMAS</v>
-      </c>
-      <c r="C144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
-        <v>355</v>
-      </c>
-      <c r="B145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
-        <v>MOLEIRO</v>
-      </c>
-      <c r="C145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
-      </c>
-      <c r="B146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
-      </c>
-      <c r="C146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-      <c r="D146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
-      </c>
-      <c r="B147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-      <c r="C147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-      <c r="D147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
-        <v>371</v>
-      </c>
-      <c r="B148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-      <c r="C148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-      <c r="D148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),381.0)</f>
-        <v>381</v>
-      </c>
-      <c r="B149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SIVERA")</f>
-        <v>SIVERA</v>
-      </c>
-      <c r="C149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
-      </c>
-      <c r="D149" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
-      </c>
-      <c r="B150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
-      </c>
-      <c r="C150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D150" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),391.0)</f>
-        <v>391</v>
-      </c>
-      <c r="B151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
-      </c>
-      <c r="C151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-      <c r="D151" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
-      </c>
-      <c r="B152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
-      </c>
-      <c r="C152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
-      </c>
-      <c r="D152" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
-      </c>
-      <c r="B153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
-      </c>
-      <c r="C153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-      <c r="D153" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
-        <v>399</v>
-      </c>
-      <c r="B154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
-      </c>
-      <c r="C154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-      <c r="D154" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),400.0)</f>
-        <v>400</v>
-      </c>
-      <c r="B155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO GARCÍA")</f>
-        <v>PABLO GARCÍA</v>
-      </c>
-      <c r="C155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-      <c r="D155" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
-        <v>404</v>
-      </c>
-      <c r="B156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
-      </c>
-      <c r="C156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-      <c r="D156" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
-        <v>407</v>
-      </c>
-      <c r="B157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
-        <v>CARLOS ÁLVAREZ</v>
-      </c>
-      <c r="C157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
-      </c>
-      <c r="D157" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
-        <v>409</v>
-      </c>
-      <c r="B158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
-        <v>FRAN GONZÁLEZ</v>
-      </c>
-      <c r="C158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D158" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
-      </c>
-      <c r="B159" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
-      </c>
-      <c r="C159" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D159" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
-      </c>
-      <c r="B160" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
-      </c>
-      <c r="C160" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-      <c r="D160" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
-      </c>
-      <c r="B161" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
-      </c>
-      <c r="C161" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-      <c r="D161" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
-      </c>
-      <c r="B162" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
-      </c>
-      <c r="C162" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
-      </c>
-      <c r="D162" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
-        <v>421</v>
-      </c>
-      <c r="B163" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
-      </c>
-      <c r="C163" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D163" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
-      </c>
-      <c r="B164" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
-      </c>
-      <c r="C164" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="D164" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.0)</f>
-        <v>425</v>
-      </c>
-      <c r="B165" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS VICENTE")</f>
-        <v>CARLOS VICENTE</v>
-      </c>
-      <c r="C165" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
-      </c>
-      <c r="D165" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.0)</f>
-        <v>436</v>
-      </c>
-      <c r="B166" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS SOLER")</f>
-        <v>CARLOS SOLER</v>
-      </c>
-      <c r="C166" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
-      </c>
-      <c r="D166" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
-      </c>
-      <c r="B167" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
-      </c>
-      <c r="C167" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="D167" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),444.0)</f>
-        <v>444</v>
-      </c>
-      <c r="B168" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OBLAK")</f>
-        <v>OBLAK</v>
-      </c>
-      <c r="C168" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-      <c r="D168" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
-        <v>448</v>
-      </c>
-      <c r="B169" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
-        <v>GRIEZMANN</v>
-      </c>
-      <c r="C169" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-      <c r="D169" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),449.0)</f>
-        <v>449</v>
-      </c>
-      <c r="B170" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KOUNDÉ")</f>
-        <v>KOUNDÉ</v>
-      </c>
-      <c r="C170" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-      <c r="D170" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
-        <v>452</v>
-      </c>
-      <c r="B171" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
-        <v>LEWANDOWSKI</v>
-      </c>
-      <c r="C171" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
-      </c>
-      <c r="D171" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),456.0)</f>
-        <v>456</v>
-      </c>
-      <c r="B172" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONY")</f>
-        <v>ANTONY</v>
-      </c>
-      <c r="C172" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
-      </c>
-      <c r="D172" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
-        <v>458</v>
-      </c>
-      <c r="B173" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
-        <v>CARRERAS</v>
-      </c>
-      <c r="C173" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
-      </c>
-      <c r="D173" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
-        <v>462</v>
-      </c>
-      <c r="B174" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
-        <v>ISI</v>
-      </c>
-      <c r="C174" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-      <c r="D174" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),467.0)</f>
-        <v>467</v>
-      </c>
-      <c r="B175" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PÉPÉ")</f>
-        <v>PÉPÉ</v>
-      </c>
-      <c r="C175" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D175" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
-        <v>469</v>
-      </c>
-      <c r="B176" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
-        <v>NICO WILLIAMS</v>
-      </c>
-      <c r="C176" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
-        <v>BALÓN DE ORO (ATHLETIC)</v>
-      </c>
-      <c r="D176" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),477.0)</f>
-        <v>477</v>
-      </c>
-      <c r="B177" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARD INVENCIBLE")</f>
-        <v>CARD INVENCIBLE</v>
-      </c>
-      <c r="C177" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÚNICA")</f>
-        <v>ÚNICA</v>
-      </c>
-      <c r="D177" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6404,9 +5505,6 @@
       <c r="D5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="21">
@@ -6577,9 +5675,6 @@
       <c r="D17" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="21">
@@ -6594,9 +5689,6 @@
       <c r="D18" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="21">
@@ -6906,9 +5998,6 @@
       <c r="D40" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="21">
@@ -6937,9 +6026,6 @@
       <c r="D42" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="21">
@@ -6954,9 +6040,6 @@
       <c r="D43" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="21">
@@ -7065,7 +6148,9 @@
       <c r="C51" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D51" s="21"/>
+      <c r="D51" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="21">
@@ -7142,9 +6227,6 @@
       <c r="D56" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E56" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="21">
@@ -7168,7 +6250,9 @@
       <c r="C58" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D58" s="21"/>
+      <c r="D58" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="21">
@@ -7482,7 +6566,9 @@
       <c r="C80" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D80" s="21"/>
+      <c r="D80" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="21">
@@ -7665,9 +6751,6 @@
       <c r="D93" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E93" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="21">
@@ -8035,9 +7118,6 @@
       <c r="D117" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E117" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="21">
@@ -8194,7 +7274,9 @@
       <c r="C128" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D128" s="21"/>
+      <c r="D128" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="21">
@@ -8387,9 +7469,6 @@
       <c r="D141" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E141" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" s="21">
@@ -8837,9 +7916,7 @@
       <c r="D173" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E173" s="22">
-        <v>1.0</v>
-      </c>
+      <c r="E173" s="22"/>
     </row>
     <row r="174">
       <c r="A174" s="21">
@@ -8872,7 +7949,7 @@
         <v>20</v>
       </c>
       <c r="E175" s="22">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="176">
@@ -8905,9 +7982,6 @@
       <c r="D177" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E177" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="178">
       <c r="A178" s="21">
@@ -8964,9 +8038,6 @@
       <c r="D181" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E181" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="182">
       <c r="A182" s="21">
@@ -9005,9 +8076,6 @@
       <c r="D184" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E184" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="185">
       <c r="A185" s="21">
@@ -9022,9 +8090,6 @@
       <c r="D185" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E185" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="186">
       <c r="A186" s="21">
@@ -9039,9 +8104,6 @@
       <c r="D186" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E186" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="187">
       <c r="A187" s="21">
@@ -9348,9 +8410,6 @@
       <c r="D208" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E208" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="209">
       <c r="A209" s="21">
@@ -9382,9 +8441,6 @@
       <c r="D210" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E210" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="211">
       <c r="A211" s="21">
@@ -9433,9 +8489,6 @@
       <c r="D213" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E213" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="214">
       <c r="A214" s="21">
@@ -9450,9 +8503,6 @@
       <c r="D214" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E214" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="215">
       <c r="A215" s="21">
@@ -9631,9 +8681,6 @@
       <c r="D226" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E226" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="227">
       <c r="A227" s="21">
@@ -9676,9 +8723,6 @@
       <c r="D229" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E229" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="230">
       <c r="A230" s="21">
@@ -9796,9 +8840,6 @@
       <c r="D237" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E237" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="238">
       <c r="A238" s="21">
@@ -9867,9 +8908,6 @@
       <c r="D242" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E242" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="243">
       <c r="A243" s="21">
@@ -9943,9 +8981,6 @@
       <c r="D247" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E247" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="248">
       <c r="A248" s="21">
@@ -10060,9 +9095,6 @@
       <c r="D255" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E255" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="256">
       <c r="A256" s="21">
@@ -10136,7 +9168,9 @@
       <c r="C260" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="D260" s="21"/>
+      <c r="D260" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="21">
@@ -10237,9 +9271,6 @@
       <c r="D267" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E267" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="268">
       <c r="A268" s="21">
@@ -10351,9 +9382,6 @@
       <c r="D275" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E275" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="276">
       <c r="A276" s="21">
@@ -10380,9 +9408,6 @@
       <c r="D277" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E277" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="278">
       <c r="A278" s="21">
@@ -10411,7 +9436,9 @@
       <c r="C279" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="D279" s="21"/>
+      <c r="D279" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="21">
@@ -10489,9 +9516,6 @@
       <c r="D284" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E284" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="285">
       <c r="A285" s="21">
@@ -10625,9 +9649,6 @@
       <c r="D293" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E293" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="294">
       <c r="A294" s="21">
@@ -10730,7 +9751,9 @@
       <c r="C300" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="D300" s="21"/>
+      <c r="D300" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="21">
@@ -10930,7 +9953,9 @@
       <c r="C314" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="D314" s="21"/>
+      <c r="D314" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="21">
@@ -10959,9 +9984,6 @@
       <c r="D316" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E316" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="317">
       <c r="A317" s="21">
@@ -11036,7 +10058,7 @@
         <v>20</v>
       </c>
       <c r="E321" s="22">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="322">
@@ -11052,9 +10074,6 @@
       <c r="D322" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E322" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="323">
       <c r="A323" s="21">
@@ -11262,9 +10281,6 @@
       <c r="D335" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E335" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="336">
       <c r="A336" s="21">
@@ -11324,7 +10340,9 @@
       <c r="C339" s="21" t="s">
         <v>344</v>
       </c>
-      <c r="D339" s="21"/>
+      <c r="D339" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="21">
@@ -11353,9 +10371,6 @@
       <c r="D341" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E341" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="342">
       <c r="A342" s="21">
@@ -11443,9 +10458,6 @@
       <c r="D347" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E347" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="348">
       <c r="A348" s="21">
@@ -11457,7 +10469,9 @@
       <c r="C348" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="D348" s="21"/>
+      <c r="D348" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="21">
@@ -11548,9 +10562,6 @@
       </c>
       <c r="D354" s="21" t="s">
         <v>20</v>
-      </c>
-      <c r="E354" s="22">
-        <v>1.0</v>
       </c>
     </row>
     <row r="355">
@@ -11885,9 +10896,6 @@
       <c r="D15" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="21">
@@ -11915,9 +10923,6 @@
       </c>
       <c r="D17" s="21" t="s">
         <v>20</v>
-      </c>
-      <c r="E17" s="22">
-        <v>1.0</v>
       </c>
     </row>
     <row r="18">
@@ -12040,7 +11045,9 @@
       <c r="C4" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="21">
@@ -12196,7 +11203,9 @@
       <c r="C15" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="D15" s="21"/>
+      <c r="D15" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="21">
@@ -14337,9 +13346,6 @@
       <c r="D1" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="21">
@@ -14494,9 +13500,6 @@
       </c>
       <c r="D4" s="21" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" s="22">
-        <v>1.0</v>
       </c>
     </row>
     <row r="5">
@@ -14601,7 +13604,9 @@
       <c r="C1" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21">
@@ -14650,9 +13655,6 @@
       <c r="D4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="22">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="21">
@@ -14664,7 +13666,9 @@
       <c r="C5" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="21"/>
+      <c r="D5" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="21">
@@ -14797,7 +13801,9 @@
       <c r="C14" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="D14" s="21"/>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="21">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="399">
   <si>
     <t>Última actualización:</t>
   </si>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B1" s="2">
         <f>TODAY()</f>
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1833,15 +1833,15 @@
       </c>
       <c r="C3" s="9">
         <f>COUNTIF(REGULARES!D:D, "SI")</f>
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D3" s="9">
         <f t="shared" ref="D3:D12" si="1">B3-C3</f>
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E4" si="2">(C3/B3)</f>
-        <v>0.8305555556</v>
+        <v>0.8416666667</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E3, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2001,15 +2001,15 @@
       </c>
       <c r="C10" s="14">
         <f>COUNTIF('Protas (424–441)'!D:D, "SI")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="3"/>
-        <v>0.6666666667</v>
+        <v>0.7777777778</v>
       </c>
       <c r="F10" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E10, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2049,15 +2049,15 @@
       </c>
       <c r="C12" s="14">
         <f>COUNTIF('Cartas Top y Únicas (468–478)'!D:D, "SI")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="15">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="10">
         <f t="shared" si="3"/>
-        <v>0.4545454545</v>
+        <v>0.5454545455</v>
       </c>
       <c r="F12" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E12, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="4"/>
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>0.8192771084</v>
+        <v>0.8333333333</v>
       </c>
       <c r="F13" s="19" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E13, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2386,7 +2386,9 @@
       <c r="C10" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="D10" s="21"/>
+      <c r="D10" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="21">
@@ -2454,7 +2456,9 @@
       <c r="C15" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="D15" s="21"/>
+      <c r="D15" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="21">
@@ -2530,7 +2534,9 @@
       <c r="C1" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21">
@@ -3211,22 +3217,22 @@
         <v>D. ALAVÉS</v>
       </c>
       <c r="D6" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
       </c>
       <c r="B7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TONI MARTÍNEZ")</f>
+        <v>TONI MARTÍNEZ</v>
       </c>
       <c r="C7" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D7" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3235,16 +3241,16 @@
     </row>
     <row r="8">
       <c r="A8" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
-        <v>21</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
+        <v>18</v>
       </c>
       <c r="B8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PADILLA")</f>
-        <v>PADILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIANO")</f>
+        <v>MARIANO</v>
       </c>
       <c r="C8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D8" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3253,12 +3259,12 @@
     </row>
     <row r="9">
       <c r="A9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="B9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VIVIAN")</f>
-        <v>VIVIAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C9" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3271,12 +3277,12 @@
     </row>
     <row r="10">
       <c r="A10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
-        <v>27</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
+        <v>21</v>
       </c>
       <c r="B10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUIZ DE GALARRETA")</f>
-        <v>RUIZ DE GALARRETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PADILLA")</f>
+        <v>PADILLA</v>
       </c>
       <c r="C10" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3289,12 +3295,12 @@
     </row>
     <row r="11">
       <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
-        <v>34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
+        <v>23</v>
       </c>
       <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
-        <v>MAROAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VIVIAN")</f>
+        <v>VIVIAN</v>
       </c>
       <c r="C11" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3307,16 +3313,16 @@
     </row>
     <row r="12">
       <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
-        <v>39</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MUSSO")</f>
-        <v>MUSSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUIZ DE GALARRETA")</f>
+        <v>RUIZ DE GALARRETA</v>
       </c>
       <c r="C12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D12" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3325,16 +3331,16 @@
     </row>
     <row r="13">
       <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
+        <v>33</v>
       </c>
       <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
-        <v>ALMADA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WILLIAMS")</f>
+        <v>WILLIAMS</v>
       </c>
       <c r="C13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D13" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3343,16 +3349,16 @@
     </row>
     <row r="14">
       <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
-        <v>52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
+        <v>34</v>
       </c>
       <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
-        <v>JULIÁN ALVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
+        <v>MAROAN</v>
       </c>
       <c r="C14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D14" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3361,16 +3367,16 @@
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
-        <v>55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D15" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3379,16 +3385,16 @@
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
-        <v>66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
+        <v>39</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
-        <v>FERMÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MUSSO")</f>
+        <v>MUSSO</v>
       </c>
       <c r="C16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D16" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3397,16 +3403,16 @@
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
-        <v>67</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
-        <v>DANI OLMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
+        <v>LENGLET</v>
       </c>
       <c r="C17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D17" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3415,16 +3421,16 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
-        <v>73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
+        <v>ALMADA</v>
       </c>
       <c r="C18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D18" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3433,16 +3439,16 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
+        <v>52</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
-        <v>PAU LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
+        <v>JULIÁN ALVAREZ</v>
       </c>
       <c r="C19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D19" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3451,16 +3457,16 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
-        <v>76</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
+        <v>55</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
-        <v>BELLERÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D20" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3469,16 +3475,16 @@
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOAN GARCÍA")</f>
+        <v>JOAN GARCÍA</v>
       </c>
       <c r="C21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D21" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3487,16 +3493,16 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
-        <v>84</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
+        <v>63</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
-        <v>PABLO FORNALS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DE JONG")</f>
+        <v>DE JONG</v>
       </c>
       <c r="C22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D22" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3505,16 +3511,16 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
+        <v>FERMÍN</v>
       </c>
       <c r="C23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D23" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3523,16 +3529,16 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
-        <v>91</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
+        <v>DANI OLMO</v>
       </c>
       <c r="C24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D24" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3541,16 +3547,16 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
-        <v>94</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
-        <v>JAVI RUEDA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D25" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3559,16 +3565,16 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
+        <v>PAU LÓPEZ</v>
       </c>
       <c r="C26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D26" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3577,16 +3583,16 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
+        <v>BELLERÍN</v>
       </c>
       <c r="C27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D27" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3595,16 +3601,16 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D28" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3613,34 +3619,34 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
-        <v>104</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
+        <v>84</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
-        <v>SWEDBERG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
+        <v>PABLO FORNALS</v>
       </c>
       <c r="C29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
       </c>
       <c r="C30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D30" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3649,12 +3655,12 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
-        <v>106</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
+        <v>91</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
-        <v>IAGO ASPAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3667,12 +3673,12 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
+        <v>94</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
+        <v>JAVI RUEDA</v>
       </c>
       <c r="C32" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3685,12 +3691,12 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3703,16 +3709,16 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
-        <v>IÑAKI PEÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D34" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3721,52 +3727,52 @@
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
-        <v>112</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
+        <v>104</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
-        <v>ÁLVARO NÚÑEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
+        <v>SWEDBERG</v>
       </c>
       <c r="C36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D37" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3775,16 +3781,16 @@
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
+        <v>IAGO ASPAS</v>
       </c>
       <c r="C38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D38" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3793,16 +3799,16 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
-        <v>126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
-        <v>RAFA MIR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D39" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3811,16 +3817,16 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
-        <v>127</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
       </c>
       <c r="C40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D40" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3829,16 +3835,16 @@
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
+        <v>IÑAKI PEÑA</v>
       </c>
       <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D41" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3847,34 +3853,34 @@
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
-        <v>139</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
-        <v>ANTONIU ROCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
+        <v>ÁLVARO NÚÑEZ</v>
       </c>
       <c r="C43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D43" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3883,16 +3889,16 @@
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D44" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3901,16 +3907,16 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D45" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3919,16 +3925,16 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
+        <v>126</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
+        <v>RAFA MIR</v>
       </c>
       <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D46" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3937,16 +3943,16 @@
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
+        <v>127</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D47" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3955,16 +3961,16 @@
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
-        <v>153</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),134.0)</f>
+        <v>134</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
-        <v>DIEGO RICO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ROMERO")</f>
+        <v>CARLOS ROMERO</v>
       </c>
       <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D48" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3973,16 +3979,16 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D49" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3991,34 +3997,34 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
-        <v>174</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
+        <v>139</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
-        <v>IVÁN MARTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
+        <v>ANTONIU ROCA</v>
       </c>
       <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D51" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4027,16 +4033,16 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D52" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4045,16 +4051,16 @@
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
-        <v>176</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
-        <v>JOEL ROCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
       </c>
       <c r="C53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D53" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4063,16 +4069,16 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
-        <v>189</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
-        <v>PAMPÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D54" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4081,16 +4087,16 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
-        <v>202</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
-        <v>CARVAJAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D55" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4099,16 +4105,16 @@
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D56" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4117,16 +4123,16 @@
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
-        <v>211</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
+        <v>153</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
-        <v>GÜLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
+        <v>DIEGO RICO</v>
       </c>
       <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D57" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4135,16 +4141,16 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
-        <v>212</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D58" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4153,16 +4159,16 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D59" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4171,16 +4177,16 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
-        <v>219</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
+        <v>174</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
-        <v>BERGSTRÖM</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
+        <v>IVÁN MARTÍN</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D60" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4189,34 +4195,34 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
-        <v>225</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
+        <v>176</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
-        <v>MOJICA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
+        <v>JOEL ROCA</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D62" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4225,16 +4231,16 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
+        <v>189</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
+        <v>PAMPÍN</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D63" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4243,34 +4249,34 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),195.0)</f>
+        <v>195</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORALES")</f>
+        <v>MORALES</v>
       </c>
       <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
+        <v>202</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
+        <v>CARVAJAL</v>
       </c>
       <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D65" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4279,16 +4285,16 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
-        <v>245</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
-        <v>MONCAYOLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D66" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4297,16 +4303,16 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
-        <v>248</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D67" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4315,16 +4321,16 @@
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
+        <v>212</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
       </c>
       <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D68" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4333,16 +4339,16 @@
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D69" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4351,16 +4357,16 @@
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
+        <v>219</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
+        <v>BERGSTRÖM</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4369,34 +4375,34 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
-        <v>265</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
+        <v>224</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
-        <v>ILIC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
+        <v>KUMBULLA</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D72" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4405,16 +4411,16 @@
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
+        <v>225</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
+        <v>MOJICA</v>
       </c>
       <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D73" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4423,16 +4429,16 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),230.0)</f>
+        <v>230</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO TORRE")</f>
+        <v>PABLO TORRE</v>
       </c>
       <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D74" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4441,16 +4447,16 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
-        <v>281</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
-        <v>ÓSCAR VALENTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
       </c>
       <c r="C75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D75" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4459,34 +4465,34 @@
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
-        <v>282</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
-        <v>ISI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
-        <v>283</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
-        <v>PEDRO DÍAZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D77" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4495,16 +4501,16 @@
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
-        <v>286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
-        <v>CAMELLO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D78" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4513,16 +4519,16 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
-        <v>290</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
+        <v>245</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
+        <v>MONCAYOLA</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D79" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4531,16 +4537,16 @@
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
-        <v>292</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
+        <v>248</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
-        <v>ARAMBURU</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
       </c>
       <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D80" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4549,52 +4555,52 @@
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
-        <v>296</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
-        <v>SERGIO GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D83" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4603,16 +4609,16 @@
     </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
-        <v>302</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
+        <v>260</v>
       </c>
       <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
-        <v>KUBO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
+        <v>RAHIM ALHASSANE</v>
       </c>
       <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D84" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4621,16 +4627,16 @@
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D85" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4639,16 +4645,16 @@
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
-        <v>312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
+        <v>265</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
-        <v>AZPILICUETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
+        <v>ILIC</v>
       </c>
       <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D86" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4657,88 +4663,88 @@
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D87" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
+      </c>
+      <c r="B88" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
+      </c>
+      <c r="C88" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D88" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
-        <v>317</v>
-      </c>
-      <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
-        <v>AGOUME</v>
-      </c>
-      <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="D88" s="20">
+    <row r="89">
+      <c r="A89" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
+        <v>281</v>
+      </c>
+      <c r="B89" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
+        <v>ÓSCAR VALENTÍN</v>
+      </c>
+      <c r="C89" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D89" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
-      </c>
-      <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
-      </c>
-      <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="D89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
+        <v>282</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
       </c>
       <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
       </c>
       <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D91" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4747,16 +4753,16 @@
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
-        <v>326</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
+        <v>286</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
+        <v>CAMELLO</v>
       </c>
       <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D92" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4765,16 +4771,16 @@
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
-        <v>327</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
+        <v>290</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
-        <v>DIMITRIEVSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
       </c>
       <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D93" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4783,16 +4789,16 @@
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
+        <v>292</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
+        <v>ARAMBURU</v>
       </c>
       <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D94" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4801,16 +4807,16 @@
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
-        <v>329</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
-        <v>CORREIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
       </c>
       <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D95" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4819,16 +4825,16 @@
     </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
+        <v>296</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
+        <v>SERGIO GÓMEZ</v>
       </c>
       <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D96" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4837,16 +4843,16 @@
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
-        <v>331</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
-        <v>COPETE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D97" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4855,16 +4861,16 @@
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
+        <v>302</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
+        <v>KUBO</v>
       </c>
       <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D98" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4873,16 +4879,16 @@
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
-        <v>337</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
-        <v>ANDRÉ ALMEIDA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D99" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4891,16 +4897,16 @@
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
+        <v>312</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
+        <v>AZPILICUETA</v>
       </c>
       <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D100" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4909,16 +4915,16 @@
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
       </c>
       <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D101" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -4927,106 +4933,106 @@
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
+        <v>317</v>
       </c>
       <c r="B102" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
+        <v>AGOUME</v>
+      </c>
+      <c r="C102" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D102" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
+      </c>
+      <c r="B103" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
+      </c>
+      <c r="C103" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D103" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
+      </c>
+      <c r="B104" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
+      </c>
+      <c r="C104" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D104" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
+      </c>
+      <c r="B105" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C105" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D105" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
+      </c>
+      <c r="B106" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
         <v>ESTADIO</v>
       </c>
-      <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
-        <v>350</v>
-      </c>
-      <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
-        <v>SERGI CARDONA</v>
-      </c>
-      <c r="C103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D103" s="20">
+      <c r="C106" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D106" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
-      </c>
-      <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
-      </c>
-      <c r="C104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
-      </c>
-      <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
-      </c>
-      <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
-        <v>355</v>
-      </c>
-      <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
-        <v>MOLEIRO</v>
-      </c>
-      <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
+        <v>326</v>
       </c>
       <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D107" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5035,16 +5041,16 @@
     </row>
     <row r="108">
       <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
       </c>
       <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
       </c>
       <c r="C108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D108" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5053,52 +5059,52 @@
     </row>
     <row r="109">
       <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
-        <v>371</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
       </c>
       <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
       </c>
       <c r="C109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
+        <v>329</v>
       </c>
       <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
+        <v>CORREIA</v>
       </c>
       <c r="C110" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
       </c>
       <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
       </c>
       <c r="C111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D111" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5107,16 +5113,16 @@
     </row>
     <row r="112">
       <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
+        <v>331</v>
       </c>
       <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
+        <v>COPETE</v>
       </c>
       <c r="C112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D112" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5125,16 +5131,16 @@
     </row>
     <row r="113">
       <c r="A113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
-        <v>399</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),332.0)</f>
+        <v>332</v>
       </c>
       <c r="B113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIAKHABY")</f>
+        <v>DIAKHABY</v>
       </c>
       <c r="C113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D113" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5143,16 +5149,16 @@
     </row>
     <row r="114">
       <c r="A114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
-        <v>404</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
       </c>
       <c r="B114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
       </c>
       <c r="C114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D114" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5161,16 +5167,16 @@
     </row>
     <row r="115">
       <c r="A115" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
-        <v>407</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
+        <v>337</v>
       </c>
       <c r="B115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
-        <v>CARLOS ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
+        <v>ANDRÉ ALMEIDA</v>
       </c>
       <c r="C115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D115" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5179,16 +5185,16 @@
     </row>
     <row r="116">
       <c r="A116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
-        <v>409</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
       </c>
       <c r="B116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
-        <v>FRAN GONZÁLEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
       </c>
       <c r="C116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D116" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5197,34 +5203,34 @@
     </row>
     <row r="117">
       <c r="A117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D118" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5233,34 +5239,34 @@
     </row>
     <row r="119">
       <c r="A119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
+        <v>350</v>
       </c>
       <c r="B119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
+        <v>SERGI CARDONA</v>
       </c>
       <c r="C119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
       </c>
       <c r="B120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
       </c>
       <c r="C120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D120" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5269,16 +5275,16 @@
     </row>
     <row r="121">
       <c r="A121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
-        <v>421</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
       </c>
       <c r="B121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
       </c>
       <c r="C121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D121" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5287,52 +5293,52 @@
     </row>
     <row r="122">
       <c r="A122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
+        <v>355</v>
       </c>
       <c r="B122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
+        <v>MOLEIRO</v>
       </c>
       <c r="C122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
       </c>
       <c r="B123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="C123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
-        <v>448</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
       </c>
       <c r="B124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
-        <v>GRIEZMANN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="C124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D124" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5341,16 +5347,16 @@
     </row>
     <row r="125">
       <c r="A125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
-        <v>452</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
+        <v>371</v>
       </c>
       <c r="B125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
-        <v>LEWANDOWSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="C125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D125" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5359,16 +5365,16 @@
     </row>
     <row r="126">
       <c r="A126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
-        <v>458</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),376.0)</f>
+        <v>376</v>
       </c>
       <c r="B126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
-        <v>CARRERAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="C126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D126" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5377,36 +5383,378 @@
     </row>
     <row r="127">
       <c r="A127" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
+      </c>
+      <c r="B127" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
+      </c>
+      <c r="C127" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D127" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
+      </c>
+      <c r="B128" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
+      </c>
+      <c r="C128" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+      <c r="D128" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
+      </c>
+      <c r="B129" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
+      </c>
+      <c r="C129" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D129" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
+        <v>399</v>
+      </c>
+      <c r="B130" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
+      </c>
+      <c r="C130" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D130" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),403.0)</f>
+        <v>403</v>
+      </c>
+      <c r="B131" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVINCHI")</f>
+        <v>DAVINCHI</v>
+      </c>
+      <c r="C131" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D131" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
+      </c>
+      <c r="B132" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
+      </c>
+      <c r="C132" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D132" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
+        <v>407</v>
+      </c>
+      <c r="B133" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
+        <v>CARLOS ÁLVAREZ</v>
+      </c>
+      <c r="C133" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+      <c r="D133" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),408.0)</f>
+        <v>408</v>
+      </c>
+      <c r="B134" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
+        <v>ETTA EYONG</v>
+      </c>
+      <c r="C134" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+      <c r="D134" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
+        <v>409</v>
+      </c>
+      <c r="B135" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
+        <v>FRAN GONZÁLEZ</v>
+      </c>
+      <c r="C135" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D135" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
+      </c>
+      <c r="B136" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
+      </c>
+      <c r="C136" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D136" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
+      </c>
+      <c r="B137" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
+      </c>
+      <c r="C137" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D137" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
+      </c>
+      <c r="B138" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
+      </c>
+      <c r="C138" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D138" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
+      </c>
+      <c r="B139" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
+      </c>
+      <c r="C139" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D139" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
+        <v>421</v>
+      </c>
+      <c r="B140" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
+      </c>
+      <c r="C140" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D140" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
+      </c>
+      <c r="B141" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
+      </c>
+      <c r="C141" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D141" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
+      </c>
+      <c r="B142" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
+      </c>
+      <c r="C142" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D142" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
+        <v>448</v>
+      </c>
+      <c r="B143" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
+        <v>GRIEZMANN</v>
+      </c>
+      <c r="C143" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D143" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
+        <v>452</v>
+      </c>
+      <c r="B144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
+        <v>LEWANDOWSKI</v>
+      </c>
+      <c r="C144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D144" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
+        <v>458</v>
+      </c>
+      <c r="B145" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
+        <v>CARRERAS</v>
+      </c>
+      <c r="C145" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D145" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
         <v>462</v>
       </c>
-      <c r="B127" s="20" t="str">
+      <c r="B146" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
         <v>ISI</v>
       </c>
-      <c r="C127" s="20" t="str">
+      <c r="C146" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
         <v>RAYO VALLECANO</v>
       </c>
-      <c r="D127" s="20">
+      <c r="D146" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="20">
+    <row r="147">
+      <c r="A147" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B128" s="20" t="str">
+      <c r="B147" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C128" s="20" t="str">
+      <c r="C147" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D128" s="20">
+      <c r="D147" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
@@ -5645,7 +5993,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="16">
@@ -5661,6 +6009,9 @@
       <c r="D16" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E16" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="21">
@@ -5689,6 +6040,9 @@
       <c r="D18" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E18" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21">
@@ -5898,6 +6252,9 @@
       <c r="D33" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E33" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="21">
@@ -6026,6 +6383,9 @@
       <c r="D42" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E42" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="21">
@@ -6107,7 +6467,9 @@
       <c r="C48" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D48" s="21"/>
+      <c r="D48" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="21">
@@ -6227,6 +6589,9 @@
       <c r="D56" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E56" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="21">
@@ -6321,6 +6686,9 @@
       <c r="D63" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E63" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="21">
@@ -6897,7 +7265,7 @@
         <v>20</v>
       </c>
       <c r="E103" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="104">
@@ -7028,7 +7396,7 @@
         <v>20</v>
       </c>
       <c r="E111" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="112">
@@ -7359,6 +7727,9 @@
       <c r="D134" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E134" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="21">
@@ -7419,7 +7790,7 @@
         <v>20</v>
       </c>
       <c r="E138" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="139">
@@ -7469,6 +7840,9 @@
       <c r="D141" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E141" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="21">
@@ -7689,7 +8063,9 @@
       <c r="C157" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D157" s="21"/>
+      <c r="D157" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="21">
@@ -7949,7 +8325,7 @@
         <v>20</v>
       </c>
       <c r="E175" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="176">
@@ -8061,7 +8437,9 @@
       <c r="C183" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D183" s="21"/>
+      <c r="D183" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="21">
@@ -8231,6 +8609,9 @@
       <c r="D195" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E195" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="21">
@@ -8620,7 +9001,7 @@
         <v>20</v>
       </c>
       <c r="E222" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="223">
@@ -8650,6 +9031,9 @@
       <c r="D224" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E224" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="21">
@@ -8737,6 +9121,9 @@
       <c r="D230" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E230" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="21">
@@ -9027,7 +9414,7 @@
         <v>20</v>
       </c>
       <c r="E250" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="251">
@@ -9138,7 +9525,7 @@
         <v>20</v>
       </c>
       <c r="E258" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="259">
@@ -9171,6 +9558,9 @@
       <c r="D260" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E260" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="21">
@@ -9353,7 +9743,9 @@
       <c r="C273" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="D273" s="21"/>
+      <c r="D273" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="21">
@@ -9423,7 +9815,7 @@
         <v>20</v>
       </c>
       <c r="E278" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="279">
@@ -10058,7 +10450,7 @@
         <v>20</v>
       </c>
       <c r="E321" s="22">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="322">
@@ -10118,7 +10510,7 @@
         <v>20</v>
       </c>
       <c r="E325" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="326">
@@ -10169,7 +10561,7 @@
         <v>20</v>
       </c>
       <c r="E328" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="329">
@@ -10235,6 +10627,9 @@
       </c>
       <c r="D332" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E332" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="333">
@@ -10722,6 +11117,9 @@
       <c r="D3" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E3" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="21">
@@ -10882,6 +11280,9 @@
       <c r="D14" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E14" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="21">
@@ -10951,6 +11352,9 @@
       </c>
       <c r="D19" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E19" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="20">
@@ -11004,7 +11408,7 @@
         <v>20</v>
       </c>
       <c r="E1" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="2">
@@ -11219,6 +11623,9 @@
       </c>
       <c r="D16" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E16" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="17">
@@ -13425,7 +13832,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="22">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
@@ -13697,6 +14104,9 @@
       <c r="D7" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E7" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21">
@@ -13772,6 +14182,9 @@
       </c>
       <c r="D12" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E12" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="13">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="399">
   <si>
     <t>Última actualización:</t>
   </si>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B1" s="2">
         <f>TODAY()</f>
-        <v>46065</v>
+        <v>46068</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1833,15 +1833,15 @@
       </c>
       <c r="C3" s="9">
         <f>COUNTIF(REGULARES!D:D, "SI")</f>
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D3" s="9">
         <f t="shared" ref="D3:D12" si="1">B3-C3</f>
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E4" si="2">(C3/B3)</f>
-        <v>0.8416666667</v>
+        <v>0.85</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E3, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2001,15 +2001,15 @@
       </c>
       <c r="C10" s="14">
         <f>COUNTIF('Protas (424–441)'!D:D, "SI")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="3"/>
-        <v>0.7777777778</v>
+        <v>0.8333333333</v>
       </c>
       <c r="F10" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E10, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2025,15 +2025,15 @@
       </c>
       <c r="C11" s="14">
         <f>COUNTIF('Super Cracks (442–467)'!D:D, "SI")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="15">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="3"/>
-        <v>0.8076923077</v>
+        <v>0.8461538462</v>
       </c>
       <c r="F11" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E11, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="4"/>
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>0.8333333333</v>
+        <v>0.843373494</v>
       </c>
       <c r="F13" s="19" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E13, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2346,7 +2346,9 @@
       <c r="C7" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="21"/>
+      <c r="D7" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21">
@@ -2755,7 +2757,9 @@
       <c r="C5" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="21"/>
+      <c r="D5" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="21">
@@ -2869,6 +2873,9 @@
       </c>
       <c r="D13" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E13" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="14">
@@ -3493,12 +3500,12 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
-        <v>63</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
+        <v>62</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DE JONG")</f>
-        <v>DE JONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALDE")</f>
+        <v>BALDE</v>
       </c>
       <c r="C22" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3511,12 +3518,12 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
-        <v>66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
+        <v>63</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
-        <v>FERMÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DE JONG")</f>
+        <v>DE JONG</v>
       </c>
       <c r="C23" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3529,12 +3536,12 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
-        <v>67</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
-        <v>DANI OLMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
+        <v>FERMÍN</v>
       </c>
       <c r="C24" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3547,16 +3554,16 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
-        <v>73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
+        <v>DANI OLMO</v>
       </c>
       <c r="C25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D25" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3565,12 +3572,12 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
-        <v>PAU LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C26" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3583,30 +3590,30 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
-        <v>76</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
-        <v>BELLERÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
+        <v>PAU LÓPEZ</v>
       </c>
       <c r="C27" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
+        <v>BELLERÍN</v>
       </c>
       <c r="C28" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3619,12 +3626,12 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
-        <v>84</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
-        <v>PABLO FORNALS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C29" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3637,12 +3644,12 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
+        <v>84</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
+        <v>PABLO FORNALS</v>
       </c>
       <c r="C30" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3655,16 +3662,16 @@
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
-        <v>91</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
       </c>
       <c r="C31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D31" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3673,12 +3680,12 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
-        <v>94</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
+        <v>91</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
-        <v>JAVI RUEDA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C32" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3691,12 +3698,12 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
+        <v>94</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
+        <v>JAVI RUEDA</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3709,12 +3716,12 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C34" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3727,30 +3734,30 @@
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C35" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
-        <v>104</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
-        <v>SWEDBERG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C36" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3763,30 +3770,30 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
+        <v>104</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
+        <v>SWEDBERG</v>
       </c>
       <c r="C37" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
-        <v>106</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
-        <v>IAGO ASPAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C38" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3799,30 +3806,30 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
+        <v>IAGO ASPAS</v>
       </c>
       <c r="C39" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C40" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3835,16 +3842,16 @@
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
-        <v>IÑAKI PEÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
       </c>
       <c r="C41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D41" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3853,48 +3860,48 @@
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
+        <v>IÑAKI PEÑA</v>
       </c>
       <c r="C42" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
         <v>ELCHE CF</v>
       </c>
       <c r="D42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
-        <v>112</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
-        <v>ÁLVARO NÚÑEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C43" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
         <v>ELCHE CF</v>
       </c>
       <c r="D43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
+        <v>ÁLVARO NÚÑEZ</v>
       </c>
       <c r="C44" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3907,12 +3914,12 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C45" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3925,34 +3932,34 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
-        <v>126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
-        <v>RAFA MIR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C46" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
         <v>ELCHE CF</v>
       </c>
       <c r="D46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
-        <v>127</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
+        <v>126</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
+        <v>RAFA MIR</v>
       </c>
       <c r="C47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D47" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3961,12 +3968,12 @@
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),134.0)</f>
-        <v>134</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
+        <v>127</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ROMERO")</f>
-        <v>CARLOS ROMERO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C48" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -3979,12 +3986,12 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
+        <v>128</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
+        <v>DMITROVIC</v>
       </c>
       <c r="C49" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -3997,30 +4004,30 @@
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),134.0)</f>
+        <v>134</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ROMERO")</f>
+        <v>CARLOS ROMERO</v>
       </c>
       <c r="C50" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
-        <v>139</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
-        <v>ANTONIU ROCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C51" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -4033,30 +4040,30 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C52" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
+        <v>139</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
+        <v>ANTONIU ROCA</v>
       </c>
       <c r="C53" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -4069,34 +4076,34 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C54" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
       </c>
       <c r="C55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D55" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4105,16 +4112,16 @@
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D56" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4123,12 +4130,12 @@
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
-        <v>153</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
-        <v>DIEGO RICO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C57" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -4141,16 +4148,16 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D58" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4159,16 +4166,16 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),152.0)</f>
+        <v>152</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABQAR")</f>
+        <v>ABQAR</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D59" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4177,16 +4184,16 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
-        <v>174</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
+        <v>153</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
-        <v>IVÁN MARTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
+        <v>DIEGO RICO</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D60" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4195,30 +4202,30 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C61" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
       </c>
       <c r="D61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
-        <v>176</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
-        <v>JOEL ROCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C62" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -4231,16 +4238,16 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
-        <v>189</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
-        <v>PAMPÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D63" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4249,16 +4256,16 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),195.0)</f>
-        <v>195</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
+        <v>174</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORALES")</f>
-        <v>MORALES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
+        <v>IVÁN MARTÍN</v>
       </c>
       <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D64" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4267,34 +4274,34 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
-        <v>202</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
-        <v>CARVAJAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
       </c>
       <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
+        <v>176</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
+        <v>JOEL ROCA</v>
       </c>
       <c r="C66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D66" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4303,16 +4310,16 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
-        <v>211</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
+        <v>189</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
-        <v>GÜLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
+        <v>PAMPÍN</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D67" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4321,16 +4328,16 @@
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
-        <v>212</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),190.0)</f>
+        <v>190</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORIOL REY")</f>
+        <v>ORIOL REY</v>
       </c>
       <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D68" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4339,16 +4346,16 @@
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),195.0)</f>
+        <v>195</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORALES")</f>
+        <v>MORALES</v>
       </c>
       <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D69" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4357,16 +4364,16 @@
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
-        <v>219</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
+        <v>202</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
-        <v>BERGSTRÖM</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
+        <v>CARVAJAL</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4375,34 +4382,34 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
-        <v>224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
-        <v>KUMBULLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D72" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4411,16 +4418,16 @@
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
-        <v>225</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
+        <v>212</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
-        <v>MOJICA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
       </c>
       <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D73" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4429,16 +4436,16 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),230.0)</f>
-        <v>230</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),215.0)</f>
+        <v>215</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO TORRE")</f>
-        <v>PABLO TORRE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
+        <v>GONZALO</v>
       </c>
       <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D74" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4447,70 +4454,70 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C75" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D75" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
+        <v>219</v>
+      </c>
+      <c r="B76" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
+        <v>BERGSTRÖM</v>
+      </c>
+      <c r="C76" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
-      <c r="D75" s="20">
+      <c r="D76" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
-      </c>
-      <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D76" s="20">
+    <row r="77">
+      <c r="A77" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
+      </c>
+      <c r="B77" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
+      </c>
+      <c r="C77" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+      <c r="D77" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
-      </c>
-      <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
-      </c>
-      <c r="D77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
+        <v>224</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
+        <v>KUMBULLA</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D78" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4519,16 +4526,16 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
-        <v>245</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
+        <v>225</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
-        <v>MONCAYOLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
+        <v>MOJICA</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D79" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4537,16 +4544,16 @@
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
-        <v>248</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),228.0)</f>
+        <v>228</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
+        <v>DARDER</v>
       </c>
       <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D80" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4555,70 +4562,70 @@
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),230.0)</f>
+        <v>230</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO TORRE")</f>
+        <v>PABLO TORRE</v>
       </c>
       <c r="C81" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+      <c r="D81" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
+      </c>
+      <c r="B82" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
+      </c>
+      <c r="C82" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
+      </c>
+      <c r="D82" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
+      </c>
+      <c r="B83" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
+      </c>
+      <c r="C83" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
         <v>CA OSASUNA</v>
       </c>
-      <c r="D81" s="20">
+      <c r="D83" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
-      </c>
-      <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
-      </c>
-      <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="D82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
-      </c>
-      <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
-      </c>
-      <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
-      </c>
-      <c r="D83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
-        <v>260</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
-        <v>RAHIM ALHASSANE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D84" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4627,16 +4634,16 @@
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D85" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4645,16 +4652,16 @@
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
-        <v>265</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
+        <v>237</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
-        <v>ILIC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
+        <v>AITOR FERNÁNDEZ</v>
       </c>
       <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D86" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4663,16 +4670,16 @@
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
+        <v>245</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
+        <v>MONCAYOLA</v>
       </c>
       <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D87" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4681,16 +4688,16 @@
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
+        <v>248</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
       </c>
       <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D88" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -4699,52 +4706,52 @@
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
-        <v>281</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
-        <v>ÓSCAR VALENTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
-        <v>282</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
-        <v>ISI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
-        <v>283</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
-        <v>PEDRO DÍAZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D91" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4753,16 +4760,16 @@
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
-        <v>286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
+        <v>260</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
-        <v>CAMELLO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
+        <v>RAHIM ALHASSANE</v>
       </c>
       <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D92" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4771,16 +4778,16 @@
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
-        <v>290</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D93" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4789,16 +4796,16 @@
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
-        <v>292</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
+        <v>265</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
-        <v>ARAMBURU</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
+        <v>ILIC</v>
       </c>
       <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D94" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4807,16 +4814,16 @@
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D95" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4825,34 +4832,34 @@
     </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
-        <v>296</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
-        <v>SERGIO GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
       </c>
       <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
+        <v>281</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
+        <v>ÓSCAR VALENTÍN</v>
       </c>
       <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D97" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4861,16 +4868,16 @@
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
-        <v>302</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
+        <v>282</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
-        <v>KUBO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
       </c>
       <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D98" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4879,16 +4886,16 @@
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D99" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4897,16 +4904,16 @@
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
-        <v>312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
+        <v>286</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
-        <v>AZPILICUETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
+        <v>CAMELLO</v>
       </c>
       <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D100" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4915,34 +4922,34 @@
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
+        <v>290</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
       </c>
       <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
-        <v>317</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
+        <v>292</v>
       </c>
       <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
-        <v>AGOUME</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
+        <v>ARAMBURU</v>
       </c>
       <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D102" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4951,70 +4958,70 @@
     </row>
     <row r="103">
       <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
       </c>
       <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
       </c>
       <c r="C103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
+        <v>296</v>
       </c>
       <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
+        <v>SERGIO GÓMEZ</v>
       </c>
       <c r="C104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
+        <v>302</v>
       </c>
       <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
+        <v>KUBO</v>
       </c>
       <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D106" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5023,16 +5030,16 @@
     </row>
     <row r="107">
       <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
-        <v>326</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D107" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5041,16 +5048,16 @@
     </row>
     <row r="108">
       <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
-        <v>327</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
+        <v>312</v>
       </c>
       <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
-        <v>DIMITRIEVSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
+        <v>AZPILICUETA</v>
       </c>
       <c r="C108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D108" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5059,16 +5066,16 @@
     </row>
     <row r="109">
       <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
       </c>
       <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
       </c>
       <c r="C109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D109" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5077,16 +5084,16 @@
     </row>
     <row r="110">
       <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
-        <v>329</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
+        <v>317</v>
       </c>
       <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
-        <v>CORREIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
+        <v>AGOUME</v>
       </c>
       <c r="C110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D110" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5095,66 +5102,66 @@
     </row>
     <row r="111">
       <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
       </c>
       <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
       </c>
       <c r="C111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
-        <v>331</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
       </c>
       <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
-        <v>COPETE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
       </c>
       <c r="C112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),332.0)</f>
-        <v>332</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
       </c>
       <c r="B113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIAKHABY")</f>
-        <v>DIAKHABY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C113" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
       </c>
       <c r="B114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C114" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -5167,12 +5174,12 @@
     </row>
     <row r="115">
       <c r="A115" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
-        <v>337</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
+        <v>326</v>
       </c>
       <c r="B115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
-        <v>ANDRÉ ALMEIDA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C115" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -5185,34 +5192,34 @@
     </row>
     <row r="116">
       <c r="A116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
       </c>
       <c r="B116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
       </c>
       <c r="C116" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
       </c>
       <c r="B117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
       </c>
       <c r="C117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D117" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5221,34 +5228,34 @@
     </row>
     <row r="118">
       <c r="A118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
+        <v>329</v>
       </c>
       <c r="B118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
+        <v>CORREIA</v>
       </c>
       <c r="C118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
-        <v>350</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
       </c>
       <c r="B119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
-        <v>SERGI CARDONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
       </c>
       <c r="C119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D119" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5257,34 +5264,34 @@
     </row>
     <row r="120">
       <c r="A120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
+        <v>331</v>
       </c>
       <c r="B120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
+        <v>COPETE</v>
       </c>
       <c r="C120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),332.0)</f>
+        <v>332</v>
       </c>
       <c r="B121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIAKHABY")</f>
+        <v>DIAKHABY</v>
       </c>
       <c r="C121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D121" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5293,52 +5300,52 @@
     </row>
     <row r="122">
       <c r="A122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
-        <v>355</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
       </c>
       <c r="B122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
-        <v>MOLEIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
       </c>
       <c r="C122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
+        <v>337</v>
       </c>
       <c r="B123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
+        <v>ANDRÉ ALMEIDA</v>
       </c>
       <c r="C123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
       </c>
       <c r="B124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
       </c>
       <c r="C124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D124" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5347,70 +5354,70 @@
     </row>
     <row r="125">
       <c r="A125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
-        <v>371</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D125" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
+      </c>
+      <c r="B126" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
+      </c>
+      <c r="C126" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D126" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),344.0)</f>
+        <v>344</v>
+      </c>
+      <c r="B127" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ JÚNIOR")</f>
+        <v>LUIZ JÚNIOR</v>
+      </c>
+      <c r="C127" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D127" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),376.0)</f>
-        <v>376</v>
-      </c>
-      <c r="B126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-      <c r="C126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-      <c r="D126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
-      </c>
-      <c r="B127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
-      </c>
-      <c r="C127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
-    </row>
     <row r="128">
       <c r="A128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
+        <v>350</v>
       </c>
       <c r="B128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
+        <v>SERGI CARDONA</v>
       </c>
       <c r="C128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D128" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5419,16 +5426,16 @@
     </row>
     <row r="129">
       <c r="A129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
       </c>
       <c r="B129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
       </c>
       <c r="C129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D129" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5437,16 +5444,16 @@
     </row>
     <row r="130">
       <c r="A130" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
-        <v>399</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
       </c>
       <c r="B130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
       </c>
       <c r="C130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D130" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5455,52 +5462,52 @@
     </row>
     <row r="131">
       <c r="A131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),403.0)</f>
-        <v>403</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
+        <v>355</v>
       </c>
       <c r="B131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVINCHI")</f>
-        <v>DAVINCHI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
+        <v>MOLEIRO</v>
       </c>
       <c r="C131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
-        <v>404</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
       </c>
       <c r="B132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="C132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
-        <v>407</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
+        <v>366</v>
       </c>
       <c r="B133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
-        <v>CARLOS ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="C133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D133" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5509,16 +5516,16 @@
     </row>
     <row r="134">
       <c r="A134" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),408.0)</f>
-        <v>408</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
       </c>
       <c r="B134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
-        <v>ETTA EYONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="C134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D134" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5527,16 +5534,16 @@
     </row>
     <row r="135">
       <c r="A135" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
-        <v>409</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
+        <v>371</v>
       </c>
       <c r="B135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
-        <v>FRAN GONZÁLEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="C135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D135" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5545,16 +5552,16 @@
     </row>
     <row r="136">
       <c r="A136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),372.0)</f>
+        <v>372</v>
       </c>
       <c r="B136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="C136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D136" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5563,70 +5570,70 @@
     </row>
     <row r="137">
       <c r="A137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),376.0)</f>
+        <v>376</v>
       </c>
       <c r="B137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="C137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
+        <v>383</v>
       </c>
       <c r="B138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D138" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
       </c>
       <c r="B139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
-        <v>421</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
       </c>
       <c r="B140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
       </c>
       <c r="C140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D140" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5635,16 +5642,16 @@
     </row>
     <row r="141">
       <c r="A141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),396.0)</f>
+        <v>396</v>
       </c>
       <c r="B141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOURIÑO")</f>
+        <v>MOURIÑO</v>
       </c>
       <c r="C141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D141" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5653,16 +5660,16 @@
     </row>
     <row r="142">
       <c r="A142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
       </c>
       <c r="B142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
       </c>
       <c r="C142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D142" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5671,16 +5678,16 @@
     </row>
     <row r="143">
       <c r="A143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
-        <v>448</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
+        <v>399</v>
       </c>
       <c r="B143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
-        <v>GRIEZMANN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
       </c>
       <c r="C143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D143" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5689,16 +5696,16 @@
     </row>
     <row r="144">
       <c r="A144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
-        <v>452</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),402.0)</f>
+        <v>402</v>
       </c>
       <c r="B144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
-        <v>LEWANDOWSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
+        <v>RIEDEL</v>
       </c>
       <c r="C144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D144" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5707,16 +5714,16 @@
     </row>
     <row r="145">
       <c r="A145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
-        <v>458</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),403.0)</f>
+        <v>403</v>
       </c>
       <c r="B145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
-        <v>CARRERAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVINCHI")</f>
+        <v>DAVINCHI</v>
       </c>
       <c r="C145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D145" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5725,16 +5732,16 @@
     </row>
     <row r="146">
       <c r="A146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
-        <v>462</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
       </c>
       <c r="B146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
-        <v>ISI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D146" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5743,18 +5750,288 @@
     </row>
     <row r="147">
       <c r="A147" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
+        <v>407</v>
+      </c>
+      <c r="B147" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
+        <v>CARLOS ÁLVAREZ</v>
+      </c>
+      <c r="C147" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+      <c r="D147" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),408.0)</f>
+        <v>408</v>
+      </c>
+      <c r="B148" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
+        <v>ETTA EYONG</v>
+      </c>
+      <c r="C148" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+      <c r="D148" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
+        <v>409</v>
+      </c>
+      <c r="B149" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
+        <v>FRAN GONZÁLEZ</v>
+      </c>
+      <c r="C149" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D149" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
+      </c>
+      <c r="B150" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
+      </c>
+      <c r="C150" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D150" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
+      </c>
+      <c r="B151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
+      </c>
+      <c r="C151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D151" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
+      </c>
+      <c r="B152" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
+      </c>
+      <c r="C152" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D152" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
+      </c>
+      <c r="B153" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
+      </c>
+      <c r="C153" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D153" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
+        <v>421</v>
+      </c>
+      <c r="B154" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
+      </c>
+      <c r="C154" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D154" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
+      </c>
+      <c r="B155" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
+      </c>
+      <c r="C155" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D155" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
+      </c>
+      <c r="B156" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
+      </c>
+      <c r="C156" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D156" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
+        <v>448</v>
+      </c>
+      <c r="B157" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
+        <v>GRIEZMANN</v>
+      </c>
+      <c r="C157" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D157" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
+        <v>452</v>
+      </c>
+      <c r="B158" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
+        <v>LEWANDOWSKI</v>
+      </c>
+      <c r="C158" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D158" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
+        <v>454</v>
+      </c>
+      <c r="B159" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
+        <v>ISCO</v>
+      </c>
+      <c r="C159" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D159" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
+        <v>458</v>
+      </c>
+      <c r="B160" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
+        <v>CARRERAS</v>
+      </c>
+      <c r="C160" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D160" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
+        <v>462</v>
+      </c>
+      <c r="B161" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
+      </c>
+      <c r="C161" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D161" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B147" s="20" t="str">
+      <c r="B162" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C147" s="20" t="str">
+      <c r="C162" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D147" s="20">
+      <c r="D162" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
@@ -6672,6 +6949,9 @@
       <c r="D62" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E62" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="21">
@@ -6848,7 +7128,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="75">
@@ -7192,7 +7472,9 @@
       <c r="C98" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D98" s="21"/>
+      <c r="D98" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="21">
@@ -7316,7 +7598,7 @@
         <v>20</v>
       </c>
       <c r="E106" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="107">
@@ -7426,7 +7708,9 @@
       <c r="C113" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D113" s="21"/>
+      <c r="D113" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="21">
@@ -7523,7 +7807,9 @@
       <c r="C120" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D120" s="21"/>
+      <c r="D120" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="21">
@@ -7539,7 +7825,7 @@
         <v>20</v>
       </c>
       <c r="E121" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="122">
@@ -7645,6 +7931,9 @@
       <c r="D128" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E128" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="21">
@@ -7824,7 +8113,7 @@
         <v>20</v>
       </c>
       <c r="E140" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="141">
@@ -7993,6 +8282,9 @@
       <c r="D152" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E152" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="21">
@@ -8541,6 +8833,9 @@
       <c r="D190" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E190" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="21">
@@ -8898,6 +9193,9 @@
       <c r="D215" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E215" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="21">
@@ -8913,7 +9211,7 @@
         <v>20</v>
       </c>
       <c r="E216" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="217">
@@ -9093,6 +9391,9 @@
       <c r="D228" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E228" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="21">
@@ -9227,6 +9528,9 @@
       <c r="D237" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E237" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="21">
@@ -9383,7 +9687,7 @@
         <v>20</v>
       </c>
       <c r="E248" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="249">
@@ -10070,7 +10374,7 @@
         <v>20</v>
       </c>
       <c r="E295" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="296">
@@ -10544,7 +10848,7 @@
         <v>20</v>
       </c>
       <c r="E327" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="328">
@@ -10612,7 +10916,7 @@
         <v>20</v>
       </c>
       <c r="E331" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="332">
@@ -10810,6 +11114,9 @@
       </c>
       <c r="D344" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E344" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="345">
@@ -11224,6 +11531,9 @@
       <c r="D10" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E10" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="21">
@@ -11478,6 +11788,9 @@
       <c r="D6" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E6" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21">
@@ -11567,6 +11880,9 @@
       </c>
       <c r="D12" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E12" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="13">
@@ -13781,6 +14097,9 @@
       <c r="D3" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E3" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="21">
@@ -13978,6 +14297,9 @@
       </c>
       <c r="D9" s="21" t="s">
         <v>20</v>
+      </c>
+      <c r="E9" s="22">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -14090,6 +14412,9 @@
       <c r="D6" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E6" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="422">
   <si>
     <t>Última actualización:</t>
   </si>
@@ -1217,6 +1217,75 @@
   </si>
   <si>
     <t>CAMPEÓN CARD</t>
+  </si>
+  <si>
+    <t>1MN</t>
+  </si>
+  <si>
+    <t>2MN</t>
+  </si>
+  <si>
+    <t>CELTA</t>
+  </si>
+  <si>
+    <t>3MN</t>
+  </si>
+  <si>
+    <t>4MN</t>
+  </si>
+  <si>
+    <t>5MN</t>
+  </si>
+  <si>
+    <t>HACNKO</t>
+  </si>
+  <si>
+    <t>ATLETICO DE MADRID</t>
+  </si>
+  <si>
+    <t>6MN</t>
+  </si>
+  <si>
+    <t>7MN</t>
+  </si>
+  <si>
+    <t>NICO GONZALEZ</t>
+  </si>
+  <si>
+    <t>8MN</t>
+  </si>
+  <si>
+    <t>SANTAMARIA</t>
+  </si>
+  <si>
+    <t>9MN</t>
+  </si>
+  <si>
+    <t>10MN</t>
+  </si>
+  <si>
+    <t>MASTANTUONDO</t>
+  </si>
+  <si>
+    <t>11MN</t>
+  </si>
+  <si>
+    <t>12MN</t>
+  </si>
+  <si>
+    <t>13MN</t>
+  </si>
+  <si>
+    <t>VILLAREAL CF</t>
+  </si>
+  <si>
+    <t>14MN</t>
+  </si>
+  <si>
+    <t>15MN</t>
+  </si>
+  <si>
+    <t>OLUWASEVI</t>
   </si>
   <si>
     <t>ÁLEX BAENA</t>
@@ -1437,7 +1506,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1488,6 +1557,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1777,7 +1849,7 @@
       </c>
       <c r="B1" s="2">
         <f>TODAY()</f>
-        <v>46068</v>
+        <v>46070</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1833,15 +1905,15 @@
       </c>
       <c r="C3" s="9">
         <f>COUNTIF(REGULARES!D:D, "SI")</f>
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D3" s="9">
         <f t="shared" ref="D3:D12" si="1">B3-C3</f>
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E4" si="2">(C3/B3)</f>
-        <v>0.85</v>
+        <v>0.8583333333</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E3, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1905,15 +1977,15 @@
       </c>
       <c r="C6" s="14">
         <f>COUNTIF('Guantes de Oro (381–387)'!D:D, "SI")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="15">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" si="3"/>
-        <v>0.5714285714</v>
+        <v>0.7142857143</v>
       </c>
       <c r="F6" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E6, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2001,15 +2073,15 @@
       </c>
       <c r="C10" s="14">
         <f>COUNTIF('Protas (424–441)'!D:D, "SI")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="3"/>
-        <v>0.8333333333</v>
+        <v>0.8888888889</v>
       </c>
       <c r="F10" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E10, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2049,15 +2121,15 @@
       </c>
       <c r="C12" s="14">
         <f>COUNTIF('Cartas Top y Únicas (468–478)'!D:D, "SI")</f>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D12" s="15">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="E12" s="10">
         <f t="shared" si="3"/>
-        <v>0.5454545455</v>
+        <v>1.363636364</v>
       </c>
       <c r="F12" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E12, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2074,15 +2146,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="4"/>
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="4"/>
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>0.843373494</v>
+        <v>0.8714859438</v>
       </c>
       <c r="F13" s="19" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E13, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2266,7 +2338,9 @@
       <c r="C1" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21">
@@ -2673,8 +2747,224 @@
         <v>20</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="D12" s="21"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="D13" s="21"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="s">
+        <v>401</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="22">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="s">
+        <v>402</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="22">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="D17" s="21"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="22">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="s">
+        <v>411</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="22">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="s">
+        <v>412</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="22">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="22">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="21"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="s">
+        <v>416</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="D24" s="21"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:D11">
+  <conditionalFormatting sqref="A1:D26">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$D1="SI"</formula>
     </cfRule>
@@ -2746,13 +3036,16 @@
       <c r="D4" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E4" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="21">
         <v>446.0</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>56</v>
@@ -3248,12 +3541,12 @@
     </row>
     <row r="8">
       <c r="A8" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="B8" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIANO")</f>
-        <v>MARIANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BOYÉ")</f>
+        <v>BOYÉ</v>
       </c>
       <c r="C8" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
@@ -3266,16 +3559,16 @@
     </row>
     <row r="9">
       <c r="A9" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
+        <v>18</v>
       </c>
       <c r="B9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIANO")</f>
+        <v>MARIANO</v>
       </c>
       <c r="C9" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
-        <v>ATHLETIC CLUB</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="D9" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3284,12 +3577,12 @@
     </row>
     <row r="10">
       <c r="A10" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
-        <v>21</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="B10" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PADILLA")</f>
-        <v>PADILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C10" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3302,12 +3595,12 @@
     </row>
     <row r="11">
       <c r="A11" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
+        <v>21</v>
       </c>
       <c r="B11" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VIVIAN")</f>
-        <v>VIVIAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PADILLA")</f>
+        <v>PADILLA</v>
       </c>
       <c r="C11" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3320,12 +3613,12 @@
     </row>
     <row r="12">
       <c r="A12" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
-        <v>27</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
+        <v>23</v>
       </c>
       <c r="B12" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUIZ DE GALARRETA")</f>
-        <v>RUIZ DE GALARRETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VIVIAN")</f>
+        <v>VIVIAN</v>
       </c>
       <c r="C12" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3338,12 +3631,12 @@
     </row>
     <row r="13">
       <c r="A13" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
-        <v>33</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="B13" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WILLIAMS")</f>
-        <v>WILLIAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RUIZ DE GALARRETA")</f>
+        <v>RUIZ DE GALARRETA</v>
       </c>
       <c r="C13" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3356,12 +3649,12 @@
     </row>
     <row r="14">
       <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
-        <v>34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
+        <v>33</v>
       </c>
       <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
-        <v>MAROAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WILLIAMS")</f>
+        <v>WILLIAMS</v>
       </c>
       <c r="C14" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3374,16 +3667,16 @@
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
-        <v>37</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
+        <v>34</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
+        <v>MAROAN</v>
       </c>
       <c r="C15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D15" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3392,12 +3685,12 @@
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
-        <v>39</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MUSSO")</f>
-        <v>MUSSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C16" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3410,12 +3703,12 @@
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
+        <v>39</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
-        <v>LENGLET</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MUSSO")</f>
+        <v>MUSSO</v>
       </c>
       <c r="C17" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3428,12 +3721,12 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
+        <v>40</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
-        <v>ALMADA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
+        <v>MARCOS LLORENTE</v>
       </c>
       <c r="C18" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3446,12 +3739,12 @@
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
-        <v>52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
-        <v>JULIÁN ALVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
+        <v>LENGLET</v>
       </c>
       <c r="C19" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3464,16 +3757,16 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
-        <v>55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
+        <v>ALMADA</v>
       </c>
       <c r="C20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D20" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3482,16 +3775,16 @@
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
-        <v>56</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
+        <v>52</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOAN GARCÍA")</f>
-        <v>JOAN GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
+        <v>JULIÁN ALVAREZ</v>
       </c>
       <c r="C21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D21" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3500,12 +3793,12 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
-        <v>62</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
+        <v>55</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALDE")</f>
-        <v>BALDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C22" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3518,12 +3811,12 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
-        <v>63</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DE JONG")</f>
-        <v>DE JONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOAN GARCÍA")</f>
+        <v>JOAN GARCÍA</v>
       </c>
       <c r="C23" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3536,12 +3829,12 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
-        <v>66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61.0)</f>
+        <v>61</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
-        <v>FERMÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAÚJO")</f>
+        <v>ARAÚJO</v>
       </c>
       <c r="C24" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3554,12 +3847,12 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
-        <v>67</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
+        <v>62</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
-        <v>DANI OLMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALDE")</f>
+        <v>BALDE</v>
       </c>
       <c r="C25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3572,16 +3865,16 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
-        <v>73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
+        <v>63</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DE JONG")</f>
+        <v>DE JONG</v>
       </c>
       <c r="C26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D26" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3590,34 +3883,34 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
-        <v>PAU LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
+        <v>FERMÍN</v>
       </c>
       <c r="C27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
-        <v>76</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
-        <v>BELLERÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
+        <v>DANI OLMO</v>
       </c>
       <c r="C28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D28" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3626,12 +3919,12 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C29" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3644,30 +3937,30 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
-        <v>84</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
-        <v>PABLO FORNALS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
+        <v>PAU LÓPEZ</v>
       </c>
       <c r="C30" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
+        <v>BELLERÍN</v>
       </c>
       <c r="C31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3680,16 +3973,16 @@
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
-        <v>91</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D32" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3698,16 +3991,16 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
-        <v>94</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
+        <v>84</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
-        <v>JAVI RUEDA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
+        <v>PABLO FORNALS</v>
       </c>
       <c r="C33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D33" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3716,16 +4009,16 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
       </c>
       <c r="C34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D34" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3734,12 +4027,12 @@
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
+        <v>91</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C35" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3752,48 +4045,48 @@
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
+        <v>94</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
+        <v>JAVI RUEDA</v>
       </c>
       <c r="C36" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
-        <v>104</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
-        <v>SWEDBERG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C37" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C38" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3806,12 +4099,12 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
-        <v>106</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
-        <v>IAGO ASPAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C39" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3824,30 +4117,30 @@
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
+        <v>104</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
+        <v>SWEDBERG</v>
       </c>
       <c r="C40" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C41" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -3860,52 +4153,52 @@
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
-        <v>IÑAKI PEÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
+        <v>IAGO ASPAS</v>
       </c>
       <c r="C42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D42" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
+      </c>
+      <c r="B43" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
+      </c>
+      <c r="C43" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D43" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
-      </c>
-      <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
-      </c>
-      <c r="C43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
-      </c>
-      <c r="D43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
-        <v>112</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
-        <v>ÁLVARO NÚÑEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
       </c>
       <c r="C44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D44" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3914,12 +4207,12 @@
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
+        <v>IÑAKI PEÑA</v>
       </c>
       <c r="C45" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3932,12 +4225,12 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C46" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3950,12 +4243,12 @@
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
-        <v>126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
-        <v>RAFA MIR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
+        <v>ÁLVARO NÚÑEZ</v>
       </c>
       <c r="C47" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -3968,16 +4261,16 @@
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
-        <v>127</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D48" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3986,34 +4279,34 @@
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
-        <v>128</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
-        <v>DMITROVIC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),134.0)</f>
-        <v>134</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
+        <v>126</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ROMERO")</f>
-        <v>CARLOS ROMERO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
+        <v>RAFA MIR</v>
       </c>
       <c r="C50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D50" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4022,12 +4315,12 @@
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
+        <v>127</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C51" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -4040,30 +4333,30 @@
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
+        <v>128</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
+        <v>DMITROVIC</v>
       </c>
       <c r="C52" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
-        <v>139</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),134.0)</f>
+        <v>134</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
-        <v>ANTONIU ROCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ROMERO")</f>
+        <v>CARLOS ROMERO</v>
       </c>
       <c r="C53" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -4076,48 +4369,48 @@
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C54" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C55" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
+        <v>139</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
+        <v>ANTONIU ROCA</v>
       </c>
       <c r="C56" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -4130,34 +4423,34 @@
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
       </c>
       <c r="C58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D58" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4166,16 +4459,16 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),152.0)</f>
-        <v>152</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABQAR")</f>
-        <v>ABQAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D59" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4184,12 +4477,12 @@
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
-        <v>153</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
-        <v>DIEGO RICO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C60" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -4202,16 +4495,16 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D61" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4220,16 +4513,16 @@
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),152.0)</f>
+        <v>152</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABQAR")</f>
+        <v>ABQAR</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D62" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4238,16 +4531,16 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
+        <v>153</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
+        <v>DIEGO RICO</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D63" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4256,12 +4549,12 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
-        <v>174</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
-        <v>IVÁN MARTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C64" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -4274,30 +4567,30 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C65" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
       </c>
       <c r="D65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
-        <v>176</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
+        <v>164</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
-        <v>JOEL ROCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAZZANIGA")</f>
+        <v>GAZZANIGA</v>
       </c>
       <c r="C66" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -4310,16 +4603,16 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
-        <v>189</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
-        <v>PAMPÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D67" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4328,52 +4621,52 @@
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),190.0)</f>
-        <v>190</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
+        <v>174</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORIOL REY")</f>
-        <v>ORIOL REY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
+        <v>IVÁN MARTÍN</v>
       </c>
       <c r="C68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),195.0)</f>
-        <v>195</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORALES")</f>
-        <v>MORALES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
       </c>
       <c r="C69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
-        <v>202</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
+        <v>176</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
-        <v>CARVAJAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
+        <v>JOEL ROCA</v>
       </c>
       <c r="C70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D70" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4382,16 +4675,16 @@
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),179.0)</f>
+        <v>179</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"STUANI")</f>
+        <v>STUANI</v>
       </c>
       <c r="C71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D71" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4400,16 +4693,16 @@
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
-        <v>211</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),187.0)</f>
+        <v>187</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
-        <v>GÜLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATÍAS MORENO")</f>
+        <v>MATÍAS MORENO</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D72" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4418,16 +4711,16 @@
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
-        <v>212</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
+        <v>189</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
+        <v>PAMPÍN</v>
       </c>
       <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D73" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4436,16 +4729,16 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),215.0)</f>
-        <v>215</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),190.0)</f>
+        <v>190</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
-        <v>GONZALO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORIOL REY")</f>
+        <v>ORIOL REY</v>
       </c>
       <c r="C74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D74" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4454,34 +4747,34 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),195.0)</f>
+        <v>195</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORALES")</f>
+        <v>MORALES</v>
       </c>
       <c r="C75" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
+      </c>
+      <c r="D75" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
+        <v>202</v>
+      </c>
+      <c r="B76" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
+        <v>CARVAJAL</v>
+      </c>
+      <c r="C76" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
         <v>REAL MADRID</v>
-      </c>
-      <c r="D75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
-        <v>219</v>
-      </c>
-      <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
-        <v>BERGSTRÖM</v>
-      </c>
-      <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
       </c>
       <c r="D76" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4490,34 +4783,34 @@
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),203.0)</f>
+        <v>203</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRENT")</f>
+        <v>TRENT</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
-        <v>224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
-        <v>KUMBULLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D78" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4526,16 +4819,16 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
-        <v>225</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
-        <v>MOJICA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
       </c>
       <c r="C79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D79" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4544,16 +4837,16 @@
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),228.0)</f>
-        <v>228</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
+        <v>212</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
-        <v>DARDER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
       </c>
       <c r="C80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D80" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4562,16 +4855,16 @@
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),230.0)</f>
-        <v>230</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),215.0)</f>
+        <v>215</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO TORRE")</f>
-        <v>PABLO TORRE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
+        <v>GONZALO</v>
       </c>
       <c r="C81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D81" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4580,52 +4873,52 @@
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
       </c>
       <c r="C82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
+        <v>217</v>
       </c>
       <c r="B83" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
         <v>ESCUDO</v>
       </c>
       <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
+        <v>217</v>
       </c>
       <c r="B84" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
         <v>ESTADIO</v>
       </c>
       <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D84" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4634,16 +4927,16 @@
     </row>
     <row r="85">
       <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
+        <v>219</v>
       </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
+        <v>BERGSTRÖM</v>
       </c>
       <c r="C85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D85" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4652,34 +4945,34 @@
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
-        <v>237</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
-        <v>AITOR FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
       </c>
       <c r="C86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
-        <v>245</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
+        <v>224</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
-        <v>MONCAYOLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
+        <v>KUMBULLA</v>
       </c>
       <c r="C87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D87" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4688,70 +4981,70 @@
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
-        <v>248</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
+        <v>225</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
+        <v>MOJICA</v>
       </c>
       <c r="C88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),228.0)</f>
+        <v>228</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
+        <v>DARDER</v>
       </c>
       <c r="C89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),230.0)</f>
+        <v>230</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO TORRE")</f>
+        <v>PABLO TORRE</v>
       </c>
       <c r="C90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
       </c>
       <c r="C91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D91" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4760,34 +5053,34 @@
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
-        <v>260</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
-        <v>RAHIM ALHASSANE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D93" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4796,16 +5089,16 @@
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
-        <v>265</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
-        <v>ILIC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D94" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4814,16 +5107,16 @@
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
+        <v>237</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
+        <v>AITOR FERNÁNDEZ</v>
       </c>
       <c r="C95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D95" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4832,106 +5125,106 @@
     </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
+        <v>245</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
+        <v>MONCAYOLA</v>
       </c>
       <c r="C96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D96" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
+        <v>248</v>
+      </c>
+      <c r="B97" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
+      </c>
+      <c r="C97" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D97" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
-        <v>281</v>
-      </c>
-      <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
-        <v>ÓSCAR VALENTÍN</v>
-      </c>
-      <c r="C97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
-      </c>
-      <c r="D97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
-        <v>282</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
-        <v>ISI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
-        <v>283</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
-        <v>PEDRO DÍAZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
-        <v>286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
-        <v>CAMELLO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
-        <v>290</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
+        <v>260</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
+        <v>RAHIM ALHASSANE</v>
       </c>
       <c r="C101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D101" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4940,16 +5233,16 @@
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
-        <v>292</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
-        <v>ARAMBURU</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D102" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4958,34 +5251,34 @@
     </row>
     <row r="103">
       <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
+        <v>265</v>
       </c>
       <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
+        <v>ILIC</v>
       </c>
       <c r="C103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
-        <v>296</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
-        <v>SERGIO GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D104" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4994,16 +5287,16 @@
     </row>
     <row r="105">
       <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
+        <v>277</v>
       </c>
       <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
+        <v>LUIZ FELIPE</v>
       </c>
       <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D105" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5012,34 +5305,34 @@
     </row>
     <row r="106">
       <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
-        <v>302</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
       </c>
       <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
-        <v>KUBO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
       </c>
       <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
+        <v>281</v>
       </c>
       <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
+        <v>ÓSCAR VALENTÍN</v>
       </c>
       <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D107" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5048,16 +5341,16 @@
     </row>
     <row r="108">
       <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
-        <v>312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
+        <v>282</v>
       </c>
       <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
-        <v>AZPILICUETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
       </c>
       <c r="C108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D108" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5066,34 +5359,34 @@
     </row>
     <row r="109">
       <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
       </c>
       <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
       </c>
       <c r="C109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
-        <v>317</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
+        <v>286</v>
       </c>
       <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
-        <v>AGOUME</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
+        <v>CAMELLO</v>
       </c>
       <c r="C110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D110" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5102,34 +5395,34 @@
     </row>
     <row r="111">
       <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),287.0)</f>
+        <v>287</v>
       </c>
       <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DE FRUTOS")</f>
+        <v>DE FRUTOS</v>
       </c>
       <c r="C111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
+        <v>290</v>
       </c>
       <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
       </c>
       <c r="C112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D112" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5138,52 +5431,52 @@
     </row>
     <row r="113">
       <c r="A113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
+        <v>292</v>
       </c>
       <c r="B113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
+        <v>ARAMBURU</v>
       </c>
       <c r="C113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D113" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
+      </c>
+      <c r="B114" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
+      </c>
+      <c r="C114" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+      <c r="D114" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
-      </c>
-      <c r="B114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="115">
       <c r="A115" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
-        <v>326</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
+        <v>296</v>
       </c>
       <c r="B115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
+        <v>SERGIO GÓMEZ</v>
       </c>
       <c r="C115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D115" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5192,52 +5485,52 @@
     </row>
     <row r="116">
       <c r="A116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
-        <v>327</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
-        <v>DIMITRIEVSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
+        <v>302</v>
       </c>
       <c r="B117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
+        <v>KUBO</v>
       </c>
       <c r="C117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
-        <v>329</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
-        <v>CORREIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D118" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5246,16 +5539,16 @@
     </row>
     <row r="119">
       <c r="A119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
+        <v>312</v>
       </c>
       <c r="B119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
+        <v>AZPILICUETA</v>
       </c>
       <c r="C119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D119" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5264,16 +5557,16 @@
     </row>
     <row r="120">
       <c r="A120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
-        <v>331</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
       </c>
       <c r="B120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
-        <v>COPETE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
       </c>
       <c r="C120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D120" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5282,16 +5575,16 @@
     </row>
     <row r="121">
       <c r="A121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),332.0)</f>
-        <v>332</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
+        <v>317</v>
       </c>
       <c r="B121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIAKHABY")</f>
-        <v>DIAKHABY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
+        <v>AGOUME</v>
       </c>
       <c r="C121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D121" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5300,142 +5593,142 @@
     </row>
     <row r="122">
       <c r="A122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
       </c>
       <c r="B122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
       </c>
       <c r="C122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
-        <v>337</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
       </c>
       <c r="B123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
-        <v>ANDRÉ ALMEIDA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
       </c>
       <c r="C123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
       </c>
       <c r="B124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C124" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D124" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
+      </c>
+      <c r="B125" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
+      </c>
+      <c r="C125" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D125" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
-      </c>
-      <c r="B125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D125" s="20">
+    <row r="126">
+      <c r="A126" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
+        <v>326</v>
+      </c>
+      <c r="B126" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
+      </c>
+      <c r="C126" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D126" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
+      </c>
+      <c r="B127" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
+      </c>
+      <c r="C127" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D127" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
-      </c>
-      <c r="B126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D126" s="20">
+    <row r="128">
+      <c r="A128" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
+      </c>
+      <c r="B128" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
+      </c>
+      <c r="C128" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
+      </c>
+      <c r="D128" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),344.0)</f>
-        <v>344</v>
-      </c>
-      <c r="B127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ JÚNIOR")</f>
-        <v>LUIZ JÚNIOR</v>
-      </c>
-      <c r="C127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
-        <v>350</v>
-      </c>
-      <c r="B128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
-        <v>SERGI CARDONA</v>
-      </c>
-      <c r="C128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
-      </c>
-      <c r="D128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="129">
       <c r="A129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
+        <v>329</v>
       </c>
       <c r="B129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
+        <v>CORREIA</v>
       </c>
       <c r="C129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D129" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5444,16 +5737,16 @@
     </row>
     <row r="130">
       <c r="A130" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
       </c>
       <c r="B130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
       </c>
       <c r="C130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D130" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5462,16 +5755,16 @@
     </row>
     <row r="131">
       <c r="A131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
-        <v>355</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
+        <v>331</v>
       </c>
       <c r="B131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
-        <v>MOLEIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
+        <v>COPETE</v>
       </c>
       <c r="C131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D131" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5480,34 +5773,34 @@
     </row>
     <row r="132">
       <c r="A132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),332.0)</f>
+        <v>332</v>
       </c>
       <c r="B132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIAKHABY")</f>
+        <v>DIAKHABY</v>
       </c>
       <c r="C132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
-        <v>366</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
       </c>
       <c r="B133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
       </c>
       <c r="C133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D133" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5516,16 +5809,16 @@
     </row>
     <row r="134">
       <c r="A134" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
+        <v>337</v>
       </c>
       <c r="B134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
+        <v>ANDRÉ ALMEIDA</v>
       </c>
       <c r="C134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D134" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5534,16 +5827,16 @@
     </row>
     <row r="135">
       <c r="A135" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
-        <v>371</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
       </c>
       <c r="B135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
       </c>
       <c r="C135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D135" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5552,52 +5845,52 @@
     </row>
     <row r="136">
       <c r="A136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),372.0)</f>
-        <v>372</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),376.0)</f>
-        <v>376</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
-        <v>383</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),344.0)</f>
+        <v>344</v>
       </c>
       <c r="B138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ JÚNIOR")</f>
+        <v>LUIZ JÚNIOR</v>
       </c>
       <c r="C138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D138" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5606,34 +5899,34 @@
     </row>
     <row r="139">
       <c r="A139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
+        <v>350</v>
       </c>
       <c r="B139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
+        <v>SERGI CARDONA</v>
       </c>
       <c r="C139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
       </c>
       <c r="B140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
       </c>
       <c r="C140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D140" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5642,12 +5935,12 @@
     </row>
     <row r="141">
       <c r="A141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),396.0)</f>
-        <v>396</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
       </c>
       <c r="B141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOURIÑO")</f>
-        <v>MOURIÑO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
       </c>
       <c r="C141" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
@@ -5660,52 +5953,52 @@
     </row>
     <row r="142">
       <c r="A142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
+        <v>355</v>
       </c>
       <c r="B142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
+        <v>MOLEIRO</v>
       </c>
       <c r="C142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
-        <v>399</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
       </c>
       <c r="B143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="C143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),402.0)</f>
-        <v>402</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
+        <v>366</v>
       </c>
       <c r="B144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
-        <v>RIEDEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="C144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D144" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5714,16 +6007,16 @@
     </row>
     <row r="145">
       <c r="A145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),403.0)</f>
-        <v>403</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
       </c>
       <c r="B145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVINCHI")</f>
-        <v>DAVINCHI</v>
-      </c>
-      <c r="C145" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
         <v>GETAFE CF</v>
+      </c>
+      <c r="C145" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D145" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5732,16 +6025,16 @@
     </row>
     <row r="146">
       <c r="A146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
-        <v>404</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
+        <v>371</v>
       </c>
       <c r="B146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="C146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D146" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5750,16 +6043,16 @@
     </row>
     <row r="147">
       <c r="A147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
-        <v>407</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),372.0)</f>
+        <v>372</v>
       </c>
       <c r="B147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
-        <v>CARLOS ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="C147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D147" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5768,16 +6061,16 @@
     </row>
     <row r="148">
       <c r="A148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),408.0)</f>
-        <v>408</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),376.0)</f>
+        <v>376</v>
       </c>
       <c r="B148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
-        <v>ETTA EYONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="C148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D148" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5786,16 +6079,16 @@
     </row>
     <row r="149">
       <c r="A149" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
-        <v>409</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
+        <v>383</v>
       </c>
       <c r="B149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
-        <v>FRAN GONZÁLEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D149" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5804,70 +6097,70 @@
     </row>
     <row r="150">
       <c r="A150" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
       </c>
       <c r="B150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D150" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
+      </c>
+      <c r="B151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
+      </c>
+      <c r="C151" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
+      </c>
+      <c r="D151" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
-      </c>
-      <c r="B151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
-      </c>
-      <c r="C151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
-      </c>
-      <c r="D151" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="152">
       <c r="A152" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),396.0)</f>
+        <v>396</v>
       </c>
       <c r="B152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOURIÑO")</f>
+        <v>MOURIÑO</v>
       </c>
       <c r="C152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D152" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
       </c>
       <c r="B153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
       </c>
       <c r="C153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D153" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5876,16 +6169,16 @@
     </row>
     <row r="154">
       <c r="A154" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
-        <v>421</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
+        <v>399</v>
       </c>
       <c r="B154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
       </c>
       <c r="C154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D154" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5894,16 +6187,16 @@
     </row>
     <row r="155">
       <c r="A155" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
+        <v>401</v>
       </c>
       <c r="B155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
+        <v>RODRI MENDOZA</v>
       </c>
       <c r="C155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D155" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5912,16 +6205,16 @@
     </row>
     <row r="156">
       <c r="A156" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),402.0)</f>
+        <v>402</v>
       </c>
       <c r="B156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
+        <v>RIEDEL</v>
       </c>
       <c r="C156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D156" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5930,16 +6223,16 @@
     </row>
     <row r="157">
       <c r="A157" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
-        <v>448</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),403.0)</f>
+        <v>403</v>
       </c>
       <c r="B157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
-        <v>GRIEZMANN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVINCHI")</f>
+        <v>DAVINCHI</v>
       </c>
       <c r="C157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D157" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5948,16 +6241,16 @@
     </row>
     <row r="158">
       <c r="A158" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
-        <v>452</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
       </c>
       <c r="B158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
-        <v>LEWANDOWSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D158" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5966,16 +6259,16 @@
     </row>
     <row r="159">
       <c r="A159" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
-        <v>454</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
+        <v>407</v>
       </c>
       <c r="B159" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
-        <v>ISCO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
+        <v>CARLOS ÁLVAREZ</v>
       </c>
       <c r="C159" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D159" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5984,16 +6277,16 @@
     </row>
     <row r="160">
       <c r="A160" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
-        <v>458</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),408.0)</f>
+        <v>408</v>
       </c>
       <c r="B160" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
-        <v>CARRERAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
+        <v>ETTA EYONG</v>
       </c>
       <c r="C160" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D160" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6002,16 +6295,16 @@
     </row>
     <row r="161">
       <c r="A161" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
-        <v>462</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
+        <v>409</v>
       </c>
       <c r="B161" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
-        <v>ISI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
+        <v>FRAN GONZÁLEZ</v>
       </c>
       <c r="C161" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D161" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6020,18 +6313,252 @@
     </row>
     <row r="162">
       <c r="A162" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
+      </c>
+      <c r="B162" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
+      </c>
+      <c r="C162" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D162" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
+      </c>
+      <c r="B163" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
+      </c>
+      <c r="C163" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D163" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
+      </c>
+      <c r="B164" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
+      </c>
+      <c r="C164" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
+      </c>
+      <c r="D164" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
+      </c>
+      <c r="B165" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
+      </c>
+      <c r="C165" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
+      </c>
+      <c r="D165" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
+        <v>421</v>
+      </c>
+      <c r="B166" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
+      </c>
+      <c r="C166" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
+      </c>
+      <c r="D166" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
+      </c>
+      <c r="B167" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
+      </c>
+      <c r="C167" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
+      </c>
+      <c r="D167" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
+      </c>
+      <c r="B168" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
+      </c>
+      <c r="C168" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D168" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),445.0)</f>
+        <v>445</v>
+      </c>
+      <c r="B169" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
+        <v>MARCOS LLORENTE</v>
+      </c>
+      <c r="C169" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D169" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
+        <v>448</v>
+      </c>
+      <c r="B170" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
+        <v>GRIEZMANN</v>
+      </c>
+      <c r="C170" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D170" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
+        <v>452</v>
+      </c>
+      <c r="B171" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
+        <v>LEWANDOWSKI</v>
+      </c>
+      <c r="C171" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D171" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
+        <v>454</v>
+      </c>
+      <c r="B172" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
+        <v>ISCO</v>
+      </c>
+      <c r="C172" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D172" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
+        <v>458</v>
+      </c>
+      <c r="B173" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
+        <v>CARRERAS</v>
+      </c>
+      <c r="C173" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D173" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
+        <v>462</v>
+      </c>
+      <c r="B174" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
+      </c>
+      <c r="C174" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D174" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B162" s="20" t="str">
+      <c r="B175" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C162" s="20" t="str">
+      <c r="C175" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D162" s="20">
+      <c r="D175" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
@@ -6303,6 +6830,9 @@
       <c r="D17" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E17" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="21">
@@ -6632,6 +7162,9 @@
       <c r="D40" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E40" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="21">
@@ -6935,6 +7468,9 @@
       <c r="D61" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E61" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="21">
@@ -7056,7 +7592,9 @@
       <c r="C69" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D69" s="21"/>
+      <c r="D69" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="21">
@@ -8267,7 +8805,9 @@
       <c r="C151" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D151" s="21"/>
+      <c r="D151" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="21">
@@ -8457,6 +8997,9 @@
       <c r="D164" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E164" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="21">
@@ -8600,7 +9143,7 @@
         <v>20</v>
       </c>
       <c r="E174" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="175">
@@ -8678,6 +9221,9 @@
       <c r="D179" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E179" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="21">
@@ -8717,7 +9263,9 @@
       <c r="C182" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D182" s="21"/>
+      <c r="D182" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="21">
@@ -8788,6 +9336,9 @@
       <c r="D187" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E187" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="21">
@@ -9016,6 +9567,9 @@
       <c r="D203" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E203" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="21">
@@ -9227,6 +9781,9 @@
       <c r="D217" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E217" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="21">
@@ -9846,7 +10403,7 @@
         <v>20</v>
       </c>
       <c r="E259" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="260">
@@ -10104,6 +10661,9 @@
       <c r="D277" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E277" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="21">
@@ -10257,6 +10817,9 @@
       <c r="D287" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E287" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="21">
@@ -10298,7 +10861,7 @@
         <v>20</v>
       </c>
       <c r="E290" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="291">
@@ -11201,7 +11764,7 @@
         <v>20</v>
       </c>
       <c r="E350" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="351">
@@ -11576,6 +12139,9 @@
       <c r="D13" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E13" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21">
@@ -14111,7 +14677,9 @@
       <c r="C4" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="21">
@@ -14398,6 +14966,9 @@
       <c r="D5" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E5" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="21">

--- a/Checklist_Adrenalyn_XL_2025-26.xlsx
+++ b/Checklist_Adrenalyn_XL_2025-26.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="424">
   <si>
     <t>Última actualización:</t>
   </si>
@@ -520,6 +520,9 @@
     <t>GETAFE CF</t>
   </si>
   <si>
+    <t>Albert</t>
+  </si>
+  <si>
     <t>DAVID SORIA</t>
   </si>
   <si>
@@ -1184,6 +1187,9 @@
   </si>
   <si>
     <t>UNAI LÓPEZ</t>
+  </si>
+  <si>
+    <t>Alert</t>
   </si>
   <si>
     <t>CARD CHAMPIONS</t>
@@ -1849,7 +1855,7 @@
       </c>
       <c r="B1" s="2">
         <f>TODAY()</f>
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1905,15 +1911,15 @@
       </c>
       <c r="C3" s="9">
         <f>COUNTIF(REGULARES!D:D, "SI")</f>
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D3" s="9">
         <f t="shared" ref="D3:D12" si="1">B3-C3</f>
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E4" si="2">(C3/B3)</f>
-        <v>0.8583333333</v>
+        <v>0.8694444444</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E3, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -1953,15 +1959,15 @@
       </c>
       <c r="C5" s="9">
         <f>COUNTIF('¡VAMOS! (361–380)'!D:D, "SI")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="9">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" ref="E5:E13" si="3">C5/B5</f>
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F5" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E5, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2049,15 +2055,15 @@
       </c>
       <c r="C9" s="14">
         <f>COUNTIF('Influencers (415–423)'!D:D, "SI")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="15">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="10">
         <f t="shared" si="3"/>
-        <v>0.6666666667</v>
+        <v>0.7777777778</v>
       </c>
       <c r="F9" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E9, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2073,15 +2079,15 @@
       </c>
       <c r="C10" s="14">
         <f>COUNTIF('Protas (424–441)'!D:D, "SI")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="3"/>
-        <v>0.8888888889</v>
+        <v>0.9444444444</v>
       </c>
       <c r="F10" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E10, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2146,15 +2152,15 @@
       </c>
       <c r="C13" s="17">
         <f t="shared" si="4"/>
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="4"/>
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E13" s="18">
         <f t="shared" si="3"/>
-        <v>0.8714859438</v>
+        <v>0.8855421687</v>
       </c>
       <c r="F13" s="19" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPARKLINE(E13, {""charttype"",""bar""; ""max"",1; ""color1"",""green""; ""empty"",""ignore""})"),"")</f>
@@ -2241,7 +2247,7 @@
         <v>419.0</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>164</v>
@@ -2258,22 +2264,24 @@
         <v>420.0</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="D6" s="21"/>
+        <v>237</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21">
         <v>421.0</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>20</v>
@@ -2287,10 +2295,10 @@
         <v>422.0</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>20</v>
@@ -2304,10 +2312,10 @@
         <v>423.0</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D9" s="21"/>
     </row>
@@ -2415,10 +2423,10 @@
         <v>430.0</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>20</v>
@@ -2429,10 +2437,10 @@
         <v>431.0</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>20</v>
@@ -2443,10 +2451,10 @@
         <v>432.0</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>20</v>
@@ -2457,10 +2465,10 @@
         <v>433.0</v>
       </c>
       <c r="B10" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>237</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>236</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>20</v>
@@ -2471,10 +2479,10 @@
         <v>434.0</v>
       </c>
       <c r="B11" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" s="21" t="s">
         <v>273</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>272</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>20</v>
@@ -2485,10 +2493,10 @@
         <v>435.0</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>20</v>
@@ -2499,10 +2507,10 @@
         <v>436.0</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>20</v>
@@ -2513,10 +2521,10 @@
         <v>437.0</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>20</v>
@@ -2527,10 +2535,10 @@
         <v>438.0</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>20</v>
@@ -2541,10 +2549,10 @@
         <v>439.0</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>20</v>
@@ -2558,10 +2566,10 @@
         <v>440.0</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>20</v>
@@ -2572,12 +2580,17 @@
         <v>441.0</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="D18" s="21"/>
+        <v>363</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>388</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:D18">
@@ -2605,10 +2618,10 @@
         <v>468.0</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D1" s="21" t="s">
         <v>20</v>
@@ -2622,7 +2635,7 @@
         <v>55</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>20</v>
@@ -2636,10 +2649,10 @@
         <v>470.0</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D3" s="21"/>
     </row>
@@ -2651,7 +2664,7 @@
         <v>84</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D4" s="21"/>
     </row>
@@ -2663,7 +2676,7 @@
         <v>88</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D5" s="21"/>
     </row>
@@ -2672,10 +2685,10 @@
         <v>473.0</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>20</v>
@@ -2686,10 +2699,10 @@
         <v>474.0</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>20</v>
@@ -2700,10 +2713,10 @@
         <v>475.0</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D8" s="21"/>
     </row>
@@ -2712,10 +2725,10 @@
         <v>476.0</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D9" s="21"/>
     </row>
@@ -2724,10 +2737,10 @@
         <v>477.0</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>20</v>
@@ -2738,10 +2751,10 @@
         <v>478.0</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>20</v>
@@ -2749,37 +2762,37 @@
     </row>
     <row r="12">
       <c r="A12" s="23" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B12" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>327</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>326</v>
       </c>
       <c r="D12" s="21"/>
     </row>
     <row r="13">
       <c r="A13" s="23" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B13" s="21" t="s">
         <v>111</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D13" s="21"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>20</v>
@@ -2790,13 +2803,13 @@
     </row>
     <row r="15">
       <c r="A15" s="23" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>20</v>
@@ -2804,13 +2817,13 @@
     </row>
     <row r="16">
       <c r="A16" s="23" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>20</v>
@@ -2821,25 +2834,25 @@
     </row>
     <row r="17">
       <c r="A17" s="23" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D17" s="21"/>
     </row>
     <row r="18">
       <c r="A18" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>407</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>405</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>20</v>
@@ -2850,19 +2863,19 @@
     </row>
     <row r="19">
       <c r="A19" s="23" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D19" s="21"/>
     </row>
     <row r="20">
       <c r="A20" s="23" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B20" s="21" t="s">
         <v>102</v>
@@ -2879,13 +2892,13 @@
     </row>
     <row r="21">
       <c r="A21" s="23" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>20</v>
@@ -2896,13 +2909,13 @@
     </row>
     <row r="22">
       <c r="A22" s="23" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B22" s="21" t="s">
         <v>68</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D22" s="21" t="s">
         <v>20</v>
@@ -2913,7 +2926,7 @@
     </row>
     <row r="23">
       <c r="A23" s="23" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B23" s="21" t="s">
         <v>159</v>
@@ -2925,19 +2938,19 @@
     </row>
     <row r="24">
       <c r="A24" s="23" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D24" s="21"/>
     </row>
     <row r="25">
       <c r="A25" s="23" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B25" s="21" t="s">
         <v>91</v>
@@ -2951,13 +2964,13 @@
     </row>
     <row r="26">
       <c r="A26" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>419</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>420</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>417</v>
       </c>
       <c r="D26" s="21" t="s">
         <v>20</v>
@@ -3045,7 +3058,7 @@
         <v>446.0</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>56</v>
@@ -3204,10 +3217,10 @@
         <v>457.0</v>
       </c>
       <c r="B16" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C16" s="21" t="s">
         <v>219</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>218</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>20</v>
@@ -3218,10 +3231,10 @@
         <v>458.0</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>20</v>
@@ -3235,10 +3248,10 @@
         <v>459.0</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>20</v>
@@ -3249,10 +3262,10 @@
         <v>460.0</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>20</v>
@@ -3263,10 +3276,10 @@
         <v>461.0</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>20</v>
@@ -3277,10 +3290,10 @@
         <v>462.0</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>20</v>
@@ -3294,10 +3307,10 @@
         <v>463.0</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D22" s="21" t="s">
         <v>20</v>
@@ -3308,10 +3321,10 @@
         <v>464.0</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D23" s="21"/>
     </row>
@@ -3320,10 +3333,10 @@
         <v>465.0</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D24" s="21" t="s">
         <v>20</v>
@@ -3334,10 +3347,10 @@
         <v>466.0</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>20</v>
@@ -3348,10 +3361,10 @@
         <v>467.0</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D26" s="21" t="s">
         <v>20</v>
@@ -3649,12 +3662,12 @@
     </row>
     <row r="14">
       <c r="A14" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
-        <v>33</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.0)</f>
+        <v>31</v>
       </c>
       <c r="B14" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WILLIAMS")</f>
-        <v>WILLIAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANCET")</f>
+        <v>SANCET</v>
       </c>
       <c r="C14" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3667,12 +3680,12 @@
     </row>
     <row r="15">
       <c r="A15" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
-        <v>34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
+        <v>33</v>
       </c>
       <c r="B15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
-        <v>MAROAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WILLIAMS")</f>
+        <v>WILLIAMS</v>
       </c>
       <c r="C15" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
@@ -3685,16 +3698,16 @@
     </row>
     <row r="16">
       <c r="A16" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
-        <v>37</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
+        <v>34</v>
       </c>
       <c r="B16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAROAN")</f>
+        <v>MAROAN</v>
       </c>
       <c r="C16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D16" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3703,12 +3716,12 @@
     </row>
     <row r="17">
       <c r="A17" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
-        <v>39</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
       </c>
       <c r="B17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MUSSO")</f>
-        <v>MUSSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C17" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3721,30 +3734,30 @@
     </row>
     <row r="18">
       <c r="A18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
-        <v>40</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
+        <v>39</v>
       </c>
       <c r="B18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
-        <v>MARCOS LLORENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MUSSO")</f>
+        <v>MUSSO</v>
       </c>
       <c r="C18" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
         <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D18" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
+        <v>40</v>
       </c>
       <c r="B19" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
-        <v>LENGLET</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
+        <v>MARCOS LLORENTE</v>
       </c>
       <c r="C19" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3757,12 +3770,12 @@
     </row>
     <row r="20">
       <c r="A20" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
       </c>
       <c r="B20" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
-        <v>ALMADA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LENGLET")</f>
+        <v>LENGLET</v>
       </c>
       <c r="C20" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3775,12 +3788,12 @@
     </row>
     <row r="21">
       <c r="A21" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
-        <v>52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
       </c>
       <c r="B21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
-        <v>JULIÁN ALVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALMADA")</f>
+        <v>ALMADA</v>
       </c>
       <c r="C21" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
@@ -3793,16 +3806,16 @@
     </row>
     <row r="22">
       <c r="A22" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
-        <v>55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
+        <v>52</v>
       </c>
       <c r="B22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JULIÁN ALVAREZ")</f>
+        <v>JULIÁN ALVAREZ</v>
       </c>
       <c r="C22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D22" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3811,12 +3824,12 @@
     </row>
     <row r="23">
       <c r="A23" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
-        <v>56</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
+        <v>55</v>
       </c>
       <c r="B23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOAN GARCÍA")</f>
-        <v>JOAN GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C23" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3829,12 +3842,12 @@
     </row>
     <row r="24">
       <c r="A24" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61.0)</f>
-        <v>61</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
       </c>
       <c r="B24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAÚJO")</f>
-        <v>ARAÚJO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOAN GARCÍA")</f>
+        <v>JOAN GARCÍA</v>
       </c>
       <c r="C24" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3847,12 +3860,12 @@
     </row>
     <row r="25">
       <c r="A25" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
-        <v>62</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61.0)</f>
+        <v>61</v>
       </c>
       <c r="B25" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALDE")</f>
-        <v>BALDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAÚJO")</f>
+        <v>ARAÚJO</v>
       </c>
       <c r="C25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3865,12 +3878,12 @@
     </row>
     <row r="26">
       <c r="A26" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
-        <v>63</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
+        <v>62</v>
       </c>
       <c r="B26" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DE JONG")</f>
-        <v>DE JONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALDE")</f>
+        <v>BALDE</v>
       </c>
       <c r="C26" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3883,12 +3896,12 @@
     </row>
     <row r="27">
       <c r="A27" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
-        <v>66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
+        <v>63</v>
       </c>
       <c r="B27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
-        <v>FERMÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DE JONG")</f>
+        <v>DE JONG</v>
       </c>
       <c r="C27" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3901,12 +3914,12 @@
     </row>
     <row r="28">
       <c r="A28" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
-        <v>67</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="B28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
-        <v>DANI OLMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FERMÍN")</f>
+        <v>FERMÍN</v>
       </c>
       <c r="C28" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
@@ -3919,16 +3932,16 @@
     </row>
     <row r="29">
       <c r="A29" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
-        <v>73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
       </c>
       <c r="B29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI OLMO")</f>
+        <v>DANI OLMO</v>
       </c>
       <c r="C29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D29" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -3937,48 +3950,48 @@
     </row>
     <row r="30">
       <c r="A30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
       </c>
       <c r="B30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
-        <v>PAU LÓPEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C30" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D30" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
-        <v>76</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="B31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
-        <v>BELLERÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAU LÓPEZ")</f>
+        <v>PAU LÓPEZ</v>
       </c>
       <c r="C31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
         <v>REAL BETIS</v>
       </c>
       <c r="D31" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
       </c>
       <c r="B32" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
-        <v>JUNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BELLERÍN")</f>
+        <v>BELLERÍN</v>
       </c>
       <c r="C32" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -3991,12 +4004,12 @@
     </row>
     <row r="33">
       <c r="A33" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
-        <v>84</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),79.0)</f>
+        <v>79</v>
       </c>
       <c r="B33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
-        <v>PABLO FORNALS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NATAN")</f>
+        <v>NATAN</v>
       </c>
       <c r="C33" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -4009,12 +4022,12 @@
     </row>
     <row r="34">
       <c r="A34" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="B34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
-        <v>CUCHO HERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUNIOR")</f>
+        <v>JUNIOR</v>
       </c>
       <c r="C34" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
@@ -4027,16 +4040,16 @@
     </row>
     <row r="35">
       <c r="A35" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
-        <v>91</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
+        <v>84</v>
       </c>
       <c r="B35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO FORNALS")</f>
+        <v>PABLO FORNALS</v>
       </c>
       <c r="C35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D35" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4045,16 +4058,16 @@
     </row>
     <row r="36">
       <c r="A36" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
-        <v>94</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="B36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
-        <v>JAVI RUEDA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CUCHO HERNÁNDEZ")</f>
+        <v>CUCHO HERNÁNDEZ</v>
       </c>
       <c r="C36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D36" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4063,12 +4076,12 @@
     </row>
     <row r="37">
       <c r="A37" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
+        <v>91</v>
       </c>
       <c r="B37" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
-        <v>MARCOS ALONSO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C37" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -4081,12 +4094,12 @@
     </row>
     <row r="38">
       <c r="A38" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
+        <v>94</v>
       </c>
       <c r="B38" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
-        <v>ILAIX MORIBA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAVI RUEDA")</f>
+        <v>JAVI RUEDA</v>
       </c>
       <c r="C38" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -4099,66 +4112,66 @@
     </row>
     <row r="39">
       <c r="A39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="B39" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
-        <v>HUGO ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS ALONSO")</f>
+        <v>MARCOS ALONSO</v>
       </c>
       <c r="C39" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D39" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
-        <v>104</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="B40" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
-        <v>SWEDBERG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILAIX MORIBA")</f>
+        <v>ILAIX MORIBA</v>
       </c>
       <c r="C40" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D40" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.0)</f>
+        <v>103</v>
       </c>
       <c r="B41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
-        <v>BRYAN ZARAGOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUGO ÁLVAREZ")</f>
+        <v>HUGO ÁLVAREZ</v>
       </c>
       <c r="C41" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D41" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
-        <v>106</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104.0)</f>
+        <v>104</v>
       </c>
       <c r="B42" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
-        <v>IAGO ASPAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SWEDBERG")</f>
+        <v>SWEDBERG</v>
       </c>
       <c r="C42" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -4171,12 +4184,12 @@
     </row>
     <row r="43">
       <c r="A43" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="B43" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
-        <v>BORJA IGLESIAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BRYAN ZARAGOZA")</f>
+        <v>BRYAN ZARAGOZA</v>
       </c>
       <c r="C43" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
@@ -4189,34 +4202,34 @@
     </row>
     <row r="44">
       <c r="A44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="B44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
-        <v>JUTGLÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IAGO ASPAS")</f>
+        <v>IAGO ASPAS</v>
       </c>
       <c r="C44" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
         <v>RC CELTA</v>
       </c>
       <c r="D44" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="B45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
-        <v>IÑAKI PEÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BORJA IGLESIAS")</f>
+        <v>BORJA IGLESIAS</v>
       </c>
       <c r="C45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D45" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4225,30 +4238,30 @@
     </row>
     <row r="46">
       <c r="A46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
-        <v>111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="B46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
-        <v>DITURO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JUTGLÀ")</f>
+        <v>JUTGLÀ</v>
       </c>
       <c r="C46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D46" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
-        <v>112</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="B47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
-        <v>ÁLVARO NÚÑEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IÑAKI PEÑA")</f>
+        <v>IÑAKI PEÑA</v>
       </c>
       <c r="C47" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -4261,48 +4274,48 @@
     </row>
     <row r="48">
       <c r="A48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
-        <v>115</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.0)</f>
+        <v>111</v>
       </c>
       <c r="B48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
-        <v>AFFENGRUBER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DITURO")</f>
+        <v>DITURO</v>
       </c>
       <c r="C48" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
         <v>ELCHE CF</v>
       </c>
       <c r="D48" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="B49" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
-        <v>MARC AGUADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÁLVARO NÚÑEZ")</f>
+        <v>ÁLVARO NÚÑEZ</v>
       </c>
       <c r="C49" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
         <v>ELCHE CF</v>
       </c>
       <c r="D49" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
-        <v>126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
       </c>
       <c r="B50" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
-        <v>RAFA MIR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AFFENGRUBER")</f>
+        <v>AFFENGRUBER</v>
       </c>
       <c r="C50" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
@@ -4315,34 +4328,34 @@
     </row>
     <row r="51">
       <c r="A51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
-        <v>127</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
       </c>
       <c r="B51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARC AGUADO")</f>
+        <v>MARC AGUADO</v>
       </c>
       <c r="C51" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D51" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
-        <v>128</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
+        <v>126</v>
       </c>
       <c r="B52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
-        <v>DMITROVIC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAFA MIR")</f>
+        <v>RAFA MIR</v>
       </c>
       <c r="C52" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D52" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4351,30 +4364,30 @@
     </row>
     <row r="53">
       <c r="A53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),134.0)</f>
-        <v>134</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),127.0)</f>
+        <v>127</v>
       </c>
       <c r="B53" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ROMERO")</f>
-        <v>CARLOS ROMERO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C53" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D53" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
-        <v>137</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
+        <v>128</v>
       </c>
       <c r="B54" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
-        <v>EDU EXPÓSITO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DMITROVIC")</f>
+        <v>DMITROVIC</v>
       </c>
       <c r="C54" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -4387,30 +4400,30 @@
     </row>
     <row r="55">
       <c r="A55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),134.0)</f>
+        <v>134</v>
       </c>
       <c r="B55" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
-        <v>TERRATS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ROMERO")</f>
+        <v>CARLOS ROMERO</v>
       </c>
       <c r="C55" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D55" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
-        <v>139</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),137.0)</f>
+        <v>137</v>
       </c>
       <c r="B56" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
-        <v>ANTONIU ROCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EDU EXPÓSITO")</f>
+        <v>EDU EXPÓSITO</v>
       </c>
       <c r="C56" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -4423,12 +4436,12 @@
     </row>
     <row r="57">
       <c r="A57" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="B57" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
-        <v>DOLAN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TERRATS")</f>
+        <v>TERRATS</v>
       </c>
       <c r="C57" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -4441,12 +4454,12 @@
     </row>
     <row r="58">
       <c r="A58" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
+        <v>139</v>
       </c>
       <c r="B58" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
-        <v>ROBERTO FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANTONIU ROCA")</f>
+        <v>ANTONIU ROCA</v>
       </c>
       <c r="C58" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
@@ -4459,34 +4472,34 @@
     </row>
     <row r="59">
       <c r="A59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
-        <v>144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="B59" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
-        <v>PERE MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOLAN")</f>
+        <v>DOLAN</v>
       </c>
       <c r="C59" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
         <v>RCD ESPANYOL</v>
       </c>
       <c r="D59" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
-        <v>145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="B60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ROBERTO FERNÁNDEZ")</f>
+        <v>ROBERTO FERNÁNDEZ</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D60" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4495,30 +4508,30 @@
     </row>
     <row r="61">
       <c r="A61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
-        <v>146</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
       </c>
       <c r="B61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PERE MILLA")</f>
+        <v>PERE MILLA</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D61" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),152.0)</f>
-        <v>152</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.0)</f>
+        <v>145</v>
       </c>
       <c r="B62" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABQAR")</f>
-        <v>ABQAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C62" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -4531,12 +4544,12 @@
     </row>
     <row r="63">
       <c r="A63" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
-        <v>153</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.0)</f>
+        <v>146</v>
       </c>
       <c r="B63" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
-        <v>DIEGO RICO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C63" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
@@ -4549,16 +4562,16 @@
     </row>
     <row r="64">
       <c r="A64" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),152.0)</f>
+        <v>152</v>
       </c>
       <c r="B64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ABQAR")</f>
+        <v>ABQAR</v>
       </c>
       <c r="C64" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D64" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4567,16 +4580,16 @@
     </row>
     <row r="65">
       <c r="A65" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
-        <v>163</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
+        <v>153</v>
       </c>
       <c r="B65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIEGO RICO")</f>
+        <v>DIEGO RICO</v>
       </c>
       <c r="C65" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
-        <v>GIRONA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D65" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4585,12 +4598,12 @@
     </row>
     <row r="66">
       <c r="A66" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
-        <v>164</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B66" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAZZANIGA")</f>
-        <v>GAZZANIGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C66" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -4603,12 +4616,12 @@
     </row>
     <row r="67">
       <c r="A67" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
-        <v>172</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),163.0)</f>
+        <v>163</v>
       </c>
       <c r="B67" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
-        <v>WITSEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C67" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
@@ -4621,88 +4634,88 @@
     </row>
     <row r="68">
       <c r="A68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
-        <v>174</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
+        <v>164</v>
       </c>
       <c r="B68" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
-        <v>IVÁN MARTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAZZANIGA")</f>
+        <v>GAZZANIGA</v>
       </c>
       <c r="C68" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
       </c>
       <c r="D68" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
-        <v>175</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),172.0)</f>
+        <v>172</v>
       </c>
       <c r="B69" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
-        <v>YÁSER ASPRILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"WITSEL")</f>
+        <v>WITSEL</v>
       </c>
       <c r="C69" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
       </c>
       <c r="D69" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
-        <v>176</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.0)</f>
+        <v>174</v>
       </c>
       <c r="B70" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
-        <v>JOEL ROCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IVÁN MARTÍN")</f>
+        <v>IVÁN MARTÍN</v>
       </c>
       <c r="C70" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
       </c>
       <c r="D70" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),179.0)</f>
-        <v>179</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),175.0)</f>
+        <v>175</v>
       </c>
       <c r="B71" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"STUANI")</f>
-        <v>STUANI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"YÁSER ASPRILLA")</f>
+        <v>YÁSER ASPRILLA</v>
       </c>
       <c r="C71" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
         <v>GIRONA FC</v>
       </c>
       <c r="D71" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),187.0)</f>
-        <v>187</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
+        <v>176</v>
       </c>
       <c r="B72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATÍAS MORENO")</f>
-        <v>MATÍAS MORENO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JOEL ROCA")</f>
+        <v>JOEL ROCA</v>
       </c>
       <c r="C72" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D72" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4711,16 +4724,16 @@
     </row>
     <row r="73">
       <c r="A73" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
-        <v>189</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),179.0)</f>
+        <v>179</v>
       </c>
       <c r="B73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
-        <v>PAMPÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"STUANI")</f>
+        <v>STUANI</v>
       </c>
       <c r="C73" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GIRONA FC")</f>
+        <v>GIRONA FC</v>
       </c>
       <c r="D73" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4729,12 +4742,12 @@
     </row>
     <row r="74">
       <c r="A74" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),190.0)</f>
-        <v>190</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),187.0)</f>
+        <v>187</v>
       </c>
       <c r="B74" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORIOL REY")</f>
-        <v>ORIOL REY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MATÍAS MORENO")</f>
+        <v>MATÍAS MORENO</v>
       </c>
       <c r="C74" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -4747,12 +4760,12 @@
     </row>
     <row r="75">
       <c r="A75" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),195.0)</f>
-        <v>195</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),189.0)</f>
+        <v>189</v>
       </c>
       <c r="B75" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORALES")</f>
-        <v>MORALES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAMPÍN")</f>
+        <v>PAMPÍN</v>
       </c>
       <c r="C75" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
@@ -4765,16 +4778,16 @@
     </row>
     <row r="76">
       <c r="A76" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
-        <v>202</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),190.0)</f>
+        <v>190</v>
       </c>
       <c r="B76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
-        <v>CARVAJAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORIOL REY")</f>
+        <v>ORIOL REY</v>
       </c>
       <c r="C76" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D76" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4783,16 +4796,16 @@
     </row>
     <row r="77">
       <c r="A77" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),203.0)</f>
-        <v>203</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),195.0)</f>
+        <v>195</v>
       </c>
       <c r="B77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRENT")</f>
-        <v>TRENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MORALES")</f>
+        <v>MORALES</v>
       </c>
       <c r="C77" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D77" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4801,12 +4814,12 @@
     </row>
     <row r="78">
       <c r="A78" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
-        <v>209</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),202.0)</f>
+        <v>202</v>
       </c>
       <c r="B78" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
-        <v>FEDE VALVERDE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARVAJAL")</f>
+        <v>CARVAJAL</v>
       </c>
       <c r="C78" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -4819,12 +4832,12 @@
     </row>
     <row r="79">
       <c r="A79" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
-        <v>211</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),203.0)</f>
+        <v>203</v>
       </c>
       <c r="B79" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
-        <v>GÜLER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRENT")</f>
+        <v>TRENT</v>
       </c>
       <c r="C79" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -4837,12 +4850,12 @@
     </row>
     <row r="80">
       <c r="A80" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
-        <v>212</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209.0)</f>
+        <v>209</v>
       </c>
       <c r="B80" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
-        <v>MASTANTUONO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VALVERDE")</f>
+        <v>FEDE VALVERDE</v>
       </c>
       <c r="C80" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -4855,12 +4868,12 @@
     </row>
     <row r="81">
       <c r="A81" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),215.0)</f>
-        <v>215</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.0)</f>
+        <v>211</v>
       </c>
       <c r="B81" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
-        <v>GONZALO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÜLER")</f>
+        <v>GÜLER</v>
       </c>
       <c r="C81" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
@@ -4873,34 +4886,34 @@
     </row>
     <row r="82">
       <c r="A82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
-        <v>216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),212.0)</f>
+        <v>212</v>
       </c>
       <c r="B82" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
-        <v>VINÍCIUS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MASTANTUONO")</f>
+        <v>MASTANTUONO</v>
       </c>
       <c r="C82" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
         <v>REAL MADRID</v>
       </c>
       <c r="D82" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
-        <v>217</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),215.0)</f>
+        <v>215</v>
       </c>
       <c r="B83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO")</f>
+        <v>GONZALO</v>
       </c>
       <c r="C83" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D83" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4909,30 +4922,30 @@
     </row>
     <row r="84">
       <c r="A84" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),216.0)</f>
+        <v>216</v>
+      </c>
+      <c r="B84" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VINÍCIUS")</f>
+        <v>VINÍCIUS</v>
+      </c>
+      <c r="C84" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D84" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
         <v>217</v>
       </c>
-      <c r="B84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C84" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
-        <v>RCD MALLORCA</v>
-      </c>
-      <c r="D84" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
-        <v>219</v>
-      </c>
       <c r="B85" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
-        <v>BERGSTRÖM</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C85" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4945,30 +4958,30 @@
     </row>
     <row r="86">
       <c r="A86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
-        <v>222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
+        <v>217</v>
       </c>
       <c r="B86" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
-        <v>VALJENT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C86" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
       <c r="D86" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
-        <v>224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),219.0)</f>
+        <v>219</v>
       </c>
       <c r="B87" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
-        <v>KUMBULLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BERGSTRÖM")</f>
+        <v>BERGSTRÖM</v>
       </c>
       <c r="C87" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -4981,30 +4994,30 @@
     </row>
     <row r="88">
       <c r="A88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
-        <v>225</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
       </c>
       <c r="B88" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
-        <v>MOJICA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALJENT")</f>
+        <v>VALJENT</v>
       </c>
       <c r="C88" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
         <v>RCD MALLORCA</v>
       </c>
       <c r="D88" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),228.0)</f>
-        <v>228</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
+        <v>224</v>
       </c>
       <c r="B89" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
-        <v>DARDER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUMBULLA")</f>
+        <v>KUMBULLA</v>
       </c>
       <c r="C89" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -5017,12 +5030,12 @@
     </row>
     <row r="90">
       <c r="A90" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),230.0)</f>
-        <v>230</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),225.0)</f>
+        <v>225</v>
       </c>
       <c r="B90" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO TORRE")</f>
-        <v>PABLO TORRE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOJICA")</f>
+        <v>MOJICA</v>
       </c>
       <c r="C90" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -5035,12 +5048,12 @@
     </row>
     <row r="91">
       <c r="A91" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
-        <v>234</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),228.0)</f>
+        <v>228</v>
       </c>
       <c r="B91" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
-        <v>JAN VIRGILI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DARDER")</f>
+        <v>DARDER</v>
       </c>
       <c r="C91" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
@@ -5053,34 +5066,34 @@
     </row>
     <row r="92">
       <c r="A92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),230.0)</f>
+        <v>230</v>
       </c>
       <c r="B92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO TORRE")</f>
+        <v>PABLO TORRE</v>
       </c>
       <c r="C92" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D92" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
-        <v>235</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),234.0)</f>
+        <v>234</v>
       </c>
       <c r="B93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JAN VIRGILI")</f>
+        <v>JAN VIRGILI</v>
       </c>
       <c r="C93" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD MALLORCA")</f>
+        <v>RCD MALLORCA</v>
       </c>
       <c r="D93" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5089,30 +5102,30 @@
     </row>
     <row r="94">
       <c r="A94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
-        <v>236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B94" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
-        <v>SERGIO HERRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C94" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
         <v>CA OSASUNA</v>
       </c>
       <c r="D94" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
-        <v>237</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),235.0)</f>
+        <v>235</v>
       </c>
       <c r="B95" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
-        <v>AITOR FERNÁNDEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C95" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -5125,12 +5138,12 @@
     </row>
     <row r="96">
       <c r="A96" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
-        <v>245</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),236.0)</f>
+        <v>236</v>
       </c>
       <c r="B96" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
-        <v>MONCAYOLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO HERRERA")</f>
+        <v>SERGIO HERRERA</v>
       </c>
       <c r="C96" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
@@ -5143,52 +5156,52 @@
     </row>
     <row r="97">
       <c r="A97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
-        <v>248</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),237.0)</f>
+        <v>237</v>
       </c>
       <c r="B97" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AITOR FERNÁNDEZ")</f>
+        <v>AITOR FERNÁNDEZ</v>
       </c>
       <c r="C97" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
         <v>CA OSASUNA</v>
       </c>
       <c r="D97" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
-        <v>250</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),245.0)</f>
+        <v>245</v>
       </c>
       <c r="B98" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
-        <v>RAÚL GARCÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MONCAYOLA")</f>
+        <v>MONCAYOLA</v>
       </c>
       <c r="C98" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
         <v>CA OSASUNA</v>
       </c>
       <c r="D98" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
-        <v>258</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.0)</f>
+        <v>248</v>
       </c>
       <c r="B99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
-        <v>DAVID CARMO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
       </c>
       <c r="C99" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D99" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5197,16 +5210,16 @@
     </row>
     <row r="100">
       <c r="A100" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
-        <v>259</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.0)</f>
+        <v>250</v>
       </c>
       <c r="B100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
-        <v>DANI CALVO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAÚL GARCÍA")</f>
+        <v>RAÚL GARCÍA</v>
       </c>
       <c r="C100" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D100" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5215,12 +5228,12 @@
     </row>
     <row r="101">
       <c r="A101" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
-        <v>260</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),257.0)</f>
+        <v>257</v>
       </c>
       <c r="B101" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
-        <v>RAHIM ALHASSANE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ERIC BAILLY")</f>
+        <v>ERIC BAILLY</v>
       </c>
       <c r="C101" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
@@ -5233,70 +5246,70 @@
     </row>
     <row r="102">
       <c r="A102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
-        <v>262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.0)</f>
+        <v>258</v>
       </c>
       <c r="B102" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
-        <v>REINA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID CARMO")</f>
+        <v>DAVID CARMO</v>
       </c>
       <c r="C102" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
         <v>REAL OVIEDO</v>
       </c>
       <c r="D102" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
-        <v>265</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.0)</f>
+        <v>259</v>
       </c>
       <c r="B103" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
-        <v>ILIC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DANI CALVO")</f>
+        <v>DANI CALVO</v>
       </c>
       <c r="C103" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
         <v>REAL OVIEDO</v>
       </c>
       <c r="D103" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
-        <v>269</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),260.0)</f>
+        <v>260</v>
       </c>
       <c r="B104" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
-        <v>FEDE VIÑAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAHIM ALHASSANE")</f>
+        <v>RAHIM ALHASSANE</v>
       </c>
       <c r="C104" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
         <v>REAL OVIEDO</v>
       </c>
       <c r="D104" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
-        <v>277</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.0)</f>
+        <v>262</v>
       </c>
       <c r="B105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
-        <v>LUIZ FELIPE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REINA")</f>
+        <v>REINA</v>
       </c>
       <c r="C105" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D105" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5305,34 +5318,34 @@
     </row>
     <row r="106">
       <c r="A106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
-        <v>278</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.0)</f>
+        <v>265</v>
       </c>
       <c r="B106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
-        <v>PEP CHAVARRÍA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ILIC")</f>
+        <v>ILIC</v>
       </c>
       <c r="C106" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D106" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
-        <v>281</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.0)</f>
+        <v>269</v>
       </c>
       <c r="B107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
-        <v>ÓSCAR VALENTÍN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FEDE VIÑAS")</f>
+        <v>FEDE VIÑAS</v>
       </c>
       <c r="C107" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D107" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5341,12 +5354,12 @@
     </row>
     <row r="108">
       <c r="A108" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
-        <v>282</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),271.0)</f>
+        <v>271</v>
       </c>
       <c r="B108" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
-        <v>ISI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C108" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -5359,12 +5372,12 @@
     </row>
     <row r="109">
       <c r="A109" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
-        <v>283</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.0)</f>
+        <v>277</v>
       </c>
       <c r="B109" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
-        <v>PEDRO DÍAZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ FELIPE")</f>
+        <v>LUIZ FELIPE</v>
       </c>
       <c r="C109" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -5377,30 +5390,30 @@
     </row>
     <row r="110">
       <c r="A110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
-        <v>286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),278.0)</f>
+        <v>278</v>
       </c>
       <c r="B110" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
-        <v>CAMELLO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEP CHAVARRÍA")</f>
+        <v>PEP CHAVARRÍA</v>
       </c>
       <c r="C110" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
         <v>RAYO VALLECANO</v>
       </c>
       <c r="D110" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),287.0)</f>
-        <v>287</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
+        <v>281</v>
       </c>
       <c r="B111" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DE FRUTOS")</f>
-        <v>DE FRUTOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ÓSCAR VALENTÍN")</f>
+        <v>ÓSCAR VALENTÍN</v>
       </c>
       <c r="C111" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
@@ -5413,34 +5426,34 @@
     </row>
     <row r="112">
       <c r="A112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
-        <v>290</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
+        <v>282</v>
       </c>
       <c r="B112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
-        <v>REMIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
       </c>
       <c r="C112" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D112" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
-        <v>292</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.0)</f>
+        <v>283</v>
       </c>
       <c r="B113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
-        <v>ARAMBURU</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEDRO DÍAZ")</f>
+        <v>PEDRO DÍAZ</v>
       </c>
       <c r="C113" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D113" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5449,34 +5462,34 @@
     </row>
     <row r="114">
       <c r="A114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
-        <v>295</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
+        <v>286</v>
       </c>
       <c r="B114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
-        <v>CALETA-CAR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMELLO")</f>
+        <v>CAMELLO</v>
       </c>
       <c r="C114" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D114" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
-        <v>296</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),287.0)</f>
+        <v>287</v>
       </c>
       <c r="B115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
-        <v>SERGIO GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DE FRUTOS")</f>
+        <v>DE FRUTOS</v>
       </c>
       <c r="C115" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
-        <v>REAL SOCIEDAD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="D115" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5485,30 +5498,30 @@
     </row>
     <row r="116">
       <c r="A116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
-        <v>299</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),290.0)</f>
+        <v>290</v>
       </c>
       <c r="B116" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
-        <v>PABLO MARIN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REMIRO")</f>
+        <v>REMIRO</v>
       </c>
       <c r="C116" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
         <v>REAL SOCIEDAD</v>
       </c>
       <c r="D116" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
-        <v>302</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),292.0)</f>
+        <v>292</v>
       </c>
       <c r="B117" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
-        <v>KUBO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARAMBURU")</f>
+        <v>ARAMBURU</v>
       </c>
       <c r="C117" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
@@ -5521,34 +5534,34 @@
     </row>
     <row r="118">
       <c r="A118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
-        <v>309</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),295.0)</f>
+        <v>295</v>
       </c>
       <c r="B118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
-        <v>NYLAND</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CALETA-CAR")</f>
+        <v>CALETA-CAR</v>
       </c>
       <c r="C118" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D118" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
-        <v>312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.0)</f>
+        <v>296</v>
       </c>
       <c r="B119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
-        <v>AZPILICUETA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGIO GÓMEZ")</f>
+        <v>SERGIO GÓMEZ</v>
       </c>
       <c r="C119" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D119" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5557,124 +5570,124 @@
     </row>
     <row r="120">
       <c r="A120" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
-        <v>313</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),299.0)</f>
+        <v>299</v>
       </c>
       <c r="B120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
-        <v>KIKE SALAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PABLO MARIN")</f>
+        <v>PABLO MARIN</v>
       </c>
       <c r="C120" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
       </c>
       <c r="D120" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),302.0)</f>
+        <v>302</v>
+      </c>
+      <c r="B121" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KUBO")</f>
+        <v>KUBO</v>
+      </c>
+      <c r="C121" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+      <c r="D121" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
-        <v>317</v>
-      </c>
-      <c r="B121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
-        <v>AGOUME</v>
-      </c>
-      <c r="C121" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="D121" s="20">
+    <row r="122">
+      <c r="A122" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),306.0)</f>
+        <v>306</v>
+      </c>
+      <c r="B122" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GUEDES")</f>
+        <v>GUEDES</v>
+      </c>
+      <c r="C122" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL SOCIEDAD")</f>
+        <v>REAL SOCIEDAD</v>
+      </c>
+      <c r="D122" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
-        <v>321</v>
-      </c>
-      <c r="B122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
-        <v>EJUKE</v>
-      </c>
-      <c r="C122" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
-      </c>
-      <c r="D122" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
-    </row>
     <row r="123">
       <c r="A123" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
-        <v>323</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.0)</f>
+        <v>309</v>
       </c>
       <c r="B123" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
-        <v>AKOR ADAMS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NYLAND")</f>
+        <v>NYLAND</v>
       </c>
       <c r="C123" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
         <v>SEVILLA FC</v>
       </c>
       <c r="D123" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),312.0)</f>
+        <v>312</v>
+      </c>
+      <c r="B124" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AZPILICUETA")</f>
+        <v>AZPILICUETA</v>
+      </c>
+      <c r="C124" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D124" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),313.0)</f>
+        <v>313</v>
+      </c>
+      <c r="B125" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"KIKE SALAS")</f>
+        <v>KIKE SALAS</v>
+      </c>
+      <c r="C125" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
+      </c>
+      <c r="D125" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
-      </c>
-      <c r="B124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
-      </c>
-      <c r="C124" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D124" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
-        <v>325</v>
-      </c>
-      <c r="B125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
-      </c>
-      <c r="C125" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
-      </c>
-      <c r="D125" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="126">
       <c r="A126" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
-        <v>326</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.0)</f>
+        <v>317</v>
       </c>
       <c r="B126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGOUME")</f>
+        <v>AGOUME</v>
       </c>
       <c r="C126" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D126" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5683,34 +5696,34 @@
     </row>
     <row r="127">
       <c r="A127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
-        <v>327</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),321.0)</f>
+        <v>321</v>
       </c>
       <c r="B127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
-        <v>DIMITRIEVSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EJUKE")</f>
+        <v>EJUKE</v>
       </c>
       <c r="C127" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D127" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),323.0)</f>
+        <v>323</v>
       </c>
       <c r="B128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
-        <v>FOULQUIER</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AKOR ADAMS")</f>
+        <v>AKOR ADAMS</v>
       </c>
       <c r="C128" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D128" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5719,30 +5732,30 @@
     </row>
     <row r="129">
       <c r="A129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
-        <v>329</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
       </c>
       <c r="B129" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
-        <v>CORREIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C129" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D129" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
-        <v>330</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325.0)</f>
+        <v>325</v>
       </c>
       <c r="B130" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
-        <v>TÁRREGA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C130" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -5755,66 +5768,66 @@
     </row>
     <row r="131">
       <c r="A131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
-        <v>331</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),326.0)</f>
+        <v>326</v>
       </c>
       <c r="B131" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
-        <v>COPETE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C131" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D131" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),332.0)</f>
-        <v>332</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),327.0)</f>
+        <v>327</v>
       </c>
       <c r="B132" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIAKHABY")</f>
-        <v>DIAKHABY</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIMITRIEVSKI")</f>
+        <v>DIMITRIEVSKI</v>
       </c>
       <c r="C132" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D132" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
       </c>
       <c r="B133" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
-        <v>GAYÀ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FOULQUIER")</f>
+        <v>FOULQUIER</v>
       </c>
       <c r="C133" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
         <v>VALENCIA CF</v>
       </c>
       <c r="D133" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
-        <v>337</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329.0)</f>
+        <v>329</v>
       </c>
       <c r="B134" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
-        <v>ANDRÉ ALMEIDA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREIA")</f>
+        <v>CORREIA</v>
       </c>
       <c r="C134" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -5827,12 +5840,12 @@
     </row>
     <row r="135">
       <c r="A135" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
-        <v>338</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),330.0)</f>
+        <v>330</v>
       </c>
       <c r="B135" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
-        <v>LUIS RIOJA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TÁRREGA")</f>
+        <v>TÁRREGA</v>
       </c>
       <c r="C135" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
@@ -5845,16 +5858,16 @@
     </row>
     <row r="136">
       <c r="A136" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.0)</f>
+        <v>331</v>
       </c>
       <c r="B136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
-        <v>ESCUDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COPETE")</f>
+        <v>COPETE</v>
       </c>
       <c r="C136" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D136" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5863,34 +5876,34 @@
     </row>
     <row r="137">
       <c r="A137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
-        <v>343</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),332.0)</f>
+        <v>332</v>
       </c>
       <c r="B137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
-        <v>ESTADIO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIAKHABY")</f>
+        <v>DIAKHABY</v>
       </c>
       <c r="C137" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D137" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),344.0)</f>
-        <v>344</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
+        <v>333</v>
       </c>
       <c r="B138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ JÚNIOR")</f>
-        <v>LUIZ JÚNIOR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GAYÀ")</f>
+        <v>GAYÀ</v>
       </c>
       <c r="C138" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D138" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5899,34 +5912,34 @@
     </row>
     <row r="139">
       <c r="A139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
-        <v>350</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),337.0)</f>
+        <v>337</v>
       </c>
       <c r="B139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
-        <v>SERGI CARDONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANDRÉ ALMEIDA")</f>
+        <v>ANDRÉ ALMEIDA</v>
       </c>
       <c r="C139" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D139" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
-        <v>351</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),338.0)</f>
+        <v>338</v>
       </c>
       <c r="B140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
-        <v>SANTI COMESAÑA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS RIOJA")</f>
+        <v>LUIS RIOJA</v>
       </c>
       <c r="C140" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D140" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -5935,30 +5948,30 @@
     </row>
     <row r="141">
       <c r="A141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
-        <v>352</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B141" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
-        <v>PAPE GUEYE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCUDO")</f>
+        <v>ESCUDO</v>
       </c>
       <c r="C141" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
         <v>VILLARREAL CF</v>
       </c>
       <c r="D141" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
-        <v>355</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),343.0)</f>
+        <v>343</v>
       </c>
       <c r="B142" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
-        <v>MOLEIRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTADIO")</f>
+        <v>ESTADIO</v>
       </c>
       <c r="C142" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
@@ -5971,52 +5984,52 @@
     </row>
     <row r="143">
       <c r="A143" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
-        <v>361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),344.0)</f>
+        <v>344</v>
       </c>
       <c r="B143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
-        <v>D. ALAVÉS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIZ JÚNIOR")</f>
+        <v>LUIZ JÚNIOR</v>
       </c>
       <c r="C143" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D143" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),350.0)</f>
+        <v>350</v>
+      </c>
+      <c r="B144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SERGI CARDONA")</f>
+        <v>SERGI CARDONA</v>
+      </c>
+      <c r="C144" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
+      </c>
+      <c r="D144" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
-        <v>366</v>
-      </c>
-      <c r="B144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
-      </c>
-      <c r="C144" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
-      </c>
-      <c r="D144" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="145">
       <c r="A145" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
-        <v>369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),351.0)</f>
+        <v>351</v>
       </c>
       <c r="B145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANTI COMESAÑA")</f>
+        <v>SANTI COMESAÑA</v>
       </c>
       <c r="C145" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D145" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6025,16 +6038,16 @@
     </row>
     <row r="146">
       <c r="A146" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
-        <v>371</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),352.0)</f>
+        <v>352</v>
       </c>
       <c r="B146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAPE GUEYE")</f>
+        <v>PAPE GUEYE</v>
       </c>
       <c r="C146" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D146" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6043,52 +6056,52 @@
     </row>
     <row r="147">
       <c r="A147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),372.0)</f>
-        <v>372</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
+        <v>355</v>
       </c>
       <c r="B147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOLEIRO")</f>
+        <v>MOLEIRO</v>
       </c>
       <c r="C147" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
-        <v>¡VAMOS!</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D147" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),376.0)</f>
-        <v>376</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),361.0)</f>
+        <v>361</v>
       </c>
       <c r="B148" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"D. ALAVÉS")</f>
+        <v>D. ALAVÉS</v>
       </c>
       <c r="C148" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
         <v>¡VAMOS!</v>
       </c>
       <c r="D148" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
-        <v>383</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.0)</f>
+        <v>366</v>
       </c>
       <c r="B149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
-        <v>DAVID SORIA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="C149" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D149" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6097,34 +6110,34 @@
     </row>
     <row r="150">
       <c r="A150" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
-        <v>387</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),369.0)</f>
+        <v>369</v>
       </c>
       <c r="B150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
-        <v>AGIRREZABALA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="C150" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
-        <v>VALENCIA CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D150" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),371.0)</f>
+        <v>371</v>
       </c>
       <c r="B151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
-        <v>CABRERA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="C151" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D151" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6133,16 +6146,16 @@
     </row>
     <row r="152">
       <c r="A152" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),396.0)</f>
-        <v>396</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),372.0)</f>
+        <v>372</v>
       </c>
       <c r="B152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOURIÑO")</f>
-        <v>MOURIÑO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="C152" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
-        <v>VILLARREAL CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D152" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6151,16 +6164,16 @@
     </row>
     <row r="153">
       <c r="A153" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
-        <v>398</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),376.0)</f>
+        <v>376</v>
       </c>
       <c r="B153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
-        <v>DRO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
       </c>
       <c r="C153" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"¡VAMOS!")</f>
+        <v>¡VAMOS!</v>
       </c>
       <c r="D153" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6169,16 +6182,16 @@
     </row>
     <row r="154">
       <c r="A154" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
-        <v>399</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),383.0)</f>
+        <v>383</v>
       </c>
       <c r="B154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
-        <v>VALENTÍN GÓMEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVID SORIA")</f>
+        <v>DAVID SORIA</v>
       </c>
       <c r="C154" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D154" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6187,34 +6200,34 @@
     </row>
     <row r="155">
       <c r="A155" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
-        <v>401</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),387.0)</f>
+        <v>387</v>
       </c>
       <c r="B155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
-        <v>RODRI MENDOZA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGIRREZABALA")</f>
+        <v>AGIRREZABALA</v>
       </c>
       <c r="C155" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
-        <v>ELCHE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENCIA CF")</f>
+        <v>VALENCIA CF</v>
       </c>
       <c r="D155" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),402.0)</f>
-        <v>402</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),389.0)</f>
+        <v>389</v>
       </c>
       <c r="B156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
-        <v>RIEDEL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VIVIAN")</f>
+        <v>VIVIAN</v>
       </c>
       <c r="C156" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
-        <v>RCD ESPANYOL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATHLETIC CLUB")</f>
+        <v>ATHLETIC CLUB</v>
       </c>
       <c r="D156" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6223,16 +6236,16 @@
     </row>
     <row r="157">
       <c r="A157" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),403.0)</f>
-        <v>403</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
+        <v>392</v>
       </c>
       <c r="B157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVINCHI")</f>
-        <v>DAVINCHI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CABRERA")</f>
+        <v>CABRERA</v>
       </c>
       <c r="C157" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D157" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6241,16 +6254,16 @@
     </row>
     <row r="158">
       <c r="A158" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
-        <v>404</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),396.0)</f>
+        <v>396</v>
       </c>
       <c r="B158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
-        <v>LISO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MOURIÑO")</f>
+        <v>MOURIÑO</v>
       </c>
       <c r="C158" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARREAL CF")</f>
+        <v>VILLARREAL CF</v>
       </c>
       <c r="D158" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6259,16 +6272,16 @@
     </row>
     <row r="159">
       <c r="A159" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
-        <v>407</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),398.0)</f>
+        <v>398</v>
       </c>
       <c r="B159" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
-        <v>CARLOS ÁLVAREZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DRO")</f>
+        <v>DRO</v>
       </c>
       <c r="C159" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
       </c>
       <c r="D159" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6277,16 +6290,16 @@
     </row>
     <row r="160">
       <c r="A160" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),408.0)</f>
-        <v>408</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),399.0)</f>
+        <v>399</v>
       </c>
       <c r="B160" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
-        <v>ETTA EYONG</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VALENTÍN GÓMEZ")</f>
+        <v>VALENTÍN GÓMEZ</v>
       </c>
       <c r="C160" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
-        <v>LEVANTE UD</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
       </c>
       <c r="D160" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6295,16 +6308,16 @@
     </row>
     <row r="161">
       <c r="A161" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
-        <v>409</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),401.0)</f>
+        <v>401</v>
       </c>
       <c r="B161" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
-        <v>FRAN GONZÁLEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRI MENDOZA")</f>
+        <v>RODRI MENDOZA</v>
       </c>
       <c r="C161" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ELCHE CF")</f>
+        <v>ELCHE CF</v>
       </c>
       <c r="D161" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6313,16 +6326,16 @@
     </row>
     <row r="162">
       <c r="A162" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
-        <v>413</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),402.0)</f>
+        <v>402</v>
       </c>
       <c r="B162" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
-        <v>VÍCTOR MUÑOZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIEDEL")</f>
+        <v>RIEDEL</v>
       </c>
       <c r="C162" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RCD ESPANYOL")</f>
+        <v>RCD ESPANYOL</v>
       </c>
       <c r="D162" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6331,52 +6344,52 @@
     </row>
     <row r="163">
       <c r="A163" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
-        <v>415</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),403.0)</f>
+        <v>403</v>
       </c>
       <c r="B163" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
-        <v>BARRIOS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DAVINCHI")</f>
+        <v>DAVINCHI</v>
       </c>
       <c r="C163" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D163" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
-        <v>416</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),404.0)</f>
+        <v>404</v>
       </c>
       <c r="B164" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
-        <v>SOTELO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LISO")</f>
+        <v>LISO</v>
       </c>
       <c r="C164" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
-        <v>RC CELTA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D164" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
-        <v>419</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),407.0)</f>
+        <v>407</v>
       </c>
       <c r="B165" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
-        <v>MILLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARLOS ÁLVAREZ")</f>
+        <v>CARLOS ÁLVAREZ</v>
       </c>
       <c r="C165" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
-        <v>GETAFE CF</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D165" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6385,16 +6398,16 @@
     </row>
     <row r="166">
       <c r="A166" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
-        <v>421</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),408.0)</f>
+        <v>408</v>
       </c>
       <c r="B166" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
-        <v>AIMAR OROZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ETTA EYONG")</f>
+        <v>ETTA EYONG</v>
       </c>
       <c r="C166" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
-        <v>CA OSASUNA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEVANTE UD")</f>
+        <v>LEVANTE UD</v>
       </c>
       <c r="D166" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6403,16 +6416,16 @@
     </row>
     <row r="167">
       <c r="A167" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
-        <v>422</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.0)</f>
+        <v>409</v>
       </c>
       <c r="B167" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
-        <v>CAZORLA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRAN GONZÁLEZ")</f>
+        <v>FRAN GONZÁLEZ</v>
       </c>
       <c r="C167" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
-        <v>REAL OVIEDO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
       </c>
       <c r="D167" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6421,16 +6434,16 @@
     </row>
     <row r="168">
       <c r="A168" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
-        <v>439</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),413.0)</f>
+        <v>413</v>
       </c>
       <c r="B168" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
-        <v>ALEXIS SÁNCHEZ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VÍCTOR MUÑOZ")</f>
+        <v>VÍCTOR MUÑOZ</v>
       </c>
       <c r="C168" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
-        <v>SEVILLA FC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D168" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6439,52 +6452,52 @@
     </row>
     <row r="169">
       <c r="A169" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),445.0)</f>
-        <v>445</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415.0)</f>
+        <v>415</v>
       </c>
       <c r="B169" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
-        <v>MARCOS LLORENTE</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BARRIOS")</f>
+        <v>BARRIOS</v>
       </c>
       <c r="C169" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
         <v>ATLÉTICO DE MADRID</v>
       </c>
       <c r="D169" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
-        <v>448</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),416.0)</f>
+        <v>416</v>
       </c>
       <c r="B170" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
-        <v>GRIEZMANN</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SOTELO")</f>
+        <v>SOTELO</v>
       </c>
       <c r="C170" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
-        <v>ATLÉTICO DE MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RC CELTA")</f>
+        <v>RC CELTA</v>
       </c>
       <c r="D170" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
-        <v>452</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),419.0)</f>
+        <v>419</v>
       </c>
       <c r="B171" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
-        <v>LEWANDOWSKI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MILLA")</f>
+        <v>MILLA</v>
       </c>
       <c r="C171" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
-        <v>FC BARCELONA</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GETAFE CF")</f>
+        <v>GETAFE CF</v>
       </c>
       <c r="D171" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6493,16 +6506,16 @@
     </row>
     <row r="172">
       <c r="A172" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
-        <v>454</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),421.0)</f>
+        <v>421</v>
       </c>
       <c r="B172" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
-        <v>ISCO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AIMAR OROZ")</f>
+        <v>AIMAR OROZ</v>
       </c>
       <c r="C172" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
-        <v>REAL BETIS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CA OSASUNA")</f>
+        <v>CA OSASUNA</v>
       </c>
       <c r="D172" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6511,16 +6524,16 @@
     </row>
     <row r="173">
       <c r="A173" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
-        <v>458</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),422.0)</f>
+        <v>422</v>
       </c>
       <c r="B173" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
-        <v>CARRERAS</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAZORLA")</f>
+        <v>CAZORLA</v>
       </c>
       <c r="C173" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
-        <v>REAL MADRID</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL OVIEDO")</f>
+        <v>REAL OVIEDO</v>
       </c>
       <c r="D173" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6529,16 +6542,16 @@
     </row>
     <row r="174">
       <c r="A174" s="20">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
-        <v>462</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),439.0)</f>
+        <v>439</v>
       </c>
       <c r="B174" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
-        <v>ISI</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEXIS SÁNCHEZ")</f>
+        <v>ALEXIS SÁNCHEZ</v>
       </c>
       <c r="C174" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
-        <v>RAYO VALLECANO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEVILLA FC")</f>
+        <v>SEVILLA FC</v>
       </c>
       <c r="D174" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -6547,18 +6560,126 @@
     </row>
     <row r="175">
       <c r="A175" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),445.0)</f>
+        <v>445</v>
+      </c>
+      <c r="B175" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARCOS LLORENTE")</f>
+        <v>MARCOS LLORENTE</v>
+      </c>
+      <c r="C175" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D175" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),448.0)</f>
+        <v>448</v>
+      </c>
+      <c r="B176" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GRIEZMANN")</f>
+        <v>GRIEZMANN</v>
+      </c>
+      <c r="C176" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATLÉTICO DE MADRID")</f>
+        <v>ATLÉTICO DE MADRID</v>
+      </c>
+      <c r="D176" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),452.0)</f>
+        <v>452</v>
+      </c>
+      <c r="B177" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEWANDOWSKI")</f>
+        <v>LEWANDOWSKI</v>
+      </c>
+      <c r="C177" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FC BARCELONA")</f>
+        <v>FC BARCELONA</v>
+      </c>
+      <c r="D177" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.0)</f>
+        <v>454</v>
+      </c>
+      <c r="B178" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISCO")</f>
+        <v>ISCO</v>
+      </c>
+      <c r="C178" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL BETIS")</f>
+        <v>REAL BETIS</v>
+      </c>
+      <c r="D178" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),458.0)</f>
+        <v>458</v>
+      </c>
+      <c r="B179" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRERAS")</f>
+        <v>CARRERAS</v>
+      </c>
+      <c r="C179" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"REAL MADRID")</f>
+        <v>REAL MADRID</v>
+      </c>
+      <c r="D179" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.0)</f>
+        <v>462</v>
+      </c>
+      <c r="B180" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISI")</f>
+        <v>ISI</v>
+      </c>
+      <c r="C180" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RAYO VALLECANO")</f>
+        <v>RAYO VALLECANO</v>
+      </c>
+      <c r="D180" s="20">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),469.0)</f>
         <v>469</v>
       </c>
-      <c r="B175" s="20" t="str">
+      <c r="B181" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NICO WILLIAMS")</f>
         <v>NICO WILLIAMS</v>
       </c>
-      <c r="C175" s="20" t="str">
+      <c r="C181" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BALÓN DE ORO (ATHLETIC)")</f>
         <v>BALÓN DE ORO (ATHLETIC)</v>
       </c>
-      <c r="D175" s="20">
+      <c r="D181" s="20">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
@@ -7031,6 +7152,9 @@
       <c r="D31" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E31" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="21">
@@ -7146,7 +7270,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="40">
@@ -7741,6 +7865,9 @@
       <c r="D79" s="21" t="s">
         <v>20</v>
       </c>
+      <c r="E79" s="22">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="21">
@@ -8453,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="E127" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="128">
@@ -8713,7 +8840,7 @@
         <v>20</v>
       </c>
       <c r="E144" s="22">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="145">
@@ -8726,14 +8853,19 @@
       <c r="C145" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D145" s="21"/>
+      <c r="D145" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F145" s="22" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="21">
         <v>146.0</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C146" s="21" t="s">
         <v>164</v>
@@ -8750,7 +8882,7 @@
         <v>147.0</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C147" s="21" t="s">
         <v>164</v>
@@ -8764,19 +8896,24 @@
         <v>148.0</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C148" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D148" s="21"/>
+      <c r="D148" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F148" s="22" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="21">
         <v>149.0</v>
       </c>
       <c r="B149" s="21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C149" s="21" t="s">
         <v>164</v>
@@ -8788,7 +8925,7 @@
         <v>150.0</v>
       </c>
       <c r="B150" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C150" s="21" t="s">
         <v>164</v>
@@ -8800,7 +8937,7 @@
         <v>151.0</v>
       </c>
       <c r="B151" s="21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C151" s="21" t="s">
         <v>164</v>
@@ -8814,7 +8951,7 @@
         <v>152.0</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C152" s="21" t="s">
         <v>164</v>
@@ -8831,7 +8968,7 @@
         <v>153.0</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C153" s="21" t="s">
         <v>164</v>
@@ -8848,7 +8985,7 @@
         <v>154.0</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C154" s="21" t="s">
         <v>164</v>
@@ -8862,7 +8999,7 @@
         <v>155.0</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C155" s="21" t="s">
         <v>164</v>
@@ -8876,7 +9013,7 @@
         <v>156.0</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C156" s="21" t="s">
         <v>164</v>
@@ -8890,7 +9027,7 @@
         <v>157.0</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C157" s="21" t="s">
         <v>164</v>
@@ -8904,7 +9041,7 @@
         <v>158.0</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C158" s="21" t="s">
         <v>164</v>
@@ -8918,7 +9055,7 @@
         <v>159.0</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C159" s="21" t="s">
         <v>164</v>
@@ -8932,7 +9069,7 @@
         <v>160.0</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C160" s="21" t="s">
         <v>164</v>
@@ -8946,7 +9083,7 @@
         <v>161.0</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C161" s="21" t="s">
         <v>164</v>
@@ -8960,7 +9097,7 @@
         <v>162.0</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C162" s="21" t="s">
         <v>164</v>
@@ -8975,7 +9112,7 @@
         <v>18</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D163" s="21" t="s">
         <v>20</v>
@@ -8989,10 +9126,10 @@
         <v>164.0</v>
       </c>
       <c r="B164" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C164" s="21" t="s">
         <v>183</v>
-      </c>
-      <c r="C164" s="21" t="s">
-        <v>182</v>
       </c>
       <c r="D164" s="21" t="s">
         <v>20</v>
@@ -9006,10 +9143,10 @@
         <v>165.0</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D165" s="21" t="s">
         <v>20</v>
@@ -9020,10 +9157,10 @@
         <v>166.0</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D166" s="21" t="s">
         <v>20</v>
@@ -9034,10 +9171,10 @@
         <v>167.0</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D167" s="21" t="s">
         <v>20</v>
@@ -9048,10 +9185,10 @@
         <v>168.0</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D168" s="21"/>
     </row>
@@ -9060,10 +9197,10 @@
         <v>169.0</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D169" s="21" t="s">
         <v>20</v>
@@ -9074,10 +9211,10 @@
         <v>170.0</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D170" s="21" t="s">
         <v>20</v>
@@ -9088,10 +9225,10 @@
         <v>171.0</v>
       </c>
       <c r="B171" s="21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D171" s="21" t="s">
         <v>20</v>
@@ -9102,10 +9239,10 @@
         <v>172.0</v>
       </c>
       <c r="B172" s="21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C172" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D172" s="21" t="s">
         <v>20</v>
@@ -9119,10 +9256,10 @@
         <v>173.0</v>
       </c>
       <c r="B173" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C173" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D173" s="21" t="s">
         <v>20</v>
@@ -9134,10 +9271,10 @@
         <v>174.0</v>
       </c>
       <c r="B174" s="21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C174" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D174" s="21" t="s">
         <v>20</v>
@@ -9151,10 +9288,10 @@
         <v>175.0</v>
       </c>
       <c r="B175" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C175" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D175" s="21" t="s">
         <v>20</v>
@@ -9168,10 +9305,10 @@
         <v>176.0</v>
       </c>
       <c r="B176" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C176" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D176" s="21" t="s">
         <v>20</v>
@@ -9185,10 +9322,10 @@
         <v>177.0</v>
       </c>
       <c r="B177" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C177" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D177" s="21" t="s">
         <v>20</v>
@@ -9199,10 +9336,10 @@
         <v>178.0</v>
       </c>
       <c r="B178" s="21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C178" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D178" s="21" t="s">
         <v>20</v>
@@ -9213,10 +9350,10 @@
         <v>179.0</v>
       </c>
       <c r="B179" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C179" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D179" s="21" t="s">
         <v>20</v>
@@ -9230,10 +9367,10 @@
         <v>180.0</v>
       </c>
       <c r="B180" s="21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C180" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D180" s="21" t="s">
         <v>20</v>
@@ -9247,7 +9384,7 @@
         <v>18</v>
       </c>
       <c r="C181" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D181" s="21" t="s">
         <v>20</v>
@@ -9258,10 +9395,10 @@
         <v>182.0</v>
       </c>
       <c r="B182" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="C182" s="21" t="s">
         <v>201</v>
-      </c>
-      <c r="C182" s="21" t="s">
-        <v>200</v>
       </c>
       <c r="D182" s="21" t="s">
         <v>20</v>
@@ -9272,10 +9409,10 @@
         <v>183.0</v>
       </c>
       <c r="B183" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C183" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D183" s="21" t="s">
         <v>20</v>
@@ -9286,10 +9423,10 @@
         <v>184.0</v>
       </c>
       <c r="B184" s="21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C184" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D184" s="21" t="s">
         <v>20</v>
@@ -9300,10 +9437,10 @@
         <v>185.0</v>
       </c>
       <c r="B185" s="21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D185" s="21" t="s">
         <v>20</v>
@@ -9314,10 +9451,10 @@
         <v>186.0</v>
       </c>
       <c r="B186" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D186" s="21" t="s">
         <v>20</v>
@@ -9328,10 +9465,10 @@
         <v>187.0</v>
       </c>
       <c r="B187" s="21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C187" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D187" s="21" t="s">
         <v>20</v>
@@ -9345,10 +9482,10 @@
         <v>188.0</v>
       </c>
       <c r="B188" s="21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C188" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D188" s="21" t="s">
         <v>20</v>
@@ -9359,10 +9496,10 @@
         <v>189.0</v>
       </c>
       <c r="B189" s="21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C189" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D189" s="21" t="s">
         <v>20</v>
@@ -9376,10 +9513,10 @@
         <v>190.0</v>
       </c>
       <c r="B190" s="21" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C190" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D190" s="21" t="s">
         <v>20</v>
@@ -9393,10 +9530,10 @@
         <v>191.0</v>
       </c>
       <c r="B191" s="21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C191" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D191" s="21"/>
     </row>
@@ -9405,10 +9542,10 @@
         <v>192.0</v>
       </c>
       <c r="B192" s="21" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C192" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D192" s="21" t="s">
         <v>20</v>
@@ -9419,10 +9556,10 @@
         <v>193.0</v>
       </c>
       <c r="B193" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C193" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D193" s="21" t="s">
         <v>20</v>
@@ -9433,10 +9570,10 @@
         <v>194.0</v>
       </c>
       <c r="B194" s="21" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C194" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D194" s="21" t="s">
         <v>20</v>
@@ -9447,10 +9584,10 @@
         <v>195.0</v>
       </c>
       <c r="B195" s="21" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C195" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D195" s="21" t="s">
         <v>20</v>
@@ -9464,10 +9601,10 @@
         <v>196.0</v>
       </c>
       <c r="B196" s="21" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C196" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D196" s="21"/>
     </row>
@@ -9476,10 +9613,10 @@
         <v>197.0</v>
       </c>
       <c r="B197" s="21" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C197" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D197" s="21" t="s">
         <v>20</v>
@@ -9490,10 +9627,10 @@
         <v>198.0</v>
       </c>
       <c r="B198" s="21" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C198" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D198" s="21"/>
     </row>
@@ -9505,7 +9642,7 @@
         <v>18</v>
       </c>
       <c r="C199" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D199" s="21" t="s">
         <v>20</v>
@@ -9516,10 +9653,10 @@
         <v>200.0</v>
       </c>
       <c r="B200" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C200" s="21" t="s">
         <v>219</v>
-      </c>
-      <c r="C200" s="21" t="s">
-        <v>218</v>
       </c>
       <c r="D200" s="21" t="s">
         <v>20</v>
@@ -9530,10 +9667,10 @@
         <v>201.0</v>
       </c>
       <c r="B201" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C201" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D201" s="21"/>
     </row>
@@ -9542,10 +9679,10 @@
         <v>202.0</v>
       </c>
       <c r="B202" s="21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C202" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D202" s="21" t="s">
         <v>20</v>
@@ -9559,10 +9696,10 @@
         <v>203.0</v>
       </c>
       <c r="B203" s="21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D203" s="21" t="s">
         <v>20</v>
@@ -9576,10 +9713,10 @@
         <v>204.0</v>
       </c>
       <c r="B204" s="21" t="s">
-        <v>223</v>
+        <v>224